--- a/TATA_GROUP_Technical_Metrics.xlsx
+++ b/TATA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="93">
   <si>
     <t>Symbol</t>
   </si>
@@ -214,58 +214,52 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>24.6 → 34.5</t>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>48.6 → 52.0</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>24.6</t>
-  </si>
-  <si>
-    <t>34.5</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>49.9 → 52.3</t>
-  </si>
-  <si>
-    <t>49.9</t>
+    <t>48.6</t>
+  </si>
+  <si>
+    <t>52.0</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
+    <t>No → Yes</t>
+  </si>
+  <si>
+    <t>RSI Overbought Entry</t>
+  </si>
+  <si>
+    <t>67.8 → 70.5</t>
+  </si>
+  <si>
+    <t>⚠️ CAUTION</t>
+  </si>
+  <si>
+    <t>67.8</t>
+  </si>
+  <si>
+    <t>70.5</t>
+  </si>
+  <si>
+    <t>52.3 → 49.4</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>52.3</t>
   </si>
   <si>
-    <t>RSI Overbought Exit</t>
-  </si>
-  <si>
-    <t>71.6 → 67.8</t>
-  </si>
-  <si>
-    <t>🔵 COOLING</t>
-  </si>
-  <si>
-    <t>71.6</t>
-  </si>
-  <si>
-    <t>67.8</t>
-  </si>
-  <si>
-    <t>51.6 → 45.2</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>51.6</t>
-  </si>
-  <si>
-    <t>45.2</t>
+    <t>49.4</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -358,7 +352,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -404,7 +398,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1005,10 +999,10 @@
         <v>53</v>
       </c>
       <c r="C2">
-        <v>721</v>
+        <v>718.5</v>
       </c>
       <c r="D2">
-        <v>-1.23</v>
+        <v>-0.35</v>
       </c>
       <c r="E2">
         <v>790.85</v>
@@ -1017,46 +1011,46 @@
         <v>570.95</v>
       </c>
       <c r="G2">
-        <v>-8.83</v>
+        <v>-9.15</v>
       </c>
       <c r="H2">
-        <v>26.28</v>
+        <v>25.84</v>
       </c>
       <c r="I2">
-        <v>-0.32</v>
+        <v>-2.36</v>
       </c>
       <c r="J2">
-        <v>-1.86</v>
+        <v>-2.67</v>
       </c>
       <c r="K2">
-        <v>7.98</v>
+        <v>9.82</v>
       </c>
       <c r="L2">
-        <v>-9.380000000000001</v>
+        <v>-8.92</v>
       </c>
       <c r="M2">
-        <v>40.42</v>
+        <v>39.82</v>
       </c>
       <c r="N2">
         <v>81</v>
       </c>
       <c r="O2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="P2">
-        <v>729.15</v>
+        <v>725.6799999999999</v>
       </c>
       <c r="Q2">
-        <v>731.22</v>
+        <v>729.6799999999999</v>
       </c>
       <c r="R2">
-        <v>729.12</v>
+        <v>729.5</v>
       </c>
       <c r="S2">
-        <v>688.39</v>
+        <v>688.46</v>
       </c>
       <c r="T2">
-        <v>4.74</v>
+        <v>4.36</v>
       </c>
       <c r="U2" t="s">
         <v>54</v>
@@ -1071,34 +1065,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>45.19</v>
+        <v>43.57</v>
       </c>
       <c r="Z2">
-        <v>-0.35</v>
+        <v>-1.02</v>
       </c>
       <c r="AA2">
-        <v>0.61</v>
+        <v>0.28</v>
       </c>
       <c r="AB2">
-        <v>-0.96</v>
+        <v>-1.3</v>
       </c>
       <c r="AC2">
-        <v>45.5</v>
+        <v>25.94</v>
       </c>
       <c r="AD2">
-        <v>53.35</v>
+        <v>42.79</v>
       </c>
       <c r="AE2">
-        <v>12.56</v>
+        <v>12.62</v>
       </c>
       <c r="AF2">
-        <v>-51.27</v>
+        <v>-40.67</v>
       </c>
       <c r="AG2">
-        <v>752.15</v>
+        <v>749.52</v>
       </c>
       <c r="AH2">
-        <v>710.29</v>
+        <v>709.84</v>
       </c>
       <c r="AI2">
         <v>700.95</v>
@@ -1107,7 +1101,7 @@
         <v>56</v>
       </c>
       <c r="AK2">
-        <v>23.24</v>
+        <v>23.28</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1118,10 +1112,10 @@
         <v>53</v>
       </c>
       <c r="C3">
-        <v>936</v>
+        <v>960.4</v>
       </c>
       <c r="D3">
-        <v>1.12</v>
+        <v>2.61</v>
       </c>
       <c r="E3">
         <v>1081.5</v>
@@ -1130,46 +1124,46 @@
         <v>505.36</v>
       </c>
       <c r="G3">
-        <v>-13.45</v>
+        <v>-11.2</v>
       </c>
       <c r="H3">
-        <v>85.20999999999999</v>
+        <v>90.04000000000001</v>
       </c>
       <c r="I3">
-        <v>2.85</v>
+        <v>5.31</v>
       </c>
       <c r="J3">
-        <v>-2.74</v>
+        <v>2.82</v>
       </c>
       <c r="K3">
-        <v>34.35</v>
+        <v>39.97</v>
       </c>
       <c r="L3">
-        <v>11.94</v>
+        <v>14.39</v>
       </c>
       <c r="M3">
-        <v>14.82</v>
+        <v>15.87</v>
       </c>
       <c r="N3">
         <v>93</v>
       </c>
       <c r="O3">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="P3">
-        <v>919.12</v>
+        <v>928.8</v>
       </c>
       <c r="Q3">
-        <v>972.53</v>
+        <v>974.0599999999999</v>
       </c>
       <c r="R3">
-        <v>930.14</v>
+        <v>934.47</v>
       </c>
       <c r="S3">
-        <v>750.59</v>
+        <v>751.0700000000001</v>
       </c>
       <c r="T3">
-        <v>24.7</v>
+        <v>27.87</v>
       </c>
       <c r="U3" t="s">
         <v>54</v>
@@ -1184,34 +1178,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>48.59</v>
+        <v>52.03</v>
       </c>
       <c r="Z3">
-        <v>1.38</v>
+        <v>2.26</v>
       </c>
       <c r="AA3">
-        <v>14.56</v>
+        <v>12.1</v>
       </c>
       <c r="AB3">
-        <v>-13.18</v>
+        <v>-9.84</v>
       </c>
       <c r="AC3">
-        <v>11.62</v>
+        <v>20.93</v>
       </c>
       <c r="AD3">
-        <v>6.42</v>
+        <v>12.71</v>
       </c>
       <c r="AE3">
-        <v>48.64</v>
+        <v>48.78</v>
       </c>
       <c r="AF3">
-        <v>-75.59</v>
+        <v>-17.97</v>
       </c>
       <c r="AG3">
-        <v>1071.59</v>
+        <v>1071.27</v>
       </c>
       <c r="AH3">
-        <v>873.47</v>
+        <v>876.86</v>
       </c>
       <c r="AI3">
         <v>1070.9</v>
@@ -1220,7 +1214,7 @@
         <v>57</v>
       </c>
       <c r="AK3">
-        <v>24.34</v>
+        <v>23.88</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1231,10 +1225,10 @@
         <v>53</v>
       </c>
       <c r="C4">
-        <v>213.93</v>
+        <v>210.24</v>
       </c>
       <c r="D4">
-        <v>0.47</v>
+        <v>-1.72</v>
       </c>
       <c r="E4">
         <v>376.23</v>
@@ -1243,46 +1237,46 @@
         <v>209.41</v>
       </c>
       <c r="G4">
-        <v>-43.14</v>
+        <v>-44.12</v>
       </c>
       <c r="H4">
-        <v>2.16</v>
+        <v>0.4</v>
       </c>
       <c r="I4">
-        <v>1.04</v>
+        <v>-1.23</v>
       </c>
       <c r="J4">
-        <v>-0.78</v>
+        <v>-3.88</v>
       </c>
       <c r="K4">
-        <v>-13.54</v>
+        <v>-12.41</v>
       </c>
       <c r="L4">
-        <v>-40.94</v>
+        <v>-43.68</v>
       </c>
       <c r="M4">
-        <v>-4.54</v>
+        <v>-4.42</v>
       </c>
       <c r="N4">
         <v>7</v>
       </c>
       <c r="O4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P4">
-        <v>212.64</v>
+        <v>212.12</v>
       </c>
       <c r="Q4">
-        <v>213.7</v>
+        <v>213.36</v>
       </c>
       <c r="R4">
-        <v>222.12</v>
+        <v>221.77</v>
       </c>
       <c r="S4">
-        <v>246.16</v>
+        <v>246</v>
       </c>
       <c r="T4">
-        <v>-13.09</v>
+        <v>-14.54</v>
       </c>
       <c r="U4" t="s">
         <v>55</v>
@@ -1297,43 +1291,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>44.31</v>
+        <v>38.04</v>
       </c>
       <c r="Z4">
-        <v>-3.01</v>
+        <v>-3.03</v>
       </c>
       <c r="AA4">
-        <v>-3.68</v>
+        <v>-3.55</v>
       </c>
       <c r="AB4">
-        <v>0.66</v>
+        <v>0.52</v>
       </c>
       <c r="AC4">
-        <v>90.7</v>
+        <v>83.39</v>
       </c>
       <c r="AD4">
-        <v>88.01000000000001</v>
+        <v>86.92</v>
       </c>
       <c r="AE4">
-        <v>4.49</v>
+        <v>4.46</v>
       </c>
       <c r="AF4">
-        <v>-25.56</v>
+        <v>-43.19</v>
       </c>
       <c r="AG4">
-        <v>218.39</v>
+        <v>218.02</v>
       </c>
       <c r="AH4">
-        <v>209.01</v>
+        <v>208.7</v>
       </c>
       <c r="AI4">
-        <v>225.64</v>
+        <v>225.25</v>
       </c>
       <c r="AJ4" t="s">
         <v>57</v>
       </c>
       <c r="AK4">
-        <v>16.71</v>
+        <v>16.32</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1344,10 +1338,10 @@
         <v>53</v>
       </c>
       <c r="C5">
-        <v>637.65</v>
+        <v>644.15</v>
       </c>
       <c r="D5">
-        <v>1.8</v>
+        <v>1.02</v>
       </c>
       <c r="E5">
         <v>989.9299999999999</v>
@@ -1356,46 +1350,46 @@
         <v>574.42</v>
       </c>
       <c r="G5">
-        <v>-35.59</v>
+        <v>-34.93</v>
       </c>
       <c r="H5">
-        <v>11.01</v>
+        <v>12.14</v>
       </c>
       <c r="I5">
-        <v>0.21</v>
+        <v>1.52</v>
       </c>
       <c r="J5">
-        <v>-5.44</v>
+        <v>-5.14</v>
       </c>
       <c r="K5">
-        <v>-16.41</v>
+        <v>-13.71</v>
       </c>
       <c r="L5">
-        <v>-31.14</v>
+        <v>-30.28</v>
       </c>
       <c r="M5">
-        <v>-3.68</v>
+        <v>-3.54</v>
       </c>
       <c r="N5">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="O5">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="P5">
-        <v>630.4400000000001</v>
+        <v>632.37</v>
       </c>
       <c r="Q5">
-        <v>657.77</v>
+        <v>656.47</v>
       </c>
       <c r="R5">
-        <v>687.2</v>
+        <v>685.5</v>
       </c>
       <c r="S5">
-        <v>716.12</v>
+        <v>715.21</v>
       </c>
       <c r="T5">
-        <v>-10.96</v>
+        <v>-9.94</v>
       </c>
       <c r="U5" t="s">
         <v>55</v>
@@ -1410,34 +1404,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>34.46</v>
+        <v>39.37</v>
       </c>
       <c r="Z5">
-        <v>-16.23</v>
+        <v>-15.13</v>
       </c>
       <c r="AA5">
-        <v>-13.98</v>
+        <v>-14.21</v>
       </c>
       <c r="AB5">
-        <v>-2.25</v>
+        <v>-0.92</v>
       </c>
       <c r="AC5">
-        <v>18.27</v>
+        <v>44.85</v>
       </c>
       <c r="AD5">
-        <v>6.3</v>
+        <v>21.15</v>
       </c>
       <c r="AE5">
-        <v>15.86</v>
+        <v>15.61</v>
       </c>
       <c r="AF5">
-        <v>-37.71</v>
+        <v>-2.66</v>
       </c>
       <c r="AG5">
-        <v>694.76</v>
+        <v>693.4299999999999</v>
       </c>
       <c r="AH5">
-        <v>620.79</v>
+        <v>619.5</v>
       </c>
       <c r="AI5">
         <v>675.42</v>
@@ -1446,7 +1440,7 @@
         <v>57</v>
       </c>
       <c r="AK5">
-        <v>24.99</v>
+        <v>22.76</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1457,10 +1451,10 @@
         <v>53</v>
       </c>
       <c r="C6">
-        <v>1649.3</v>
+        <v>1689.6</v>
       </c>
       <c r="D6">
-        <v>-2.98</v>
+        <v>2.44</v>
       </c>
       <c r="E6">
         <v>2061.7</v>
@@ -1469,46 +1463,46 @@
         <v>1347.9</v>
       </c>
       <c r="G6">
-        <v>-20</v>
+        <v>-18.05</v>
       </c>
       <c r="H6">
-        <v>22.36</v>
+        <v>25.35</v>
       </c>
       <c r="I6">
-        <v>-0.64</v>
+        <v>0.72</v>
       </c>
       <c r="J6">
-        <v>-6.53</v>
+        <v>-5.12</v>
       </c>
       <c r="K6">
-        <v>-16.13</v>
+        <v>-14.02</v>
       </c>
       <c r="L6">
-        <v>3.79</v>
+        <v>5.3</v>
       </c>
       <c r="M6">
-        <v>4.68</v>
+        <v>5.25</v>
       </c>
       <c r="N6">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="O6">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="P6">
-        <v>1674.12</v>
+        <v>1676.54</v>
       </c>
       <c r="Q6">
-        <v>1722.88</v>
+        <v>1718.67</v>
       </c>
       <c r="R6">
-        <v>1819.63</v>
+        <v>1815.42</v>
       </c>
       <c r="S6">
-        <v>1721.91</v>
+        <v>1721.14</v>
       </c>
       <c r="T6">
-        <v>-4.22</v>
+        <v>-1.83</v>
       </c>
       <c r="U6" t="s">
         <v>55</v>
@@ -1523,34 +1517,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>35.28</v>
+        <v>42.94</v>
       </c>
       <c r="Z6">
-        <v>-39.12</v>
+        <v>-36.75</v>
       </c>
       <c r="AA6">
-        <v>-37.61</v>
+        <v>-37.44</v>
       </c>
       <c r="AB6">
-        <v>-1.51</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AC6">
-        <v>64.12</v>
+        <v>72.98999999999999</v>
       </c>
       <c r="AD6">
-        <v>52.57</v>
+        <v>64.34</v>
       </c>
       <c r="AE6">
-        <v>49.08</v>
+        <v>50.16</v>
       </c>
       <c r="AF6">
-        <v>25.66</v>
+        <v>20.21</v>
       </c>
       <c r="AG6">
-        <v>1806.31</v>
+        <v>1799.76</v>
       </c>
       <c r="AH6">
-        <v>1639.44</v>
+        <v>1637.58</v>
       </c>
       <c r="AI6">
         <v>1813.9</v>
@@ -1559,7 +1553,7 @@
         <v>57</v>
       </c>
       <c r="AK6">
-        <v>41.84</v>
+        <v>41.99</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1570,10 +1564,10 @@
         <v>53</v>
       </c>
       <c r="C7">
-        <v>1047.1</v>
+        <v>1042</v>
       </c>
       <c r="D7">
-        <v>-1.26</v>
+        <v>-0.49</v>
       </c>
       <c r="E7">
         <v>1260.34</v>
@@ -1582,46 +1576,46 @@
         <v>1006.29</v>
       </c>
       <c r="G7">
-        <v>-16.92</v>
+        <v>-17.32</v>
       </c>
       <c r="H7">
-        <v>4.06</v>
+        <v>3.55</v>
       </c>
       <c r="I7">
-        <v>-1.96</v>
+        <v>-1.35</v>
       </c>
       <c r="J7">
-        <v>-3.23</v>
+        <v>-4.94</v>
       </c>
       <c r="K7">
-        <v>-13.07</v>
+        <v>-11.58</v>
       </c>
       <c r="L7">
-        <v>-2.95</v>
+        <v>-3.07</v>
       </c>
       <c r="M7">
-        <v>5.05</v>
+        <v>5.08</v>
       </c>
       <c r="N7">
         <v>56</v>
       </c>
       <c r="O7">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P7">
-        <v>1055.08</v>
+        <v>1052.22</v>
       </c>
       <c r="Q7">
-        <v>1077.2</v>
+        <v>1074.6</v>
       </c>
       <c r="R7">
-        <v>1092.01</v>
+        <v>1090.36</v>
       </c>
       <c r="S7">
-        <v>1127.81</v>
+        <v>1127.35</v>
       </c>
       <c r="T7">
-        <v>-7.16</v>
+        <v>-7.57</v>
       </c>
       <c r="U7" t="s">
         <v>55</v>
@@ -1636,43 +1630,43 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>40.45</v>
+        <v>39.22</v>
       </c>
       <c r="Z7">
-        <v>-12.03</v>
+        <v>-13</v>
       </c>
       <c r="AA7">
-        <v>-9.880000000000001</v>
+        <v>-10.5</v>
       </c>
       <c r="AB7">
-        <v>-2.16</v>
+        <v>-2.5</v>
       </c>
       <c r="AC7">
-        <v>22.77</v>
+        <v>11.39</v>
       </c>
       <c r="AD7">
-        <v>18.89</v>
+        <v>18.53</v>
       </c>
       <c r="AE7">
-        <v>21.19</v>
+        <v>20.59</v>
       </c>
       <c r="AF7">
-        <v>-20.65</v>
+        <v>-24.95</v>
       </c>
       <c r="AG7">
-        <v>1114.38</v>
+        <v>1114.01</v>
       </c>
       <c r="AH7">
-        <v>1040.03</v>
+        <v>1035.18</v>
       </c>
       <c r="AI7">
-        <v>1115.13</v>
+        <v>1103.78</v>
       </c>
       <c r="AJ7" t="s">
         <v>57</v>
       </c>
       <c r="AK7">
-        <v>30.11</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1683,10 +1677,10 @@
         <v>53</v>
       </c>
       <c r="C8">
-        <v>3650</v>
+        <v>3633.2</v>
       </c>
       <c r="D8">
-        <v>-0.43</v>
+        <v>-0.46</v>
       </c>
       <c r="E8">
         <v>5749.89</v>
@@ -1695,49 +1689,49 @@
         <v>3387.6</v>
       </c>
       <c r="G8">
-        <v>-36.52</v>
+        <v>-36.81</v>
       </c>
       <c r="H8">
-        <v>7.75</v>
+        <v>7.25</v>
       </c>
       <c r="I8">
-        <v>-0.27</v>
+        <v>-0.73</v>
       </c>
       <c r="J8">
-        <v>1.9</v>
+        <v>-1.09</v>
       </c>
       <c r="K8">
-        <v>-14.22</v>
+        <v>-13.7</v>
       </c>
       <c r="L8">
-        <v>-34.34</v>
+        <v>-33.72</v>
       </c>
       <c r="M8">
-        <v>-4.59</v>
+        <v>-4.71</v>
       </c>
       <c r="N8">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="O8">
         <v>12</v>
       </c>
       <c r="P8">
-        <v>3671.48</v>
+        <v>3666.12</v>
       </c>
       <c r="Q8">
-        <v>3719.66</v>
+        <v>3718.41</v>
       </c>
       <c r="R8">
-        <v>3723.72</v>
+        <v>3714.49</v>
       </c>
       <c r="S8">
-        <v>4442.74</v>
+        <v>4435.33</v>
       </c>
       <c r="T8">
-        <v>-17.84</v>
+        <v>-18.09</v>
       </c>
       <c r="U8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="V8" t="s">
         <v>55</v>
@@ -1746,37 +1740,37 @@
         <v>55</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y8">
-        <v>44.74</v>
+        <v>43.3</v>
       </c>
       <c r="Z8">
-        <v>-11.63</v>
+        <v>-15.3</v>
       </c>
       <c r="AA8">
-        <v>-6.36</v>
+        <v>-8.15</v>
       </c>
       <c r="AB8">
-        <v>-5.27</v>
+        <v>-7.15</v>
       </c>
       <c r="AC8">
-        <v>6.45</v>
+        <v>2.36</v>
       </c>
       <c r="AD8">
-        <v>13.6</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="AE8">
-        <v>90.29000000000001</v>
+        <v>86.84</v>
       </c>
       <c r="AF8">
-        <v>-57.16</v>
+        <v>-59.76</v>
       </c>
       <c r="AG8">
-        <v>3828.04</v>
+        <v>3830.3</v>
       </c>
       <c r="AH8">
-        <v>3611.29</v>
+        <v>3606.52</v>
       </c>
       <c r="AI8">
         <v>3521.58</v>
@@ -1785,7 +1779,7 @@
         <v>56</v>
       </c>
       <c r="AK8">
-        <v>13.95</v>
+        <v>13.38</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1796,10 +1790,10 @@
         <v>53</v>
       </c>
       <c r="C9">
-        <v>644.45</v>
+        <v>642.1</v>
       </c>
       <c r="D9">
-        <v>0.02</v>
+        <v>-0.36</v>
       </c>
       <c r="E9">
         <v>1052.57</v>
@@ -1808,46 +1802,46 @@
         <v>538.37</v>
       </c>
       <c r="G9">
-        <v>-38.77</v>
+        <v>-39</v>
       </c>
       <c r="H9">
-        <v>19.7</v>
+        <v>19.27</v>
       </c>
       <c r="I9">
-        <v>-1.29</v>
+        <v>-1.12</v>
       </c>
       <c r="J9">
-        <v>-1.51</v>
+        <v>-4.98</v>
       </c>
       <c r="K9">
-        <v>-5.14</v>
+        <v>-6.48</v>
       </c>
       <c r="L9">
-        <v>-6.85</v>
+        <v>-6.67</v>
       </c>
       <c r="M9">
-        <v>40.77</v>
+        <v>40.37</v>
       </c>
       <c r="N9">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="O9">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="P9">
-        <v>646.41</v>
+        <v>644.96</v>
       </c>
       <c r="Q9">
-        <v>666.47</v>
+        <v>664.64</v>
       </c>
       <c r="R9">
-        <v>667.5</v>
+        <v>666.83</v>
       </c>
       <c r="S9">
-        <v>672.21</v>
+        <v>671.53</v>
       </c>
       <c r="T9">
-        <v>-4.13</v>
+        <v>-4.38</v>
       </c>
       <c r="U9" t="s">
         <v>55</v>
@@ -1862,43 +1856,43 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>38.85</v>
+        <v>37.67</v>
       </c>
       <c r="Z9">
-        <v>-6.34</v>
+        <v>-6.87</v>
       </c>
       <c r="AA9">
-        <v>-3.21</v>
+        <v>-3.95</v>
       </c>
       <c r="AB9">
-        <v>-3.13</v>
+        <v>-2.92</v>
       </c>
       <c r="AC9">
-        <v>0.57</v>
+        <v>0.11</v>
       </c>
       <c r="AD9">
-        <v>2.55</v>
+        <v>0.96</v>
       </c>
       <c r="AE9">
-        <v>13.72</v>
+        <v>13.58</v>
       </c>
       <c r="AF9">
-        <v>-58.04</v>
+        <v>-61.63</v>
       </c>
       <c r="AG9">
-        <v>699.71</v>
+        <v>699.0599999999999</v>
       </c>
       <c r="AH9">
-        <v>633.22</v>
+        <v>630.22</v>
       </c>
       <c r="AI9">
-        <v>642.2</v>
+        <v>683.58</v>
       </c>
       <c r="AJ9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK9">
-        <v>14.91</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1909,10 +1903,10 @@
         <v>53</v>
       </c>
       <c r="C10">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="D10">
-        <v>-1.78</v>
+        <v>-3.3</v>
       </c>
       <c r="E10">
         <v>461.8</v>
@@ -1921,46 +1915,46 @@
         <v>345.25</v>
       </c>
       <c r="G10">
-        <v>-21.18</v>
+        <v>-23.78</v>
       </c>
       <c r="H10">
-        <v>5.43</v>
+        <v>1.96</v>
       </c>
       <c r="I10">
-        <v>-3.93</v>
+        <v>-6.2</v>
       </c>
       <c r="J10">
-        <v>-1.98</v>
+        <v>-6.69</v>
       </c>
       <c r="K10">
-        <v>-14.51</v>
+        <v>-16.34</v>
       </c>
       <c r="L10">
-        <v>-6.2</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="M10">
-        <v>24.4</v>
+        <v>23.25</v>
       </c>
       <c r="N10">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="O10">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="P10">
-        <v>371.53</v>
+        <v>366.88</v>
       </c>
       <c r="Q10">
-        <v>378.31</v>
+        <v>377.11</v>
       </c>
       <c r="R10">
-        <v>381.07</v>
+        <v>380.08</v>
       </c>
       <c r="S10">
-        <v>389.59</v>
+        <v>389.38</v>
       </c>
       <c r="T10">
-        <v>-6.57</v>
+        <v>-9.6</v>
       </c>
       <c r="U10" t="s">
         <v>55</v>
@@ -1975,16 +1969,16 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>29.2</v>
+        <v>21.58</v>
       </c>
       <c r="Z10">
-        <v>-3.06</v>
+        <v>-4.66</v>
       </c>
       <c r="AA10">
-        <v>-1.83</v>
+        <v>-2.4</v>
       </c>
       <c r="AB10">
-        <v>-1.22</v>
+        <v>-2.26</v>
       </c>
       <c r="AC10">
         <v>0</v>
@@ -1993,25 +1987,25 @@
         <v>0</v>
       </c>
       <c r="AE10">
-        <v>6.37</v>
+        <v>7.05</v>
       </c>
       <c r="AF10">
-        <v>25.73</v>
+        <v>320.01</v>
       </c>
       <c r="AG10">
-        <v>387.9</v>
+        <v>392.29</v>
       </c>
       <c r="AH10">
-        <v>368.71</v>
+        <v>361.93</v>
       </c>
       <c r="AI10">
-        <v>389.11</v>
+        <v>374.8</v>
       </c>
       <c r="AJ10" t="s">
         <v>57</v>
       </c>
       <c r="AK10">
-        <v>22.8</v>
+        <v>30.01</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -2022,10 +2016,10 @@
         <v>53</v>
       </c>
       <c r="C11">
-        <v>188.01</v>
+        <v>186.8</v>
       </c>
       <c r="D11">
-        <v>0.57</v>
+        <v>-0.64</v>
       </c>
       <c r="E11">
         <v>216.66</v>
@@ -2034,46 +2028,46 @@
         <v>150.53</v>
       </c>
       <c r="G11">
-        <v>-13.22</v>
+        <v>-13.78</v>
       </c>
       <c r="H11">
-        <v>24.9</v>
+        <v>24.09</v>
       </c>
       <c r="I11">
-        <v>2.18</v>
+        <v>1.8</v>
       </c>
       <c r="J11">
-        <v>2.95</v>
+        <v>-0.25</v>
       </c>
       <c r="K11">
-        <v>-10.62</v>
+        <v>-8.35</v>
       </c>
       <c r="L11">
-        <v>18.81</v>
+        <v>20.24</v>
       </c>
       <c r="M11">
-        <v>9.66</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="N11">
         <v>87</v>
       </c>
       <c r="O11">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="P11">
-        <v>185.55</v>
+        <v>186.21</v>
       </c>
       <c r="Q11">
         <v>187.23</v>
       </c>
       <c r="R11">
-        <v>188.32</v>
+        <v>188.08</v>
       </c>
       <c r="S11">
-        <v>189.58</v>
+        <v>189.63</v>
       </c>
       <c r="T11">
-        <v>-0.83</v>
+        <v>-1.49</v>
       </c>
       <c r="U11" t="s">
         <v>55</v>
@@ -2088,34 +2082,34 @@
         <v>0</v>
       </c>
       <c r="Y11">
-        <v>52.3</v>
+        <v>49.42</v>
       </c>
       <c r="Z11">
-        <v>-0.85</v>
+        <v>-0.73</v>
       </c>
       <c r="AA11">
-        <v>-1.11</v>
+        <v>-1.03</v>
       </c>
       <c r="AB11">
-        <v>0.27</v>
+        <v>0.31</v>
       </c>
       <c r="AC11">
-        <v>75.90000000000001</v>
+        <v>86.14</v>
       </c>
       <c r="AD11">
-        <v>45.55</v>
+        <v>68.34</v>
       </c>
       <c r="AE11">
         <v>3.8</v>
       </c>
       <c r="AF11">
-        <v>42.13</v>
+        <v>75.84</v>
       </c>
       <c r="AG11">
-        <v>192.87</v>
+        <v>192.86</v>
       </c>
       <c r="AH11">
-        <v>181.6</v>
+        <v>181.59</v>
       </c>
       <c r="AI11">
         <v>180.21</v>
@@ -2124,7 +2118,7 @@
         <v>56</v>
       </c>
       <c r="AK11">
-        <v>17.99</v>
+        <v>19.16</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -2135,10 +2129,10 @@
         <v>53</v>
       </c>
       <c r="C12">
-        <v>2270</v>
+        <v>2248.4</v>
       </c>
       <c r="D12">
-        <v>-1.14</v>
+        <v>-0.95</v>
       </c>
       <c r="E12">
         <v>3221.85</v>
@@ -2147,46 +2141,46 @@
         <v>1982.6</v>
       </c>
       <c r="G12">
-        <v>-29.54</v>
+        <v>-30.21</v>
       </c>
       <c r="H12">
-        <v>14.5</v>
+        <v>13.41</v>
       </c>
       <c r="I12">
-        <v>-0.83</v>
+        <v>-2.16</v>
       </c>
       <c r="J12">
-        <v>-5.34</v>
+        <v>-8.1</v>
       </c>
       <c r="K12">
-        <v>-0.62</v>
+        <v>-0.46</v>
       </c>
       <c r="L12">
-        <v>-24.21</v>
+        <v>-23.74</v>
       </c>
       <c r="M12">
-        <v>-6.68</v>
+        <v>-7.1</v>
       </c>
       <c r="N12">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="O12">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="P12">
-        <v>2290.06</v>
+        <v>2280.14</v>
       </c>
       <c r="Q12">
-        <v>2362.97</v>
+        <v>2353.8</v>
       </c>
       <c r="R12">
-        <v>2243.29</v>
+        <v>2243.79</v>
       </c>
       <c r="S12">
-        <v>2590.15</v>
+        <v>2586.73</v>
       </c>
       <c r="T12">
-        <v>-12.36</v>
+        <v>-13.08</v>
       </c>
       <c r="U12" t="s">
         <v>54</v>
@@ -2201,43 +2195,43 @@
         <v>1</v>
       </c>
       <c r="Y12">
-        <v>44.91</v>
+        <v>42.68</v>
       </c>
       <c r="Z12">
-        <v>0.43</v>
+        <v>-4.8</v>
       </c>
       <c r="AA12">
-        <v>19.34</v>
+        <v>14.51</v>
       </c>
       <c r="AB12">
-        <v>-18.91</v>
+        <v>-19.31</v>
       </c>
       <c r="AC12">
-        <v>4.41</v>
+        <v>3.62</v>
       </c>
       <c r="AD12">
-        <v>6.43</v>
+        <v>5.32</v>
       </c>
       <c r="AE12">
-        <v>57.05</v>
+        <v>55.81</v>
       </c>
       <c r="AF12">
-        <v>-51.64</v>
+        <v>-45.21</v>
       </c>
       <c r="AG12">
-        <v>2500.83</v>
+        <v>2496.69</v>
       </c>
       <c r="AH12">
-        <v>2225.11</v>
+        <v>2210.91</v>
       </c>
       <c r="AI12">
-        <v>2263.35</v>
+        <v>2431.19</v>
       </c>
       <c r="AJ12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK12">
-        <v>30.03</v>
+        <v>31.51</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2248,58 +2242,58 @@
         <v>53</v>
       </c>
       <c r="C13">
-        <v>5100</v>
+        <v>5139.3</v>
       </c>
       <c r="D13">
-        <v>-0.48</v>
+        <v>0.77</v>
       </c>
       <c r="E13">
-        <v>5128</v>
+        <v>5139.3</v>
       </c>
       <c r="F13">
         <v>3327.3</v>
       </c>
       <c r="G13">
-        <v>-0.55</v>
+        <v>0</v>
       </c>
       <c r="H13">
-        <v>53.28</v>
+        <v>54.46</v>
       </c>
       <c r="I13">
-        <v>0.63</v>
+        <v>1.41</v>
       </c>
       <c r="J13">
-        <v>5.16</v>
+        <v>5.96</v>
       </c>
       <c r="K13">
-        <v>23.25</v>
+        <v>26.12</v>
       </c>
       <c r="L13">
-        <v>41.03</v>
+        <v>41.93</v>
       </c>
       <c r="M13">
-        <v>23.27</v>
+        <v>23.36</v>
       </c>
       <c r="N13">
         <v>99</v>
       </c>
       <c r="O13">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P13">
-        <v>5091.58</v>
+        <v>5105.84</v>
       </c>
       <c r="Q13">
-        <v>5028.96</v>
+        <v>5043.43</v>
       </c>
       <c r="R13">
-        <v>4735.48</v>
+        <v>4750.66</v>
       </c>
       <c r="S13">
-        <v>4275.55</v>
+        <v>4282.23</v>
       </c>
       <c r="T13">
-        <v>19.28</v>
+        <v>20.01</v>
       </c>
       <c r="U13" t="s">
         <v>54</v>
@@ -2314,34 +2308,34 @@
         <v>3</v>
       </c>
       <c r="Y13">
-        <v>67.79000000000001</v>
+        <v>70.47</v>
       </c>
       <c r="Z13">
-        <v>106.48</v>
+        <v>104.86</v>
       </c>
       <c r="AA13">
-        <v>120.01</v>
+        <v>116.98</v>
       </c>
       <c r="AB13">
-        <v>-13.53</v>
+        <v>-12.12</v>
       </c>
       <c r="AC13">
-        <v>23.5</v>
+        <v>30.94</v>
       </c>
       <c r="AD13">
-        <v>23.59</v>
+        <v>28.4</v>
       </c>
       <c r="AE13">
-        <v>77.48</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="AF13">
-        <v>-58.44</v>
+        <v>27.55</v>
       </c>
       <c r="AG13">
-        <v>5195.78</v>
+        <v>5194.32</v>
       </c>
       <c r="AH13">
-        <v>4862.14</v>
+        <v>4892.53</v>
       </c>
       <c r="AI13">
         <v>4888</v>
@@ -2350,7 +2344,7 @@
         <v>56</v>
       </c>
       <c r="AK13">
-        <v>45.76</v>
+        <v>46.56</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2361,10 +2355,10 @@
         <v>53</v>
       </c>
       <c r="C14">
-        <v>2908.2</v>
+        <v>2878.5</v>
       </c>
       <c r="D14">
-        <v>-0.74</v>
+        <v>-1.02</v>
       </c>
       <c r="E14">
         <v>5520.84</v>
@@ -2373,46 +2367,46 @@
         <v>2193.96</v>
       </c>
       <c r="G14">
-        <v>-47.32</v>
+        <v>-47.86</v>
       </c>
       <c r="H14">
-        <v>32.55</v>
+        <v>31.2</v>
       </c>
       <c r="I14">
-        <v>-1.52</v>
+        <v>-3.08</v>
       </c>
       <c r="J14">
-        <v>-0.77</v>
+        <v>-4.22</v>
       </c>
       <c r="K14">
-        <v>2.83</v>
+        <v>2.37</v>
       </c>
       <c r="L14">
-        <v>-46.58</v>
+        <v>-46.79</v>
       </c>
       <c r="M14">
-        <v>25.43</v>
+        <v>24.98</v>
       </c>
       <c r="N14">
         <v>32</v>
       </c>
       <c r="O14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P14">
-        <v>2927.44</v>
+        <v>2909.14</v>
       </c>
       <c r="Q14">
-        <v>2992.71</v>
+        <v>2986.68</v>
       </c>
       <c r="R14">
-        <v>3026.16</v>
+        <v>3021.68</v>
       </c>
       <c r="S14">
-        <v>3040.35</v>
+        <v>3033.36</v>
       </c>
       <c r="T14">
-        <v>-4.35</v>
+        <v>-5.11</v>
       </c>
       <c r="U14" t="s">
         <v>55</v>
@@ -2427,43 +2421,43 @@
         <v>0</v>
       </c>
       <c r="Y14">
-        <v>41.77</v>
+        <v>38.61</v>
       </c>
       <c r="Z14">
-        <v>-18.22</v>
+        <v>-22.52</v>
       </c>
       <c r="AA14">
-        <v>-7.69</v>
+        <v>-10.66</v>
       </c>
       <c r="AB14">
-        <v>-10.52</v>
+        <v>-11.86</v>
       </c>
       <c r="AC14">
         <v>9.31</v>
       </c>
       <c r="AD14">
-        <v>7.06</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="AE14">
-        <v>61.28</v>
+        <v>60.86</v>
       </c>
       <c r="AF14">
-        <v>-54.52</v>
+        <v>-42.32</v>
       </c>
       <c r="AG14">
-        <v>3122.55</v>
+        <v>3126.11</v>
       </c>
       <c r="AH14">
-        <v>2862.87</v>
+        <v>2847.24</v>
       </c>
       <c r="AI14">
-        <v>3103.13</v>
+        <v>3078.42</v>
       </c>
       <c r="AJ14" t="s">
         <v>57</v>
       </c>
       <c r="AK14">
-        <v>21.96</v>
+        <v>23.64</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2474,10 +2468,10 @@
         <v>53</v>
       </c>
       <c r="C15">
-        <v>229.94</v>
+        <v>229.22</v>
       </c>
       <c r="D15">
-        <v>-0.76</v>
+        <v>-0.31</v>
       </c>
       <c r="E15">
         <v>392.75</v>
@@ -2486,46 +2480,46 @@
         <v>217.05</v>
       </c>
       <c r="G15">
-        <v>-41.45</v>
+        <v>-41.64</v>
       </c>
       <c r="H15">
-        <v>5.94</v>
+        <v>5.61</v>
       </c>
       <c r="I15">
-        <v>0.39</v>
+        <v>-0.83</v>
       </c>
       <c r="J15">
-        <v>0.9399999999999999</v>
+        <v>-0.49</v>
       </c>
       <c r="K15">
-        <v>-4.45</v>
+        <v>-3.97</v>
       </c>
       <c r="L15">
-        <v>-29.68</v>
+        <v>-29.3</v>
       </c>
       <c r="M15">
-        <v>16.83</v>
+        <v>16.53</v>
       </c>
       <c r="N15">
         <v>38</v>
       </c>
       <c r="O15">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="P15">
-        <v>230.64</v>
+        <v>230.25</v>
       </c>
       <c r="Q15">
-        <v>230.51</v>
+        <v>230.7</v>
       </c>
       <c r="R15">
-        <v>235.31</v>
+        <v>235.23</v>
       </c>
       <c r="S15">
-        <v>260.33</v>
+        <v>259.92</v>
       </c>
       <c r="T15">
-        <v>-11.67</v>
+        <v>-11.81</v>
       </c>
       <c r="U15" t="s">
         <v>55</v>
@@ -2540,34 +2534,34 @@
         <v>0</v>
       </c>
       <c r="Y15">
-        <v>45.86</v>
+        <v>44.69</v>
       </c>
       <c r="Z15">
-        <v>-1.24</v>
+        <v>-1.28</v>
       </c>
       <c r="AA15">
-        <v>-1.43</v>
+        <v>-1.4</v>
       </c>
       <c r="AB15">
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
       <c r="AC15">
-        <v>36.41</v>
+        <v>32.25</v>
       </c>
       <c r="AD15">
-        <v>37.79</v>
+        <v>36.4</v>
       </c>
       <c r="AE15">
-        <v>6.25</v>
+        <v>6.02</v>
       </c>
       <c r="AF15">
-        <v>-77.06999999999999</v>
+        <v>-75.45999999999999</v>
       </c>
       <c r="AG15">
-        <v>235.4</v>
+        <v>235.04</v>
       </c>
       <c r="AH15">
-        <v>225.62</v>
+        <v>226.35</v>
       </c>
       <c r="AI15">
         <v>219.81</v>
@@ -2576,7 +2570,7 @@
         <v>56</v>
       </c>
       <c r="AK15">
-        <v>14.99</v>
+        <v>14.73</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2587,58 +2581,58 @@
         <v>53</v>
       </c>
       <c r="C16">
-        <v>37.41</v>
+        <v>36.46</v>
       </c>
       <c r="D16">
-        <v>-0.37</v>
+        <v>-2.54</v>
       </c>
       <c r="E16">
-        <v>59.04</v>
+        <v>58.79</v>
       </c>
       <c r="F16">
         <v>31.36</v>
       </c>
       <c r="G16">
-        <v>-36.64</v>
+        <v>-37.98</v>
       </c>
       <c r="H16">
-        <v>19.29</v>
+        <v>16.26</v>
       </c>
       <c r="I16">
-        <v>-0.6899999999999999</v>
+        <v>-2.64</v>
       </c>
       <c r="J16">
-        <v>-4.03</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="K16">
-        <v>-13.14</v>
+        <v>-14.83</v>
       </c>
       <c r="L16">
-        <v>-36.09</v>
+        <v>-38.25</v>
       </c>
       <c r="M16">
-        <v>1.03</v>
+        <v>-0.45</v>
       </c>
       <c r="N16">
         <v>13</v>
       </c>
       <c r="O16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P16">
-        <v>37.51</v>
+        <v>37.31</v>
       </c>
       <c r="Q16">
-        <v>38.67</v>
+        <v>38.51</v>
       </c>
       <c r="R16">
-        <v>40.46</v>
+        <v>40.28</v>
       </c>
       <c r="S16">
-        <v>43.64</v>
+        <v>43.55</v>
       </c>
       <c r="T16">
-        <v>-14.27</v>
+        <v>-16.28</v>
       </c>
       <c r="U16" t="s">
         <v>55</v>
@@ -2653,43 +2647,43 @@
         <v>0</v>
       </c>
       <c r="Y16">
-        <v>32.64</v>
+        <v>26.77</v>
       </c>
       <c r="Z16">
-        <v>-0.84</v>
+        <v>-0.9</v>
       </c>
       <c r="AA16">
-        <v>-0.8100000000000001</v>
+        <v>-0.83</v>
       </c>
       <c r="AB16">
-        <v>-0.03</v>
+        <v>-0.08</v>
       </c>
       <c r="AC16">
-        <v>30.37</v>
+        <v>25.5</v>
       </c>
       <c r="AD16">
-        <v>25.59</v>
+        <v>28.6</v>
       </c>
       <c r="AE16">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="AF16">
-        <v>-32.26</v>
+        <v>-0.16</v>
       </c>
       <c r="AG16">
-        <v>40.61</v>
+        <v>40.64</v>
       </c>
       <c r="AH16">
-        <v>36.73</v>
+        <v>36.39</v>
       </c>
       <c r="AI16">
-        <v>40.56</v>
+        <v>39.99</v>
       </c>
       <c r="AJ16" t="s">
         <v>57</v>
       </c>
       <c r="AK16">
-        <v>17.92</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2700,10 +2694,10 @@
         <v>53</v>
       </c>
       <c r="C17">
-        <v>1217</v>
+        <v>1217.5</v>
       </c>
       <c r="D17">
-        <v>-2.09</v>
+        <v>0.04</v>
       </c>
       <c r="E17">
         <v>1556.41</v>
@@ -2712,46 +2706,46 @@
         <v>1216.38</v>
       </c>
       <c r="G17">
-        <v>-21.81</v>
+        <v>-21.78</v>
       </c>
       <c r="H17">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="I17">
-        <v>-0.49</v>
+        <v>-0.16</v>
       </c>
       <c r="J17">
-        <v>-7.18</v>
+        <v>-7.29</v>
       </c>
       <c r="K17">
-        <v>-3.25</v>
+        <v>-1.96</v>
       </c>
       <c r="L17">
-        <v>-10.41</v>
+        <v>-9.75</v>
       </c>
       <c r="M17">
-        <v>5.4</v>
+        <v>4.81</v>
       </c>
       <c r="N17">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="O17">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="P17">
-        <v>1231.3</v>
+        <v>1230.9</v>
       </c>
       <c r="Q17">
-        <v>1276.12</v>
+        <v>1270.34</v>
       </c>
       <c r="R17">
-        <v>1301.71</v>
+        <v>1299</v>
       </c>
       <c r="S17">
-        <v>1356.52</v>
+        <v>1355.93</v>
       </c>
       <c r="T17">
-        <v>-10.29</v>
+        <v>-10.21</v>
       </c>
       <c r="U17" t="s">
         <v>55</v>
@@ -2766,43 +2760,43 @@
         <v>0</v>
       </c>
       <c r="Y17">
-        <v>35.95</v>
+        <v>36.1</v>
       </c>
       <c r="Z17">
-        <v>-22.49</v>
+        <v>-23.56</v>
       </c>
       <c r="AA17">
-        <v>-16.94</v>
+        <v>-18.27</v>
       </c>
       <c r="AB17">
-        <v>-5.54</v>
+        <v>-5.29</v>
       </c>
       <c r="AC17">
-        <v>24.83</v>
+        <v>17.39</v>
       </c>
       <c r="AD17">
-        <v>24.07</v>
+        <v>23.83</v>
       </c>
       <c r="AE17">
-        <v>32.94</v>
+        <v>32.3</v>
       </c>
       <c r="AF17">
-        <v>17.37</v>
+        <v>-18.03</v>
       </c>
       <c r="AG17">
-        <v>1353.27</v>
+        <v>1346.81</v>
       </c>
       <c r="AH17">
-        <v>1198.97</v>
+        <v>1193.86</v>
       </c>
       <c r="AI17">
-        <v>1324.82</v>
+        <v>1320.5</v>
       </c>
       <c r="AJ17" t="s">
         <v>57</v>
       </c>
       <c r="AK17">
-        <v>21.84</v>
+        <v>23.47</v>
       </c>
     </row>
   </sheetData>
@@ -2943,7 +2937,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F141"/>
+  <dimension ref="A1:F144"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2983,7 +2977,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>64</v>
@@ -3003,7 +2997,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>69</v>
@@ -3015,10 +3009,10 @@
         <v>66</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3026,44 +3020,44 @@
         <v>48</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="E5" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="F5" s="5" t="s">
         <v>75</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="6" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C6" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="F6" s="6" t="s">
         <v>79</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -3075,16 +3069,16 @@
         <v>0</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="E9" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3095,13 +3089,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="8">
-        <v>-0.51</v>
+        <v>-1.86</v>
       </c>
       <c r="D10" s="8">
-        <v>-1.86</v>
+        <v>-2.67</v>
       </c>
       <c r="E10" s="9">
-        <v>-1.35</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3112,13 +3106,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="8">
-        <v>-0.87</v>
+        <v>-2.74</v>
       </c>
       <c r="D11" s="8">
-        <v>-2.74</v>
-      </c>
-      <c r="E11" s="9">
-        <v>-1.87</v>
+        <v>2.82</v>
+      </c>
+      <c r="E11" s="10">
+        <v>5.56</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -3129,13 +3123,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="8">
-        <v>-3.91</v>
+        <v>-0.78</v>
       </c>
       <c r="D12" s="8">
-        <v>-0.78</v>
-      </c>
-      <c r="E12" s="10">
-        <v>3.13</v>
+        <v>-3.88</v>
+      </c>
+      <c r="E12" s="9">
+        <v>-3.1</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -3146,13 +3140,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="8">
-        <v>-10.38</v>
+        <v>-5.44</v>
       </c>
       <c r="D13" s="8">
-        <v>-5.44</v>
+        <v>-5.14</v>
       </c>
       <c r="E13" s="10">
-        <v>4.94</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -3163,13 +3157,13 @@
         <v>9</v>
       </c>
       <c r="C14" s="8">
-        <v>-2.03</v>
+        <v>-6.53</v>
       </c>
       <c r="D14" s="8">
-        <v>-6.53</v>
-      </c>
-      <c r="E14" s="9">
-        <v>-4.5</v>
+        <v>-5.12</v>
+      </c>
+      <c r="E14" s="10">
+        <v>1.41</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -3180,13 +3174,13 @@
         <v>9</v>
       </c>
       <c r="C15" s="8">
-        <v>-4.24</v>
+        <v>-3.23</v>
       </c>
       <c r="D15" s="8">
-        <v>-3.23</v>
-      </c>
-      <c r="E15" s="10">
-        <v>1.01</v>
+        <v>-4.94</v>
+      </c>
+      <c r="E15" s="9">
+        <v>-1.71</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -3197,13 +3191,13 @@
         <v>9</v>
       </c>
       <c r="C16" s="8">
-        <v>3.14</v>
+        <v>1.9</v>
       </c>
       <c r="D16" s="8">
-        <v>1.9</v>
+        <v>-1.09</v>
       </c>
       <c r="E16" s="9">
-        <v>-1.24</v>
+        <v>-2.99</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -3214,13 +3208,13 @@
         <v>9</v>
       </c>
       <c r="C17" s="8">
-        <v>-0.86</v>
+        <v>-1.51</v>
       </c>
       <c r="D17" s="8">
-        <v>-1.51</v>
+        <v>-4.98</v>
       </c>
       <c r="E17" s="9">
-        <v>-0.65</v>
+        <v>-3.47</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -3231,13 +3225,13 @@
         <v>9</v>
       </c>
       <c r="C18" s="8">
-        <v>-1.79</v>
+        <v>-1.98</v>
       </c>
       <c r="D18" s="8">
-        <v>-1.98</v>
+        <v>-6.69</v>
       </c>
       <c r="E18" s="9">
-        <v>-0.19</v>
+        <v>-4.71</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -3248,13 +3242,13 @@
         <v>9</v>
       </c>
       <c r="C19" s="8">
-        <v>1.46</v>
+        <v>2.95</v>
       </c>
       <c r="D19" s="8">
-        <v>2.95</v>
-      </c>
-      <c r="E19" s="10">
-        <v>1.49</v>
+        <v>-0.25</v>
+      </c>
+      <c r="E19" s="9">
+        <v>-3.2</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -3265,13 +3259,13 @@
         <v>9</v>
       </c>
       <c r="C20" s="8">
-        <v>0.03</v>
+        <v>-5.34</v>
       </c>
       <c r="D20" s="8">
-        <v>-5.34</v>
+        <v>-8.1</v>
       </c>
       <c r="E20" s="9">
-        <v>-5.37</v>
+        <v>-2.76</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -3282,13 +3276,13 @@
         <v>9</v>
       </c>
       <c r="C21" s="8">
-        <v>8.119999999999999</v>
+        <v>5.16</v>
       </c>
       <c r="D21" s="8">
-        <v>5.16</v>
-      </c>
-      <c r="E21" s="9">
-        <v>-2.96</v>
+        <v>5.96</v>
+      </c>
+      <c r="E21" s="10">
+        <v>0.8</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -3299,13 +3293,13 @@
         <v>9</v>
       </c>
       <c r="C22" s="8">
-        <v>-0.28</v>
+        <v>-0.77</v>
       </c>
       <c r="D22" s="8">
-        <v>-0.77</v>
+        <v>-4.22</v>
       </c>
       <c r="E22" s="9">
-        <v>-0.49</v>
+        <v>-3.45</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -3316,13 +3310,13 @@
         <v>9</v>
       </c>
       <c r="C23" s="8">
-        <v>-0.42</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D23" s="8">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="E23" s="10">
-        <v>1.36</v>
+        <v>-0.49</v>
+      </c>
+      <c r="E23" s="9">
+        <v>-1.43</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -3333,13 +3327,13 @@
         <v>9</v>
       </c>
       <c r="C24" s="8">
-        <v>-4.89</v>
+        <v>-4.03</v>
       </c>
       <c r="D24" s="8">
-        <v>-4.03</v>
-      </c>
-      <c r="E24" s="10">
-        <v>0.86</v>
+        <v>-8.279999999999999</v>
+      </c>
+      <c r="E24" s="9">
+        <v>-4.25</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -3350,13 +3344,13 @@
         <v>9</v>
       </c>
       <c r="C25" s="8">
-        <v>-5.78</v>
+        <v>-7.18</v>
       </c>
       <c r="D25" s="8">
-        <v>-7.18</v>
+        <v>-7.29</v>
       </c>
       <c r="E25" s="9">
-        <v>-1.4</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -3367,13 +3361,13 @@
         <v>8</v>
       </c>
       <c r="C26" s="8">
-        <v>1.53</v>
+        <v>-0.32</v>
       </c>
       <c r="D26" s="8">
-        <v>-0.32</v>
+        <v>-2.36</v>
       </c>
       <c r="E26" s="9">
-        <v>-1.85</v>
+        <v>-2.04</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -3384,13 +3378,13 @@
         <v>8</v>
       </c>
       <c r="C27" s="8">
-        <v>-2.45</v>
+        <v>2.85</v>
       </c>
       <c r="D27" s="8">
-        <v>2.85</v>
+        <v>5.31</v>
       </c>
       <c r="E27" s="10">
-        <v>5.3</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -3401,13 +3395,13 @@
         <v>8</v>
       </c>
       <c r="C28" s="8">
-        <v>-0.16</v>
+        <v>1.04</v>
       </c>
       <c r="D28" s="8">
-        <v>1.04</v>
-      </c>
-      <c r="E28" s="10">
-        <v>1.2</v>
+        <v>-1.23</v>
+      </c>
+      <c r="E28" s="9">
+        <v>-2.27</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -3418,13 +3412,13 @@
         <v>8</v>
       </c>
       <c r="C29" s="8">
-        <v>-4.08</v>
+        <v>0.21</v>
       </c>
       <c r="D29" s="8">
-        <v>0.21</v>
+        <v>1.52</v>
       </c>
       <c r="E29" s="10">
-        <v>4.29</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -3435,13 +3429,13 @@
         <v>8</v>
       </c>
       <c r="C30" s="8">
-        <v>0.6</v>
+        <v>-0.64</v>
       </c>
       <c r="D30" s="8">
-        <v>-0.64</v>
-      </c>
-      <c r="E30" s="9">
-        <v>-1.24</v>
+        <v>0.72</v>
+      </c>
+      <c r="E30" s="10">
+        <v>1.36</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -3452,13 +3446,13 @@
         <v>8</v>
       </c>
       <c r="C31" s="8">
-        <v>-0.1</v>
+        <v>-1.96</v>
       </c>
       <c r="D31" s="8">
-        <v>-1.96</v>
-      </c>
-      <c r="E31" s="9">
-        <v>-1.86</v>
+        <v>-1.35</v>
+      </c>
+      <c r="E31" s="10">
+        <v>0.61</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -3469,13 +3463,13 @@
         <v>8</v>
       </c>
       <c r="C32" s="8">
-        <v>0.11</v>
+        <v>-0.27</v>
       </c>
       <c r="D32" s="8">
-        <v>-0.27</v>
+        <v>-0.73</v>
       </c>
       <c r="E32" s="9">
-        <v>-0.38</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -3486,13 +3480,13 @@
         <v>8</v>
       </c>
       <c r="C33" s="8">
-        <v>-0.44</v>
+        <v>-1.29</v>
       </c>
       <c r="D33" s="8">
-        <v>-1.29</v>
-      </c>
-      <c r="E33" s="9">
-        <v>-0.85</v>
+        <v>-1.12</v>
+      </c>
+      <c r="E33" s="10">
+        <v>0.17</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -3503,13 +3497,13 @@
         <v>8</v>
       </c>
       <c r="C34" s="8">
-        <v>-2.73</v>
+        <v>-3.93</v>
       </c>
       <c r="D34" s="8">
-        <v>-3.93</v>
+        <v>-6.2</v>
       </c>
       <c r="E34" s="9">
-        <v>-1.2</v>
+        <v>-2.27</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -3520,13 +3514,13 @@
         <v>8</v>
       </c>
       <c r="C35" s="8">
-        <v>0.78</v>
+        <v>2.18</v>
       </c>
       <c r="D35" s="8">
-        <v>2.18</v>
-      </c>
-      <c r="E35" s="10">
-        <v>1.4</v>
+        <v>1.8</v>
+      </c>
+      <c r="E35" s="9">
+        <v>-0.38</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -3537,13 +3531,13 @@
         <v>8</v>
       </c>
       <c r="C36" s="8">
-        <v>0.71</v>
+        <v>-0.83</v>
       </c>
       <c r="D36" s="8">
-        <v>-0.83</v>
+        <v>-2.16</v>
       </c>
       <c r="E36" s="9">
-        <v>-1.54</v>
+        <v>-1.33</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -3554,13 +3548,13 @@
         <v>8</v>
       </c>
       <c r="C37" s="8">
-        <v>1.51</v>
+        <v>0.63</v>
       </c>
       <c r="D37" s="8">
-        <v>0.63</v>
-      </c>
-      <c r="E37" s="9">
-        <v>-0.88</v>
+        <v>1.41</v>
+      </c>
+      <c r="E37" s="10">
+        <v>0.78</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -3571,13 +3565,13 @@
         <v>8</v>
       </c>
       <c r="C38" s="8">
-        <v>-0.41</v>
+        <v>-1.52</v>
       </c>
       <c r="D38" s="8">
-        <v>-1.52</v>
+        <v>-3.08</v>
       </c>
       <c r="E38" s="9">
-        <v>-1.11</v>
+        <v>-1.56</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -3588,13 +3582,13 @@
         <v>8</v>
       </c>
       <c r="C39" s="8">
-        <v>0.26</v>
+        <v>0.39</v>
       </c>
       <c r="D39" s="8">
-        <v>0.39</v>
-      </c>
-      <c r="E39" s="10">
-        <v>0.13</v>
+        <v>-0.83</v>
+      </c>
+      <c r="E39" s="9">
+        <v>-1.22</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -3605,13 +3599,13 @@
         <v>8</v>
       </c>
       <c r="C40" s="8">
-        <v>-0.79</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="D40" s="8">
-        <v>-0.6899999999999999</v>
-      </c>
-      <c r="E40" s="10">
-        <v>0.1</v>
+        <v>-2.64</v>
+      </c>
+      <c r="E40" s="9">
+        <v>-1.95</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -3622,13 +3616,13 @@
         <v>8</v>
       </c>
       <c r="C41" s="8">
-        <v>-0.79</v>
+        <v>-0.49</v>
       </c>
       <c r="D41" s="8">
-        <v>-0.49</v>
+        <v>-0.16</v>
       </c>
       <c r="E41" s="10">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -3639,13 +3633,13 @@
         <v>11</v>
       </c>
       <c r="C42" s="8">
-        <v>-9.52</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="D42" s="8">
-        <v>-9.380000000000001</v>
+        <v>-8.92</v>
       </c>
       <c r="E42" s="10">
-        <v>0.14</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -3656,13 +3650,13 @@
         <v>11</v>
       </c>
       <c r="C43" s="8">
-        <v>10.47</v>
+        <v>11.94</v>
       </c>
       <c r="D43" s="8">
-        <v>11.94</v>
+        <v>14.39</v>
       </c>
       <c r="E43" s="10">
-        <v>1.47</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -3673,13 +3667,13 @@
         <v>11</v>
       </c>
       <c r="C44" s="8">
-        <v>-42.56</v>
+        <v>-40.94</v>
       </c>
       <c r="D44" s="8">
-        <v>-40.94</v>
-      </c>
-      <c r="E44" s="10">
-        <v>1.62</v>
+        <v>-43.68</v>
+      </c>
+      <c r="E44" s="9">
+        <v>-2.74</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -3690,13 +3684,13 @@
         <v>11</v>
       </c>
       <c r="C45" s="8">
-        <v>-32.68</v>
+        <v>-31.14</v>
       </c>
       <c r="D45" s="8">
-        <v>-31.14</v>
+        <v>-30.28</v>
       </c>
       <c r="E45" s="10">
-        <v>1.54</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -3707,13 +3701,13 @@
         <v>11</v>
       </c>
       <c r="C46" s="8">
-        <v>3.32</v>
+        <v>3.79</v>
       </c>
       <c r="D46" s="8">
-        <v>3.79</v>
+        <v>5.3</v>
       </c>
       <c r="E46" s="10">
-        <v>0.47</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -3724,13 +3718,13 @@
         <v>11</v>
       </c>
       <c r="C47" s="8">
-        <v>-3.24</v>
+        <v>-2.95</v>
       </c>
       <c r="D47" s="8">
-        <v>-2.95</v>
-      </c>
-      <c r="E47" s="10">
-        <v>0.29</v>
+        <v>-3.07</v>
+      </c>
+      <c r="E47" s="9">
+        <v>-0.12</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -3741,13 +3735,13 @@
         <v>11</v>
       </c>
       <c r="C48" s="8">
-        <v>-35.05</v>
+        <v>-34.34</v>
       </c>
       <c r="D48" s="8">
-        <v>-34.34</v>
+        <v>-33.72</v>
       </c>
       <c r="E48" s="10">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -3758,13 +3752,13 @@
         <v>11</v>
       </c>
       <c r="C49" s="8">
+        <v>-6.85</v>
+      </c>
+      <c r="D49" s="8">
         <v>-6.67</v>
       </c>
-      <c r="D49" s="8">
-        <v>-6.85</v>
-      </c>
-      <c r="E49" s="9">
-        <v>-0.18</v>
+      <c r="E49" s="10">
+        <v>0.18</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -3775,13 +3769,13 @@
         <v>11</v>
       </c>
       <c r="C50" s="8">
-        <v>-5.11</v>
+        <v>-6.2</v>
       </c>
       <c r="D50" s="8">
-        <v>-6.2</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="E50" s="9">
-        <v>-1.09</v>
+        <v>-2.51</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -3792,13 +3786,13 @@
         <v>11</v>
       </c>
       <c r="C51" s="8">
-        <v>17.83</v>
+        <v>18.81</v>
       </c>
       <c r="D51" s="8">
-        <v>18.81</v>
+        <v>20.24</v>
       </c>
       <c r="E51" s="10">
-        <v>0.98</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -3809,13 +3803,13 @@
         <v>11</v>
       </c>
       <c r="C52" s="8">
-        <v>-23.24</v>
+        <v>-24.21</v>
       </c>
       <c r="D52" s="8">
-        <v>-24.21</v>
-      </c>
-      <c r="E52" s="9">
-        <v>-0.97</v>
+        <v>-23.74</v>
+      </c>
+      <c r="E52" s="10">
+        <v>0.47</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -3826,13 +3820,13 @@
         <v>11</v>
       </c>
       <c r="C53" s="8">
-        <v>42.55</v>
+        <v>41.03</v>
       </c>
       <c r="D53" s="8">
-        <v>41.03</v>
-      </c>
-      <c r="E53" s="9">
-        <v>-1.52</v>
+        <v>41.93</v>
+      </c>
+      <c r="E53" s="10">
+        <v>0.9</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -3843,13 +3837,13 @@
         <v>11</v>
       </c>
       <c r="C54" s="8">
-        <v>-46.19</v>
+        <v>-46.58</v>
       </c>
       <c r="D54" s="8">
-        <v>-46.58</v>
+        <v>-46.79</v>
       </c>
       <c r="E54" s="9">
-        <v>-0.39</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -3860,13 +3854,13 @@
         <v>11</v>
       </c>
       <c r="C55" s="8">
-        <v>-29.5</v>
+        <v>-29.68</v>
       </c>
       <c r="D55" s="8">
-        <v>-29.68</v>
-      </c>
-      <c r="E55" s="9">
-        <v>-0.18</v>
+        <v>-29.3</v>
+      </c>
+      <c r="E55" s="10">
+        <v>0.38</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -3877,13 +3871,13 @@
         <v>11</v>
       </c>
       <c r="C56" s="8">
-        <v>-36.24</v>
+        <v>-36.09</v>
       </c>
       <c r="D56" s="8">
-        <v>-36.09</v>
-      </c>
-      <c r="E56" s="10">
-        <v>0.15</v>
+        <v>-38.25</v>
+      </c>
+      <c r="E56" s="9">
+        <v>-2.16</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -3894,13 +3888,13 @@
         <v>11</v>
       </c>
       <c r="C57" s="8">
-        <v>-8.970000000000001</v>
+        <v>-10.41</v>
       </c>
       <c r="D57" s="8">
-        <v>-10.41</v>
-      </c>
-      <c r="E57" s="9">
-        <v>-1.44</v>
+        <v>-9.75</v>
+      </c>
+      <c r="E57" s="10">
+        <v>0.66</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -3911,13 +3905,13 @@
         <v>10</v>
       </c>
       <c r="C58" s="8">
-        <v>9.33</v>
+        <v>7.98</v>
       </c>
       <c r="D58" s="8">
-        <v>7.98</v>
-      </c>
-      <c r="E58" s="9">
-        <v>-1.35</v>
+        <v>9.82</v>
+      </c>
+      <c r="E58" s="10">
+        <v>1.84</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -3928,13 +3922,13 @@
         <v>10</v>
       </c>
       <c r="C59" s="8">
-        <v>32.86</v>
+        <v>34.35</v>
       </c>
       <c r="D59" s="8">
-        <v>34.35</v>
+        <v>39.97</v>
       </c>
       <c r="E59" s="10">
-        <v>1.49</v>
+        <v>5.62</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -3945,13 +3939,13 @@
         <v>10</v>
       </c>
       <c r="C60" s="8">
-        <v>-13.94</v>
+        <v>-13.54</v>
       </c>
       <c r="D60" s="8">
-        <v>-13.54</v>
+        <v>-12.41</v>
       </c>
       <c r="E60" s="10">
-        <v>0.4</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -3962,13 +3956,13 @@
         <v>10</v>
       </c>
       <c r="C61" s="8">
-        <v>-17.89</v>
+        <v>-16.41</v>
       </c>
       <c r="D61" s="8">
-        <v>-16.41</v>
+        <v>-13.71</v>
       </c>
       <c r="E61" s="10">
-        <v>1.48</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -3979,13 +3973,13 @@
         <v>10</v>
       </c>
       <c r="C62" s="8">
-        <v>-13.56</v>
+        <v>-16.13</v>
       </c>
       <c r="D62" s="8">
-        <v>-16.13</v>
-      </c>
-      <c r="E62" s="9">
-        <v>-2.57</v>
+        <v>-14.02</v>
+      </c>
+      <c r="E62" s="10">
+        <v>2.11</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -3996,13 +3990,13 @@
         <v>10</v>
       </c>
       <c r="C63" s="8">
-        <v>-11.96</v>
+        <v>-13.07</v>
       </c>
       <c r="D63" s="8">
-        <v>-13.07</v>
-      </c>
-      <c r="E63" s="9">
-        <v>-1.11</v>
+        <v>-11.58</v>
+      </c>
+      <c r="E63" s="10">
+        <v>1.49</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -4013,13 +4007,13 @@
         <v>10</v>
       </c>
       <c r="C64" s="8">
-        <v>-13.84</v>
+        <v>-14.22</v>
       </c>
       <c r="D64" s="8">
-        <v>-14.22</v>
-      </c>
-      <c r="E64" s="9">
-        <v>-0.38</v>
+        <v>-13.7</v>
+      </c>
+      <c r="E64" s="10">
+        <v>0.52</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -4030,13 +4024,13 @@
         <v>10</v>
       </c>
       <c r="C65" s="8">
-        <v>-5.15</v>
+        <v>-5.14</v>
       </c>
       <c r="D65" s="8">
-        <v>-5.14</v>
-      </c>
-      <c r="E65" s="10">
-        <v>0.01</v>
+        <v>-6.48</v>
+      </c>
+      <c r="E65" s="9">
+        <v>-1.34</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -4047,13 +4041,13 @@
         <v>10</v>
       </c>
       <c r="C66" s="8">
-        <v>-12.96</v>
+        <v>-14.51</v>
       </c>
       <c r="D66" s="8">
-        <v>-14.51</v>
+        <v>-16.34</v>
       </c>
       <c r="E66" s="9">
-        <v>-1.55</v>
+        <v>-1.83</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -4064,13 +4058,13 @@
         <v>10</v>
       </c>
       <c r="C67" s="8">
-        <v>-11.13</v>
+        <v>-10.62</v>
       </c>
       <c r="D67" s="8">
-        <v>-10.62</v>
+        <v>-8.35</v>
       </c>
       <c r="E67" s="10">
-        <v>0.51</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -4081,13 +4075,13 @@
         <v>10</v>
       </c>
       <c r="C68" s="8">
-        <v>0.53</v>
+        <v>-0.62</v>
       </c>
       <c r="D68" s="8">
-        <v>-0.62</v>
-      </c>
-      <c r="E68" s="9">
-        <v>-1.15</v>
+        <v>-0.46</v>
+      </c>
+      <c r="E68" s="10">
+        <v>0.16</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -4098,13 +4092,13 @@
         <v>10</v>
       </c>
       <c r="C69" s="8">
-        <v>23.85</v>
+        <v>23.25</v>
       </c>
       <c r="D69" s="8">
-        <v>23.25</v>
-      </c>
-      <c r="E69" s="9">
-        <v>-0.6</v>
+        <v>26.12</v>
+      </c>
+      <c r="E69" s="10">
+        <v>2.87</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -4115,13 +4109,13 @@
         <v>10</v>
       </c>
       <c r="C70" s="8">
-        <v>3.6</v>
+        <v>2.83</v>
       </c>
       <c r="D70" s="8">
-        <v>2.83</v>
+        <v>2.37</v>
       </c>
       <c r="E70" s="9">
-        <v>-0.77</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -4132,13 +4126,13 @@
         <v>10</v>
       </c>
       <c r="C71" s="8">
-        <v>-3.72</v>
+        <v>-4.45</v>
       </c>
       <c r="D71" s="8">
-        <v>-4.45</v>
-      </c>
-      <c r="E71" s="9">
-        <v>-0.73</v>
+        <v>-3.97</v>
+      </c>
+      <c r="E71" s="10">
+        <v>0.48</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -4149,13 +4143,13 @@
         <v>10</v>
       </c>
       <c r="C72" s="8">
-        <v>-12.82</v>
+        <v>-13.14</v>
       </c>
       <c r="D72" s="8">
-        <v>-13.14</v>
+        <v>-14.83</v>
       </c>
       <c r="E72" s="9">
-        <v>-0.32</v>
+        <v>-1.69</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -4166,13 +4160,13 @@
         <v>10</v>
       </c>
       <c r="C73" s="8">
-        <v>-1.18</v>
+        <v>-3.25</v>
       </c>
       <c r="D73" s="8">
-        <v>-3.25</v>
-      </c>
-      <c r="E73" s="9">
-        <v>-2.07</v>
+        <v>-1.96</v>
+      </c>
+      <c r="E73" s="10">
+        <v>1.29</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -4183,13 +4177,13 @@
         <v>6</v>
       </c>
       <c r="C74" s="8">
-        <v>-8.25</v>
+        <v>-8.83</v>
       </c>
       <c r="D74" s="8">
-        <v>-8.83</v>
+        <v>-9.15</v>
       </c>
       <c r="E74" s="9">
-        <v>-0.58</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -4200,13 +4194,13 @@
         <v>6</v>
       </c>
       <c r="C75" s="8">
-        <v>-14.42</v>
+        <v>-13.45</v>
       </c>
       <c r="D75" s="8">
-        <v>-13.45</v>
+        <v>-11.2</v>
       </c>
       <c r="E75" s="10">
-        <v>0.97</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -4217,13 +4211,13 @@
         <v>6</v>
       </c>
       <c r="C76" s="8">
-        <v>-43.4</v>
+        <v>-43.14</v>
       </c>
       <c r="D76" s="8">
-        <v>-43.14</v>
-      </c>
-      <c r="E76" s="10">
-        <v>0.26</v>
+        <v>-44.12</v>
+      </c>
+      <c r="E76" s="9">
+        <v>-0.98</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -4234,13 +4228,13 @@
         <v>6</v>
       </c>
       <c r="C77" s="8">
-        <v>-36.73</v>
+        <v>-35.59</v>
       </c>
       <c r="D77" s="8">
-        <v>-35.59</v>
+        <v>-34.93</v>
       </c>
       <c r="E77" s="10">
-        <v>1.14</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -4251,13 +4245,13 @@
         <v>6</v>
       </c>
       <c r="C78" s="8">
-        <v>-17.55</v>
+        <v>-20</v>
       </c>
       <c r="D78" s="8">
-        <v>-20</v>
-      </c>
-      <c r="E78" s="9">
-        <v>-2.45</v>
+        <v>-18.05</v>
+      </c>
+      <c r="E78" s="10">
+        <v>1.95</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -4268,13 +4262,13 @@
         <v>6</v>
       </c>
       <c r="C79" s="8">
-        <v>-15.86</v>
+        <v>-16.92</v>
       </c>
       <c r="D79" s="8">
-        <v>-16.92</v>
+        <v>-17.32</v>
       </c>
       <c r="E79" s="9">
-        <v>-1.06</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -4285,13 +4279,13 @@
         <v>6</v>
       </c>
       <c r="C80" s="8">
-        <v>-36.24</v>
+        <v>-36.52</v>
       </c>
       <c r="D80" s="8">
-        <v>-36.52</v>
+        <v>-36.81</v>
       </c>
       <c r="E80" s="9">
-        <v>-0.28</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -4302,13 +4296,13 @@
         <v>6</v>
       </c>
       <c r="C81" s="8">
-        <v>-38.78</v>
+        <v>-38.77</v>
       </c>
       <c r="D81" s="8">
-        <v>-38.77</v>
-      </c>
-      <c r="E81" s="10">
-        <v>0.01</v>
+        <v>-39</v>
+      </c>
+      <c r="E81" s="9">
+        <v>-0.23</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -4319,13 +4313,13 @@
         <v>6</v>
       </c>
       <c r="C82" s="8">
-        <v>-19.75</v>
+        <v>-21.18</v>
       </c>
       <c r="D82" s="8">
-        <v>-21.18</v>
+        <v>-23.78</v>
       </c>
       <c r="E82" s="9">
-        <v>-1.43</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -4336,13 +4330,13 @@
         <v>6</v>
       </c>
       <c r="C83" s="8">
-        <v>-13.72</v>
+        <v>-13.22</v>
       </c>
       <c r="D83" s="8">
-        <v>-13.22</v>
-      </c>
-      <c r="E83" s="10">
-        <v>0.5</v>
+        <v>-13.78</v>
+      </c>
+      <c r="E83" s="9">
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -4353,13 +4347,13 @@
         <v>6</v>
       </c>
       <c r="C84" s="8">
-        <v>-28.73</v>
+        <v>-29.54</v>
       </c>
       <c r="D84" s="8">
-        <v>-29.54</v>
+        <v>-30.21</v>
       </c>
       <c r="E84" s="9">
-        <v>-0.8100000000000001</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -4370,13 +4364,13 @@
         <v>6</v>
       </c>
       <c r="C85" s="8">
-        <v>-0.06</v>
+        <v>-0.55</v>
       </c>
       <c r="D85" s="8">
-        <v>-0.55</v>
-      </c>
-      <c r="E85" s="9">
-        <v>-0.49</v>
+        <v>0</v>
+      </c>
+      <c r="E85" s="10">
+        <v>0.55</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -4387,13 +4381,13 @@
         <v>6</v>
       </c>
       <c r="C86" s="8">
-        <v>-46.93</v>
+        <v>-47.32</v>
       </c>
       <c r="D86" s="8">
-        <v>-47.32</v>
+        <v>-47.86</v>
       </c>
       <c r="E86" s="9">
-        <v>-0.39</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -4404,13 +4398,13 @@
         <v>6</v>
       </c>
       <c r="C87" s="8">
-        <v>-41.01</v>
+        <v>-41.45</v>
       </c>
       <c r="D87" s="8">
-        <v>-41.45</v>
+        <v>-41.64</v>
       </c>
       <c r="E87" s="9">
-        <v>-0.44</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -4421,13 +4415,13 @@
         <v>6</v>
       </c>
       <c r="C88" s="8">
-        <v>-36.4</v>
+        <v>-36.64</v>
       </c>
       <c r="D88" s="8">
-        <v>-36.64</v>
+        <v>-37.98</v>
       </c>
       <c r="E88" s="9">
-        <v>-0.24</v>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -4438,13 +4432,13 @@
         <v>6</v>
       </c>
       <c r="C89" s="8">
-        <v>-20.14</v>
+        <v>-21.81</v>
       </c>
       <c r="D89" s="8">
-        <v>-21.81</v>
-      </c>
-      <c r="E89" s="9">
-        <v>-1.67</v>
+        <v>-21.78</v>
+      </c>
+      <c r="E89" s="10">
+        <v>0.03</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -4455,13 +4449,13 @@
         <v>2</v>
       </c>
       <c r="C90" s="8">
-        <v>730</v>
+        <v>721</v>
       </c>
       <c r="D90" s="8">
-        <v>721</v>
+        <v>718.5</v>
       </c>
       <c r="E90" s="9">
-        <v>-9</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -4472,13 +4466,13 @@
         <v>2</v>
       </c>
       <c r="C91" s="8">
-        <v>925.6</v>
+        <v>936</v>
       </c>
       <c r="D91" s="8">
-        <v>936</v>
+        <v>960.4</v>
       </c>
       <c r="E91" s="10">
-        <v>10.4</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -4489,13 +4483,13 @@
         <v>2</v>
       </c>
       <c r="C92" s="8">
-        <v>212.93</v>
+        <v>213.93</v>
       </c>
       <c r="D92" s="8">
-        <v>213.93</v>
-      </c>
-      <c r="E92" s="10">
-        <v>1</v>
+        <v>210.24</v>
+      </c>
+      <c r="E92" s="9">
+        <v>-3.69</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -4506,13 +4500,13 @@
         <v>2</v>
       </c>
       <c r="C93" s="8">
-        <v>626.35</v>
+        <v>637.65</v>
       </c>
       <c r="D93" s="8">
-        <v>637.65</v>
+        <v>644.15</v>
       </c>
       <c r="E93" s="10">
-        <v>11.3</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -4523,13 +4517,13 @@
         <v>2</v>
       </c>
       <c r="C94" s="8">
-        <v>1699.9</v>
+        <v>1649.3</v>
       </c>
       <c r="D94" s="8">
-        <v>1649.3</v>
-      </c>
-      <c r="E94" s="9">
-        <v>-50.6</v>
+        <v>1689.6</v>
+      </c>
+      <c r="E94" s="10">
+        <v>40.3</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -4540,13 +4534,13 @@
         <v>2</v>
       </c>
       <c r="C95" s="8">
-        <v>1060.5</v>
+        <v>1047.1</v>
       </c>
       <c r="D95" s="8">
-        <v>1047.1</v>
+        <v>1042</v>
       </c>
       <c r="E95" s="9">
-        <v>-13.4</v>
+        <v>-5.1</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -4557,13 +4551,13 @@
         <v>2</v>
       </c>
       <c r="C96" s="8">
-        <v>3665.9</v>
+        <v>3650</v>
       </c>
       <c r="D96" s="8">
-        <v>3650</v>
+        <v>3633.2</v>
       </c>
       <c r="E96" s="9">
-        <v>-15.9</v>
+        <v>-16.8</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -4574,13 +4568,13 @@
         <v>2</v>
       </c>
       <c r="C97" s="8">
-        <v>644.35</v>
+        <v>644.45</v>
       </c>
       <c r="D97" s="8">
-        <v>644.45</v>
-      </c>
-      <c r="E97" s="10">
-        <v>0.1</v>
+        <v>642.1</v>
+      </c>
+      <c r="E97" s="9">
+        <v>-2.35</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -4591,13 +4585,13 @@
         <v>2</v>
       </c>
       <c r="C98" s="8">
-        <v>370.6</v>
+        <v>364</v>
       </c>
       <c r="D98" s="8">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="E98" s="9">
-        <v>-6.6</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -4608,13 +4602,13 @@
         <v>2</v>
       </c>
       <c r="C99" s="8">
-        <v>186.94</v>
+        <v>188.01</v>
       </c>
       <c r="D99" s="8">
-        <v>188.01</v>
-      </c>
-      <c r="E99" s="10">
-        <v>1.07</v>
+        <v>186.8</v>
+      </c>
+      <c r="E99" s="9">
+        <v>-1.21</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -4625,13 +4619,13 @@
         <v>2</v>
       </c>
       <c r="C100" s="8">
-        <v>2296.2</v>
+        <v>2270</v>
       </c>
       <c r="D100" s="8">
-        <v>2270</v>
+        <v>2248.4</v>
       </c>
       <c r="E100" s="9">
-        <v>-26.2</v>
+        <v>-21.6</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -4642,13 +4636,13 @@
         <v>2</v>
       </c>
       <c r="C101" s="8">
-        <v>5124.8</v>
+        <v>5100</v>
       </c>
       <c r="D101" s="8">
-        <v>5100</v>
-      </c>
-      <c r="E101" s="9">
-        <v>-24.8</v>
+        <v>5139.3</v>
+      </c>
+      <c r="E101" s="10">
+        <v>39.3</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -4659,13 +4653,13 @@
         <v>2</v>
       </c>
       <c r="C102" s="8">
-        <v>2930</v>
+        <v>2908.2</v>
       </c>
       <c r="D102" s="8">
-        <v>2908.2</v>
+        <v>2878.5</v>
       </c>
       <c r="E102" s="9">
-        <v>-21.8</v>
+        <v>-29.7</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -4676,13 +4670,13 @@
         <v>2</v>
       </c>
       <c r="C103" s="8">
-        <v>231.7</v>
+        <v>229.94</v>
       </c>
       <c r="D103" s="8">
-        <v>229.94</v>
+        <v>229.22</v>
       </c>
       <c r="E103" s="9">
-        <v>-1.76</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -4693,13 +4687,13 @@
         <v>2</v>
       </c>
       <c r="C104" s="8">
-        <v>37.55</v>
+        <v>37.41</v>
       </c>
       <c r="D104" s="8">
-        <v>37.41</v>
+        <v>36.46</v>
       </c>
       <c r="E104" s="9">
-        <v>-0.14</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -4710,13 +4704,13 @@
         <v>2</v>
       </c>
       <c r="C105" s="8">
-        <v>1243</v>
+        <v>1217</v>
       </c>
       <c r="D105" s="8">
-        <v>1217</v>
-      </c>
-      <c r="E105" s="9">
-        <v>-26</v>
+        <v>1217.5</v>
+      </c>
+      <c r="E105" s="10">
+        <v>0.5</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -4727,13 +4721,13 @@
         <v>13</v>
       </c>
       <c r="C106" s="8">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D106" s="8">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E106" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -4744,591 +4738,642 @@
         <v>13</v>
       </c>
       <c r="C107" s="8">
+        <v>68</v>
+      </c>
+      <c r="D107" s="8">
         <v>74</v>
       </c>
-      <c r="D107" s="8">
-        <v>68</v>
-      </c>
-      <c r="E107" s="9">
-        <v>-6</v>
+      <c r="E107" s="10">
+        <v>6</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B108" s="7" t="s">
         <v>13</v>
       </c>
       <c r="C108" s="8">
-        <v>68</v>
+        <v>26</v>
       </c>
       <c r="D108" s="8">
-        <v>74</v>
-      </c>
-      <c r="E108" s="10">
-        <v>6</v>
+        <v>19</v>
+      </c>
+      <c r="E108" s="9">
+        <v>-7</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="7" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B109" s="7" t="s">
         <v>13</v>
       </c>
       <c r="C109" s="8">
-        <v>19</v>
+        <v>74</v>
       </c>
       <c r="D109" s="8">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="E109" s="9">
-        <v>-6</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="7" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B110" s="7" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C110" s="8">
-        <v>51.62</v>
+        <v>50</v>
       </c>
       <c r="D110" s="8">
-        <v>45.19</v>
+        <v>44</v>
       </c>
       <c r="E110" s="9">
-        <v>-6.43</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="7" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="B111" s="7" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C111" s="8">
-        <v>47.08</v>
+        <v>44</v>
       </c>
       <c r="D111" s="8">
-        <v>48.59</v>
+        <v>50</v>
       </c>
       <c r="E111" s="10">
-        <v>1.51</v>
+        <v>6</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="7" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="B112" s="7" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C112" s="8">
-        <v>41.9</v>
+        <v>62</v>
       </c>
       <c r="D112" s="8">
-        <v>44.31</v>
+        <v>68</v>
       </c>
       <c r="E112" s="10">
-        <v>2.41</v>
+        <v>6</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="7" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B113" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C113" s="8">
-        <v>24.6</v>
+        <v>45.19</v>
       </c>
       <c r="D113" s="8">
-        <v>34.46</v>
-      </c>
-      <c r="E113" s="10">
-        <v>9.859999999999999</v>
+        <v>43.57</v>
+      </c>
+      <c r="E113" s="9">
+        <v>-1.62</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B114" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C114" s="8">
-        <v>41.83</v>
+        <v>48.59</v>
       </c>
       <c r="D114" s="8">
-        <v>35.28</v>
-      </c>
-      <c r="E114" s="9">
-        <v>-6.55</v>
+        <v>52.03</v>
+      </c>
+      <c r="E114" s="10">
+        <v>3.44</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B115" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C115" s="8">
-        <v>43.82</v>
+        <v>44.31</v>
       </c>
       <c r="D115" s="8">
-        <v>40.45</v>
+        <v>38.04</v>
       </c>
       <c r="E115" s="9">
-        <v>-3.37</v>
+        <v>-6.27</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="7" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B116" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C116" s="8">
-        <v>46.08</v>
+        <v>34.46</v>
       </c>
       <c r="D116" s="8">
-        <v>44.74</v>
-      </c>
-      <c r="E116" s="9">
-        <v>-1.34</v>
+        <v>39.37</v>
+      </c>
+      <c r="E116" s="10">
+        <v>4.91</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B117" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C117" s="8">
-        <v>38.78</v>
+        <v>35.28</v>
       </c>
       <c r="D117" s="8">
-        <v>38.85</v>
+        <v>42.94</v>
       </c>
       <c r="E117" s="10">
-        <v>0.07000000000000001</v>
+        <v>7.66</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="7" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B118" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C118" s="8">
-        <v>35.62</v>
+        <v>40.45</v>
       </c>
       <c r="D118" s="8">
-        <v>29.2</v>
+        <v>39.22</v>
       </c>
       <c r="E118" s="9">
-        <v>-6.42</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="7" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B119" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C119" s="8">
-        <v>49.91</v>
+        <v>44.74</v>
       </c>
       <c r="D119" s="8">
-        <v>52.3</v>
-      </c>
-      <c r="E119" s="10">
-        <v>2.39</v>
+        <v>43.3</v>
+      </c>
+      <c r="E119" s="9">
+        <v>-1.44</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="7" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B120" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C120" s="8">
-        <v>47.73</v>
+        <v>38.85</v>
       </c>
       <c r="D120" s="8">
-        <v>44.91</v>
+        <v>37.67</v>
       </c>
       <c r="E120" s="9">
-        <v>-2.82</v>
+        <v>-1.18</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="7" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B121" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C121" s="8">
-        <v>71.59999999999999</v>
+        <v>29.2</v>
       </c>
       <c r="D121" s="8">
-        <v>67.79000000000001</v>
+        <v>21.58</v>
       </c>
       <c r="E121" s="9">
-        <v>-3.81</v>
+        <v>-7.62</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B122" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C122" s="8">
-        <v>44.24</v>
+        <v>52.3</v>
       </c>
       <c r="D122" s="8">
-        <v>41.77</v>
+        <v>49.42</v>
       </c>
       <c r="E122" s="9">
-        <v>-2.47</v>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="7" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C123" s="8">
-        <v>48.74</v>
+        <v>44.91</v>
       </c>
       <c r="D123" s="8">
-        <v>45.86</v>
+        <v>42.68</v>
       </c>
       <c r="E123" s="9">
-        <v>-2.88</v>
+        <v>-2.23</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="7" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B124" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C124" s="8">
-        <v>33.65</v>
+        <v>67.79000000000001</v>
       </c>
       <c r="D124" s="8">
-        <v>32.64</v>
-      </c>
-      <c r="E124" s="9">
-        <v>-1.01</v>
+        <v>70.47</v>
+      </c>
+      <c r="E124" s="10">
+        <v>2.68</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="7" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B125" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C125" s="8">
-        <v>40.68</v>
+        <v>41.77</v>
       </c>
       <c r="D125" s="8">
-        <v>35.95</v>
+        <v>38.61</v>
       </c>
       <c r="E125" s="9">
-        <v>-4.73</v>
+        <v>-3.16</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="7" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="B126" s="7" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C126" s="8">
-        <v>-33.68</v>
+        <v>45.86</v>
       </c>
       <c r="D126" s="8">
-        <v>-51.27</v>
+        <v>44.69</v>
       </c>
       <c r="E126" s="9">
-        <v>-17.59</v>
+        <v>-1.17</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="7" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B127" s="7" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C127" s="8">
-        <v>-76.51000000000001</v>
+        <v>32.64</v>
       </c>
       <c r="D127" s="8">
-        <v>-75.59</v>
-      </c>
-      <c r="E127" s="10">
-        <v>0.92</v>
+        <v>26.77</v>
+      </c>
+      <c r="E127" s="9">
+        <v>-5.87</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="7" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="B128" s="7" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C128" s="8">
-        <v>11.16</v>
+        <v>35.95</v>
       </c>
       <c r="D128" s="8">
-        <v>-25.56</v>
-      </c>
-      <c r="E128" s="9">
-        <v>-36.72</v>
+        <v>36.1</v>
+      </c>
+      <c r="E128" s="10">
+        <v>0.15</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="7" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B129" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C129" s="8">
-        <v>-58.44</v>
+        <v>-51.27</v>
       </c>
       <c r="D129" s="8">
-        <v>-37.71</v>
+        <v>-40.67</v>
       </c>
       <c r="E129" s="10">
-        <v>20.73</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B130" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C130" s="8">
-        <v>69.54000000000001</v>
+        <v>-75.59</v>
       </c>
       <c r="D130" s="8">
-        <v>25.66</v>
-      </c>
-      <c r="E130" s="9">
-        <v>-43.88</v>
+        <v>-17.97</v>
+      </c>
+      <c r="E130" s="10">
+        <v>57.62</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B131" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C131" s="8">
-        <v>-49.71</v>
+        <v>-25.56</v>
       </c>
       <c r="D131" s="8">
-        <v>-20.65</v>
-      </c>
-      <c r="E131" s="10">
-        <v>29.06</v>
+        <v>-43.19</v>
+      </c>
+      <c r="E131" s="9">
+        <v>-17.63</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="7" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B132" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C132" s="8">
-        <v>-41.07</v>
+        <v>-37.71</v>
       </c>
       <c r="D132" s="8">
-        <v>-57.16</v>
-      </c>
-      <c r="E132" s="9">
-        <v>-16.09</v>
+        <v>-2.66</v>
+      </c>
+      <c r="E132" s="10">
+        <v>35.05</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B133" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C133" s="8">
-        <v>-71.62</v>
+        <v>25.66</v>
       </c>
       <c r="D133" s="8">
-        <v>-58.04</v>
-      </c>
-      <c r="E133" s="10">
-        <v>13.58</v>
+        <v>20.21</v>
+      </c>
+      <c r="E133" s="9">
+        <v>-5.45</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="7" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C134" s="8">
-        <v>145.52</v>
+        <v>-20.65</v>
       </c>
       <c r="D134" s="8">
-        <v>25.73</v>
+        <v>-24.95</v>
       </c>
       <c r="E134" s="9">
-        <v>-119.79</v>
+        <v>-4.3</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="7" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B135" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C135" s="8">
-        <v>10.96</v>
+        <v>-57.16</v>
       </c>
       <c r="D135" s="8">
-        <v>42.13</v>
-      </c>
-      <c r="E135" s="10">
-        <v>31.17</v>
+        <v>-59.76</v>
+      </c>
+      <c r="E135" s="9">
+        <v>-2.6</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="7" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B136" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C136" s="8">
-        <v>-12.66</v>
+        <v>-58.04</v>
       </c>
       <c r="D136" s="8">
-        <v>-51.64</v>
+        <v>-61.63</v>
       </c>
       <c r="E136" s="9">
-        <v>-38.98</v>
+        <v>-3.59</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="7" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B137" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C137" s="8">
-        <v>-62.08</v>
+        <v>25.73</v>
       </c>
       <c r="D137" s="8">
-        <v>-58.44</v>
+        <v>320.01</v>
       </c>
       <c r="E137" s="10">
-        <v>3.64</v>
+        <v>294.28</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B138" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C138" s="8">
-        <v>-40.1</v>
+        <v>42.13</v>
       </c>
       <c r="D138" s="8">
-        <v>-54.52</v>
-      </c>
-      <c r="E138" s="9">
-        <v>-14.42</v>
+        <v>75.84</v>
+      </c>
+      <c r="E138" s="10">
+        <v>33.71</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="7" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B139" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C139" s="8">
-        <v>-69.58</v>
+        <v>-51.64</v>
       </c>
       <c r="D139" s="8">
-        <v>-77.06999999999999</v>
-      </c>
-      <c r="E139" s="9">
-        <v>-7.49</v>
+        <v>-45.21</v>
+      </c>
+      <c r="E139" s="10">
+        <v>6.43</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="7" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B140" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C140" s="8">
-        <v>-12.06</v>
+        <v>-58.44</v>
       </c>
       <c r="D140" s="8">
-        <v>-32.26</v>
-      </c>
-      <c r="E140" s="9">
-        <v>-20.2</v>
+        <v>27.55</v>
+      </c>
+      <c r="E140" s="10">
+        <v>85.98999999999999</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="7" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B141" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C141" s="8">
-        <v>-64.23</v>
+        <v>-54.52</v>
       </c>
       <c r="D141" s="8">
+        <v>-42.32</v>
+      </c>
+      <c r="E141" s="10">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5">
+      <c r="A142" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B142" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C142" s="8">
+        <v>-77.06999999999999</v>
+      </c>
+      <c r="D142" s="8">
+        <v>-75.45999999999999</v>
+      </c>
+      <c r="E142" s="10">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5">
+      <c r="A143" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B143" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C143" s="8">
+        <v>-32.26</v>
+      </c>
+      <c r="D143" s="8">
+        <v>-0.16</v>
+      </c>
+      <c r="E143" s="10">
+        <v>32.1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5">
+      <c r="A144" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B144" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C144" s="8">
         <v>17.37</v>
       </c>
-      <c r="E141" s="10">
-        <v>81.59999999999999</v>
+      <c r="D144" s="8">
+        <v>-18.03</v>
+      </c>
+      <c r="E144" s="9">
+        <v>-35.4</v>
       </c>
     </row>
   </sheetData>
@@ -5358,28 +5403,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="D1" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="E1" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="F1" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="G1" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="H1" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="I1" s="11" t="s">
         <v>92</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -5393,16 +5438,16 @@
         <v>16</v>
       </c>
       <c r="D2" s="13">
-        <v>42.6</v>
+        <v>41.7</v>
       </c>
       <c r="E2" s="13">
         <v>20</v>
       </c>
       <c r="F2" s="13">
-        <v>-1.9</v>
+        <v>-3.4</v>
       </c>
       <c r="G2" s="13">
-        <v>-3.5</v>
+        <v>-2.5</v>
       </c>
       <c r="H2" s="13">
         <v>53.1</v>
@@ -5519,10 +5564,10 @@
         <v>49</v>
       </c>
       <c r="D1" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" s="15" t="s">
         <v>45</v>
-      </c>
-      <c r="E1" s="15" t="s">
-        <v>48</v>
       </c>
       <c r="F1" s="15" t="s">
         <v>50</v>
@@ -5534,7 +5579,7 @@
         <v>46</v>
       </c>
       <c r="I1" s="15" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="J1" s="15" t="s">
         <v>42</v>
@@ -5542,39 +5587,39 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="16">
-        <v>0.4077</v>
+        <v>0.4036999999999999</v>
       </c>
       <c r="B2" s="16">
-        <v>0.4042</v>
+        <v>0.3982</v>
       </c>
       <c r="C2" s="16">
-        <v>0.2543</v>
+        <v>0.2498</v>
       </c>
       <c r="D2" s="16">
-        <v>0.244</v>
+        <v>0.2336</v>
       </c>
       <c r="E2" s="16">
-        <v>0.2327</v>
+        <v>0.2325</v>
       </c>
       <c r="F2" s="16">
-        <v>0.1683</v>
+        <v>0.1653</v>
       </c>
       <c r="G2" s="16">
-        <v>0.1482</v>
+        <v>0.1587</v>
       </c>
       <c r="H2" s="16">
-        <v>0.09660000000000001</v>
+        <v>0.09369999999999999</v>
       </c>
       <c r="I2" s="16">
-        <v>0.05400000000000001</v>
+        <v>0.0525</v>
       </c>
       <c r="J2" s="16">
-        <v>0.0505</v>
+        <v>0.0508</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="15" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="B3" s="15" t="s">
         <v>51</v>
@@ -5594,22 +5639,22 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="16">
-        <v>0.04679999999999999</v>
+        <v>0.0481</v>
       </c>
       <c r="B4" s="16">
-        <v>0.0103</v>
+        <v>-0.004500000000000001</v>
       </c>
       <c r="C4" s="16">
-        <v>-0.0368</v>
+        <v>-0.0354</v>
       </c>
       <c r="D4" s="16">
-        <v>-0.0454</v>
+        <v>-0.0442</v>
       </c>
       <c r="E4" s="16">
-        <v>-0.0459</v>
+        <v>-0.0471</v>
       </c>
       <c r="F4" s="16">
-        <v>-0.0668</v>
+        <v>-0.07099999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/TATA_GROUP_Technical_Metrics.xlsx
+++ b/TATA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="95">
   <si>
     <t>Symbol</t>
   </si>
@@ -217,43 +217,55 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>36.7 → 56.1</t>
+    <t>48.8 → 50.5</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>36.7</t>
+    <t>48.8</t>
+  </si>
+  <si>
+    <t>50.5</t>
+  </si>
+  <si>
+    <t>48.8 → 51.4</t>
+  </si>
+  <si>
+    <t>51.4</t>
+  </si>
+  <si>
+    <t>Left 52W High Zone</t>
+  </si>
+  <si>
+    <t>-1.3% → -2.3%</t>
+  </si>
+  <si>
+    <t>⚪ NEUTRAL</t>
+  </si>
+  <si>
+    <t>-1.3%</t>
+  </si>
+  <si>
+    <t>-2.3%</t>
+  </si>
+  <si>
+    <t>56.1 → 46.4</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>56.1</t>
   </si>
   <si>
-    <t>RSI Overbought Exit</t>
-  </si>
-  <si>
-    <t>72.4 → 62.7</t>
-  </si>
-  <si>
-    <t>🔵 COOLING</t>
-  </si>
-  <si>
-    <t>72.4</t>
-  </si>
-  <si>
-    <t>62.7</t>
-  </si>
-  <si>
-    <t>50.7 → 48.8</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>50.7</t>
-  </si>
-  <si>
-    <t>48.8</t>
+    <t>46.4</t>
+  </si>
+  <si>
+    <t>50.6 → 46.4</t>
+  </si>
+  <si>
+    <t>50.6</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -480,8 +492,8 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -993,10 +1005,10 @@
         <v>53</v>
       </c>
       <c r="C2">
-        <v>737.9</v>
+        <v>718</v>
       </c>
       <c r="D2">
-        <v>4.46</v>
+        <v>-2.7</v>
       </c>
       <c r="E2">
         <v>790.85</v>
@@ -1005,46 +1017,46 @@
         <v>570.95</v>
       </c>
       <c r="G2">
-        <v>-6.7</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="H2">
-        <v>29.24</v>
+        <v>25.76</v>
       </c>
       <c r="I2">
-        <v>1.23</v>
+        <v>-1.64</v>
       </c>
       <c r="J2">
-        <v>-0.09</v>
+        <v>-4.52</v>
       </c>
       <c r="K2">
-        <v>11.52</v>
+        <v>9.4</v>
       </c>
       <c r="L2">
-        <v>-4.05</v>
+        <v>-6.16</v>
       </c>
       <c r="M2">
-        <v>40.51</v>
+        <v>38.47</v>
       </c>
       <c r="N2">
         <v>81</v>
       </c>
       <c r="O2">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="P2">
-        <v>722.76</v>
+        <v>720.36</v>
       </c>
       <c r="Q2">
-        <v>727.37</v>
+        <v>725.77</v>
       </c>
       <c r="R2">
-        <v>729.6900000000001</v>
+        <v>729.39</v>
       </c>
       <c r="S2">
         <v>688.66</v>
       </c>
       <c r="T2">
-        <v>7.15</v>
+        <v>4.26</v>
       </c>
       <c r="U2" t="s">
         <v>54</v>
@@ -1059,34 +1071,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>56.1</v>
+        <v>46.42</v>
       </c>
       <c r="Z2">
-        <v>-1.12</v>
+        <v>-1.62</v>
       </c>
       <c r="AA2">
-        <v>-0.45</v>
+        <v>-0.68</v>
       </c>
       <c r="AB2">
-        <v>-0.68</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AC2">
-        <v>33.33</v>
+        <v>50.03</v>
       </c>
       <c r="AD2">
-        <v>21.16</v>
+        <v>29.19</v>
       </c>
       <c r="AE2">
-        <v>14.47</v>
+        <v>15.37</v>
       </c>
       <c r="AF2">
-        <v>247.48</v>
+        <v>-29.54</v>
       </c>
       <c r="AG2">
-        <v>746.8099999999999</v>
+        <v>742.4400000000001</v>
       </c>
       <c r="AH2">
-        <v>707.9299999999999</v>
+        <v>709.1</v>
       </c>
       <c r="AI2">
         <v>700.95</v>
@@ -1095,7 +1107,7 @@
         <v>56</v>
       </c>
       <c r="AK2">
-        <v>24.68</v>
+        <v>23.43</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1106,10 +1118,10 @@
         <v>53</v>
       </c>
       <c r="C3">
-        <v>951.5</v>
+        <v>924.35</v>
       </c>
       <c r="D3">
-        <v>-1.01</v>
+        <v>-2.85</v>
       </c>
       <c r="E3">
         <v>1081.5</v>
@@ -1118,46 +1130,46 @@
         <v>505.36</v>
       </c>
       <c r="G3">
-        <v>-12.02</v>
+        <v>-14.53</v>
       </c>
       <c r="H3">
-        <v>88.28</v>
+        <v>82.91</v>
       </c>
       <c r="I3">
-        <v>3.95</v>
+        <v>-0.14</v>
       </c>
       <c r="J3">
-        <v>-6.32</v>
+        <v>-7.64</v>
       </c>
       <c r="K3">
-        <v>36.17</v>
+        <v>31.99</v>
       </c>
       <c r="L3">
-        <v>17.08</v>
+        <v>13.06</v>
       </c>
       <c r="M3">
-        <v>13.42</v>
+        <v>11.68</v>
       </c>
       <c r="N3">
         <v>93</v>
       </c>
       <c r="O3">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="P3">
-        <v>946.9400000000001</v>
+        <v>946.6900000000001</v>
       </c>
       <c r="Q3">
-        <v>968.87</v>
+        <v>966.01</v>
       </c>
       <c r="R3">
-        <v>936.48</v>
+        <v>936.47</v>
       </c>
       <c r="S3">
-        <v>752.01</v>
+        <v>752.35</v>
       </c>
       <c r="T3">
-        <v>26.53</v>
+        <v>22.86</v>
       </c>
       <c r="U3" t="s">
         <v>55</v>
@@ -1172,34 +1184,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>50.58</v>
+        <v>46.4</v>
       </c>
       <c r="Z3">
-        <v>2.75</v>
+        <v>0.37</v>
       </c>
       <c r="AA3">
-        <v>8.77</v>
+        <v>7.09</v>
       </c>
       <c r="AB3">
-        <v>-6.02</v>
+        <v>-6.73</v>
       </c>
       <c r="AC3">
-        <v>31.19</v>
+        <v>23.01</v>
       </c>
       <c r="AD3">
-        <v>26.8</v>
+        <v>27.49</v>
       </c>
       <c r="AE3">
-        <v>46.28</v>
+        <v>45.69</v>
       </c>
       <c r="AF3">
-        <v>-74.45</v>
+        <v>-74.18000000000001</v>
       </c>
       <c r="AG3">
-        <v>1063.55</v>
+        <v>1062.5</v>
       </c>
       <c r="AH3">
-        <v>874.2</v>
+        <v>869.51</v>
       </c>
       <c r="AI3">
         <v>1070.9</v>
@@ -1208,7 +1220,7 @@
         <v>57</v>
       </c>
       <c r="AK3">
-        <v>23.5</v>
+        <v>20.58</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1219,16 +1231,16 @@
         <v>53</v>
       </c>
       <c r="C4">
-        <v>207.19</v>
+        <v>207.17</v>
       </c>
       <c r="D4">
-        <v>-1.16</v>
+        <v>-0.01</v>
       </c>
       <c r="E4">
         <v>358.75</v>
       </c>
       <c r="F4">
-        <v>207.19</v>
+        <v>207.17</v>
       </c>
       <c r="G4">
         <v>-42.25</v>
@@ -1237,40 +1249,40 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>-1.95</v>
+        <v>-2.71</v>
       </c>
       <c r="J4">
-        <v>-4.58</v>
+        <v>-4.89</v>
       </c>
       <c r="K4">
-        <v>-11.79</v>
+        <v>-11.52</v>
       </c>
       <c r="L4">
-        <v>-42.71</v>
+        <v>-38.56</v>
       </c>
       <c r="M4">
-        <v>-4.87</v>
+        <v>-4.59</v>
       </c>
       <c r="N4">
         <v>7</v>
       </c>
       <c r="O4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P4">
-        <v>210.78</v>
+        <v>209.63</v>
       </c>
       <c r="Q4">
-        <v>212.45</v>
+        <v>211.93</v>
       </c>
       <c r="R4">
-        <v>220.94</v>
+        <v>220.41</v>
       </c>
       <c r="S4">
-        <v>245.64</v>
+        <v>245.43</v>
       </c>
       <c r="T4">
-        <v>-15.65</v>
+        <v>-15.59</v>
       </c>
       <c r="U4" t="s">
         <v>54</v>
@@ -1285,34 +1297,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>33.56</v>
+        <v>33.53</v>
       </c>
       <c r="Z4">
-        <v>-3.24</v>
+        <v>-3.34</v>
       </c>
       <c r="AA4">
-        <v>-3.41</v>
+        <v>-3.39</v>
       </c>
       <c r="AB4">
-        <v>0.17</v>
+        <v>0.05</v>
       </c>
       <c r="AC4">
-        <v>35.81</v>
+        <v>19.08</v>
       </c>
       <c r="AD4">
-        <v>61.17</v>
+        <v>39.73</v>
       </c>
       <c r="AE4">
-        <v>4.44</v>
+        <v>4.41</v>
       </c>
       <c r="AF4">
-        <v>358.21</v>
+        <v>-57.08</v>
       </c>
       <c r="AG4">
-        <v>217.14</v>
+        <v>216.53</v>
       </c>
       <c r="AH4">
-        <v>207.76</v>
+        <v>207.33</v>
       </c>
       <c r="AI4">
         <v>220.96</v>
@@ -1321,7 +1333,7 @@
         <v>57</v>
       </c>
       <c r="AK4">
-        <v>21.29</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1332,10 +1344,10 @@
         <v>53</v>
       </c>
       <c r="C5">
-        <v>643</v>
+        <v>633.6</v>
       </c>
       <c r="D5">
-        <v>-1.94</v>
+        <v>-1.46</v>
       </c>
       <c r="E5">
         <v>989.9299999999999</v>
@@ -1344,46 +1356,46 @@
         <v>574.42</v>
       </c>
       <c r="G5">
-        <v>-35.05</v>
+        <v>-36</v>
       </c>
       <c r="H5">
-        <v>11.94</v>
+        <v>10.3</v>
       </c>
       <c r="I5">
-        <v>2.56</v>
+        <v>1.16</v>
       </c>
       <c r="J5">
-        <v>-4.54</v>
+        <v>-6.08</v>
       </c>
       <c r="K5">
-        <v>-11.54</v>
+        <v>-10.62</v>
       </c>
       <c r="L5">
-        <v>-30.2</v>
+        <v>-29.9</v>
       </c>
       <c r="M5">
-        <v>-3.94</v>
+        <v>-4.13</v>
       </c>
       <c r="N5">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="O5">
         <v>15</v>
       </c>
       <c r="P5">
-        <v>641.38</v>
+        <v>642.83</v>
       </c>
       <c r="Q5">
-        <v>653.99</v>
+        <v>652.26</v>
       </c>
       <c r="R5">
-        <v>682.24</v>
+        <v>680.25</v>
       </c>
       <c r="S5">
-        <v>713.36</v>
+        <v>712.38</v>
       </c>
       <c r="T5">
-        <v>-9.859999999999999</v>
+        <v>-11.06</v>
       </c>
       <c r="U5" t="s">
         <v>54</v>
@@ -1398,34 +1410,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>40.9</v>
+        <v>37.09</v>
       </c>
       <c r="Z5">
-        <v>-12.5</v>
+        <v>-12.58</v>
       </c>
       <c r="AA5">
-        <v>-13.7</v>
+        <v>-13.48</v>
       </c>
       <c r="AB5">
-        <v>1.2</v>
+        <v>0.89</v>
       </c>
       <c r="AC5">
-        <v>84.48999999999999</v>
+        <v>76.18000000000001</v>
       </c>
       <c r="AD5">
-        <v>69.18000000000001</v>
+        <v>79.62</v>
       </c>
       <c r="AE5">
-        <v>17.1</v>
+        <v>16.84</v>
       </c>
       <c r="AF5">
-        <v>-14.78</v>
+        <v>-48.79</v>
       </c>
       <c r="AG5">
-        <v>689.3200000000001</v>
+        <v>688.03</v>
       </c>
       <c r="AH5">
-        <v>618.66</v>
+        <v>616.48</v>
       </c>
       <c r="AI5">
         <v>675.42</v>
@@ -1434,7 +1446,7 @@
         <v>57</v>
       </c>
       <c r="AK5">
-        <v>26.65</v>
+        <v>25.56</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1445,10 +1457,10 @@
         <v>53</v>
       </c>
       <c r="C6">
-        <v>1723.4</v>
+        <v>1733.8</v>
       </c>
       <c r="D6">
-        <v>1.69</v>
+        <v>0.6</v>
       </c>
       <c r="E6">
         <v>2061.7</v>
@@ -1457,25 +1469,25 @@
         <v>1347.9</v>
       </c>
       <c r="G6">
-        <v>-16.41</v>
+        <v>-15.9</v>
       </c>
       <c r="H6">
-        <v>27.86</v>
+        <v>28.63</v>
       </c>
       <c r="I6">
-        <v>2.07</v>
+        <v>1.99</v>
       </c>
       <c r="J6">
-        <v>-1.88</v>
+        <v>-2.6</v>
       </c>
       <c r="K6">
-        <v>-9.59</v>
+        <v>-10.34</v>
       </c>
       <c r="L6">
-        <v>10.28</v>
+        <v>11.17</v>
       </c>
       <c r="M6">
-        <v>5.2</v>
+        <v>5.87</v>
       </c>
       <c r="N6">
         <v>74</v>
@@ -1484,19 +1496,19 @@
         <v>51</v>
       </c>
       <c r="P6">
-        <v>1691.38</v>
+        <v>1698.16</v>
       </c>
       <c r="Q6">
-        <v>1712.75</v>
+        <v>1710.52</v>
       </c>
       <c r="R6">
-        <v>1805.17</v>
+        <v>1798.61</v>
       </c>
       <c r="S6">
-        <v>1719.83</v>
+        <v>1719.06</v>
       </c>
       <c r="T6">
-        <v>0.21</v>
+        <v>0.86</v>
       </c>
       <c r="U6" t="s">
         <v>54</v>
@@ -1511,34 +1523,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>48.78</v>
+        <v>50.48</v>
       </c>
       <c r="Z6">
-        <v>-29.28</v>
+        <v>-24.37</v>
       </c>
       <c r="AA6">
-        <v>-35.27</v>
+        <v>-33.09</v>
       </c>
       <c r="AB6">
-        <v>5.99</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="AC6">
-        <v>98.48999999999999</v>
+        <v>100</v>
       </c>
       <c r="AD6">
-        <v>82.94</v>
+        <v>91.95</v>
       </c>
       <c r="AE6">
-        <v>48.04</v>
+        <v>47.25</v>
       </c>
       <c r="AF6">
-        <v>31.92</v>
+        <v>-22.6</v>
       </c>
       <c r="AG6">
-        <v>1786.64</v>
+        <v>1778.5</v>
       </c>
       <c r="AH6">
-        <v>1638.86</v>
+        <v>1642.53</v>
       </c>
       <c r="AI6">
         <v>1813.9</v>
@@ -1547,7 +1559,7 @@
         <v>57</v>
       </c>
       <c r="AK6">
-        <v>37.57</v>
+        <v>32.98</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1558,10 +1570,10 @@
         <v>53</v>
       </c>
       <c r="C7">
-        <v>1037.5</v>
+        <v>1030.5</v>
       </c>
       <c r="D7">
-        <v>-0.31</v>
+        <v>-0.67</v>
       </c>
       <c r="E7">
         <v>1260.34</v>
@@ -1570,25 +1582,25 @@
         <v>1006.29</v>
       </c>
       <c r="G7">
-        <v>-17.68</v>
+        <v>-18.24</v>
       </c>
       <c r="H7">
-        <v>3.1</v>
+        <v>2.41</v>
       </c>
       <c r="I7">
-        <v>-2.35</v>
+        <v>-2.83</v>
       </c>
       <c r="J7">
-        <v>-4.21</v>
+        <v>-7.16</v>
       </c>
       <c r="K7">
-        <v>-10.15</v>
+        <v>-9.92</v>
       </c>
       <c r="L7">
-        <v>-3.11</v>
+        <v>-2.18</v>
       </c>
       <c r="M7">
-        <v>4.57</v>
+        <v>4.37</v>
       </c>
       <c r="N7">
         <v>62</v>
@@ -1597,19 +1609,19 @@
         <v>38</v>
       </c>
       <c r="P7">
-        <v>1045.56</v>
+        <v>1039.56</v>
       </c>
       <c r="Q7">
-        <v>1068.85</v>
+        <v>1065.78</v>
       </c>
       <c r="R7">
-        <v>1087.47</v>
+        <v>1085.82</v>
       </c>
       <c r="S7">
-        <v>1126.25</v>
+        <v>1125.68</v>
       </c>
       <c r="T7">
-        <v>-7.88</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="U7" t="s">
         <v>54</v>
@@ -1624,43 +1636,43 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>38.06</v>
+        <v>36.22</v>
       </c>
       <c r="Z7">
-        <v>-14.38</v>
+        <v>-15.29</v>
       </c>
       <c r="AA7">
-        <v>-11.79</v>
+        <v>-12.49</v>
       </c>
       <c r="AB7">
-        <v>-2.59</v>
+        <v>-2.8</v>
       </c>
       <c r="AC7">
         <v>0</v>
       </c>
       <c r="AD7">
-        <v>4.24</v>
+        <v>0.44</v>
       </c>
       <c r="AE7">
-        <v>20.08</v>
+        <v>19.84</v>
       </c>
       <c r="AF7">
-        <v>31.05</v>
+        <v>-22.45</v>
       </c>
       <c r="AG7">
-        <v>1109.68</v>
+        <v>1108.48</v>
       </c>
       <c r="AH7">
-        <v>1028.02</v>
+        <v>1023.07</v>
       </c>
       <c r="AI7">
-        <v>1096.79</v>
+        <v>1092.97</v>
       </c>
       <c r="AJ7" t="s">
         <v>57</v>
       </c>
       <c r="AK7">
-        <v>40.91</v>
+        <v>44.26</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1671,10 +1683,10 @@
         <v>53</v>
       </c>
       <c r="C8">
-        <v>3578.6</v>
+        <v>3638</v>
       </c>
       <c r="D8">
-        <v>-2.89</v>
+        <v>1.66</v>
       </c>
       <c r="E8">
         <v>5749.89</v>
@@ -1683,46 +1695,46 @@
         <v>3387.6</v>
       </c>
       <c r="G8">
-        <v>-37.76</v>
+        <v>-36.73</v>
       </c>
       <c r="H8">
-        <v>5.64</v>
+        <v>7.39</v>
       </c>
       <c r="I8">
-        <v>-2.58</v>
+        <v>-0.76</v>
       </c>
       <c r="J8">
-        <v>-2.57</v>
+        <v>-3.29</v>
       </c>
       <c r="K8">
-        <v>-19.59</v>
+        <v>-14.81</v>
       </c>
       <c r="L8">
-        <v>-33.51</v>
+        <v>-30.62</v>
       </c>
       <c r="M8">
-        <v>-4.61</v>
+        <v>-4.6</v>
       </c>
       <c r="N8">
+        <v>19</v>
+      </c>
+      <c r="O8">
         <v>13</v>
       </c>
-      <c r="O8">
-        <v>9</v>
-      </c>
       <c r="P8">
-        <v>3642.54</v>
+        <v>3636.96</v>
       </c>
       <c r="Q8">
-        <v>3709.85</v>
+        <v>3704.9</v>
       </c>
       <c r="R8">
-        <v>3696.13</v>
+        <v>3686.59</v>
       </c>
       <c r="S8">
-        <v>4419.23</v>
+        <v>4411.35</v>
       </c>
       <c r="T8">
-        <v>-19.02</v>
+        <v>-17.53</v>
       </c>
       <c r="U8" t="s">
         <v>55</v>
@@ -1737,34 +1749,34 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>40.19</v>
+        <v>45.91</v>
       </c>
       <c r="Z8">
-        <v>-21.08</v>
+        <v>-21.74</v>
       </c>
       <c r="AA8">
-        <v>-11.65</v>
+        <v>-13.67</v>
       </c>
       <c r="AB8">
-        <v>-9.43</v>
+        <v>-8.08</v>
       </c>
       <c r="AC8">
-        <v>14.11</v>
+        <v>27.66</v>
       </c>
       <c r="AD8">
-        <v>10.19</v>
+        <v>18.63</v>
       </c>
       <c r="AE8">
-        <v>87.45</v>
+        <v>88.68000000000001</v>
       </c>
       <c r="AF8">
-        <v>-14.04</v>
+        <v>-11.28</v>
       </c>
       <c r="AG8">
-        <v>3835.26</v>
+        <v>3833.57</v>
       </c>
       <c r="AH8">
-        <v>3584.44</v>
+        <v>3576.23</v>
       </c>
       <c r="AI8">
         <v>3521.58</v>
@@ -1773,7 +1785,7 @@
         <v>56</v>
       </c>
       <c r="AK8">
-        <v>13.21</v>
+        <v>14.09</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1784,10 +1796,10 @@
         <v>53</v>
       </c>
       <c r="C9">
-        <v>642.2</v>
+        <v>633.65</v>
       </c>
       <c r="D9">
-        <v>0.54</v>
+        <v>-1.33</v>
       </c>
       <c r="E9">
         <v>1052.57</v>
@@ -1796,25 +1808,25 @@
         <v>538.37</v>
       </c>
       <c r="G9">
-        <v>-38.99</v>
+        <v>-39.8</v>
       </c>
       <c r="H9">
-        <v>19.29</v>
+        <v>17.7</v>
       </c>
       <c r="I9">
-        <v>-0.58</v>
+        <v>-1.66</v>
       </c>
       <c r="J9">
-        <v>-5.48</v>
+        <v>-6.35</v>
       </c>
       <c r="K9">
-        <v>-3.73</v>
+        <v>-4.25</v>
       </c>
       <c r="L9">
-        <v>-6.19</v>
+        <v>-6.81</v>
       </c>
       <c r="M9">
-        <v>40.46</v>
+        <v>40.19</v>
       </c>
       <c r="N9">
         <v>68</v>
@@ -1823,19 +1835,19 @@
         <v>40</v>
       </c>
       <c r="P9">
-        <v>642.37</v>
+        <v>640.23</v>
       </c>
       <c r="Q9">
-        <v>660.88</v>
+        <v>658.6799999999999</v>
       </c>
       <c r="R9">
-        <v>664.74</v>
+        <v>663.62</v>
       </c>
       <c r="S9">
-        <v>670.2</v>
+        <v>669.5</v>
       </c>
       <c r="T9">
-        <v>-4.18</v>
+        <v>-5.35</v>
       </c>
       <c r="U9" t="s">
         <v>54</v>
@@ -1850,43 +1862,43 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>39.01</v>
+        <v>34.66</v>
       </c>
       <c r="Z9">
-        <v>-7.59</v>
+        <v>-8.27</v>
       </c>
       <c r="AA9">
-        <v>-5.24</v>
+        <v>-5.84</v>
       </c>
       <c r="AB9">
-        <v>-2.35</v>
+        <v>-2.42</v>
       </c>
       <c r="AC9">
         <v>5.49</v>
       </c>
       <c r="AD9">
-        <v>1.9</v>
+        <v>3.69</v>
       </c>
       <c r="AE9">
-        <v>14.14</v>
+        <v>13.98</v>
       </c>
       <c r="AF9">
-        <v>-36.73</v>
+        <v>-66.12</v>
       </c>
       <c r="AG9">
-        <v>696.88</v>
+        <v>695.73</v>
       </c>
       <c r="AH9">
-        <v>624.88</v>
+        <v>621.63</v>
       </c>
       <c r="AI9">
-        <v>683.58</v>
+        <v>679.33</v>
       </c>
       <c r="AJ9" t="s">
         <v>57</v>
       </c>
       <c r="AK9">
-        <v>12.02</v>
+        <v>11.44</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1897,10 +1909,10 @@
         <v>53</v>
       </c>
       <c r="C10">
-        <v>347</v>
+        <v>350.55</v>
       </c>
       <c r="D10">
-        <v>-1.38</v>
+        <v>1.02</v>
       </c>
       <c r="E10">
         <v>461.8</v>
@@ -1909,46 +1921,46 @@
         <v>345.25</v>
       </c>
       <c r="G10">
-        <v>-24.86</v>
+        <v>-24.09</v>
       </c>
       <c r="H10">
-        <v>0.51</v>
+        <v>1.54</v>
       </c>
       <c r="I10">
-        <v>-7.1</v>
+        <v>-5.41</v>
       </c>
       <c r="J10">
-        <v>-8.85</v>
+        <v>-8.23</v>
       </c>
       <c r="K10">
-        <v>-16.37</v>
+        <v>-14.86</v>
       </c>
       <c r="L10">
-        <v>-8.140000000000001</v>
+        <v>-5.54</v>
       </c>
       <c r="M10">
-        <v>22.56</v>
+        <v>21.99</v>
       </c>
       <c r="N10">
         <v>44</v>
       </c>
       <c r="O10">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="P10">
-        <v>357.09</v>
+        <v>353.08</v>
       </c>
       <c r="Q10">
-        <v>373.92</v>
+        <v>372.44</v>
       </c>
       <c r="R10">
-        <v>377.95</v>
+        <v>376.84</v>
       </c>
       <c r="S10">
-        <v>388.95</v>
+        <v>388.76</v>
       </c>
       <c r="T10">
-        <v>-10.78</v>
+        <v>-9.83</v>
       </c>
       <c r="U10" t="s">
         <v>54</v>
@@ -1963,43 +1975,43 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>19.17</v>
+        <v>25.55</v>
       </c>
       <c r="Z10">
-        <v>-7.14</v>
+        <v>-7.77</v>
       </c>
       <c r="AA10">
-        <v>-3.9</v>
+        <v>-4.68</v>
       </c>
       <c r="AB10">
-        <v>-3.24</v>
+        <v>-3.09</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>6.52</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AE10">
-        <v>6.67</v>
+        <v>6.55</v>
       </c>
       <c r="AF10">
-        <v>33.3</v>
+        <v>-22.33</v>
       </c>
       <c r="AG10">
-        <v>396.39</v>
+        <v>397</v>
       </c>
       <c r="AH10">
-        <v>351.44</v>
+        <v>347.89</v>
       </c>
       <c r="AI10">
-        <v>369.44</v>
+        <v>369.35</v>
       </c>
       <c r="AJ10" t="s">
         <v>57</v>
       </c>
       <c r="AK10">
-        <v>41.94</v>
+        <v>46.76</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -2010,58 +2022,58 @@
         <v>53</v>
       </c>
       <c r="C11">
-        <v>184.35</v>
+        <v>184.07</v>
       </c>
       <c r="D11">
-        <v>-1.15</v>
+        <v>-0.15</v>
       </c>
       <c r="E11">
         <v>216.66</v>
       </c>
       <c r="F11">
-        <v>150.53</v>
+        <v>151.36</v>
       </c>
       <c r="G11">
-        <v>-14.91</v>
+        <v>-15.04</v>
       </c>
       <c r="H11">
-        <v>22.47</v>
+        <v>21.61</v>
       </c>
       <c r="I11">
-        <v>-1.05</v>
+        <v>-1.54</v>
       </c>
       <c r="J11">
-        <v>-2.82</v>
+        <v>-3.63</v>
       </c>
       <c r="K11">
-        <v>-10.66</v>
+        <v>-11.34</v>
       </c>
       <c r="L11">
-        <v>21.36</v>
+        <v>22.28</v>
       </c>
       <c r="M11">
-        <v>8.07</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="N11">
         <v>87</v>
       </c>
       <c r="O11">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P11">
-        <v>186.52</v>
+        <v>185.95</v>
       </c>
       <c r="Q11">
-        <v>186.74</v>
+        <v>186.39</v>
       </c>
       <c r="R11">
-        <v>187.5</v>
+        <v>187.21</v>
       </c>
       <c r="S11">
-        <v>189.72</v>
+        <v>189.77</v>
       </c>
       <c r="T11">
-        <v>-2.83</v>
+        <v>-3.01</v>
       </c>
       <c r="U11" t="s">
         <v>54</v>
@@ -2076,34 +2088,34 @@
         <v>0</v>
       </c>
       <c r="Y11">
-        <v>43.81</v>
+        <v>43.2</v>
       </c>
       <c r="Z11">
-        <v>-0.76</v>
+        <v>-0.85</v>
       </c>
       <c r="AA11">
-        <v>-0.92</v>
+        <v>-0.91</v>
       </c>
       <c r="AB11">
-        <v>0.16</v>
+        <v>0.05</v>
       </c>
       <c r="AC11">
-        <v>59.35</v>
+        <v>42.45</v>
       </c>
       <c r="AD11">
-        <v>75.97</v>
+        <v>61.4</v>
       </c>
       <c r="AE11">
-        <v>3.95</v>
+        <v>4.14</v>
       </c>
       <c r="AF11">
-        <v>45.72</v>
+        <v>83.93000000000001</v>
       </c>
       <c r="AG11">
-        <v>192.06</v>
+        <v>191.45</v>
       </c>
       <c r="AH11">
-        <v>181.41</v>
+        <v>181.33</v>
       </c>
       <c r="AI11">
         <v>180.21</v>
@@ -2112,7 +2124,7 @@
         <v>56</v>
       </c>
       <c r="AK11">
-        <v>17.23</v>
+        <v>15.45</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -2123,10 +2135,10 @@
         <v>53</v>
       </c>
       <c r="C12">
-        <v>2399.3</v>
+        <v>2369</v>
       </c>
       <c r="D12">
-        <v>2.45</v>
+        <v>-1.26</v>
       </c>
       <c r="E12">
         <v>3221.85</v>
@@ -2135,46 +2147,46 @@
         <v>1982.6</v>
       </c>
       <c r="G12">
-        <v>-25.53</v>
+        <v>-26.47</v>
       </c>
       <c r="H12">
-        <v>21.02</v>
+        <v>19.49</v>
       </c>
       <c r="I12">
-        <v>5.04</v>
+        <v>3.17</v>
       </c>
       <c r="J12">
-        <v>1.42</v>
+        <v>-4.23</v>
       </c>
       <c r="K12">
-        <v>-1.95</v>
+        <v>5.68</v>
       </c>
       <c r="L12">
-        <v>-21.28</v>
+        <v>-20.68</v>
       </c>
       <c r="M12">
-        <v>-6.22</v>
+        <v>-6.1</v>
       </c>
       <c r="N12">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="O12">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="P12">
-        <v>2311.18</v>
+        <v>2325.74</v>
       </c>
       <c r="Q12">
-        <v>2348.9</v>
+        <v>2344.35</v>
       </c>
       <c r="R12">
-        <v>2252.05</v>
+        <v>2256.88</v>
       </c>
       <c r="S12">
-        <v>2580.5</v>
+        <v>2577.3</v>
       </c>
       <c r="T12">
-        <v>-7.02</v>
+        <v>-8.08</v>
       </c>
       <c r="U12" t="s">
         <v>55</v>
@@ -2189,34 +2201,34 @@
         <v>1</v>
       </c>
       <c r="Y12">
-        <v>58.62</v>
+        <v>55.15</v>
       </c>
       <c r="Z12">
-        <v>5.9</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="AA12">
-        <v>10.25</v>
+        <v>10.02</v>
       </c>
       <c r="AB12">
-        <v>-4.34</v>
+        <v>-0.9</v>
       </c>
       <c r="AC12">
-        <v>52.51</v>
+        <v>78.59</v>
       </c>
       <c r="AD12">
-        <v>25.1</v>
+        <v>50.09</v>
       </c>
       <c r="AE12">
-        <v>61.41</v>
+        <v>62.34</v>
       </c>
       <c r="AF12">
-        <v>2.6</v>
+        <v>-2.61</v>
       </c>
       <c r="AG12">
-        <v>2482.04</v>
+        <v>2467.33</v>
       </c>
       <c r="AH12">
-        <v>2215.76</v>
+        <v>2221.37</v>
       </c>
       <c r="AI12">
         <v>2431.19</v>
@@ -2225,7 +2237,7 @@
         <v>57</v>
       </c>
       <c r="AK12">
-        <v>27</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2236,10 +2248,10 @@
         <v>53</v>
       </c>
       <c r="C13">
-        <v>5102.4</v>
+        <v>5050</v>
       </c>
       <c r="D13">
-        <v>-1.29</v>
+        <v>-1.03</v>
       </c>
       <c r="E13">
         <v>5169.2</v>
@@ -2248,46 +2260,46 @@
         <v>3327.3</v>
       </c>
       <c r="G13">
-        <v>-1.29</v>
+        <v>-2.31</v>
       </c>
       <c r="H13">
-        <v>53.35</v>
+        <v>51.77</v>
       </c>
       <c r="I13">
-        <v>0.46</v>
+        <v>-1.46</v>
       </c>
       <c r="J13">
-        <v>4.66</v>
+        <v>1</v>
       </c>
       <c r="K13">
-        <v>25.12</v>
+        <v>23.51</v>
       </c>
       <c r="L13">
-        <v>41.97</v>
+        <v>38.82</v>
       </c>
       <c r="M13">
-        <v>21.89</v>
+        <v>21.41</v>
       </c>
       <c r="N13">
         <v>99</v>
       </c>
       <c r="O13">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="P13">
-        <v>5127.14</v>
+        <v>5112.18</v>
       </c>
       <c r="Q13">
-        <v>5063.25</v>
+        <v>5069</v>
       </c>
       <c r="R13">
-        <v>4779.93</v>
+        <v>4793.48</v>
       </c>
       <c r="S13">
-        <v>4295.27</v>
+        <v>4301.33</v>
       </c>
       <c r="T13">
-        <v>18.79</v>
+        <v>17.41</v>
       </c>
       <c r="U13" t="s">
         <v>55</v>
@@ -2302,34 +2314,34 @@
         <v>3</v>
       </c>
       <c r="Y13">
-        <v>62.71</v>
+        <v>56.37</v>
       </c>
       <c r="Z13">
-        <v>98.2</v>
+        <v>87.73999999999999</v>
       </c>
       <c r="AA13">
-        <v>111.27</v>
+        <v>106.57</v>
       </c>
       <c r="AB13">
-        <v>-13.08</v>
+        <v>-18.83</v>
       </c>
       <c r="AC13">
-        <v>32.06</v>
+        <v>19.72</v>
       </c>
       <c r="AD13">
-        <v>32.3</v>
+        <v>28.56</v>
       </c>
       <c r="AE13">
-        <v>77.31</v>
+        <v>80.06999999999999</v>
       </c>
       <c r="AF13">
-        <v>-27.12</v>
+        <v>-44.92</v>
       </c>
       <c r="AG13">
-        <v>5200.44</v>
+        <v>5192.51</v>
       </c>
       <c r="AH13">
-        <v>4926.05</v>
+        <v>4945.48</v>
       </c>
       <c r="AI13">
         <v>4921.93</v>
@@ -2338,7 +2350,7 @@
         <v>56</v>
       </c>
       <c r="AK13">
-        <v>43.3</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2349,10 +2361,10 @@
         <v>53</v>
       </c>
       <c r="C14">
-        <v>2879.9</v>
+        <v>2855</v>
       </c>
       <c r="D14">
-        <v>-0.62</v>
+        <v>-0.86</v>
       </c>
       <c r="E14">
         <v>5520.84</v>
@@ -2361,46 +2373,46 @@
         <v>2193.96</v>
       </c>
       <c r="G14">
-        <v>-47.84</v>
+        <v>-48.29</v>
       </c>
       <c r="H14">
-        <v>31.26</v>
+        <v>30.13</v>
       </c>
       <c r="I14">
-        <v>-0.86</v>
+        <v>-2.56</v>
       </c>
       <c r="J14">
-        <v>-4.19</v>
+        <v>-6.39</v>
       </c>
       <c r="K14">
-        <v>2.75</v>
+        <v>0.73</v>
       </c>
       <c r="L14">
-        <v>-45.53</v>
+        <v>-45.39</v>
       </c>
       <c r="M14">
-        <v>23.51</v>
+        <v>23.6</v>
       </c>
       <c r="N14">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="O14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="P14">
-        <v>2898.92</v>
+        <v>2883.92</v>
       </c>
       <c r="Q14">
-        <v>2972.78</v>
+        <v>2960.14</v>
       </c>
       <c r="R14">
-        <v>3009.53</v>
+        <v>3003.01</v>
       </c>
       <c r="S14">
-        <v>3018.86</v>
+        <v>3011.53</v>
       </c>
       <c r="T14">
-        <v>-4.6</v>
+        <v>-5.2</v>
       </c>
       <c r="U14" t="s">
         <v>54</v>
@@ -2415,34 +2427,34 @@
         <v>0</v>
       </c>
       <c r="Y14">
-        <v>39.71</v>
+        <v>37.06</v>
       </c>
       <c r="Z14">
-        <v>-26.46</v>
+        <v>-30.01</v>
       </c>
       <c r="AA14">
-        <v>-15.96</v>
+        <v>-18.77</v>
       </c>
       <c r="AB14">
-        <v>-10.49</v>
+        <v>-11.24</v>
       </c>
       <c r="AC14">
         <v>12.6</v>
       </c>
       <c r="AD14">
-        <v>11.52</v>
+        <v>12.62</v>
       </c>
       <c r="AE14">
-        <v>57.4</v>
+        <v>57.36</v>
       </c>
       <c r="AF14">
-        <v>-1.21</v>
+        <v>-35.2</v>
       </c>
       <c r="AG14">
-        <v>3120.29</v>
+        <v>3102.19</v>
       </c>
       <c r="AH14">
-        <v>2825.26</v>
+        <v>2818.09</v>
       </c>
       <c r="AI14">
         <v>3055.35</v>
@@ -2451,7 +2463,7 @@
         <v>57</v>
       </c>
       <c r="AK14">
-        <v>27.14</v>
+        <v>27.18</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2462,10 +2474,10 @@
         <v>53</v>
       </c>
       <c r="C15">
-        <v>227.55</v>
+        <v>224.18</v>
       </c>
       <c r="D15">
-        <v>-0.84</v>
+        <v>-1.48</v>
       </c>
       <c r="E15">
         <v>392.75</v>
@@ -2474,25 +2486,25 @@
         <v>217.05</v>
       </c>
       <c r="G15">
-        <v>-42.06</v>
+        <v>-42.92</v>
       </c>
       <c r="H15">
-        <v>4.84</v>
+        <v>3.28</v>
       </c>
       <c r="I15">
-        <v>-1.06</v>
+        <v>-3.25</v>
       </c>
       <c r="J15">
-        <v>0.72</v>
+        <v>-1.92</v>
       </c>
       <c r="K15">
-        <v>-2.7</v>
+        <v>-3.57</v>
       </c>
       <c r="L15">
-        <v>-29.11</v>
+        <v>-30.05</v>
       </c>
       <c r="M15">
-        <v>15.34</v>
+        <v>15.25</v>
       </c>
       <c r="N15">
         <v>38</v>
@@ -2501,19 +2513,19 @@
         <v>25</v>
       </c>
       <c r="P15">
-        <v>229.58</v>
+        <v>228.07</v>
       </c>
       <c r="Q15">
-        <v>230.82</v>
+        <v>230.61</v>
       </c>
       <c r="R15">
-        <v>234.96</v>
+        <v>234.8</v>
       </c>
       <c r="S15">
-        <v>259.08</v>
+        <v>258.62</v>
       </c>
       <c r="T15">
-        <v>-12.17</v>
+        <v>-13.32</v>
       </c>
       <c r="U15" t="s">
         <v>54</v>
@@ -2528,34 +2540,34 @@
         <v>0</v>
       </c>
       <c r="Y15">
-        <v>41.95</v>
+        <v>36.91</v>
       </c>
       <c r="Z15">
-        <v>-1.41</v>
+        <v>-1.77</v>
       </c>
       <c r="AA15">
-        <v>-1.38</v>
+        <v>-1.46</v>
       </c>
       <c r="AB15">
-        <v>-0.03</v>
+        <v>-0.31</v>
       </c>
       <c r="AC15">
-        <v>8.880000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="AD15">
-        <v>19.43</v>
+        <v>10.55</v>
       </c>
       <c r="AE15">
-        <v>5.76</v>
+        <v>5.8</v>
       </c>
       <c r="AF15">
-        <v>-60.21</v>
+        <v>-41.42</v>
       </c>
       <c r="AG15">
-        <v>234.75</v>
+        <v>235.44</v>
       </c>
       <c r="AH15">
-        <v>226.89</v>
+        <v>225.78</v>
       </c>
       <c r="AI15">
         <v>219.81</v>
@@ -2564,7 +2576,7 @@
         <v>56</v>
       </c>
       <c r="AK15">
-        <v>18.76</v>
+        <v>24.39</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2575,10 +2587,10 @@
         <v>53</v>
       </c>
       <c r="C16">
-        <v>38.58</v>
+        <v>38.92</v>
       </c>
       <c r="D16">
-        <v>-0.67</v>
+        <v>0.88</v>
       </c>
       <c r="E16">
         <v>58.79</v>
@@ -2587,46 +2599,46 @@
         <v>31.36</v>
       </c>
       <c r="G16">
-        <v>-34.38</v>
+        <v>-33.8</v>
       </c>
       <c r="H16">
-        <v>23.02</v>
+        <v>24.11</v>
       </c>
       <c r="I16">
-        <v>3.24</v>
+        <v>3.65</v>
       </c>
       <c r="J16">
-        <v>-3.43</v>
+        <v>-3.21</v>
       </c>
       <c r="K16">
-        <v>-10.59</v>
+        <v>-10.71</v>
       </c>
       <c r="L16">
-        <v>-32.48</v>
+        <v>-30.77</v>
       </c>
       <c r="M16">
-        <v>0.98</v>
+        <v>1.18</v>
       </c>
       <c r="N16">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="O16">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P16">
-        <v>37.77</v>
+        <v>38.04</v>
       </c>
       <c r="Q16">
-        <v>38.38</v>
+        <v>38.33</v>
       </c>
       <c r="R16">
-        <v>40.05</v>
+        <v>39.93</v>
       </c>
       <c r="S16">
-        <v>43.39</v>
+        <v>43.32</v>
       </c>
       <c r="T16">
-        <v>-11.09</v>
+        <v>-10.15</v>
       </c>
       <c r="U16" t="s">
         <v>54</v>
@@ -2641,34 +2653,34 @@
         <v>0</v>
       </c>
       <c r="Y16">
-        <v>48.82</v>
+        <v>51.36</v>
       </c>
       <c r="Z16">
-        <v>-0.64</v>
+        <v>-0.53</v>
       </c>
       <c r="AA16">
-        <v>-0.78</v>
+        <v>-0.73</v>
       </c>
       <c r="AB16">
-        <v>0.13</v>
+        <v>0.2</v>
       </c>
       <c r="AC16">
-        <v>64.05</v>
+        <v>97.39</v>
       </c>
       <c r="AD16">
-        <v>44.98</v>
+        <v>68.94</v>
       </c>
       <c r="AE16">
         <v>1.22</v>
       </c>
       <c r="AF16">
-        <v>-19.37</v>
+        <v>-38.47</v>
       </c>
       <c r="AG16">
-        <v>40.23</v>
+        <v>40.06</v>
       </c>
       <c r="AH16">
-        <v>36.53</v>
+        <v>36.6</v>
       </c>
       <c r="AI16">
         <v>39.99</v>
@@ -2677,7 +2689,7 @@
         <v>57</v>
       </c>
       <c r="AK16">
-        <v>24.68</v>
+        <v>26.36</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2688,10 +2700,10 @@
         <v>53</v>
       </c>
       <c r="C17">
-        <v>1194.4</v>
+        <v>1205</v>
       </c>
       <c r="D17">
-        <v>-0.47</v>
+        <v>0.89</v>
       </c>
       <c r="E17">
         <v>1556.41</v>
@@ -2700,46 +2712,46 @@
         <v>1194.4</v>
       </c>
       <c r="G17">
-        <v>-23.26</v>
+        <v>-22.58</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="I17">
-        <v>-3.83</v>
+        <v>-3.06</v>
       </c>
       <c r="J17">
-        <v>-10.12</v>
+        <v>-9.039999999999999</v>
       </c>
       <c r="K17">
-        <v>-3.41</v>
+        <v>-2.12</v>
       </c>
       <c r="L17">
         <v>-11.07</v>
       </c>
       <c r="M17">
-        <v>4.19</v>
+        <v>3.35</v>
       </c>
       <c r="N17">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="O17">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P17">
-        <v>1214.38</v>
+        <v>1206.78</v>
       </c>
       <c r="Q17">
-        <v>1257.37</v>
+        <v>1251.24</v>
       </c>
       <c r="R17">
-        <v>1292.87</v>
+        <v>1289.89</v>
       </c>
       <c r="S17">
-        <v>1354.73</v>
+        <v>1354.09</v>
       </c>
       <c r="T17">
-        <v>-11.84</v>
+        <v>-11.01</v>
       </c>
       <c r="U17" t="s">
         <v>54</v>
@@ -2754,34 +2766,34 @@
         <v>0</v>
       </c>
       <c r="Y17">
-        <v>32.18</v>
+        <v>35.82</v>
       </c>
       <c r="Z17">
-        <v>-27.22</v>
+        <v>-27.39</v>
       </c>
       <c r="AA17">
-        <v>-21.22</v>
+        <v>-22.45</v>
       </c>
       <c r="AB17">
-        <v>-6</v>
+        <v>-4.94</v>
       </c>
       <c r="AC17">
-        <v>3.24</v>
+        <v>5.7</v>
       </c>
       <c r="AD17">
-        <v>8.949999999999999</v>
+        <v>5.05</v>
       </c>
       <c r="AE17">
-        <v>31.48</v>
+        <v>30.3</v>
       </c>
       <c r="AF17">
-        <v>39.03</v>
+        <v>-70.65000000000001</v>
       </c>
       <c r="AG17">
-        <v>1335.15</v>
+        <v>1324.9</v>
       </c>
       <c r="AH17">
-        <v>1179.59</v>
+        <v>1177.57</v>
       </c>
       <c r="AI17">
         <v>1288.75</v>
@@ -2790,7 +2802,7 @@
         <v>57</v>
       </c>
       <c r="AK17">
-        <v>30.16</v>
+        <v>33.02</v>
       </c>
     </row>
   </sheetData>
@@ -2931,7 +2943,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F140"/>
+  <dimension ref="A1:F142"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2971,7 +2983,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>64</v>
@@ -2990,1208 +3002,1214 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D4" s="5" t="s">
+      <c r="B5" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="C5" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="D5" s="5" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B5" s="6" t="s">
+      <c r="E5" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="E5" s="6" t="s">
+      <c r="C6" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>77</v>
       </c>
+      <c r="E6" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A7" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="8">
-        <v>-5.72</v>
-      </c>
-      <c r="D9" s="8">
-        <v>-0.09</v>
-      </c>
-      <c r="E9" s="9">
-        <v>5.63</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="8">
-        <v>3.38</v>
-      </c>
-      <c r="D10" s="8">
-        <v>-6.32</v>
-      </c>
-      <c r="E10" s="10">
-        <v>-9.699999999999999</v>
+      <c r="B10" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="8">
-        <v>-3.4</v>
+        <v>-0.09</v>
       </c>
       <c r="D11" s="8">
-        <v>-4.58</v>
-      </c>
-      <c r="E11" s="10">
-        <v>-1.18</v>
+        <v>-4.52</v>
+      </c>
+      <c r="E11" s="9">
+        <v>-4.43</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="8">
-        <v>-2.17</v>
+        <v>-6.32</v>
       </c>
       <c r="D12" s="8">
-        <v>-4.54</v>
-      </c>
-      <c r="E12" s="10">
-        <v>-2.37</v>
+        <v>-7.64</v>
+      </c>
+      <c r="E12" s="9">
+        <v>-1.32</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="8">
-        <v>-4.45</v>
+        <v>-4.58</v>
       </c>
       <c r="D13" s="8">
-        <v>-1.88</v>
+        <v>-4.89</v>
       </c>
       <c r="E13" s="9">
-        <v>2.57</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="8">
-        <v>-4.89</v>
+        <v>-4.54</v>
       </c>
       <c r="D14" s="8">
-        <v>-4.21</v>
+        <v>-6.08</v>
       </c>
       <c r="E14" s="9">
-        <v>0.68</v>
+        <v>-1.54</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="8">
-        <v>0.73</v>
+        <v>-1.88</v>
       </c>
       <c r="D15" s="8">
-        <v>-2.57</v>
-      </c>
-      <c r="E15" s="10">
-        <v>-3.3</v>
+        <v>-2.6</v>
+      </c>
+      <c r="E15" s="9">
+        <v>-0.72</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="8">
-        <v>-5.88</v>
+        <v>-4.21</v>
       </c>
       <c r="D16" s="8">
-        <v>-5.48</v>
+        <v>-7.16</v>
       </c>
       <c r="E16" s="9">
-        <v>0.4</v>
+        <v>-2.95</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="8">
-        <v>-6.41</v>
+        <v>-2.57</v>
       </c>
       <c r="D17" s="8">
-        <v>-8.85</v>
-      </c>
-      <c r="E17" s="10">
-        <v>-2.44</v>
+        <v>-3.29</v>
+      </c>
+      <c r="E17" s="9">
+        <v>-0.72</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="8">
-        <v>-0.22</v>
+        <v>-5.48</v>
       </c>
       <c r="D18" s="8">
-        <v>-2.82</v>
-      </c>
-      <c r="E18" s="10">
-        <v>-2.6</v>
+        <v>-6.35</v>
+      </c>
+      <c r="E18" s="9">
+        <v>-0.87</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="8">
-        <v>-3.69</v>
+        <v>-8.85</v>
       </c>
       <c r="D19" s="8">
-        <v>1.42</v>
-      </c>
-      <c r="E19" s="9">
-        <v>5.11</v>
+        <v>-8.23</v>
+      </c>
+      <c r="E19" s="10">
+        <v>0.62</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="8">
-        <v>6.58</v>
+        <v>-2.82</v>
       </c>
       <c r="D20" s="8">
-        <v>4.66</v>
-      </c>
-      <c r="E20" s="10">
-        <v>-1.92</v>
+        <v>-3.63</v>
+      </c>
+      <c r="E20" s="9">
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C21" s="8">
-        <v>-3.37</v>
+        <v>1.42</v>
       </c>
       <c r="D21" s="8">
-        <v>-4.19</v>
-      </c>
-      <c r="E21" s="10">
-        <v>-0.82</v>
+        <v>-4.23</v>
+      </c>
+      <c r="E21" s="9">
+        <v>-5.65</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C22" s="8">
-        <v>1.76</v>
+        <v>4.66</v>
       </c>
       <c r="D22" s="8">
-        <v>0.72</v>
-      </c>
-      <c r="E22" s="10">
-        <v>-1.04</v>
+        <v>1</v>
+      </c>
+      <c r="E22" s="9">
+        <v>-3.66</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C23" s="8">
-        <v>-1.84</v>
+        <v>-4.19</v>
       </c>
       <c r="D23" s="8">
-        <v>-3.43</v>
-      </c>
-      <c r="E23" s="10">
-        <v>-1.59</v>
+        <v>-6.39</v>
+      </c>
+      <c r="E23" s="9">
+        <v>-2.2</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C24" s="8">
-        <v>-9.99</v>
+        <v>0.72</v>
       </c>
       <c r="D24" s="8">
-        <v>-10.12</v>
-      </c>
-      <c r="E24" s="10">
-        <v>-0.13</v>
+        <v>-1.92</v>
+      </c>
+      <c r="E24" s="9">
+        <v>-2.64</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="7" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C25" s="8">
-        <v>-3.23</v>
+        <v>-3.43</v>
       </c>
       <c r="D25" s="8">
-        <v>1.23</v>
-      </c>
-      <c r="E25" s="9">
-        <v>4.46</v>
+        <v>-3.21</v>
+      </c>
+      <c r="E25" s="10">
+        <v>0.22</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="7" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C26" s="8">
-        <v>6.01</v>
+        <v>-10.12</v>
       </c>
       <c r="D26" s="8">
-        <v>3.95</v>
+        <v>-9.039999999999999</v>
       </c>
       <c r="E26" s="10">
-        <v>-2.06</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C27" s="8">
-        <v>-1.2</v>
+        <v>1.23</v>
       </c>
       <c r="D27" s="8">
-        <v>-1.95</v>
-      </c>
-      <c r="E27" s="10">
-        <v>-0.75</v>
+        <v>-1.64</v>
+      </c>
+      <c r="E27" s="9">
+        <v>-2.87</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C28" s="8">
-        <v>4.63</v>
+        <v>3.95</v>
       </c>
       <c r="D28" s="8">
-        <v>2.56</v>
-      </c>
-      <c r="E28" s="10">
-        <v>-2.07</v>
+        <v>-0.14</v>
+      </c>
+      <c r="E28" s="9">
+        <v>-4.09</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C29" s="8">
-        <v>2.37</v>
+        <v>-1.95</v>
       </c>
       <c r="D29" s="8">
-        <v>2.07</v>
-      </c>
-      <c r="E29" s="10">
-        <v>-0.3</v>
+        <v>-2.71</v>
+      </c>
+      <c r="E29" s="9">
+        <v>-0.76</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C30" s="8">
-        <v>-0.79</v>
+        <v>2.56</v>
       </c>
       <c r="D30" s="8">
-        <v>-2.35</v>
-      </c>
-      <c r="E30" s="10">
-        <v>-1.56</v>
+        <v>1.16</v>
+      </c>
+      <c r="E30" s="9">
+        <v>-1.4</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C31" s="8">
-        <v>-0.62</v>
+        <v>2.07</v>
       </c>
       <c r="D31" s="8">
-        <v>-2.58</v>
-      </c>
-      <c r="E31" s="10">
-        <v>-1.96</v>
+        <v>1.99</v>
+      </c>
+      <c r="E31" s="9">
+        <v>-0.08</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C32" s="8">
-        <v>-1.42</v>
+        <v>-2.35</v>
       </c>
       <c r="D32" s="8">
-        <v>-0.58</v>
+        <v>-2.83</v>
       </c>
       <c r="E32" s="9">
-        <v>0.84</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C33" s="8">
-        <v>-6</v>
+        <v>-2.58</v>
       </c>
       <c r="D33" s="8">
-        <v>-7.1</v>
+        <v>-0.76</v>
       </c>
       <c r="E33" s="10">
-        <v>-1.1</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C34" s="8">
-        <v>1.91</v>
+        <v>-0.58</v>
       </c>
       <c r="D34" s="8">
-        <v>-1.05</v>
-      </c>
-      <c r="E34" s="10">
-        <v>-2.96</v>
+        <v>-1.66</v>
+      </c>
+      <c r="E34" s="9">
+        <v>-1.08</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C35" s="8">
-        <v>1.74</v>
+        <v>-7.1</v>
       </c>
       <c r="D35" s="8">
-        <v>5.04</v>
-      </c>
-      <c r="E35" s="9">
-        <v>3.3</v>
+        <v>-5.41</v>
+      </c>
+      <c r="E35" s="10">
+        <v>1.69</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C36" s="8">
-        <v>1.63</v>
+        <v>-1.05</v>
       </c>
       <c r="D36" s="8">
-        <v>0.46</v>
-      </c>
-      <c r="E36" s="10">
-        <v>-1.17</v>
+        <v>-1.54</v>
+      </c>
+      <c r="E36" s="9">
+        <v>-0.49</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C37" s="8">
-        <v>-0.89</v>
+        <v>5.04</v>
       </c>
       <c r="D37" s="8">
-        <v>-0.86</v>
+        <v>3.17</v>
       </c>
       <c r="E37" s="9">
-        <v>0.03</v>
+        <v>-1.87</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B38" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C38" s="8">
-        <v>-0.4</v>
+        <v>0.46</v>
       </c>
       <c r="D38" s="8">
-        <v>-1.06</v>
-      </c>
-      <c r="E38" s="10">
-        <v>-0.66</v>
+        <v>-1.46</v>
+      </c>
+      <c r="E38" s="9">
+        <v>-1.92</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C39" s="8">
-        <v>2.81</v>
+        <v>-0.86</v>
       </c>
       <c r="D39" s="8">
-        <v>3.24</v>
+        <v>-2.56</v>
       </c>
       <c r="E39" s="9">
-        <v>0.43</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C40" s="8">
-        <v>-2.83</v>
+        <v>-1.06</v>
       </c>
       <c r="D40" s="8">
-        <v>-3.83</v>
-      </c>
-      <c r="E40" s="10">
-        <v>-1</v>
+        <v>-3.25</v>
+      </c>
+      <c r="E40" s="9">
+        <v>-2.19</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="7" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C41" s="8">
-        <v>-10.08</v>
+        <v>3.24</v>
       </c>
       <c r="D41" s="8">
-        <v>-4.05</v>
-      </c>
-      <c r="E41" s="9">
-        <v>6.03</v>
+        <v>3.65</v>
+      </c>
+      <c r="E41" s="10">
+        <v>0.41</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="7" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C42" s="8">
-        <v>16.64</v>
+        <v>-3.83</v>
       </c>
       <c r="D42" s="8">
-        <v>17.08</v>
-      </c>
-      <c r="E42" s="9">
-        <v>0.44</v>
+        <v>-3.06</v>
+      </c>
+      <c r="E42" s="10">
+        <v>0.77</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C43" s="8">
-        <v>-44.28</v>
+        <v>-4.05</v>
       </c>
       <c r="D43" s="8">
-        <v>-42.71</v>
+        <v>-6.16</v>
       </c>
       <c r="E43" s="9">
-        <v>1.57</v>
+        <v>-2.11</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B44" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C44" s="8">
-        <v>-29.93</v>
+        <v>17.08</v>
       </c>
       <c r="D44" s="8">
-        <v>-30.2</v>
-      </c>
-      <c r="E44" s="10">
-        <v>-0.27</v>
+        <v>13.06</v>
+      </c>
+      <c r="E44" s="9">
+        <v>-4.02</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B45" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C45" s="8">
-        <v>6.26</v>
+        <v>-42.71</v>
       </c>
       <c r="D45" s="8">
-        <v>10.28</v>
-      </c>
-      <c r="E45" s="9">
-        <v>4.02</v>
+        <v>-38.56</v>
+      </c>
+      <c r="E45" s="10">
+        <v>4.15</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C46" s="8">
-        <v>-2.97</v>
+        <v>-30.2</v>
       </c>
       <c r="D46" s="8">
-        <v>-3.11</v>
+        <v>-29.9</v>
       </c>
       <c r="E46" s="10">
-        <v>-0.14</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C47" s="8">
-        <v>-32.37</v>
+        <v>10.28</v>
       </c>
       <c r="D47" s="8">
-        <v>-33.51</v>
+        <v>11.17</v>
       </c>
       <c r="E47" s="10">
-        <v>-1.14</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B48" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C48" s="8">
-        <v>-8.23</v>
+        <v>-3.11</v>
       </c>
       <c r="D48" s="8">
-        <v>-6.19</v>
-      </c>
-      <c r="E48" s="9">
-        <v>2.04</v>
+        <v>-2.18</v>
+      </c>
+      <c r="E48" s="10">
+        <v>0.93</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B49" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C49" s="8">
-        <v>-8.19</v>
+        <v>-33.51</v>
       </c>
       <c r="D49" s="8">
-        <v>-8.140000000000001</v>
-      </c>
-      <c r="E49" s="9">
-        <v>0.05</v>
+        <v>-30.62</v>
+      </c>
+      <c r="E49" s="10">
+        <v>2.89</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B50" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C50" s="8">
-        <v>19.25</v>
+        <v>-6.19</v>
       </c>
       <c r="D50" s="8">
-        <v>21.36</v>
+        <v>-6.81</v>
       </c>
       <c r="E50" s="9">
-        <v>2.11</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B51" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C51" s="8">
-        <v>-22.76</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="D51" s="8">
-        <v>-21.28</v>
-      </c>
-      <c r="E51" s="9">
-        <v>1.48</v>
+        <v>-5.54</v>
+      </c>
+      <c r="E51" s="10">
+        <v>2.6</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B52" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C52" s="8">
-        <v>41.57</v>
+        <v>21.36</v>
       </c>
       <c r="D52" s="8">
-        <v>41.97</v>
-      </c>
-      <c r="E52" s="9">
-        <v>0.4</v>
+        <v>22.28</v>
+      </c>
+      <c r="E52" s="10">
+        <v>0.92</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B53" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C53" s="8">
-        <v>-46.48</v>
+        <v>-21.28</v>
       </c>
       <c r="D53" s="8">
-        <v>-45.53</v>
-      </c>
-      <c r="E53" s="9">
-        <v>0.95</v>
+        <v>-20.68</v>
+      </c>
+      <c r="E53" s="10">
+        <v>0.6</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B54" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C54" s="8">
-        <v>-28.96</v>
+        <v>41.97</v>
       </c>
       <c r="D54" s="8">
-        <v>-29.11</v>
-      </c>
-      <c r="E54" s="10">
-        <v>-0.15</v>
+        <v>38.82</v>
+      </c>
+      <c r="E54" s="9">
+        <v>-3.15</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B55" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C55" s="8">
-        <v>-33.2</v>
+        <v>-45.53</v>
       </c>
       <c r="D55" s="8">
-        <v>-32.48</v>
-      </c>
-      <c r="E55" s="9">
-        <v>0.72</v>
+        <v>-45.39</v>
+      </c>
+      <c r="E55" s="10">
+        <v>0.14</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B56" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C56" s="8">
-        <v>-11.32</v>
+        <v>-29.11</v>
       </c>
       <c r="D56" s="8">
-        <v>-11.07</v>
+        <v>-30.05</v>
       </c>
       <c r="E56" s="9">
-        <v>0.25</v>
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="7" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C57" s="8">
-        <v>9.220000000000001</v>
+        <v>-32.48</v>
       </c>
       <c r="D57" s="8">
-        <v>11.52</v>
-      </c>
-      <c r="E57" s="9">
-        <v>2.3</v>
+        <v>-30.77</v>
+      </c>
+      <c r="E57" s="10">
+        <v>1.71</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B58" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C58" s="8">
-        <v>40.06</v>
+        <v>11.52</v>
       </c>
       <c r="D58" s="8">
-        <v>36.17</v>
-      </c>
-      <c r="E58" s="10">
-        <v>-3.89</v>
+        <v>9.4</v>
+      </c>
+      <c r="E58" s="9">
+        <v>-2.12</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B59" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C59" s="8">
-        <v>-10.13</v>
+        <v>36.17</v>
       </c>
       <c r="D59" s="8">
-        <v>-11.79</v>
-      </c>
-      <c r="E59" s="10">
-        <v>-1.66</v>
+        <v>31.99</v>
+      </c>
+      <c r="E59" s="9">
+        <v>-4.18</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B60" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C60" s="8">
-        <v>-9.289999999999999</v>
+        <v>-11.79</v>
       </c>
       <c r="D60" s="8">
-        <v>-11.54</v>
+        <v>-11.52</v>
       </c>
       <c r="E60" s="10">
-        <v>-2.25</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B61" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C61" s="8">
-        <v>-12.76</v>
+        <v>-11.54</v>
       </c>
       <c r="D61" s="8">
-        <v>-9.59</v>
-      </c>
-      <c r="E61" s="9">
-        <v>3.17</v>
+        <v>-10.62</v>
+      </c>
+      <c r="E61" s="10">
+        <v>0.92</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C62" s="8">
-        <v>-8.970000000000001</v>
+        <v>-9.59</v>
       </c>
       <c r="D62" s="8">
-        <v>-10.15</v>
-      </c>
-      <c r="E62" s="10">
-        <v>-1.18</v>
+        <v>-10.34</v>
+      </c>
+      <c r="E62" s="9">
+        <v>-0.75</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B63" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C63" s="8">
-        <v>-12.82</v>
+        <v>-10.15</v>
       </c>
       <c r="D63" s="8">
-        <v>-19.59</v>
+        <v>-9.92</v>
       </c>
       <c r="E63" s="10">
-        <v>-6.77</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B64" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C64" s="8">
-        <v>-4.41</v>
+        <v>-19.59</v>
       </c>
       <c r="D64" s="8">
-        <v>-3.73</v>
-      </c>
-      <c r="E64" s="9">
-        <v>0.68</v>
+        <v>-14.81</v>
+      </c>
+      <c r="E64" s="10">
+        <v>4.78</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B65" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C65" s="8">
-        <v>-16.13</v>
+        <v>-3.73</v>
       </c>
       <c r="D65" s="8">
-        <v>-16.37</v>
-      </c>
-      <c r="E65" s="10">
-        <v>-0.24</v>
+        <v>-4.25</v>
+      </c>
+      <c r="E65" s="9">
+        <v>-0.52</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B66" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C66" s="8">
-        <v>-9.609999999999999</v>
+        <v>-16.37</v>
       </c>
       <c r="D66" s="8">
-        <v>-10.66</v>
+        <v>-14.86</v>
       </c>
       <c r="E66" s="10">
-        <v>-1.05</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B67" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C67" s="8">
-        <v>1.94</v>
+        <v>-10.66</v>
       </c>
       <c r="D67" s="8">
-        <v>-1.95</v>
-      </c>
-      <c r="E67" s="10">
-        <v>-3.89</v>
+        <v>-11.34</v>
+      </c>
+      <c r="E67" s="9">
+        <v>-0.68</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C68" s="8">
-        <v>28.44</v>
+        <v>-1.95</v>
       </c>
       <c r="D68" s="8">
-        <v>25.12</v>
+        <v>5.68</v>
       </c>
       <c r="E68" s="10">
-        <v>-3.32</v>
+        <v>7.63</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B69" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C69" s="8">
-        <v>4.72</v>
+        <v>25.12</v>
       </c>
       <c r="D69" s="8">
-        <v>2.75</v>
-      </c>
-      <c r="E69" s="10">
-        <v>-1.97</v>
+        <v>23.51</v>
+      </c>
+      <c r="E69" s="9">
+        <v>-1.61</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B70" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C70" s="8">
-        <v>1.57</v>
+        <v>2.75</v>
       </c>
       <c r="D70" s="8">
-        <v>-2.7</v>
-      </c>
-      <c r="E70" s="10">
-        <v>-4.27</v>
+        <v>0.73</v>
+      </c>
+      <c r="E70" s="9">
+        <v>-2.02</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B71" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C71" s="8">
-        <v>-8.59</v>
+        <v>-2.7</v>
       </c>
       <c r="D71" s="8">
-        <v>-10.59</v>
-      </c>
-      <c r="E71" s="10">
-        <v>-2</v>
+        <v>-3.57</v>
+      </c>
+      <c r="E71" s="9">
+        <v>-0.87</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B72" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C72" s="8">
-        <v>-2</v>
+        <v>-10.59</v>
       </c>
       <c r="D72" s="8">
-        <v>-3.41</v>
-      </c>
-      <c r="E72" s="10">
-        <v>-1.41</v>
+        <v>-10.71</v>
+      </c>
+      <c r="E72" s="9">
+        <v>-0.12</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="7" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C73" s="8">
-        <v>-10.68</v>
+        <v>-3.41</v>
       </c>
       <c r="D73" s="8">
-        <v>-6.7</v>
-      </c>
-      <c r="E73" s="9">
-        <v>3.98</v>
+        <v>-2.12</v>
+      </c>
+      <c r="E73" s="10">
+        <v>1.29</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B74" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C74" s="8">
-        <v>-11.12</v>
+        <v>-6.7</v>
       </c>
       <c r="D74" s="8">
-        <v>-12.02</v>
-      </c>
-      <c r="E74" s="10">
-        <v>-0.9</v>
+        <v>-9.210000000000001</v>
+      </c>
+      <c r="E74" s="9">
+        <v>-2.51</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B75" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C75" s="8">
-        <v>-42.03</v>
+        <v>-12.02</v>
       </c>
       <c r="D75" s="8">
-        <v>-42.25</v>
-      </c>
-      <c r="E75" s="10">
-        <v>-0.22</v>
+        <v>-14.53</v>
+      </c>
+      <c r="E75" s="9">
+        <v>-2.51</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -4202,13 +4220,13 @@
         <v>6</v>
       </c>
       <c r="C76" s="8">
-        <v>-33.76</v>
+        <v>-35.05</v>
       </c>
       <c r="D76" s="8">
-        <v>-35.05</v>
-      </c>
-      <c r="E76" s="10">
-        <v>-1.29</v>
+        <v>-36</v>
+      </c>
+      <c r="E76" s="9">
+        <v>-0.95</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -4219,13 +4237,13 @@
         <v>6</v>
       </c>
       <c r="C77" s="8">
-        <v>-17.8</v>
+        <v>-16.41</v>
       </c>
       <c r="D77" s="8">
-        <v>-16.41</v>
-      </c>
-      <c r="E77" s="9">
-        <v>1.39</v>
+        <v>-15.9</v>
+      </c>
+      <c r="E77" s="10">
+        <v>0.51</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -4236,13 +4254,13 @@
         <v>6</v>
       </c>
       <c r="C78" s="8">
-        <v>-17.43</v>
+        <v>-17.68</v>
       </c>
       <c r="D78" s="8">
-        <v>-17.68</v>
-      </c>
-      <c r="E78" s="10">
-        <v>-0.25</v>
+        <v>-18.24</v>
+      </c>
+      <c r="E78" s="9">
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -4253,13 +4271,13 @@
         <v>6</v>
       </c>
       <c r="C79" s="8">
-        <v>-35.91</v>
+        <v>-37.76</v>
       </c>
       <c r="D79" s="8">
-        <v>-37.76</v>
+        <v>-36.73</v>
       </c>
       <c r="E79" s="10">
-        <v>-1.85</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -4270,13 +4288,13 @@
         <v>6</v>
       </c>
       <c r="C80" s="8">
-        <v>-39.32</v>
+        <v>-38.99</v>
       </c>
       <c r="D80" s="8">
-        <v>-38.99</v>
+        <v>-39.8</v>
       </c>
       <c r="E80" s="9">
-        <v>0.33</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -4287,13 +4305,13 @@
         <v>6</v>
       </c>
       <c r="C81" s="8">
-        <v>-23.81</v>
+        <v>-24.86</v>
       </c>
       <c r="D81" s="8">
-        <v>-24.86</v>
+        <v>-24.09</v>
       </c>
       <c r="E81" s="10">
-        <v>-1.05</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -4304,13 +4322,13 @@
         <v>6</v>
       </c>
       <c r="C82" s="8">
-        <v>-13.92</v>
+        <v>-14.91</v>
       </c>
       <c r="D82" s="8">
-        <v>-14.91</v>
-      </c>
-      <c r="E82" s="10">
-        <v>-0.99</v>
+        <v>-15.04</v>
+      </c>
+      <c r="E82" s="9">
+        <v>-0.13</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -4321,13 +4339,13 @@
         <v>6</v>
       </c>
       <c r="C83" s="8">
-        <v>-27.31</v>
+        <v>-25.53</v>
       </c>
       <c r="D83" s="8">
-        <v>-25.53</v>
+        <v>-26.47</v>
       </c>
       <c r="E83" s="9">
-        <v>1.78</v>
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -4338,13 +4356,13 @@
         <v>6</v>
       </c>
       <c r="C84" s="8">
-        <v>0</v>
+        <v>-1.29</v>
       </c>
       <c r="D84" s="8">
-        <v>-1.29</v>
-      </c>
-      <c r="E84" s="10">
-        <v>-1.29</v>
+        <v>-2.31</v>
+      </c>
+      <c r="E84" s="9">
+        <v>-1.02</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -4355,13 +4373,13 @@
         <v>6</v>
       </c>
       <c r="C85" s="8">
-        <v>-47.51</v>
+        <v>-47.84</v>
       </c>
       <c r="D85" s="8">
-        <v>-47.84</v>
-      </c>
-      <c r="E85" s="10">
-        <v>-0.33</v>
+        <v>-48.29</v>
+      </c>
+      <c r="E85" s="9">
+        <v>-0.45</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -4372,13 +4390,13 @@
         <v>6</v>
       </c>
       <c r="C86" s="8">
-        <v>-41.57</v>
+        <v>-42.06</v>
       </c>
       <c r="D86" s="8">
-        <v>-42.06</v>
-      </c>
-      <c r="E86" s="10">
-        <v>-0.49</v>
+        <v>-42.92</v>
+      </c>
+      <c r="E86" s="9">
+        <v>-0.86</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -4389,13 +4407,13 @@
         <v>6</v>
       </c>
       <c r="C87" s="8">
-        <v>-33.93</v>
+        <v>-34.38</v>
       </c>
       <c r="D87" s="8">
-        <v>-34.38</v>
+        <v>-33.8</v>
       </c>
       <c r="E87" s="10">
-        <v>-0.45</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -4406,13 +4424,13 @@
         <v>6</v>
       </c>
       <c r="C88" s="8">
-        <v>-22.9</v>
+        <v>-23.26</v>
       </c>
       <c r="D88" s="8">
-        <v>-23.26</v>
+        <v>-22.58</v>
       </c>
       <c r="E88" s="10">
-        <v>-0.36</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -4423,13 +4441,13 @@
         <v>2</v>
       </c>
       <c r="C89" s="8">
-        <v>706.4</v>
+        <v>737.9</v>
       </c>
       <c r="D89" s="8">
-        <v>737.9</v>
+        <v>718</v>
       </c>
       <c r="E89" s="9">
-        <v>31.5</v>
+        <v>-19.9</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -4440,13 +4458,13 @@
         <v>2</v>
       </c>
       <c r="C90" s="8">
-        <v>961.2</v>
+        <v>951.5</v>
       </c>
       <c r="D90" s="8">
-        <v>951.5</v>
-      </c>
-      <c r="E90" s="10">
-        <v>-9.699999999999999</v>
+        <v>924.35</v>
+      </c>
+      <c r="E90" s="9">
+        <v>-27.15</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -4457,13 +4475,13 @@
         <v>2</v>
       </c>
       <c r="C91" s="8">
-        <v>209.63</v>
+        <v>207.19</v>
       </c>
       <c r="D91" s="8">
-        <v>207.19</v>
-      </c>
-      <c r="E91" s="10">
-        <v>-2.44</v>
+        <v>207.17</v>
+      </c>
+      <c r="E91" s="9">
+        <v>-0.02</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -4474,13 +4492,13 @@
         <v>2</v>
       </c>
       <c r="C92" s="8">
-        <v>655.75</v>
+        <v>643</v>
       </c>
       <c r="D92" s="8">
-        <v>643</v>
-      </c>
-      <c r="E92" s="10">
-        <v>-12.75</v>
+        <v>633.6</v>
+      </c>
+      <c r="E92" s="9">
+        <v>-9.4</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -4491,13 +4509,13 @@
         <v>2</v>
       </c>
       <c r="C93" s="8">
-        <v>1694.7</v>
+        <v>1723.4</v>
       </c>
       <c r="D93" s="8">
-        <v>1723.4</v>
-      </c>
-      <c r="E93" s="9">
-        <v>28.7</v>
+        <v>1733.8</v>
+      </c>
+      <c r="E93" s="10">
+        <v>10.4</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -4508,13 +4526,13 @@
         <v>2</v>
       </c>
       <c r="C94" s="8">
-        <v>1040.7</v>
+        <v>1037.5</v>
       </c>
       <c r="D94" s="8">
-        <v>1037.5</v>
-      </c>
-      <c r="E94" s="10">
-        <v>-3.2</v>
+        <v>1030.5</v>
+      </c>
+      <c r="E94" s="9">
+        <v>-7</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -4525,13 +4543,13 @@
         <v>2</v>
       </c>
       <c r="C95" s="8">
-        <v>3685</v>
+        <v>3578.6</v>
       </c>
       <c r="D95" s="8">
-        <v>3578.6</v>
+        <v>3638</v>
       </c>
       <c r="E95" s="10">
-        <v>-106.4</v>
+        <v>59.4</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -4542,13 +4560,13 @@
         <v>2</v>
       </c>
       <c r="C96" s="8">
-        <v>638.75</v>
+        <v>642.2</v>
       </c>
       <c r="D96" s="8">
-        <v>642.2</v>
+        <v>633.65</v>
       </c>
       <c r="E96" s="9">
-        <v>3.45</v>
+        <v>-8.550000000000001</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -4559,13 +4577,13 @@
         <v>2</v>
       </c>
       <c r="C97" s="8">
-        <v>351.85</v>
+        <v>347</v>
       </c>
       <c r="D97" s="8">
-        <v>347</v>
+        <v>350.55</v>
       </c>
       <c r="E97" s="10">
-        <v>-4.85</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -4576,13 +4594,13 @@
         <v>2</v>
       </c>
       <c r="C98" s="8">
-        <v>186.5</v>
+        <v>184.35</v>
       </c>
       <c r="D98" s="8">
-        <v>184.35</v>
-      </c>
-      <c r="E98" s="10">
-        <v>-2.15</v>
+        <v>184.07</v>
+      </c>
+      <c r="E98" s="9">
+        <v>-0.28</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -4593,13 +4611,13 @@
         <v>2</v>
       </c>
       <c r="C99" s="8">
-        <v>2342</v>
+        <v>2399.3</v>
       </c>
       <c r="D99" s="8">
-        <v>2399.3</v>
+        <v>2369</v>
       </c>
       <c r="E99" s="9">
-        <v>57.3</v>
+        <v>-30.3</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -4610,13 +4628,13 @@
         <v>2</v>
       </c>
       <c r="C100" s="8">
-        <v>5169.2</v>
+        <v>5102.4</v>
       </c>
       <c r="D100" s="8">
-        <v>5102.4</v>
-      </c>
-      <c r="E100" s="10">
-        <v>-66.8</v>
+        <v>5050</v>
+      </c>
+      <c r="E100" s="9">
+        <v>-52.4</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -4627,13 +4645,13 @@
         <v>2</v>
       </c>
       <c r="C101" s="8">
-        <v>2898</v>
+        <v>2879.9</v>
       </c>
       <c r="D101" s="8">
-        <v>2879.9</v>
-      </c>
-      <c r="E101" s="10">
-        <v>-18.1</v>
+        <v>2855</v>
+      </c>
+      <c r="E101" s="9">
+        <v>-24.9</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -4644,13 +4662,13 @@
         <v>2</v>
       </c>
       <c r="C102" s="8">
-        <v>229.48</v>
+        <v>227.55</v>
       </c>
       <c r="D102" s="8">
-        <v>227.55</v>
-      </c>
-      <c r="E102" s="10">
-        <v>-1.93</v>
+        <v>224.18</v>
+      </c>
+      <c r="E102" s="9">
+        <v>-3.37</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -4661,13 +4679,13 @@
         <v>2</v>
       </c>
       <c r="C103" s="8">
-        <v>38.84</v>
+        <v>38.58</v>
       </c>
       <c r="D103" s="8">
-        <v>38.58</v>
+        <v>38.92</v>
       </c>
       <c r="E103" s="10">
-        <v>-0.26</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -4678,631 +4696,665 @@
         <v>2</v>
       </c>
       <c r="C104" s="8">
-        <v>1200</v>
+        <v>1194.4</v>
       </c>
       <c r="D104" s="8">
-        <v>1194.4</v>
+        <v>1205</v>
       </c>
       <c r="E104" s="10">
-        <v>-5.6</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B105" s="7" t="s">
         <v>13</v>
       </c>
       <c r="C105" s="8">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="D105" s="8">
-        <v>62</v>
-      </c>
-      <c r="E105" s="10">
+        <v>26</v>
+      </c>
+      <c r="E105" s="9">
         <v>-6</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B106" s="7" t="s">
         <v>13</v>
       </c>
       <c r="C106" s="8">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="D106" s="8">
-        <v>68</v>
-      </c>
-      <c r="E106" s="9">
+        <v>19</v>
+      </c>
+      <c r="E106" s="10">
         <v>6</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B107" s="7" t="s">
         <v>13</v>
       </c>
       <c r="C107" s="8">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D107" s="8">
-        <v>44</v>
-      </c>
-      <c r="E107" s="9">
+        <v>56</v>
+      </c>
+      <c r="E107" s="10">
         <v>6</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B108" s="7" t="s">
         <v>13</v>
       </c>
       <c r="C108" s="8">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="D108" s="8">
-        <v>38</v>
-      </c>
-      <c r="E108" s="10">
+        <v>13</v>
+      </c>
+      <c r="E108" s="9">
         <v>-6</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="7" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B109" s="7" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C109" s="8">
-        <v>36.71</v>
+        <v>26</v>
       </c>
       <c r="D109" s="8">
-        <v>56.1</v>
-      </c>
-      <c r="E109" s="9">
-        <v>19.39</v>
+        <v>32</v>
+      </c>
+      <c r="E109" s="10">
+        <v>6</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="7" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B110" s="7" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C110" s="8">
-        <v>52.14</v>
+        <v>56</v>
       </c>
       <c r="D110" s="8">
-        <v>50.58</v>
-      </c>
-      <c r="E110" s="10">
-        <v>-1.56</v>
+        <v>50</v>
+      </c>
+      <c r="E110" s="9">
+        <v>-6</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B111" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C111" s="8">
-        <v>37.11</v>
+        <v>56.1</v>
       </c>
       <c r="D111" s="8">
-        <v>33.56</v>
-      </c>
-      <c r="E111" s="10">
-        <v>-3.55</v>
+        <v>46.42</v>
+      </c>
+      <c r="E111" s="9">
+        <v>-9.68</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C112" s="8">
-        <v>47</v>
+        <v>50.58</v>
       </c>
       <c r="D112" s="8">
-        <v>40.9</v>
-      </c>
-      <c r="E112" s="10">
-        <v>-6.1</v>
+        <v>46.4</v>
+      </c>
+      <c r="E112" s="9">
+        <v>-4.18</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B113" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C113" s="8">
-        <v>43.85</v>
+        <v>33.56</v>
       </c>
       <c r="D113" s="8">
-        <v>48.78</v>
+        <v>33.53</v>
       </c>
       <c r="E113" s="9">
-        <v>4.93</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B114" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C114" s="8">
-        <v>38.9</v>
+        <v>40.9</v>
       </c>
       <c r="D114" s="8">
-        <v>38.06</v>
-      </c>
-      <c r="E114" s="10">
-        <v>-0.84</v>
+        <v>37.09</v>
+      </c>
+      <c r="E114" s="9">
+        <v>-3.81</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B115" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C115" s="8">
-        <v>48.77</v>
+        <v>48.78</v>
       </c>
       <c r="D115" s="8">
-        <v>40.19</v>
+        <v>50.48</v>
       </c>
       <c r="E115" s="10">
-        <v>-8.58</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B116" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C116" s="8">
-        <v>36</v>
+        <v>38.06</v>
       </c>
       <c r="D116" s="8">
-        <v>39.01</v>
+        <v>36.22</v>
       </c>
       <c r="E116" s="9">
-        <v>3.01</v>
+        <v>-1.84</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B117" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C117" s="8">
-        <v>21.51</v>
+        <v>40.19</v>
       </c>
       <c r="D117" s="8">
-        <v>19.17</v>
+        <v>45.91</v>
       </c>
       <c r="E117" s="10">
-        <v>-2.34</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B118" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C118" s="8">
-        <v>48.71</v>
+        <v>39.01</v>
       </c>
       <c r="D118" s="8">
-        <v>43.81</v>
-      </c>
-      <c r="E118" s="10">
-        <v>-4.9</v>
+        <v>34.66</v>
+      </c>
+      <c r="E118" s="9">
+        <v>-4.35</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B119" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C119" s="8">
-        <v>53.48</v>
+        <v>19.17</v>
       </c>
       <c r="D119" s="8">
-        <v>58.62</v>
-      </c>
-      <c r="E119" s="9">
-        <v>5.14</v>
+        <v>25.55</v>
+      </c>
+      <c r="E119" s="10">
+        <v>6.38</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B120" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C120" s="8">
-        <v>72.36</v>
+        <v>43.81</v>
       </c>
       <c r="D120" s="8">
-        <v>62.71</v>
-      </c>
-      <c r="E120" s="10">
-        <v>-9.65</v>
+        <v>43.2</v>
+      </c>
+      <c r="E120" s="9">
+        <v>-0.61</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B121" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C121" s="8">
-        <v>41.73</v>
+        <v>58.62</v>
       </c>
       <c r="D121" s="8">
-        <v>39.71</v>
-      </c>
-      <c r="E121" s="10">
-        <v>-2.02</v>
+        <v>55.15</v>
+      </c>
+      <c r="E121" s="9">
+        <v>-3.47</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B122" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C122" s="8">
-        <v>45.23</v>
+        <v>62.71</v>
       </c>
       <c r="D122" s="8">
-        <v>41.95</v>
-      </c>
-      <c r="E122" s="10">
-        <v>-3.28</v>
+        <v>56.37</v>
+      </c>
+      <c r="E122" s="9">
+        <v>-6.34</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C123" s="8">
-        <v>50.7</v>
+        <v>39.71</v>
       </c>
       <c r="D123" s="8">
-        <v>48.82</v>
-      </c>
-      <c r="E123" s="10">
-        <v>-1.88</v>
+        <v>37.06</v>
+      </c>
+      <c r="E123" s="9">
+        <v>-2.65</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B124" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C124" s="8">
-        <v>33.1</v>
+        <v>41.95</v>
       </c>
       <c r="D124" s="8">
-        <v>32.18</v>
-      </c>
-      <c r="E124" s="10">
-        <v>-0.92</v>
+        <v>36.91</v>
+      </c>
+      <c r="E124" s="9">
+        <v>-5.04</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="7" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B125" s="7" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C125" s="8">
-        <v>121.92</v>
+        <v>48.82</v>
       </c>
       <c r="D125" s="8">
-        <v>247.48</v>
-      </c>
-      <c r="E125" s="9">
-        <v>125.56</v>
+        <v>51.36</v>
+      </c>
+      <c r="E125" s="10">
+        <v>2.54</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="7" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B126" s="7" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C126" s="8">
-        <v>-75.56</v>
+        <v>32.18</v>
       </c>
       <c r="D126" s="8">
-        <v>-74.45</v>
-      </c>
-      <c r="E126" s="9">
-        <v>1.11</v>
+        <v>35.82</v>
+      </c>
+      <c r="E126" s="10">
+        <v>3.64</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B127" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C127" s="8">
-        <v>-44.74</v>
+        <v>247.48</v>
       </c>
       <c r="D127" s="8">
-        <v>358.21</v>
+        <v>-29.54</v>
       </c>
       <c r="E127" s="9">
-        <v>402.95</v>
+        <v>-277.02</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B128" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C128" s="8">
-        <v>124.77</v>
+        <v>-74.45</v>
       </c>
       <c r="D128" s="8">
-        <v>-14.78</v>
+        <v>-74.18000000000001</v>
       </c>
       <c r="E128" s="10">
-        <v>-139.55</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B129" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C129" s="8">
-        <v>-16.21</v>
+        <v>358.21</v>
       </c>
       <c r="D129" s="8">
-        <v>31.92</v>
+        <v>-57.08</v>
       </c>
       <c r="E129" s="9">
-        <v>48.13</v>
+        <v>-415.29</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B130" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C130" s="8">
-        <v>-26.43</v>
+        <v>-14.78</v>
       </c>
       <c r="D130" s="8">
-        <v>31.05</v>
+        <v>-48.79</v>
       </c>
       <c r="E130" s="9">
-        <v>57.48</v>
+        <v>-34.01</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B131" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C131" s="8">
-        <v>52.34</v>
+        <v>31.92</v>
       </c>
       <c r="D131" s="8">
-        <v>-14.04</v>
-      </c>
-      <c r="E131" s="10">
-        <v>-66.38</v>
+        <v>-22.6</v>
+      </c>
+      <c r="E131" s="9">
+        <v>-54.52</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B132" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C132" s="8">
-        <v>-26.82</v>
+        <v>31.05</v>
       </c>
       <c r="D132" s="8">
-        <v>-36.73</v>
-      </c>
-      <c r="E132" s="10">
-        <v>-9.91</v>
+        <v>-22.45</v>
+      </c>
+      <c r="E132" s="9">
+        <v>-53.5</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B133" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C133" s="8">
-        <v>-2.87</v>
+        <v>-14.04</v>
       </c>
       <c r="D133" s="8">
-        <v>33.3</v>
-      </c>
-      <c r="E133" s="9">
-        <v>36.17</v>
+        <v>-11.28</v>
+      </c>
+      <c r="E133" s="10">
+        <v>2.76</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C134" s="8">
-        <v>63.84</v>
+        <v>-36.73</v>
       </c>
       <c r="D134" s="8">
-        <v>45.72</v>
-      </c>
-      <c r="E134" s="10">
-        <v>-18.12</v>
+        <v>-66.12</v>
+      </c>
+      <c r="E134" s="9">
+        <v>-29.39</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B135" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C135" s="8">
-        <v>41.78</v>
+        <v>33.3</v>
       </c>
       <c r="D135" s="8">
-        <v>2.6</v>
-      </c>
-      <c r="E135" s="10">
-        <v>-39.18</v>
+        <v>-22.33</v>
+      </c>
+      <c r="E135" s="9">
+        <v>-55.63</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B136" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C136" s="8">
-        <v>-37.48</v>
+        <v>45.72</v>
       </c>
       <c r="D136" s="8">
-        <v>-27.12</v>
-      </c>
-      <c r="E136" s="9">
-        <v>10.36</v>
+        <v>83.93000000000001</v>
+      </c>
+      <c r="E136" s="10">
+        <v>38.21</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B137" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C137" s="8">
-        <v>-53.24</v>
+        <v>2.6</v>
       </c>
       <c r="D137" s="8">
-        <v>-1.21</v>
+        <v>-2.61</v>
       </c>
       <c r="E137" s="9">
-        <v>52.03</v>
+        <v>-5.21</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B138" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C138" s="8">
-        <v>-75.23</v>
+        <v>-27.12</v>
       </c>
       <c r="D138" s="8">
-        <v>-60.21</v>
+        <v>-44.92</v>
       </c>
       <c r="E138" s="9">
-        <v>15.02</v>
+        <v>-17.8</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B139" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C139" s="8">
-        <v>3362.61</v>
+        <v>-1.21</v>
       </c>
       <c r="D139" s="8">
-        <v>-19.37</v>
-      </c>
-      <c r="E139" s="10">
-        <v>-3381.98</v>
+        <v>-35.2</v>
+      </c>
+      <c r="E139" s="9">
+        <v>-33.99</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B140" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C140" s="8">
-        <v>-19.75</v>
+        <v>-60.21</v>
       </c>
       <c r="D140" s="8">
+        <v>-41.42</v>
+      </c>
+      <c r="E140" s="10">
+        <v>18.79</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5">
+      <c r="A141" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B141" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C141" s="8">
+        <v>-19.37</v>
+      </c>
+      <c r="D141" s="8">
+        <v>-38.47</v>
+      </c>
+      <c r="E141" s="9">
+        <v>-19.1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5">
+      <c r="A142" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B142" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C142" s="8">
         <v>39.03</v>
       </c>
-      <c r="E140" s="9">
-        <v>58.78</v>
+      <c r="D142" s="8">
+        <v>-70.65000000000001</v>
+      </c>
+      <c r="E142" s="9">
+        <v>-109.68</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5326,28 +5378,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -5361,16 +5413,16 @@
         <v>16</v>
       </c>
       <c r="D2" s="13">
-        <v>43.4</v>
+        <v>42</v>
       </c>
       <c r="E2" s="13">
         <v>20</v>
       </c>
       <c r="F2" s="13">
-        <v>-3.3</v>
+        <v>-4.9</v>
       </c>
       <c r="G2" s="13">
-        <v>-2.3</v>
+        <v>-2</v>
       </c>
       <c r="H2" s="13">
         <v>53.1</v>
@@ -5478,10 +5530,10 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="15" t="s">
         <v>37</v>
-      </c>
-      <c r="B1" s="15" t="s">
-        <v>44</v>
       </c>
       <c r="C1" s="15" t="s">
         <v>49</v>
@@ -5510,34 +5562,34 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="16">
-        <v>0.4051</v>
+        <v>0.4019</v>
       </c>
       <c r="B2" s="16">
-        <v>0.4046</v>
+        <v>0.3847</v>
       </c>
       <c r="C2" s="16">
-        <v>0.2351</v>
+        <v>0.236</v>
       </c>
       <c r="D2" s="16">
-        <v>0.2256</v>
+        <v>0.2199</v>
       </c>
       <c r="E2" s="16">
-        <v>0.2189</v>
+        <v>0.2141</v>
       </c>
       <c r="F2" s="16">
-        <v>0.1534</v>
+        <v>0.1525</v>
       </c>
       <c r="G2" s="16">
-        <v>0.1342</v>
+        <v>0.1168</v>
       </c>
       <c r="H2" s="16">
-        <v>0.08070000000000001</v>
+        <v>0.0863</v>
       </c>
       <c r="I2" s="16">
-        <v>0.052</v>
+        <v>0.0587</v>
       </c>
       <c r="J2" s="16">
-        <v>0.0457</v>
+        <v>0.0437</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -5551,10 +5603,10 @@
         <v>40</v>
       </c>
       <c r="D3" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" s="15" t="s">
         <v>43</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>39</v>
       </c>
       <c r="F3" s="15" t="s">
         <v>47</v>
@@ -5562,22 +5614,22 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="16">
-        <v>0.04190000000000001</v>
+        <v>0.0335</v>
       </c>
       <c r="B4" s="16">
-        <v>0.0098</v>
+        <v>0.0118</v>
       </c>
       <c r="C4" s="16">
-        <v>-0.0394</v>
+        <v>-0.0413</v>
       </c>
       <c r="D4" s="16">
-        <v>-0.0461</v>
+        <v>-0.0459</v>
       </c>
       <c r="E4" s="16">
-        <v>-0.0487</v>
+        <v>-0.046</v>
       </c>
       <c r="F4" s="16">
-        <v>-0.0622</v>
+        <v>-0.061</v>
       </c>
     </row>
   </sheetData>

--- a/TATA_GROUP_Technical_Metrics.xlsx
+++ b/TATA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="82">
   <si>
     <t>Symbol</t>
   </si>
@@ -217,25 +217,16 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>56.0 → 48.2</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>56.0</t>
-  </si>
-  <si>
-    <t>48.2</t>
-  </si>
-  <si>
-    <t>52.4 → 49.6</t>
-  </si>
-  <si>
-    <t>52.4</t>
-  </si>
-  <si>
-    <t>49.6</t>
+    <t>48.5 → 55.1</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>48.5</t>
+  </si>
+  <si>
+    <t>55.1</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -321,14 +312,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -361,13 +352,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -447,8 +438,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -960,10 +951,10 @@
         <v>53</v>
       </c>
       <c r="C2">
-        <v>716.2</v>
+        <v>720</v>
       </c>
       <c r="D2">
-        <v>-0.53</v>
+        <v>0.53</v>
       </c>
       <c r="E2">
         <v>790.85</v>
@@ -972,46 +963,46 @@
         <v>570.95</v>
       </c>
       <c r="G2">
-        <v>-9.44</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="H2">
-        <v>25.44</v>
+        <v>26.11</v>
       </c>
       <c r="I2">
-        <v>-2.94</v>
+        <v>0.28</v>
       </c>
       <c r="J2">
-        <v>-2.02</v>
+        <v>-1.19</v>
       </c>
       <c r="K2">
-        <v>7.42</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="L2">
-        <v>-7.46</v>
+        <v>-7.07</v>
       </c>
       <c r="M2">
-        <v>39</v>
+        <v>38.61</v>
       </c>
       <c r="N2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="O2">
         <v>52</v>
       </c>
       <c r="P2">
-        <v>722.78</v>
+        <v>723.1799999999999</v>
       </c>
       <c r="Q2">
-        <v>723.73</v>
+        <v>723.53</v>
       </c>
       <c r="R2">
-        <v>729.76</v>
+        <v>729.88</v>
       </c>
       <c r="S2">
-        <v>688.76</v>
+        <v>688.7</v>
       </c>
       <c r="T2">
-        <v>3.98</v>
+        <v>4.55</v>
       </c>
       <c r="U2" t="s">
         <v>54</v>
@@ -1026,34 +1017,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>45.72</v>
+        <v>47.63</v>
       </c>
       <c r="Z2">
-        <v>-1.58</v>
+        <v>-1.75</v>
       </c>
       <c r="AA2">
-        <v>-0.9399999999999999</v>
+        <v>-1.1</v>
       </c>
       <c r="AB2">
-        <v>-0.64</v>
+        <v>-0.65</v>
       </c>
       <c r="AC2">
-        <v>61.3</v>
+        <v>52.51</v>
       </c>
       <c r="AD2">
-        <v>66.69</v>
+        <v>61.32</v>
       </c>
       <c r="AE2">
-        <v>15.34</v>
+        <v>15.03</v>
       </c>
       <c r="AF2">
-        <v>39.89</v>
+        <v>-35.82</v>
       </c>
       <c r="AG2">
-        <v>738.45</v>
+        <v>738.35</v>
       </c>
       <c r="AH2">
-        <v>709</v>
+        <v>708.71</v>
       </c>
       <c r="AI2">
         <v>700.95</v>
@@ -1062,7 +1053,7 @@
         <v>56</v>
       </c>
       <c r="AK2">
-        <v>17.7</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1073,10 +1064,10 @@
         <v>53</v>
       </c>
       <c r="C3">
-        <v>933.2</v>
+        <v>973.1</v>
       </c>
       <c r="D3">
-        <v>2.41</v>
+        <v>4.28</v>
       </c>
       <c r="E3">
         <v>1081.5</v>
@@ -1085,46 +1076,46 @@
         <v>505.36</v>
       </c>
       <c r="G3">
-        <v>-13.71</v>
+        <v>-10.02</v>
       </c>
       <c r="H3">
-        <v>84.66</v>
+        <v>92.56</v>
       </c>
       <c r="I3">
-        <v>-1.92</v>
+        <v>5.27</v>
       </c>
       <c r="J3">
-        <v>-2.68</v>
+        <v>-3.42</v>
       </c>
       <c r="K3">
-        <v>33.35</v>
+        <v>36.59</v>
       </c>
       <c r="L3">
-        <v>12.96</v>
+        <v>19.84</v>
       </c>
       <c r="M3">
-        <v>12.32</v>
+        <v>12.17</v>
       </c>
       <c r="N3">
         <v>93</v>
       </c>
       <c r="O3">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="P3">
-        <v>926.4400000000001</v>
+        <v>936.1900000000001</v>
       </c>
       <c r="Q3">
-        <v>954.13</v>
+        <v>953.03</v>
       </c>
       <c r="R3">
-        <v>940.67</v>
+        <v>941.53</v>
       </c>
       <c r="S3">
-        <v>753.87</v>
+        <v>754.48</v>
       </c>
       <c r="T3">
-        <v>23.79</v>
+        <v>28.98</v>
       </c>
       <c r="U3" t="s">
         <v>55</v>
@@ -1139,34 +1130,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>48.52</v>
+        <v>55.07</v>
       </c>
       <c r="Z3">
-        <v>-4.35</v>
+        <v>-1.18</v>
       </c>
       <c r="AA3">
-        <v>1</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AB3">
-        <v>-5.35</v>
+        <v>-1.75</v>
       </c>
       <c r="AC3">
-        <v>23.05</v>
+        <v>51.11</v>
       </c>
       <c r="AD3">
-        <v>14.95</v>
+        <v>27.88</v>
       </c>
       <c r="AE3">
-        <v>42.73</v>
+        <v>46.92</v>
       </c>
       <c r="AF3">
-        <v>-54.15</v>
+        <v>295.88</v>
       </c>
       <c r="AG3">
-        <v>1051.36</v>
+        <v>1048.79</v>
       </c>
       <c r="AH3">
-        <v>856.9</v>
+        <v>857.27</v>
       </c>
       <c r="AI3">
         <v>1054.09</v>
@@ -1175,7 +1166,7 @@
         <v>57</v>
       </c>
       <c r="AK3">
-        <v>15.18</v>
+        <v>18.34</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1186,58 +1177,58 @@
         <v>53</v>
       </c>
       <c r="C4">
-        <v>206.15</v>
+        <v>205.29</v>
       </c>
       <c r="D4">
-        <v>-1.28</v>
+        <v>-0.42</v>
       </c>
       <c r="E4">
         <v>356.93</v>
       </c>
       <c r="F4">
-        <v>206.15</v>
+        <v>205.29</v>
       </c>
       <c r="G4">
-        <v>-42.24</v>
+        <v>-42.48</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>-0.5</v>
+        <v>-0.91</v>
       </c>
       <c r="J4">
-        <v>-3.23</v>
+        <v>-3.68</v>
       </c>
       <c r="K4">
-        <v>-10.68</v>
+        <v>-9.56</v>
       </c>
       <c r="L4">
-        <v>-42.54</v>
+        <v>-42.45</v>
       </c>
       <c r="M4">
-        <v>-5.65</v>
+        <v>-5.64</v>
       </c>
       <c r="N4">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="O4">
         <v>9</v>
       </c>
       <c r="P4">
-        <v>208.29</v>
+        <v>207.92</v>
       </c>
       <c r="Q4">
-        <v>210.78</v>
+        <v>210.47</v>
       </c>
       <c r="R4">
-        <v>218.88</v>
+        <v>218.53</v>
       </c>
       <c r="S4">
-        <v>244.69</v>
+        <v>244.49</v>
       </c>
       <c r="T4">
-        <v>-15.75</v>
+        <v>-16.03</v>
       </c>
       <c r="U4" t="s">
         <v>54</v>
@@ -1252,43 +1243,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>34.47</v>
+        <v>33.15</v>
       </c>
       <c r="Z4">
-        <v>-3.05</v>
+        <v>-3.17</v>
       </c>
       <c r="AA4">
         <v>-3.18</v>
       </c>
       <c r="AB4">
-        <v>0.14</v>
+        <v>0.01</v>
       </c>
       <c r="AC4">
-        <v>41.91</v>
+        <v>19.55</v>
       </c>
       <c r="AD4">
-        <v>47.54</v>
+        <v>40.05</v>
       </c>
       <c r="AE4">
-        <v>4.54</v>
+        <v>4.37</v>
       </c>
       <c r="AF4">
-        <v>-34.34</v>
+        <v>-45.05</v>
       </c>
       <c r="AG4">
-        <v>215.28</v>
+        <v>215.58</v>
       </c>
       <c r="AH4">
-        <v>206.27</v>
+        <v>205.36</v>
       </c>
       <c r="AI4">
-        <v>220.7</v>
+        <v>218.92</v>
       </c>
       <c r="AJ4" t="s">
         <v>57</v>
       </c>
       <c r="AK4">
-        <v>27.51</v>
+        <v>29.37</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1299,10 +1290,10 @@
         <v>53</v>
       </c>
       <c r="C5">
-        <v>613.35</v>
+        <v>607.7</v>
       </c>
       <c r="D5">
-        <v>-1.88</v>
+        <v>-0.92</v>
       </c>
       <c r="E5">
         <v>989.9299999999999</v>
@@ -1311,46 +1302,46 @@
         <v>574.42</v>
       </c>
       <c r="G5">
-        <v>-38.04</v>
+        <v>-38.61</v>
       </c>
       <c r="H5">
-        <v>6.78</v>
+        <v>5.79</v>
       </c>
       <c r="I5">
-        <v>-4.61</v>
+        <v>-4.09</v>
       </c>
       <c r="J5">
-        <v>-8.94</v>
+        <v>-9.15</v>
       </c>
       <c r="K5">
-        <v>-14.27</v>
+        <v>-15.64</v>
       </c>
       <c r="L5">
-        <v>-33.69</v>
+        <v>-34.27</v>
       </c>
       <c r="M5">
-        <v>-4.35</v>
+        <v>-4.74</v>
       </c>
       <c r="N5">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="O5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P5">
-        <v>629.47</v>
+        <v>624.29</v>
       </c>
       <c r="Q5">
-        <v>644.35</v>
+        <v>641.3</v>
       </c>
       <c r="R5">
-        <v>671.8200000000001</v>
+        <v>669.66</v>
       </c>
       <c r="S5">
-        <v>708.63</v>
+        <v>707.64</v>
       </c>
       <c r="T5">
-        <v>-13.45</v>
+        <v>-14.12</v>
       </c>
       <c r="U5" t="s">
         <v>54</v>
@@ -1365,43 +1356,43 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>31.77</v>
+        <v>30.08</v>
       </c>
       <c r="Z5">
-        <v>-13.39</v>
+        <v>-14.64</v>
       </c>
       <c r="AA5">
-        <v>-12.92</v>
+        <v>-13.26</v>
       </c>
       <c r="AB5">
-        <v>-0.48</v>
+        <v>-1.38</v>
       </c>
       <c r="AC5">
-        <v>53.32</v>
+        <v>35.25</v>
       </c>
       <c r="AD5">
-        <v>59.55</v>
+        <v>50.05</v>
       </c>
       <c r="AE5">
-        <v>16.35</v>
+        <v>15.86</v>
       </c>
       <c r="AF5">
-        <v>-32.5</v>
+        <v>-47.39</v>
       </c>
       <c r="AG5">
-        <v>681.3099999999999</v>
+        <v>679.83</v>
       </c>
       <c r="AH5">
-        <v>607.39</v>
+        <v>602.77</v>
       </c>
       <c r="AI5">
-        <v>668.1900000000001</v>
+        <v>657.8099999999999</v>
       </c>
       <c r="AJ5" t="s">
         <v>57</v>
       </c>
       <c r="AK5">
-        <v>19.68</v>
+        <v>19.65</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1412,10 +1403,10 @@
         <v>53</v>
       </c>
       <c r="C6">
-        <v>1738.5</v>
+        <v>1752.8</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>0.82</v>
       </c>
       <c r="E6">
         <v>2061.7</v>
@@ -1424,46 +1415,46 @@
         <v>1347.9</v>
       </c>
       <c r="G6">
-        <v>-15.68</v>
+        <v>-14.98</v>
       </c>
       <c r="H6">
-        <v>28.98</v>
+        <v>30.04</v>
       </c>
       <c r="I6">
-        <v>0.88</v>
+        <v>1.1</v>
       </c>
       <c r="J6">
-        <v>-0.95</v>
+        <v>0.77</v>
       </c>
       <c r="K6">
-        <v>-12.01</v>
+        <v>-11.41</v>
       </c>
       <c r="L6">
-        <v>11.01</v>
+        <v>12.77</v>
       </c>
       <c r="M6">
-        <v>6.04</v>
+        <v>6.3</v>
       </c>
       <c r="N6">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="O6">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="P6">
-        <v>1726.96</v>
+        <v>1730.76</v>
       </c>
       <c r="Q6">
-        <v>1706.67</v>
+        <v>1707.01</v>
       </c>
       <c r="R6">
-        <v>1775.89</v>
+        <v>1771.54</v>
       </c>
       <c r="S6">
-        <v>1715.88</v>
+        <v>1715.05</v>
       </c>
       <c r="T6">
-        <v>1.32</v>
+        <v>2.2</v>
       </c>
       <c r="U6" t="s">
         <v>54</v>
@@ -1478,34 +1469,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>51.38</v>
+        <v>53.5</v>
       </c>
       <c r="Z6">
-        <v>-12.26</v>
+        <v>-8.43</v>
       </c>
       <c r="AA6">
-        <v>-23.47</v>
+        <v>-20.46</v>
       </c>
       <c r="AB6">
-        <v>11.21</v>
+        <v>12.03</v>
       </c>
       <c r="AC6">
-        <v>86.2</v>
+        <v>94.95999999999999</v>
       </c>
       <c r="AD6">
-        <v>84.61</v>
+        <v>88.31999999999999</v>
       </c>
       <c r="AE6">
-        <v>46.45</v>
+        <v>46.12</v>
       </c>
       <c r="AF6">
-        <v>-28.75</v>
+        <v>-1.53</v>
       </c>
       <c r="AG6">
-        <v>1771.35</v>
+        <v>1772.61</v>
       </c>
       <c r="AH6">
-        <v>1641.99</v>
+        <v>1641.4</v>
       </c>
       <c r="AI6">
         <v>1813.9</v>
@@ -1514,7 +1505,7 @@
         <v>57</v>
       </c>
       <c r="AK6">
-        <v>25.88</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1525,10 +1516,10 @@
         <v>53</v>
       </c>
       <c r="C7">
-        <v>1015</v>
+        <v>1014.1</v>
       </c>
       <c r="D7">
-        <v>0.5</v>
+        <v>-0.09</v>
       </c>
       <c r="E7">
         <v>1260.34</v>
@@ -1537,25 +1528,25 @@
         <v>1006.29</v>
       </c>
       <c r="G7">
-        <v>-19.47</v>
+        <v>-19.54</v>
       </c>
       <c r="H7">
-        <v>0.87</v>
+        <v>0.78</v>
       </c>
       <c r="I7">
-        <v>-2.17</v>
+        <v>-1.59</v>
       </c>
       <c r="J7">
-        <v>-6.22</v>
+        <v>-8.529999999999999</v>
       </c>
       <c r="K7">
-        <v>-8.27</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="L7">
-        <v>-7.32</v>
+        <v>-4.52</v>
       </c>
       <c r="M7">
-        <v>4.03</v>
+        <v>3.74</v>
       </c>
       <c r="N7">
         <v>56</v>
@@ -1564,19 +1555,19 @@
         <v>37</v>
       </c>
       <c r="P7">
-        <v>1017.34</v>
+        <v>1014.06</v>
       </c>
       <c r="Q7">
-        <v>1049.72</v>
+        <v>1046.52</v>
       </c>
       <c r="R7">
-        <v>1078.02</v>
+        <v>1076.79</v>
       </c>
       <c r="S7">
-        <v>1122.89</v>
+        <v>1122.14</v>
       </c>
       <c r="T7">
-        <v>-9.609999999999999</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="U7" t="s">
         <v>54</v>
@@ -1591,43 +1582,43 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>35.3</v>
+        <v>35.06</v>
       </c>
       <c r="Z7">
-        <v>-19.56</v>
+        <v>-19.64</v>
       </c>
       <c r="AA7">
-        <v>-16.2</v>
+        <v>-16.89</v>
       </c>
       <c r="AB7">
-        <v>-3.36</v>
+        <v>-2.75</v>
       </c>
       <c r="AC7">
-        <v>20.58</v>
+        <v>20.75</v>
       </c>
       <c r="AD7">
-        <v>13.45</v>
+        <v>17.56</v>
       </c>
       <c r="AE7">
-        <v>19.03</v>
+        <v>18.45</v>
       </c>
       <c r="AF7">
-        <v>13.86</v>
+        <v>-41.15</v>
       </c>
       <c r="AG7">
-        <v>1097.01</v>
+        <v>1094.4</v>
       </c>
       <c r="AH7">
-        <v>1002.43</v>
+        <v>998.65</v>
       </c>
       <c r="AI7">
-        <v>1069.05</v>
+        <v>1068.64</v>
       </c>
       <c r="AJ7" t="s">
         <v>57</v>
       </c>
       <c r="AK7">
-        <v>58.82</v>
+        <v>61.58</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1638,10 +1629,10 @@
         <v>53</v>
       </c>
       <c r="C8">
-        <v>3497</v>
+        <v>3492</v>
       </c>
       <c r="D8">
-        <v>-1.71</v>
+        <v>-0.14</v>
       </c>
       <c r="E8">
         <v>5749.89</v>
@@ -1650,46 +1641,46 @@
         <v>3387.6</v>
       </c>
       <c r="G8">
-        <v>-39.18</v>
+        <v>-39.27</v>
       </c>
       <c r="H8">
-        <v>3.23</v>
+        <v>3.08</v>
       </c>
       <c r="I8">
-        <v>-2.28</v>
+        <v>-4.01</v>
       </c>
       <c r="J8">
-        <v>-7.51</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="K8">
-        <v>-16.38</v>
+        <v>-14.67</v>
       </c>
       <c r="L8">
-        <v>-34.41</v>
+        <v>-34.51</v>
       </c>
       <c r="M8">
-        <v>-5.63</v>
+        <v>-5.44</v>
       </c>
       <c r="N8">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="O8">
         <v>9</v>
       </c>
       <c r="P8">
-        <v>3576.4</v>
+        <v>3547.2</v>
       </c>
       <c r="Q8">
-        <v>3664.41</v>
+        <v>3649.26</v>
       </c>
       <c r="R8">
-        <v>3649.26</v>
+        <v>3642.51</v>
       </c>
       <c r="S8">
-        <v>4378.47</v>
+        <v>4369.57</v>
       </c>
       <c r="T8">
-        <v>-20.13</v>
+        <v>-20.08</v>
       </c>
       <c r="U8" t="s">
         <v>55</v>
@@ -1704,43 +1695,43 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>35.85</v>
+        <v>35.53</v>
       </c>
       <c r="Z8">
-        <v>-41.12</v>
+        <v>-47.4</v>
       </c>
       <c r="AA8">
-        <v>-25.23</v>
+        <v>-29.66</v>
       </c>
       <c r="AB8">
-        <v>-15.89</v>
+        <v>-17.74</v>
       </c>
       <c r="AC8">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="AD8">
-        <v>13.61</v>
+        <v>5.11</v>
       </c>
       <c r="AE8">
-        <v>90.19</v>
+        <v>86.83</v>
       </c>
       <c r="AF8">
-        <v>-11.67</v>
+        <v>-45.63</v>
       </c>
       <c r="AG8">
-        <v>3821.29</v>
+        <v>3811.47</v>
       </c>
       <c r="AH8">
-        <v>3507.53</v>
+        <v>3487.05</v>
       </c>
       <c r="AI8">
-        <v>3782.02</v>
+        <v>3744.23</v>
       </c>
       <c r="AJ8" t="s">
         <v>57</v>
       </c>
       <c r="AK8">
-        <v>24.43</v>
+        <v>28.33</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1751,10 +1742,10 @@
         <v>53</v>
       </c>
       <c r="C9">
-        <v>627.8</v>
+        <v>622.05</v>
       </c>
       <c r="D9">
-        <v>-0.93</v>
+        <v>-0.92</v>
       </c>
       <c r="E9">
         <v>1052.57</v>
@@ -1763,25 +1754,25 @@
         <v>538.37</v>
       </c>
       <c r="G9">
-        <v>-40.36</v>
+        <v>-40.9</v>
       </c>
       <c r="H9">
-        <v>16.61</v>
+        <v>15.54</v>
       </c>
       <c r="I9">
-        <v>-2.24</v>
+        <v>-1.83</v>
       </c>
       <c r="J9">
-        <v>-9.49</v>
+        <v>-9.57</v>
       </c>
       <c r="K9">
-        <v>-4.77</v>
+        <v>-4.26</v>
       </c>
       <c r="L9">
-        <v>-7.23</v>
+        <v>-7.34</v>
       </c>
       <c r="M9">
-        <v>39.84</v>
+        <v>39.5</v>
       </c>
       <c r="N9">
         <v>62</v>
@@ -1790,19 +1781,19 @@
         <v>38</v>
       </c>
       <c r="P9">
-        <v>632.24</v>
+        <v>629.92</v>
       </c>
       <c r="Q9">
-        <v>649.1</v>
+        <v>645.77</v>
       </c>
       <c r="R9">
-        <v>660.28</v>
+        <v>659.39</v>
       </c>
       <c r="S9">
-        <v>666.8</v>
+        <v>666.13</v>
       </c>
       <c r="T9">
-        <v>-5.85</v>
+        <v>-6.62</v>
       </c>
       <c r="U9" t="s">
         <v>54</v>
@@ -1817,43 +1808,43 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>35.41</v>
+        <v>32.86</v>
       </c>
       <c r="Z9">
-        <v>-9.470000000000001</v>
+        <v>-10.16</v>
       </c>
       <c r="AA9">
-        <v>-7.82</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="AB9">
-        <v>-1.65</v>
+        <v>-1.87</v>
       </c>
       <c r="AC9">
-        <v>56.96</v>
+        <v>32.92</v>
       </c>
       <c r="AD9">
-        <v>43.36</v>
+        <v>45.43</v>
       </c>
       <c r="AE9">
-        <v>13.07</v>
+        <v>12.63</v>
       </c>
       <c r="AF9">
-        <v>-74.25</v>
+        <v>-38.69</v>
       </c>
       <c r="AG9">
-        <v>682.63</v>
+        <v>675.78</v>
       </c>
       <c r="AH9">
-        <v>615.5700000000001</v>
+        <v>615.76</v>
       </c>
       <c r="AI9">
-        <v>667.87</v>
+        <v>661.83</v>
       </c>
       <c r="AJ9" t="s">
         <v>57</v>
       </c>
       <c r="AK9">
-        <v>10.51</v>
+        <v>11.73</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1864,10 +1855,10 @@
         <v>53</v>
       </c>
       <c r="C10">
-        <v>365.7</v>
+        <v>365.55</v>
       </c>
       <c r="D10">
-        <v>-0.62</v>
+        <v>-0.04</v>
       </c>
       <c r="E10">
         <v>461.8</v>
@@ -1876,46 +1867,46 @@
         <v>345.25</v>
       </c>
       <c r="G10">
-        <v>-20.81</v>
+        <v>-20.84</v>
       </c>
       <c r="H10">
-        <v>5.92</v>
+        <v>5.88</v>
       </c>
       <c r="I10">
-        <v>5.39</v>
+        <v>4.28</v>
       </c>
       <c r="J10">
-        <v>-3.9</v>
+        <v>-4.31</v>
       </c>
       <c r="K10">
-        <v>-8.27</v>
+        <v>-7.4</v>
       </c>
       <c r="L10">
-        <v>-6.03</v>
+        <v>-4.46</v>
       </c>
       <c r="M10">
-        <v>23.66</v>
+        <v>23.05</v>
       </c>
       <c r="N10">
         <v>68</v>
       </c>
       <c r="O10">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P10">
-        <v>362.79</v>
+        <v>365.79</v>
       </c>
       <c r="Q10">
-        <v>369.41</v>
+        <v>368.68</v>
       </c>
       <c r="R10">
-        <v>374.78</v>
+        <v>374.38</v>
       </c>
       <c r="S10">
-        <v>388.29</v>
+        <v>388.18</v>
       </c>
       <c r="T10">
-        <v>-5.82</v>
+        <v>-5.83</v>
       </c>
       <c r="U10" t="s">
         <v>54</v>
@@ -1930,34 +1921,34 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>45.71</v>
+        <v>45.57</v>
       </c>
       <c r="Z10">
-        <v>-4.99</v>
+        <v>-4.53</v>
       </c>
       <c r="AA10">
-        <v>-5.34</v>
+        <v>-5.18</v>
       </c>
       <c r="AB10">
-        <v>0.35</v>
+        <v>0.65</v>
       </c>
       <c r="AC10">
-        <v>91.09999999999999</v>
+        <v>93.25</v>
       </c>
       <c r="AD10">
-        <v>79.36</v>
+        <v>90.17</v>
       </c>
       <c r="AE10">
-        <v>7.1</v>
+        <v>6.95</v>
       </c>
       <c r="AF10">
-        <v>-11</v>
+        <v>-48.17</v>
       </c>
       <c r="AG10">
-        <v>392.61</v>
+        <v>391.39</v>
       </c>
       <c r="AH10">
-        <v>346.21</v>
+        <v>345.98</v>
       </c>
       <c r="AI10">
         <v>369.35</v>
@@ -1966,7 +1957,7 @@
         <v>57</v>
       </c>
       <c r="AK10">
-        <v>31.84</v>
+        <v>29.21</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1977,10 +1968,10 @@
         <v>53</v>
       </c>
       <c r="C11">
-        <v>185.61</v>
+        <v>184.15</v>
       </c>
       <c r="D11">
-        <v>-1.68</v>
+        <v>-0.79</v>
       </c>
       <c r="E11">
         <v>216.66</v>
@@ -1989,46 +1980,46 @@
         <v>157.42</v>
       </c>
       <c r="G11">
-        <v>-14.33</v>
+        <v>-15.01</v>
       </c>
       <c r="H11">
-        <v>17.91</v>
+        <v>16.98</v>
       </c>
       <c r="I11">
-        <v>0.68</v>
+        <v>0.04</v>
       </c>
       <c r="J11">
-        <v>-1.03</v>
+        <v>-3.2</v>
       </c>
       <c r="K11">
-        <v>-6.76</v>
+        <v>-5.7</v>
       </c>
       <c r="L11">
-        <v>12.86</v>
+        <v>12.67</v>
       </c>
       <c r="M11">
-        <v>8.539999999999999</v>
+        <v>8.35</v>
       </c>
       <c r="N11">
         <v>87</v>
       </c>
       <c r="O11">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P11">
-        <v>185.3</v>
+        <v>185.32</v>
       </c>
       <c r="Q11">
-        <v>185.51</v>
+        <v>185.31</v>
       </c>
       <c r="R11">
-        <v>186.82</v>
+        <v>186.74</v>
       </c>
       <c r="S11">
-        <v>190.09</v>
+        <v>190.17</v>
       </c>
       <c r="T11">
-        <v>-2.36</v>
+        <v>-3.16</v>
       </c>
       <c r="U11" t="s">
         <v>54</v>
@@ -2043,31 +2034,31 @@
         <v>0</v>
       </c>
       <c r="Y11">
-        <v>48.19</v>
+        <v>45.09</v>
       </c>
       <c r="Z11">
-        <v>-0.57</v>
+        <v>-0.66</v>
       </c>
       <c r="AA11">
-        <v>-0.8</v>
+        <v>-0.77</v>
       </c>
       <c r="AB11">
-        <v>0.23</v>
+        <v>0.11</v>
       </c>
       <c r="AC11">
-        <v>60.02</v>
+        <v>60.43</v>
       </c>
       <c r="AD11">
-        <v>45.39</v>
+        <v>56.96</v>
       </c>
       <c r="AE11">
-        <v>4.46</v>
+        <v>4.35</v>
       </c>
       <c r="AF11">
         <v>-12.12</v>
       </c>
       <c r="AG11">
-        <v>188.93</v>
+        <v>188.52</v>
       </c>
       <c r="AH11">
         <v>182.09</v>
@@ -2079,7 +2070,7 @@
         <v>56</v>
       </c>
       <c r="AK11">
-        <v>20.15</v>
+        <v>21.22</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -2090,10 +2081,10 @@
         <v>53</v>
       </c>
       <c r="C12">
-        <v>2270</v>
+        <v>2255.5</v>
       </c>
       <c r="D12">
-        <v>-1.48</v>
+        <v>-0.64</v>
       </c>
       <c r="E12">
         <v>3221.85</v>
@@ -2102,25 +2093,25 @@
         <v>1982.6</v>
       </c>
       <c r="G12">
-        <v>-29.54</v>
+        <v>-29.99</v>
       </c>
       <c r="H12">
-        <v>14.5</v>
+        <v>13.76</v>
       </c>
       <c r="I12">
-        <v>-5.39</v>
+        <v>-4.79</v>
       </c>
       <c r="J12">
-        <v>-7.45</v>
+        <v>-7.02</v>
       </c>
       <c r="K12">
-        <v>5.53</v>
+        <v>4.72</v>
       </c>
       <c r="L12">
-        <v>-24.09</v>
+        <v>-24.53</v>
       </c>
       <c r="M12">
-        <v>-7.4</v>
+        <v>-7.31</v>
       </c>
       <c r="N12">
         <v>50</v>
@@ -2129,19 +2120,19 @@
         <v>34</v>
       </c>
       <c r="P12">
-        <v>2322.22</v>
+        <v>2299.52</v>
       </c>
       <c r="Q12">
-        <v>2323.23</v>
+        <v>2313.72</v>
       </c>
       <c r="R12">
-        <v>2274.5</v>
+        <v>2278.98</v>
       </c>
       <c r="S12">
-        <v>2563.22</v>
+        <v>2559.26</v>
       </c>
       <c r="T12">
-        <v>-11.44</v>
+        <v>-11.87</v>
       </c>
       <c r="U12" t="s">
         <v>55</v>
@@ -2156,34 +2147,34 @@
         <v>1</v>
       </c>
       <c r="Y12">
-        <v>44.62</v>
+        <v>43.18</v>
       </c>
       <c r="Z12">
-        <v>0.41</v>
+        <v>-4.61</v>
       </c>
       <c r="AA12">
-        <v>7.09</v>
+        <v>4.75</v>
       </c>
       <c r="AB12">
-        <v>-6.68</v>
+        <v>-9.359999999999999</v>
       </c>
       <c r="AC12">
-        <v>30.28</v>
+        <v>16.44</v>
       </c>
       <c r="AD12">
-        <v>46.62</v>
+        <v>31.38</v>
       </c>
       <c r="AE12">
-        <v>59.61</v>
+        <v>57.53</v>
       </c>
       <c r="AF12">
-        <v>-13.61</v>
+        <v>-16.01</v>
       </c>
       <c r="AG12">
-        <v>2422.48</v>
+        <v>2399.04</v>
       </c>
       <c r="AH12">
-        <v>2223.99</v>
+        <v>2228.41</v>
       </c>
       <c r="AI12">
         <v>2431.19</v>
@@ -2192,7 +2183,7 @@
         <v>57</v>
       </c>
       <c r="AK12">
-        <v>19.88</v>
+        <v>21.21</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2203,10 +2194,10 @@
         <v>53</v>
       </c>
       <c r="C13">
-        <v>4995</v>
+        <v>4987</v>
       </c>
       <c r="D13">
-        <v>-0.5</v>
+        <v>-0.16</v>
       </c>
       <c r="E13">
         <v>5169.2</v>
@@ -2215,46 +2206,46 @@
         <v>3327.3</v>
       </c>
       <c r="G13">
-        <v>-3.37</v>
+        <v>-3.52</v>
       </c>
       <c r="H13">
-        <v>50.12</v>
+        <v>49.88</v>
       </c>
       <c r="I13">
-        <v>-2.1</v>
+        <v>-1.25</v>
       </c>
       <c r="J13">
-        <v>1.09</v>
+        <v>-2.02</v>
       </c>
       <c r="K13">
-        <v>21.68</v>
+        <v>23.38</v>
       </c>
       <c r="L13">
-        <v>35.34</v>
+        <v>35.11</v>
       </c>
       <c r="M13">
-        <v>20</v>
+        <v>19.7</v>
       </c>
       <c r="N13">
         <v>99</v>
       </c>
       <c r="O13">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P13">
-        <v>5033.2</v>
+        <v>5020.6</v>
       </c>
       <c r="Q13">
-        <v>5077.73</v>
+        <v>5070.68</v>
       </c>
       <c r="R13">
-        <v>4851.85</v>
+        <v>4863.51</v>
       </c>
       <c r="S13">
-        <v>4324.36</v>
+        <v>4329.78</v>
       </c>
       <c r="T13">
-        <v>15.51</v>
+        <v>15.18</v>
       </c>
       <c r="U13" t="s">
         <v>55</v>
@@ -2269,34 +2260,34 @@
         <v>3</v>
       </c>
       <c r="Y13">
-        <v>49.6</v>
+        <v>48.72</v>
       </c>
       <c r="Z13">
-        <v>50.5</v>
+        <v>41.36</v>
       </c>
       <c r="AA13">
-        <v>80.66</v>
+        <v>72.8</v>
       </c>
       <c r="AB13">
-        <v>-30.16</v>
+        <v>-31.44</v>
       </c>
       <c r="AC13">
         <v>0</v>
       </c>
       <c r="AD13">
-        <v>2.88</v>
+        <v>1.44</v>
       </c>
       <c r="AE13">
-        <v>82.02</v>
+        <v>79.48</v>
       </c>
       <c r="AF13">
-        <v>-38.66</v>
+        <v>-42.34</v>
       </c>
       <c r="AG13">
-        <v>5162.61</v>
+        <v>5161.21</v>
       </c>
       <c r="AH13">
-        <v>4992.84</v>
+        <v>4980.14</v>
       </c>
       <c r="AI13">
         <v>4921.93</v>
@@ -2305,7 +2296,7 @@
         <v>56</v>
       </c>
       <c r="AK13">
-        <v>38.08</v>
+        <v>38.54</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2316,58 +2307,58 @@
         <v>53</v>
       </c>
       <c r="C14">
-        <v>2814.5</v>
+        <v>2793.6</v>
       </c>
       <c r="D14">
-        <v>-1.35</v>
+        <v>-0.74</v>
       </c>
       <c r="E14">
-        <v>5520.84</v>
+        <v>5520.34</v>
       </c>
       <c r="F14">
         <v>2193.96</v>
       </c>
       <c r="G14">
-        <v>-49.02</v>
+        <v>-49.39</v>
       </c>
       <c r="H14">
-        <v>28.28</v>
+        <v>27.33</v>
       </c>
       <c r="I14">
-        <v>-2.27</v>
+        <v>-2.15</v>
       </c>
       <c r="J14">
-        <v>-6.09</v>
+        <v>-7.65</v>
       </c>
       <c r="K14">
-        <v>1.71</v>
+        <v>1.56</v>
       </c>
       <c r="L14">
-        <v>-48.56</v>
+        <v>-49.4</v>
       </c>
       <c r="M14">
-        <v>23.13</v>
+        <v>22.11</v>
       </c>
       <c r="N14">
         <v>32</v>
       </c>
       <c r="O14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P14">
-        <v>2838.08</v>
+        <v>2825.8</v>
       </c>
       <c r="Q14">
-        <v>2914.01</v>
+        <v>2903.69</v>
       </c>
       <c r="R14">
-        <v>2972.43</v>
+        <v>2962.65</v>
       </c>
       <c r="S14">
-        <v>2980.69</v>
+        <v>2972.75</v>
       </c>
       <c r="T14">
-        <v>-5.58</v>
+        <v>-6.03</v>
       </c>
       <c r="U14" t="s">
         <v>54</v>
@@ -2382,43 +2373,43 @@
         <v>0</v>
       </c>
       <c r="Y14">
-        <v>35.78</v>
+        <v>33.8</v>
       </c>
       <c r="Z14">
-        <v>-40.36</v>
+        <v>-43.78</v>
       </c>
       <c r="AA14">
-        <v>-29.89</v>
+        <v>-32.67</v>
       </c>
       <c r="AB14">
-        <v>-10.47</v>
+        <v>-11.11</v>
       </c>
       <c r="AC14">
-        <v>21.29</v>
+        <v>23</v>
       </c>
       <c r="AD14">
-        <v>12.14</v>
+        <v>19.8</v>
       </c>
       <c r="AE14">
-        <v>60.26</v>
+        <v>59.11</v>
       </c>
       <c r="AF14">
-        <v>32.59</v>
+        <v>-16.03</v>
       </c>
       <c r="AG14">
-        <v>3029</v>
+        <v>3023.14</v>
       </c>
       <c r="AH14">
-        <v>2799.01</v>
+        <v>2784.23</v>
       </c>
       <c r="AI14">
-        <v>2994.23</v>
+        <v>2968.92</v>
       </c>
       <c r="AJ14" t="s">
         <v>57</v>
       </c>
       <c r="AK14">
-        <v>37.3</v>
+        <v>40.93</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2429,10 +2420,10 @@
         <v>53</v>
       </c>
       <c r="C15">
-        <v>235.13</v>
+        <v>230.98</v>
       </c>
       <c r="D15">
-        <v>1.53</v>
+        <v>-1.76</v>
       </c>
       <c r="E15">
         <v>392.75</v>
@@ -2441,46 +2432,46 @@
         <v>217.05</v>
       </c>
       <c r="G15">
-        <v>-40.13</v>
+        <v>-41.19</v>
       </c>
       <c r="H15">
-        <v>8.33</v>
+        <v>6.42</v>
       </c>
       <c r="I15">
-        <v>3.33</v>
+        <v>3.03</v>
       </c>
       <c r="J15">
-        <v>1.01</v>
+        <v>-1.52</v>
       </c>
       <c r="K15">
-        <v>3.74</v>
+        <v>3.88</v>
       </c>
       <c r="L15">
-        <v>-27.02</v>
+        <v>-26.51</v>
       </c>
       <c r="M15">
-        <v>13.08</v>
+        <v>12.93</v>
       </c>
       <c r="N15">
         <v>44</v>
       </c>
       <c r="O15">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="P15">
-        <v>228.91</v>
+        <v>230.27</v>
       </c>
       <c r="Q15">
-        <v>230.17</v>
+        <v>229.95</v>
       </c>
       <c r="R15">
-        <v>233.56</v>
+        <v>233.39</v>
       </c>
       <c r="S15">
-        <v>256.78</v>
+        <v>256.34</v>
       </c>
       <c r="T15">
-        <v>-8.43</v>
+        <v>-9.890000000000001</v>
       </c>
       <c r="U15" t="s">
         <v>54</v>
@@ -2495,34 +2486,34 @@
         <v>0</v>
       </c>
       <c r="Y15">
-        <v>57.24</v>
+        <v>50.19</v>
       </c>
       <c r="Z15">
-        <v>-0.82</v>
+        <v>-0.67</v>
       </c>
       <c r="AA15">
-        <v>-1.43</v>
+        <v>-1.28</v>
       </c>
       <c r="AB15">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="AC15">
-        <v>100</v>
+        <v>88.84</v>
       </c>
       <c r="AD15">
-        <v>66.67</v>
+        <v>85.17</v>
       </c>
       <c r="AE15">
-        <v>5.72</v>
+        <v>5.85</v>
       </c>
       <c r="AF15">
-        <v>31.71</v>
+        <v>-35.92</v>
       </c>
       <c r="AG15">
-        <v>235.83</v>
+        <v>235.04</v>
       </c>
       <c r="AH15">
-        <v>224.51</v>
+        <v>224.85</v>
       </c>
       <c r="AI15">
         <v>219.81</v>
@@ -2531,7 +2522,7 @@
         <v>56</v>
       </c>
       <c r="AK15">
-        <v>22.47</v>
+        <v>24.04</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2542,10 +2533,10 @@
         <v>53</v>
       </c>
       <c r="C16">
-        <v>37.35</v>
+        <v>36.49</v>
       </c>
       <c r="D16">
-        <v>-1.03</v>
+        <v>-2.3</v>
       </c>
       <c r="E16">
         <v>58.79</v>
@@ -2554,46 +2545,46 @@
         <v>31.36</v>
       </c>
       <c r="G16">
-        <v>-36.47</v>
+        <v>-37.93</v>
       </c>
       <c r="H16">
-        <v>19.1</v>
+        <v>16.36</v>
       </c>
       <c r="I16">
-        <v>-3.19</v>
+        <v>-6.24</v>
       </c>
       <c r="J16">
-        <v>-5.13</v>
+        <v>-6.48</v>
       </c>
       <c r="K16">
-        <v>-13.84</v>
+        <v>-14.14</v>
       </c>
       <c r="L16">
-        <v>-35.55</v>
+        <v>-36.05</v>
       </c>
       <c r="M16">
-        <v>1.96</v>
+        <v>0.52</v>
       </c>
       <c r="N16">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="O16">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="P16">
-        <v>38</v>
+        <v>37.52</v>
       </c>
       <c r="Q16">
-        <v>37.99</v>
+        <v>37.88</v>
       </c>
       <c r="R16">
-        <v>39.53</v>
+        <v>39.4</v>
       </c>
       <c r="S16">
-        <v>43.01</v>
+        <v>42.94</v>
       </c>
       <c r="T16">
-        <v>-13.17</v>
+        <v>-15.02</v>
       </c>
       <c r="U16" t="s">
         <v>54</v>
@@ -2608,34 +2599,34 @@
         <v>0</v>
       </c>
       <c r="Y16">
-        <v>40.52</v>
+        <v>35.46</v>
       </c>
       <c r="Z16">
-        <v>-0.49</v>
+        <v>-0.57</v>
       </c>
       <c r="AA16">
         <v>-0.58</v>
       </c>
       <c r="AB16">
-        <v>0.09</v>
+        <v>0.01</v>
       </c>
       <c r="AC16">
-        <v>65.45</v>
+        <v>52.57</v>
       </c>
       <c r="AD16">
-        <v>73.12</v>
+        <v>63.13</v>
       </c>
       <c r="AE16">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF16">
-        <v>-65.84</v>
+        <v>-60.02</v>
       </c>
       <c r="AG16">
-        <v>39.3</v>
+        <v>39.29</v>
       </c>
       <c r="AH16">
-        <v>36.69</v>
+        <v>36.47</v>
       </c>
       <c r="AI16">
         <v>39.99</v>
@@ -2644,7 +2635,7 @@
         <v>57</v>
       </c>
       <c r="AK16">
-        <v>23.47</v>
+        <v>22.27</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2655,58 +2646,58 @@
         <v>53</v>
       </c>
       <c r="C17">
-        <v>1167.2</v>
+        <v>1144.8</v>
       </c>
       <c r="D17">
-        <v>-0.24</v>
+        <v>-1.92</v>
       </c>
       <c r="E17">
         <v>1556.41</v>
       </c>
       <c r="F17">
-        <v>1152.1</v>
+        <v>1144.8</v>
       </c>
       <c r="G17">
-        <v>-25.01</v>
+        <v>-26.45</v>
       </c>
       <c r="H17">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="I17">
-        <v>-2.28</v>
+        <v>-5</v>
       </c>
       <c r="J17">
-        <v>-9.17</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="K17">
-        <v>-10.24</v>
+        <v>-10.98</v>
       </c>
       <c r="L17">
-        <v>-18.14</v>
+        <v>-18.12</v>
       </c>
       <c r="M17">
-        <v>0.12</v>
+        <v>-0.59</v>
       </c>
       <c r="N17">
         <v>38</v>
       </c>
       <c r="O17">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="P17">
-        <v>1174.46</v>
+        <v>1162.42</v>
       </c>
       <c r="Q17">
-        <v>1228.18</v>
+        <v>1221.42</v>
       </c>
       <c r="R17">
-        <v>1278.52</v>
+        <v>1275.87</v>
       </c>
       <c r="S17">
-        <v>1349.96</v>
+        <v>1348.65</v>
       </c>
       <c r="T17">
-        <v>-13.54</v>
+        <v>-15.12</v>
       </c>
       <c r="U17" t="s">
         <v>54</v>
@@ -2721,43 +2712,43 @@
         <v>0</v>
       </c>
       <c r="Y17">
-        <v>33.79</v>
+        <v>30.47</v>
       </c>
       <c r="Z17">
-        <v>-33.55</v>
+        <v>-35.36</v>
       </c>
       <c r="AA17">
-        <v>-28.53</v>
+        <v>-29.9</v>
       </c>
       <c r="AB17">
-        <v>-5.02</v>
+        <v>-5.46</v>
       </c>
       <c r="AC17">
-        <v>50.27</v>
+        <v>39.04</v>
       </c>
       <c r="AD17">
-        <v>36.29</v>
+        <v>41.36</v>
       </c>
       <c r="AE17">
-        <v>29.91</v>
+        <v>29.76</v>
       </c>
       <c r="AF17">
-        <v>-62.28</v>
+        <v>-21.83</v>
       </c>
       <c r="AG17">
-        <v>1319.47</v>
+        <v>1316.5</v>
       </c>
       <c r="AH17">
-        <v>1136.89</v>
+        <v>1126.34</v>
       </c>
       <c r="AI17">
-        <v>1260.12</v>
+        <v>1244.54</v>
       </c>
       <c r="AJ17" t="s">
         <v>57</v>
       </c>
       <c r="AK17">
-        <v>46.05</v>
+        <v>49.1</v>
       </c>
     </row>
   </sheetData>
@@ -2898,7 +2889,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F145"/>
+  <dimension ref="A1:F139"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2938,7 +2929,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>64</v>
@@ -2956,1704 +2947,1701 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C4" s="4" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
+      <c r="E6" s="3" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>76</v>
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-2.02</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-1.19</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0.83</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-2.17</v>
+        <v>-2.68</v>
       </c>
       <c r="D8" s="6">
-        <v>-2.02</v>
-      </c>
-      <c r="E8" s="7">
-        <v>0.15</v>
+        <v>-3.42</v>
+      </c>
+      <c r="E8" s="8">
+        <v>-0.74</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-7.37</v>
+        <v>-3.23</v>
       </c>
       <c r="D9" s="6">
-        <v>-2.68</v>
-      </c>
-      <c r="E9" s="7">
-        <v>4.69</v>
+        <v>-3.68</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-0.45</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-2.81</v>
+        <v>-8.94</v>
       </c>
       <c r="D10" s="6">
-        <v>-3.23</v>
+        <v>-9.15</v>
       </c>
       <c r="E10" s="8">
-        <v>-0.42</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-5.76</v>
+        <v>-0.95</v>
       </c>
       <c r="D11" s="6">
-        <v>-8.94</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-3.18</v>
+        <v>0.77</v>
+      </c>
+      <c r="E11" s="7">
+        <v>1.72</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>1.19</v>
+        <v>-6.22</v>
       </c>
       <c r="D12" s="6">
-        <v>-0.95</v>
+        <v>-8.529999999999999</v>
       </c>
       <c r="E12" s="8">
-        <v>-2.14</v>
+        <v>-2.31</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-7.34</v>
+        <v>-7.51</v>
       </c>
       <c r="D13" s="6">
-        <v>-6.22</v>
-      </c>
-      <c r="E13" s="7">
-        <v>1.12</v>
+        <v>-8.300000000000001</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-0.79</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-4.23</v>
+        <v>-9.49</v>
       </c>
       <c r="D14" s="6">
-        <v>-7.51</v>
+        <v>-9.57</v>
       </c>
       <c r="E14" s="8">
-        <v>-3.28</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>-5.01</v>
+        <v>-3.9</v>
       </c>
       <c r="D15" s="6">
-        <v>-9.49</v>
+        <v>-4.31</v>
       </c>
       <c r="E15" s="8">
-        <v>-4.48</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="6">
-        <v>-2.8</v>
+        <v>-1.03</v>
       </c>
       <c r="D16" s="6">
-        <v>-3.9</v>
+        <v>-3.2</v>
       </c>
       <c r="E16" s="8">
-        <v>-1.1</v>
+        <v>-2.17</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="6">
-        <v>-0.27</v>
+        <v>-7.45</v>
       </c>
       <c r="D17" s="6">
-        <v>-1.03</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-0.76</v>
+        <v>-7.02</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0.43</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="6">
-        <v>-2.91</v>
+        <v>1.09</v>
       </c>
       <c r="D18" s="6">
-        <v>-7.45</v>
+        <v>-2.02</v>
       </c>
       <c r="E18" s="8">
-        <v>-4.54</v>
+        <v>-3.11</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="6">
-        <v>0.44</v>
+        <v>-6.09</v>
       </c>
       <c r="D19" s="6">
-        <v>1.09</v>
-      </c>
-      <c r="E19" s="7">
-        <v>0.65</v>
+        <v>-7.65</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-1.56</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="6">
-        <v>-8.18</v>
+        <v>1.01</v>
       </c>
       <c r="D20" s="6">
-        <v>-6.09</v>
-      </c>
-      <c r="E20" s="7">
-        <v>2.09</v>
+        <v>-1.52</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-2.53</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C21" s="6">
-        <v>-0.35</v>
+        <v>-5.13</v>
       </c>
       <c r="D21" s="6">
-        <v>1.01</v>
-      </c>
-      <c r="E21" s="7">
-        <v>1.36</v>
+        <v>-6.48</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-1.35</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C22" s="6">
-        <v>-4.62</v>
+        <v>-9.17</v>
       </c>
       <c r="D22" s="6">
-        <v>-5.13</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="E22" s="8">
-        <v>-0.51</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C23" s="6">
-        <v>-8.24</v>
+        <v>-2.94</v>
       </c>
       <c r="D23" s="6">
-        <v>-9.17</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-0.93</v>
+        <v>0.28</v>
+      </c>
+      <c r="E23" s="7">
+        <v>3.22</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="6">
-        <v>1.93</v>
+        <v>-1.92</v>
       </c>
       <c r="D24" s="6">
-        <v>-2.94</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-4.87</v>
+        <v>5.27</v>
+      </c>
+      <c r="E24" s="7">
+        <v>7.19</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C25" s="6">
-        <v>-5.2</v>
+        <v>-0.5</v>
       </c>
       <c r="D25" s="6">
-        <v>-1.92</v>
-      </c>
-      <c r="E25" s="7">
-        <v>3.28</v>
+        <v>-0.91</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-0.41</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C26" s="6">
-        <v>-0.39</v>
+        <v>-4.61</v>
       </c>
       <c r="D26" s="6">
-        <v>-0.5</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-0.11</v>
+        <v>-4.09</v>
+      </c>
+      <c r="E26" s="7">
+        <v>0.52</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C27" s="6">
-        <v>-4.67</v>
+        <v>0.88</v>
       </c>
       <c r="D27" s="6">
-        <v>-4.61</v>
+        <v>1.1</v>
       </c>
       <c r="E27" s="7">
-        <v>0.06</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C28" s="6">
-        <v>3.62</v>
+        <v>-2.17</v>
       </c>
       <c r="D28" s="6">
-        <v>0.88</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-2.74</v>
+        <v>-1.59</v>
+      </c>
+      <c r="E28" s="7">
+        <v>0.58</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C29" s="6">
-        <v>-2.95</v>
+        <v>-2.28</v>
       </c>
       <c r="D29" s="6">
-        <v>-2.17</v>
-      </c>
-      <c r="E29" s="7">
-        <v>0.78</v>
+        <v>-4.01</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-1.73</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C30" s="6">
-        <v>-3.45</v>
+        <v>-2.24</v>
       </c>
       <c r="D30" s="6">
-        <v>-2.28</v>
+        <v>-1.83</v>
       </c>
       <c r="E30" s="7">
-        <v>1.17</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C31" s="6">
-        <v>-0.79</v>
+        <v>5.39</v>
       </c>
       <c r="D31" s="6">
-        <v>-2.24</v>
+        <v>4.28</v>
       </c>
       <c r="E31" s="8">
-        <v>-1.45</v>
+        <v>-1.11</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C32" s="6">
-        <v>4.59</v>
+        <v>0.68</v>
       </c>
       <c r="D32" s="6">
-        <v>5.39</v>
-      </c>
-      <c r="E32" s="7">
-        <v>0.8</v>
+        <v>0.04</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-0.64</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C33" s="6">
-        <v>1.23</v>
+        <v>-5.39</v>
       </c>
       <c r="D33" s="6">
-        <v>0.68</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-0.55</v>
+        <v>-4.79</v>
+      </c>
+      <c r="E33" s="7">
+        <v>0.6</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C34" s="6">
-        <v>-1.62</v>
+        <v>-2.1</v>
       </c>
       <c r="D34" s="6">
-        <v>-5.39</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-3.77</v>
+        <v>-1.25</v>
+      </c>
+      <c r="E34" s="7">
+        <v>0.85</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C35" s="6">
-        <v>-2.89</v>
+        <v>-2.27</v>
       </c>
       <c r="D35" s="6">
-        <v>-2.1</v>
+        <v>-2.15</v>
       </c>
       <c r="E35" s="7">
-        <v>0.79</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C36" s="6">
-        <v>-1.55</v>
+        <v>3.33</v>
       </c>
       <c r="D36" s="6">
-        <v>-2.27</v>
+        <v>3.03</v>
       </c>
       <c r="E36" s="8">
-        <v>-0.72</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C37" s="6">
-        <v>0.92</v>
+        <v>-3.19</v>
       </c>
       <c r="D37" s="6">
-        <v>3.33</v>
-      </c>
-      <c r="E37" s="7">
-        <v>2.41</v>
+        <v>-6.24</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-3.05</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C38" s="6">
-        <v>-2.83</v>
+        <v>-2.28</v>
       </c>
       <c r="D38" s="6">
-        <v>-3.19</v>
+        <v>-5</v>
       </c>
       <c r="E38" s="8">
-        <v>-0.36</v>
+        <v>-2.72</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C39" s="6">
-        <v>-2.5</v>
+        <v>-7.46</v>
       </c>
       <c r="D39" s="6">
-        <v>-2.28</v>
+        <v>-7.07</v>
       </c>
       <c r="E39" s="7">
-        <v>0.22</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C40" s="6">
-        <v>-5.96</v>
+        <v>12.96</v>
       </c>
       <c r="D40" s="6">
-        <v>-7.46</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-1.5</v>
+        <v>19.84</v>
+      </c>
+      <c r="E40" s="7">
+        <v>6.88</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C41" s="6">
-        <v>11</v>
+        <v>-42.54</v>
       </c>
       <c r="D41" s="6">
-        <v>12.96</v>
+        <v>-42.45</v>
       </c>
       <c r="E41" s="7">
-        <v>1.96</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C42" s="6">
-        <v>-40.79</v>
+        <v>-33.69</v>
       </c>
       <c r="D42" s="6">
-        <v>-42.54</v>
+        <v>-34.27</v>
       </c>
       <c r="E42" s="8">
-        <v>-1.75</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C43" s="6">
-        <v>-31.86</v>
+        <v>11.01</v>
       </c>
       <c r="D43" s="6">
-        <v>-33.69</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-1.83</v>
+        <v>12.77</v>
+      </c>
+      <c r="E43" s="7">
+        <v>1.76</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C44" s="6">
-        <v>13.19</v>
+        <v>-7.32</v>
       </c>
       <c r="D44" s="6">
-        <v>11.01</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-2.18</v>
+        <v>-4.52</v>
+      </c>
+      <c r="E44" s="7">
+        <v>2.8</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C45" s="6">
-        <v>-7.47</v>
+        <v>-34.41</v>
       </c>
       <c r="D45" s="6">
-        <v>-7.32</v>
-      </c>
-      <c r="E45" s="7">
-        <v>0.15</v>
+        <v>-34.51</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-0.1</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C46" s="6">
-        <v>-33.24</v>
+        <v>-7.23</v>
       </c>
       <c r="D46" s="6">
-        <v>-34.41</v>
+        <v>-7.34</v>
       </c>
       <c r="E46" s="8">
-        <v>-1.17</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C47" s="6">
-        <v>-6.69</v>
+        <v>-6.03</v>
       </c>
       <c r="D47" s="6">
-        <v>-7.23</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-0.54</v>
+        <v>-4.46</v>
+      </c>
+      <c r="E47" s="7">
+        <v>1.57</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C48" s="6">
-        <v>-4.68</v>
+        <v>12.86</v>
       </c>
       <c r="D48" s="6">
-        <v>-6.03</v>
+        <v>12.67</v>
       </c>
       <c r="E48" s="8">
-        <v>-1.35</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C49" s="6">
-        <v>21.65</v>
+        <v>-24.09</v>
       </c>
       <c r="D49" s="6">
-        <v>12.86</v>
+        <v>-24.53</v>
       </c>
       <c r="E49" s="8">
-        <v>-8.789999999999999</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C50" s="6">
-        <v>-23.3</v>
+        <v>35.34</v>
       </c>
       <c r="D50" s="6">
-        <v>-24.09</v>
+        <v>35.11</v>
       </c>
       <c r="E50" s="8">
-        <v>-0.79</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C51" s="6">
-        <v>38.65</v>
+        <v>-48.56</v>
       </c>
       <c r="D51" s="6">
-        <v>35.34</v>
+        <v>-49.4</v>
       </c>
       <c r="E51" s="8">
-        <v>-3.31</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C52" s="6">
-        <v>-47.21</v>
+        <v>-27.02</v>
       </c>
       <c r="D52" s="6">
-        <v>-48.56</v>
-      </c>
-      <c r="E52" s="8">
-        <v>-1.35</v>
+        <v>-26.51</v>
+      </c>
+      <c r="E52" s="7">
+        <v>0.51</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C53" s="6">
-        <v>-27.66</v>
+        <v>-35.55</v>
       </c>
       <c r="D53" s="6">
-        <v>-27.02</v>
-      </c>
-      <c r="E53" s="7">
-        <v>0.64</v>
+        <v>-36.05</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-0.5</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C54" s="6">
-        <v>-35.76</v>
+        <v>-18.14</v>
       </c>
       <c r="D54" s="6">
-        <v>-35.55</v>
+        <v>-18.12</v>
       </c>
       <c r="E54" s="7">
-        <v>0.21</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C55" s="6">
-        <v>-18.53</v>
+        <v>7.42</v>
       </c>
       <c r="D55" s="6">
-        <v>-18.14</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="E55" s="7">
-        <v>0.39</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C56" s="6">
-        <v>10.39</v>
+        <v>33.35</v>
       </c>
       <c r="D56" s="6">
-        <v>7.42</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-2.97</v>
+        <v>36.59</v>
+      </c>
+      <c r="E56" s="7">
+        <v>3.24</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C57" s="6">
-        <v>33.56</v>
+        <v>-10.68</v>
       </c>
       <c r="D57" s="6">
-        <v>33.35</v>
-      </c>
-      <c r="E57" s="8">
-        <v>-0.21</v>
+        <v>-9.56</v>
+      </c>
+      <c r="E57" s="7">
+        <v>1.12</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C58" s="6">
-        <v>-7.87</v>
+        <v>-14.27</v>
       </c>
       <c r="D58" s="6">
-        <v>-10.68</v>
+        <v>-15.64</v>
       </c>
       <c r="E58" s="8">
-        <v>-2.81</v>
+        <v>-1.37</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C59" s="6">
-        <v>-11.6</v>
+        <v>-12.01</v>
       </c>
       <c r="D59" s="6">
-        <v>-14.27</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-2.67</v>
+        <v>-11.41</v>
+      </c>
+      <c r="E59" s="7">
+        <v>0.6</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C60" s="6">
-        <v>-7.85</v>
+        <v>-8.27</v>
       </c>
       <c r="D60" s="6">
-        <v>-12.01</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="E60" s="8">
-        <v>-4.16</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C61" s="6">
-        <v>-8.76</v>
+        <v>-16.38</v>
       </c>
       <c r="D61" s="6">
-        <v>-8.27</v>
+        <v>-14.67</v>
       </c>
       <c r="E61" s="7">
-        <v>0.49</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C62" s="6">
-        <v>-14.89</v>
+        <v>-4.77</v>
       </c>
       <c r="D62" s="6">
-        <v>-16.38</v>
-      </c>
-      <c r="E62" s="8">
-        <v>-1.49</v>
+        <v>-4.26</v>
+      </c>
+      <c r="E62" s="7">
+        <v>0.51</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C63" s="6">
-        <v>-1.78</v>
+        <v>-8.27</v>
       </c>
       <c r="D63" s="6">
-        <v>-4.77</v>
-      </c>
-      <c r="E63" s="8">
-        <v>-2.99</v>
+        <v>-7.4</v>
+      </c>
+      <c r="E63" s="7">
+        <v>0.87</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C64" s="6">
-        <v>-8.960000000000001</v>
+        <v>-6.76</v>
       </c>
       <c r="D64" s="6">
-        <v>-8.27</v>
+        <v>-5.7</v>
       </c>
       <c r="E64" s="7">
-        <v>0.6899999999999999</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C65" s="6">
-        <v>-4.95</v>
+        <v>5.53</v>
       </c>
       <c r="D65" s="6">
-        <v>-6.76</v>
+        <v>4.72</v>
       </c>
       <c r="E65" s="8">
-        <v>-1.81</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C66" s="6">
-        <v>7.09</v>
+        <v>21.68</v>
       </c>
       <c r="D66" s="6">
-        <v>5.53</v>
-      </c>
-      <c r="E66" s="8">
-        <v>-1.56</v>
+        <v>23.38</v>
+      </c>
+      <c r="E66" s="7">
+        <v>1.7</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C67" s="6">
-        <v>19.74</v>
+        <v>1.71</v>
       </c>
       <c r="D67" s="6">
-        <v>21.68</v>
-      </c>
-      <c r="E67" s="7">
-        <v>1.94</v>
+        <v>1.56</v>
+      </c>
+      <c r="E67" s="8">
+        <v>-0.15</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C68" s="6">
-        <v>4.89</v>
+        <v>3.74</v>
       </c>
       <c r="D68" s="6">
-        <v>1.71</v>
-      </c>
-      <c r="E68" s="8">
-        <v>-3.18</v>
+        <v>3.88</v>
+      </c>
+      <c r="E68" s="7">
+        <v>0.14</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C69" s="6">
-        <v>5.85</v>
+        <v>-13.84</v>
       </c>
       <c r="D69" s="6">
-        <v>3.74</v>
+        <v>-14.14</v>
       </c>
       <c r="E69" s="8">
-        <v>-2.11</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C70" s="6">
-        <v>-13.2</v>
+        <v>-10.24</v>
       </c>
       <c r="D70" s="6">
-        <v>-13.84</v>
+        <v>-10.98</v>
       </c>
       <c r="E70" s="8">
-        <v>-0.64</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C71" s="6">
-        <v>-8.029999999999999</v>
+        <v>-9.44</v>
       </c>
       <c r="D71" s="6">
-        <v>-10.24</v>
-      </c>
-      <c r="E71" s="8">
-        <v>-2.21</v>
+        <v>-8.960000000000001</v>
+      </c>
+      <c r="E71" s="7">
+        <v>0.48</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C72" s="6">
-        <v>-8.960000000000001</v>
+        <v>-13.71</v>
       </c>
       <c r="D72" s="6">
-        <v>-9.44</v>
-      </c>
-      <c r="E72" s="8">
-        <v>-0.48</v>
+        <v>-10.02</v>
+      </c>
+      <c r="E72" s="7">
+        <v>3.69</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C73" s="6">
-        <v>-15.74</v>
+        <v>-42.24</v>
       </c>
       <c r="D73" s="6">
-        <v>-13.71</v>
-      </c>
-      <c r="E73" s="7">
-        <v>2.03</v>
+        <v>-42.48</v>
+      </c>
+      <c r="E73" s="8">
+        <v>-0.24</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C74" s="6">
-        <v>-41.79</v>
+        <v>-38.04</v>
       </c>
       <c r="D74" s="6">
-        <v>-42.24</v>
+        <v>-38.61</v>
       </c>
       <c r="E74" s="8">
-        <v>-0.45</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C75" s="6">
-        <v>-36.85</v>
+        <v>-15.68</v>
       </c>
       <c r="D75" s="6">
-        <v>-38.04</v>
-      </c>
-      <c r="E75" s="8">
-        <v>-1.19</v>
+        <v>-14.98</v>
+      </c>
+      <c r="E75" s="7">
+        <v>0.7</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C76" s="6">
-        <v>-14.82</v>
+        <v>-19.47</v>
       </c>
       <c r="D76" s="6">
-        <v>-15.68</v>
+        <v>-19.54</v>
       </c>
       <c r="E76" s="8">
-        <v>-0.86</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C77" s="6">
-        <v>-19.86</v>
+        <v>-39.18</v>
       </c>
       <c r="D77" s="6">
-        <v>-19.47</v>
-      </c>
-      <c r="E77" s="7">
-        <v>0.39</v>
+        <v>-39.27</v>
+      </c>
+      <c r="E77" s="8">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C78" s="6">
-        <v>-38.12</v>
+        <v>-40.36</v>
       </c>
       <c r="D78" s="6">
-        <v>-39.18</v>
+        <v>-40.9</v>
       </c>
       <c r="E78" s="8">
-        <v>-1.06</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C79" s="6">
-        <v>-39.79</v>
+        <v>-20.81</v>
       </c>
       <c r="D79" s="6">
-        <v>-40.36</v>
+        <v>-20.84</v>
       </c>
       <c r="E79" s="8">
-        <v>-0.57</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C80" s="6">
-        <v>-20.31</v>
+        <v>-14.33</v>
       </c>
       <c r="D80" s="6">
-        <v>-20.81</v>
+        <v>-15.01</v>
       </c>
       <c r="E80" s="8">
-        <v>-0.5</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C81" s="6">
-        <v>-12.86</v>
+        <v>-29.54</v>
       </c>
       <c r="D81" s="6">
-        <v>-14.33</v>
+        <v>-29.99</v>
       </c>
       <c r="E81" s="8">
-        <v>-1.47</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B82" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C82" s="6">
-        <v>-28.49</v>
+        <v>-3.37</v>
       </c>
       <c r="D82" s="6">
-        <v>-29.54</v>
+        <v>-3.52</v>
       </c>
       <c r="E82" s="8">
-        <v>-1.05</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B83" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C83" s="6">
-        <v>-2.89</v>
+        <v>-49.02</v>
       </c>
       <c r="D83" s="6">
-        <v>-3.37</v>
+        <v>-49.39</v>
       </c>
       <c r="E83" s="8">
-        <v>-0.48</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B84" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C84" s="6">
-        <v>-48.32</v>
+        <v>-40.13</v>
       </c>
       <c r="D84" s="6">
-        <v>-49.02</v>
+        <v>-41.19</v>
       </c>
       <c r="E84" s="8">
-        <v>-0.7</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B85" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C85" s="6">
-        <v>-41.03</v>
+        <v>-36.47</v>
       </c>
       <c r="D85" s="6">
-        <v>-40.13</v>
-      </c>
-      <c r="E85" s="7">
-        <v>0.9</v>
+        <v>-37.93</v>
+      </c>
+      <c r="E85" s="8">
+        <v>-1.46</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B86" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C86" s="6">
-        <v>-35.81</v>
+        <v>-25.01</v>
       </c>
       <c r="D86" s="6">
-        <v>-36.47</v>
+        <v>-26.45</v>
       </c>
       <c r="E86" s="8">
-        <v>-0.66</v>
+        <v>-1.44</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="5" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C87" s="6">
-        <v>-24.83</v>
+        <v>716.2</v>
       </c>
       <c r="D87" s="6">
-        <v>-25.01</v>
-      </c>
-      <c r="E87" s="8">
-        <v>-0.18</v>
+        <v>720</v>
+      </c>
+      <c r="E87" s="7">
+        <v>3.8</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B88" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C88" s="6">
-        <v>720</v>
+        <v>933.2</v>
       </c>
       <c r="D88" s="6">
-        <v>716.2</v>
-      </c>
-      <c r="E88" s="8">
-        <v>-3.8</v>
+        <v>973.1</v>
+      </c>
+      <c r="E88" s="7">
+        <v>39.9</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B89" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C89" s="6">
-        <v>911.25</v>
+        <v>206.15</v>
       </c>
       <c r="D89" s="6">
-        <v>933.2</v>
-      </c>
-      <c r="E89" s="7">
-        <v>21.95</v>
+        <v>205.29</v>
+      </c>
+      <c r="E89" s="8">
+        <v>-0.86</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B90" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C90" s="6">
-        <v>208.82</v>
+        <v>613.35</v>
       </c>
       <c r="D90" s="6">
-        <v>206.15</v>
+        <v>607.7</v>
       </c>
       <c r="E90" s="8">
-        <v>-2.67</v>
+        <v>-5.65</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B91" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C91" s="6">
-        <v>625.1</v>
+        <v>1738.5</v>
       </c>
       <c r="D91" s="6">
-        <v>613.35</v>
-      </c>
-      <c r="E91" s="8">
-        <v>-11.75</v>
+        <v>1752.8</v>
+      </c>
+      <c r="E91" s="7">
+        <v>14.3</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B92" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C92" s="6">
-        <v>1756.1</v>
+        <v>1015</v>
       </c>
       <c r="D92" s="6">
-        <v>1738.5</v>
+        <v>1014.1</v>
       </c>
       <c r="E92" s="8">
-        <v>-17.6</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C93" s="6">
-        <v>1010</v>
+        <v>3497</v>
       </c>
       <c r="D93" s="6">
-        <v>1015</v>
-      </c>
-      <c r="E93" s="7">
-        <v>5</v>
+        <v>3492</v>
+      </c>
+      <c r="E93" s="8">
+        <v>-5</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B94" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C94" s="6">
-        <v>3558</v>
+        <v>627.8</v>
       </c>
       <c r="D94" s="6">
-        <v>3497</v>
+        <v>622.05</v>
       </c>
       <c r="E94" s="8">
-        <v>-61</v>
+        <v>-5.75</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C95" s="6">
-        <v>633.7</v>
+        <v>365.7</v>
       </c>
       <c r="D95" s="6">
-        <v>627.8</v>
+        <v>365.55</v>
       </c>
       <c r="E95" s="8">
-        <v>-5.9</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B96" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C96" s="6">
-        <v>368</v>
+        <v>185.61</v>
       </c>
       <c r="D96" s="6">
-        <v>365.7</v>
+        <v>184.15</v>
       </c>
       <c r="E96" s="8">
-        <v>-2.3</v>
+        <v>-1.46</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C97" s="6">
-        <v>188.79</v>
+        <v>2270</v>
       </c>
       <c r="D97" s="6">
-        <v>185.61</v>
+        <v>2255.5</v>
       </c>
       <c r="E97" s="8">
-        <v>-3.18</v>
+        <v>-14.5</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B98" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C98" s="6">
-        <v>2304</v>
+        <v>4995</v>
       </c>
       <c r="D98" s="6">
-        <v>2270</v>
+        <v>4987</v>
       </c>
       <c r="E98" s="8">
-        <v>-34</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C99" s="6">
-        <v>5020</v>
+        <v>2814.5</v>
       </c>
       <c r="D99" s="6">
-        <v>4995</v>
+        <v>2793.6</v>
       </c>
       <c r="E99" s="8">
-        <v>-25</v>
+        <v>-20.9</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B100" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C100" s="6">
-        <v>2853</v>
+        <v>235.13</v>
       </c>
       <c r="D100" s="6">
-        <v>2814.5</v>
+        <v>230.98</v>
       </c>
       <c r="E100" s="8">
-        <v>-38.5</v>
+        <v>-4.15</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C101" s="6">
-        <v>231.59</v>
+        <v>37.35</v>
       </c>
       <c r="D101" s="6">
-        <v>235.13</v>
-      </c>
-      <c r="E101" s="7">
-        <v>3.54</v>
+        <v>36.49</v>
+      </c>
+      <c r="E101" s="8">
+        <v>-0.86</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B102" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C102" s="6">
-        <v>37.74</v>
+        <v>1167.2</v>
       </c>
       <c r="D102" s="6">
-        <v>37.35</v>
+        <v>1144.8</v>
       </c>
       <c r="E102" s="8">
-        <v>-0.39</v>
+        <v>-22.4</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="5" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C103" s="6">
-        <v>1170</v>
+        <v>81</v>
       </c>
       <c r="D103" s="6">
-        <v>1167.2</v>
+        <v>74</v>
       </c>
       <c r="E103" s="8">
-        <v>-2.8</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B104" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C104" s="6">
-        <v>74</v>
+        <v>7</v>
       </c>
       <c r="D104" s="6">
-        <v>81</v>
+        <v>13</v>
       </c>
       <c r="E104" s="7">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B105" s="5" t="s">
         <v>13</v>
@@ -4670,688 +4658,586 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B106" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C106" s="6">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="D106" s="6">
-        <v>19</v>
-      </c>
-      <c r="E106" s="8">
-        <v>-13</v>
+        <v>81</v>
+      </c>
+      <c r="E106" s="7">
+        <v>7</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B107" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C107" s="6">
-        <v>81</v>
+        <v>13</v>
       </c>
       <c r="D107" s="6">
-        <v>74</v>
-      </c>
-      <c r="E107" s="8">
-        <v>-7</v>
+        <v>26</v>
+      </c>
+      <c r="E107" s="7">
+        <v>13</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="5" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="B108" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C108" s="6">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="D108" s="6">
-        <v>56</v>
-      </c>
-      <c r="E108" s="7">
-        <v>6</v>
+        <v>19</v>
+      </c>
+      <c r="E108" s="8">
+        <v>-7</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C109" s="6">
-        <v>68</v>
+        <v>45.72</v>
       </c>
       <c r="D109" s="6">
-        <v>62</v>
-      </c>
-      <c r="E109" s="8">
-        <v>-6</v>
+        <v>47.63</v>
+      </c>
+      <c r="E109" s="7">
+        <v>1.91</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="5" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C110" s="6">
-        <v>62</v>
+        <v>48.52</v>
       </c>
       <c r="D110" s="6">
-        <v>68</v>
+        <v>55.07</v>
       </c>
       <c r="E110" s="7">
-        <v>6</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="5" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C111" s="6">
-        <v>56</v>
+        <v>34.47</v>
       </c>
       <c r="D111" s="6">
-        <v>50</v>
+        <v>33.15</v>
       </c>
       <c r="E111" s="8">
-        <v>-6</v>
+        <v>-1.32</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="5" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C112" s="6">
-        <v>26</v>
+        <v>31.77</v>
       </c>
       <c r="D112" s="6">
-        <v>32</v>
-      </c>
-      <c r="E112" s="7">
-        <v>6</v>
+        <v>30.08</v>
+      </c>
+      <c r="E112" s="8">
+        <v>-1.69</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="5" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C113" s="6">
-        <v>7</v>
+        <v>51.38</v>
       </c>
       <c r="D113" s="6">
-        <v>26</v>
+        <v>53.5</v>
       </c>
       <c r="E113" s="7">
-        <v>19</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B114" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C114" s="6">
-        <v>47.32</v>
+        <v>35.3</v>
       </c>
       <c r="D114" s="6">
-        <v>45.72</v>
+        <v>35.06</v>
       </c>
       <c r="E114" s="8">
-        <v>-1.6</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B115" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C115" s="6">
-        <v>44.38</v>
+        <v>35.85</v>
       </c>
       <c r="D115" s="6">
-        <v>48.52</v>
-      </c>
-      <c r="E115" s="7">
-        <v>4.14</v>
+        <v>35.53</v>
+      </c>
+      <c r="E115" s="8">
+        <v>-0.32</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="5" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C116" s="6">
-        <v>38.91</v>
+        <v>35.41</v>
       </c>
       <c r="D116" s="6">
-        <v>34.47</v>
+        <v>32.86</v>
       </c>
       <c r="E116" s="8">
-        <v>-4.44</v>
+        <v>-2.55</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C117" s="6">
-        <v>35.63</v>
+        <v>45.71</v>
       </c>
       <c r="D117" s="6">
-        <v>31.77</v>
+        <v>45.57</v>
       </c>
       <c r="E117" s="8">
-        <v>-3.86</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C118" s="6">
-        <v>54.21</v>
+        <v>48.19</v>
       </c>
       <c r="D118" s="6">
-        <v>51.38</v>
+        <v>45.09</v>
       </c>
       <c r="E118" s="8">
-        <v>-2.83</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C119" s="6">
-        <v>32.95</v>
+        <v>44.62</v>
       </c>
       <c r="D119" s="6">
-        <v>35.3</v>
-      </c>
-      <c r="E119" s="7">
-        <v>2.35</v>
+        <v>43.18</v>
+      </c>
+      <c r="E119" s="8">
+        <v>-1.44</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="5" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C120" s="6">
-        <v>39.97</v>
+        <v>49.6</v>
       </c>
       <c r="D120" s="6">
-        <v>35.85</v>
+        <v>48.72</v>
       </c>
       <c r="E120" s="8">
-        <v>-4.12</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="5" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C121" s="6">
-        <v>38.23</v>
+        <v>35.78</v>
       </c>
       <c r="D121" s="6">
-        <v>35.41</v>
+        <v>33.8</v>
       </c>
       <c r="E121" s="8">
-        <v>-2.82</v>
+        <v>-1.98</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="5" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B122" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C122" s="6">
-        <v>47.91</v>
+        <v>57.24</v>
       </c>
       <c r="D122" s="6">
-        <v>45.71</v>
+        <v>50.19</v>
       </c>
       <c r="E122" s="8">
-        <v>-2.2</v>
+        <v>-7.05</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="5" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B123" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C123" s="6">
-        <v>55.97</v>
+        <v>40.52</v>
       </c>
       <c r="D123" s="6">
-        <v>48.19</v>
+        <v>35.46</v>
       </c>
       <c r="E123" s="8">
-        <v>-7.78</v>
+        <v>-5.06</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="5" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B124" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C124" s="6">
-        <v>48.09</v>
+        <v>33.79</v>
       </c>
       <c r="D124" s="6">
-        <v>44.62</v>
+        <v>30.47</v>
       </c>
       <c r="E124" s="8">
-        <v>-3.47</v>
+        <v>-3.32</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="5" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C125" s="6">
-        <v>52.35</v>
+        <v>39.89</v>
       </c>
       <c r="D125" s="6">
-        <v>49.6</v>
+        <v>-35.82</v>
       </c>
       <c r="E125" s="8">
-        <v>-2.75</v>
+        <v>-75.70999999999999</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="5" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C126" s="6">
-        <v>39.76</v>
+        <v>-54.15</v>
       </c>
       <c r="D126" s="6">
-        <v>35.78</v>
-      </c>
-      <c r="E126" s="8">
-        <v>-3.98</v>
+        <v>295.88</v>
+      </c>
+      <c r="E126" s="7">
+        <v>350.03</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="5" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C127" s="6">
-        <v>51.88</v>
+        <v>-34.34</v>
       </c>
       <c r="D127" s="6">
-        <v>57.24</v>
-      </c>
-      <c r="E127" s="7">
-        <v>5.36</v>
+        <v>-45.05</v>
+      </c>
+      <c r="E127" s="8">
+        <v>-10.71</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="5" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C128" s="6">
-        <v>43.11</v>
+        <v>-32.5</v>
       </c>
       <c r="D128" s="6">
-        <v>40.52</v>
+        <v>-47.39</v>
       </c>
       <c r="E128" s="8">
-        <v>-2.59</v>
+        <v>-14.89</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="5" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C129" s="6">
-        <v>34.22</v>
+        <v>-28.75</v>
       </c>
       <c r="D129" s="6">
-        <v>33.79</v>
-      </c>
-      <c r="E129" s="8">
-        <v>-0.43</v>
+        <v>-1.53</v>
+      </c>
+      <c r="E129" s="7">
+        <v>27.22</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B130" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C130" s="6">
-        <v>-1.31</v>
+        <v>13.86</v>
       </c>
       <c r="D130" s="6">
-        <v>39.89</v>
-      </c>
-      <c r="E130" s="7">
-        <v>41.2</v>
+        <v>-41.15</v>
+      </c>
+      <c r="E130" s="8">
+        <v>-55.01</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B131" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C131" s="6">
-        <v>-67.81999999999999</v>
+        <v>-11.67</v>
       </c>
       <c r="D131" s="6">
-        <v>-54.15</v>
-      </c>
-      <c r="E131" s="7">
-        <v>13.67</v>
+        <v>-45.63</v>
+      </c>
+      <c r="E131" s="8">
+        <v>-33.96</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="5" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B132" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C132" s="6">
-        <v>-55.02</v>
+        <v>-74.25</v>
       </c>
       <c r="D132" s="6">
-        <v>-34.34</v>
+        <v>-38.69</v>
       </c>
       <c r="E132" s="7">
-        <v>20.68</v>
+        <v>35.56</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B133" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C133" s="6">
-        <v>36.62</v>
+        <v>-11</v>
       </c>
       <c r="D133" s="6">
-        <v>-32.5</v>
+        <v>-48.17</v>
       </c>
       <c r="E133" s="8">
-        <v>-69.12</v>
+        <v>-37.17</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="5" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B134" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C134" s="6">
-        <v>7.7</v>
+        <v>-13.61</v>
       </c>
       <c r="D134" s="6">
-        <v>-28.75</v>
+        <v>-16.01</v>
       </c>
       <c r="E134" s="8">
-        <v>-36.45</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="5" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B135" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C135" s="6">
-        <v>-15.3</v>
+        <v>-38.66</v>
       </c>
       <c r="D135" s="6">
-        <v>13.86</v>
-      </c>
-      <c r="E135" s="7">
-        <v>29.16</v>
+        <v>-42.34</v>
+      </c>
+      <c r="E135" s="8">
+        <v>-3.68</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="5" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B136" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C136" s="6">
-        <v>12.32</v>
+        <v>32.59</v>
       </c>
       <c r="D136" s="6">
-        <v>-11.67</v>
+        <v>-16.03</v>
       </c>
       <c r="E136" s="8">
-        <v>-23.99</v>
+        <v>-48.62</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="5" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B137" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C137" s="6">
-        <v>-64.19</v>
+        <v>31.71</v>
       </c>
       <c r="D137" s="6">
-        <v>-74.25</v>
+        <v>-35.92</v>
       </c>
       <c r="E137" s="8">
-        <v>-10.06</v>
+        <v>-67.63</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="5" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B138" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C138" s="6">
-        <v>-29.01</v>
+        <v>-65.84</v>
       </c>
       <c r="D138" s="6">
-        <v>-11</v>
+        <v>-60.02</v>
       </c>
       <c r="E138" s="7">
-        <v>18.01</v>
+        <v>5.82</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="5" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B139" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C139" s="6">
-        <v>39.74</v>
+        <v>-62.28</v>
       </c>
       <c r="D139" s="6">
-        <v>-12.12</v>
-      </c>
-      <c r="E139" s="8">
-        <v>-51.86</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5">
-      <c r="A140" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B140" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C140" s="6">
-        <v>-3.84</v>
-      </c>
-      <c r="D140" s="6">
-        <v>-13.61</v>
-      </c>
-      <c r="E140" s="8">
-        <v>-9.77</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5">
-      <c r="A141" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B141" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C141" s="6">
-        <v>-62.52</v>
-      </c>
-      <c r="D141" s="6">
-        <v>-38.66</v>
-      </c>
-      <c r="E141" s="7">
-        <v>23.86</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5">
-      <c r="A142" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B142" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C142" s="6">
-        <v>-39.36</v>
-      </c>
-      <c r="D142" s="6">
-        <v>32.59</v>
-      </c>
-      <c r="E142" s="7">
-        <v>71.95</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5">
-      <c r="A143" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B143" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C143" s="6">
-        <v>-62.88</v>
-      </c>
-      <c r="D143" s="6">
-        <v>31.71</v>
-      </c>
-      <c r="E143" s="7">
-        <v>94.59</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5">
-      <c r="A144" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B144" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C144" s="6">
-        <v>-64.44</v>
-      </c>
-      <c r="D144" s="6">
-        <v>-65.84</v>
-      </c>
-      <c r="E144" s="8">
-        <v>-1.4</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5">
-      <c r="A145" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B145" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C145" s="6">
-        <v>-57.13</v>
-      </c>
-      <c r="D145" s="6">
-        <v>-62.28</v>
-      </c>
-      <c r="E145" s="8">
-        <v>-5.15</v>
+        <v>-21.83</v>
+      </c>
+      <c r="E139" s="7">
+        <v>40.45</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5375,28 +5261,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>81</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -5410,16 +5296,16 @@
         <v>16</v>
       </c>
       <c r="D2" s="11">
-        <v>42.1</v>
+        <v>41</v>
       </c>
       <c r="E2" s="11">
         <v>20</v>
       </c>
       <c r="F2" s="11">
-        <v>-4.5</v>
+        <v>-5.3</v>
       </c>
       <c r="G2" s="11">
-        <v>-2</v>
+        <v>-1.5</v>
       </c>
       <c r="H2" s="11">
         <v>53.1</v>
@@ -5559,34 +5445,34 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="14">
-        <v>0.3984</v>
+        <v>0.395</v>
       </c>
       <c r="B2" s="14">
-        <v>0.39</v>
+        <v>0.3861</v>
       </c>
       <c r="C2" s="14">
-        <v>0.2366</v>
+        <v>0.2305</v>
       </c>
       <c r="D2" s="14">
-        <v>0.2313</v>
+        <v>0.2211</v>
       </c>
       <c r="E2" s="14">
-        <v>0.2</v>
+        <v>0.197</v>
       </c>
       <c r="F2" s="14">
-        <v>0.1308</v>
+        <v>0.1293</v>
       </c>
       <c r="G2" s="14">
-        <v>0.1232</v>
+        <v>0.1217</v>
       </c>
       <c r="H2" s="14">
-        <v>0.08539999999999999</v>
+        <v>0.08349999999999999</v>
       </c>
       <c r="I2" s="14">
-        <v>0.0604</v>
+        <v>0.063</v>
       </c>
       <c r="J2" s="14">
-        <v>0.0403</v>
+        <v>0.0374</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -5611,22 +5497,22 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="14">
-        <v>0.0196</v>
+        <v>0.0052</v>
       </c>
       <c r="B4" s="14">
-        <v>0.0012</v>
+        <v>-0.0059</v>
       </c>
       <c r="C4" s="14">
-        <v>-0.0435</v>
+        <v>-0.0474</v>
       </c>
       <c r="D4" s="14">
-        <v>-0.0563</v>
+        <v>-0.0544</v>
       </c>
       <c r="E4" s="14">
-        <v>-0.0565</v>
+        <v>-0.0564</v>
       </c>
       <c r="F4" s="14">
-        <v>-0.07400000000000001</v>
+        <v>-0.0731</v>
       </c>
     </row>
   </sheetData>

--- a/TATA_GROUP_Technical_Metrics.xlsx
+++ b/TATA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="93">
   <si>
     <t>Symbol</t>
   </si>
@@ -214,55 +214,52 @@
     <t>Curr Value</t>
   </si>
   <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>28.7 → 33.9</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>28.7</t>
+  </si>
+  <si>
+    <t>33.9</t>
+  </si>
+  <si>
+    <t>29.3 → 32.4</t>
+  </si>
+  <si>
+    <t>29.3</t>
+  </si>
+  <si>
+    <t>32.4</t>
+  </si>
+  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>45.6 → 50.6</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>45.6</t>
+    <t>52.4 → 48.8</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>52.4</t>
+  </si>
+  <si>
+    <t>48.8</t>
+  </si>
+  <si>
+    <t>50.6 → 47.4</t>
   </si>
   <si>
     <t>50.6</t>
   </si>
   <si>
-    <t>45.1 → 54.9</t>
-  </si>
-  <si>
-    <t>45.1</t>
-  </si>
-  <si>
-    <t>54.9</t>
-  </si>
-  <si>
-    <t>48.7 → 50.8</t>
-  </si>
-  <si>
-    <t>48.7</t>
-  </si>
-  <si>
-    <t>50.8</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>50.2 → 46.9</t>
-  </si>
-  <si>
-    <t>50.2</t>
-  </si>
-  <si>
-    <t>46.9</t>
+    <t>47.4</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -475,8 +472,8 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -988,10 +985,10 @@
         <v>53</v>
       </c>
       <c r="C2">
-        <v>722.75</v>
+        <v>715.75</v>
       </c>
       <c r="D2">
-        <v>0.38</v>
+        <v>-0.97</v>
       </c>
       <c r="E2">
         <v>790.85</v>
@@ -1000,46 +997,46 @@
         <v>570.95</v>
       </c>
       <c r="G2">
-        <v>-8.609999999999999</v>
+        <v>-9.5</v>
       </c>
       <c r="H2">
-        <v>26.59</v>
+        <v>25.36</v>
       </c>
       <c r="I2">
-        <v>-0.68</v>
+        <v>-2.22</v>
       </c>
       <c r="J2">
-        <v>-0.17</v>
+        <v>-1.14</v>
       </c>
       <c r="K2">
-        <v>10.23</v>
+        <v>5.34</v>
       </c>
       <c r="L2">
-        <v>-6.71</v>
+        <v>-7.97</v>
       </c>
       <c r="M2">
-        <v>37.95</v>
+        <v>37.16</v>
       </c>
       <c r="N2">
         <v>74</v>
       </c>
       <c r="O2">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="P2">
-        <v>722.1900000000001</v>
+        <v>718.9400000000001</v>
       </c>
       <c r="Q2">
-        <v>723.47</v>
+        <v>723.17</v>
       </c>
       <c r="R2">
-        <v>729.96</v>
+        <v>729.86</v>
       </c>
       <c r="S2">
-        <v>688.64</v>
+        <v>688.62</v>
       </c>
       <c r="T2">
-        <v>4.95</v>
+        <v>3.94</v>
       </c>
       <c r="U2" t="s">
         <v>54</v>
@@ -1054,34 +1051,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>49.03</v>
+        <v>45.68</v>
       </c>
       <c r="Z2">
-        <v>-1.64</v>
+        <v>-2.1</v>
       </c>
       <c r="AA2">
-        <v>-1.21</v>
+        <v>-1.39</v>
       </c>
       <c r="AB2">
-        <v>-0.43</v>
+        <v>-0.71</v>
       </c>
       <c r="AC2">
-        <v>55.44</v>
+        <v>55.38</v>
       </c>
       <c r="AD2">
-        <v>56.42</v>
+        <v>54.45</v>
       </c>
       <c r="AE2">
-        <v>14.54</v>
+        <v>14.23</v>
       </c>
       <c r="AF2">
-        <v>-43.48</v>
+        <v>-34.71</v>
       </c>
       <c r="AG2">
-        <v>738.29</v>
+        <v>738.37</v>
       </c>
       <c r="AH2">
-        <v>708.64</v>
+        <v>707.96</v>
       </c>
       <c r="AI2">
         <v>700.95</v>
@@ -1090,7 +1087,7 @@
         <v>56</v>
       </c>
       <c r="AK2">
-        <v>14.15</v>
+        <v>13.68</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1101,10 +1098,10 @@
         <v>53</v>
       </c>
       <c r="C3">
-        <v>958.3</v>
+        <v>937.55</v>
       </c>
       <c r="D3">
-        <v>-1.52</v>
+        <v>-2.17</v>
       </c>
       <c r="E3">
         <v>1081.5</v>
@@ -1113,46 +1110,46 @@
         <v>505.36</v>
       </c>
       <c r="G3">
-        <v>-11.39</v>
+        <v>-13.31</v>
       </c>
       <c r="H3">
-        <v>89.63</v>
+        <v>85.52</v>
       </c>
       <c r="I3">
-        <v>3.08</v>
+        <v>0.41</v>
       </c>
       <c r="J3">
-        <v>-3.7</v>
+        <v>-3.75</v>
       </c>
       <c r="K3">
-        <v>35.85</v>
+        <v>29.76</v>
       </c>
       <c r="L3">
-        <v>19.1</v>
+        <v>15.41</v>
       </c>
       <c r="M3">
-        <v>12.11</v>
+        <v>11.9</v>
       </c>
       <c r="N3">
         <v>93</v>
       </c>
       <c r="O3">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="P3">
-        <v>941.92</v>
+        <v>942.6799999999999</v>
       </c>
       <c r="Q3">
-        <v>952.24</v>
+        <v>946.74</v>
       </c>
       <c r="R3">
-        <v>941.88</v>
+        <v>942.0700000000001</v>
       </c>
       <c r="S3">
-        <v>755.04</v>
+        <v>755.5</v>
       </c>
       <c r="T3">
-        <v>26.92</v>
+        <v>24.1</v>
       </c>
       <c r="U3" t="s">
         <v>55</v>
@@ -1167,34 +1164,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>52.4</v>
+        <v>48.84</v>
       </c>
       <c r="Z3">
-        <v>0.13</v>
+        <v>-0.49</v>
       </c>
       <c r="AA3">
-        <v>0.48</v>
+        <v>0.28</v>
       </c>
       <c r="AB3">
-        <v>-0.34</v>
+        <v>-0.77</v>
       </c>
       <c r="AC3">
-        <v>76.14</v>
+        <v>72.27</v>
       </c>
       <c r="AD3">
-        <v>50.1</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="AE3">
-        <v>46.34</v>
+        <v>45.76</v>
       </c>
       <c r="AF3">
-        <v>-28.85</v>
+        <v>-69.2</v>
       </c>
       <c r="AG3">
-        <v>1047.53</v>
+        <v>1030.93</v>
       </c>
       <c r="AH3">
-        <v>856.95</v>
+        <v>862.55</v>
       </c>
       <c r="AI3">
         <v>1054.09</v>
@@ -1203,7 +1200,7 @@
         <v>57</v>
       </c>
       <c r="AK3">
-        <v>21.08</v>
+        <v>21.15</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1214,37 +1211,37 @@
         <v>53</v>
       </c>
       <c r="C4">
-        <v>204.01</v>
+        <v>203.06</v>
       </c>
       <c r="D4">
-        <v>-0.62</v>
+        <v>-0.47</v>
       </c>
       <c r="E4">
-        <v>356.93</v>
+        <v>342.51</v>
       </c>
       <c r="F4">
-        <v>204.01</v>
+        <v>203.06</v>
       </c>
       <c r="G4">
-        <v>-42.84</v>
+        <v>-40.71</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>-2.62</v>
+        <v>-3.23</v>
       </c>
       <c r="J4">
-        <v>-3.54</v>
+        <v>-3.03</v>
       </c>
       <c r="K4">
-        <v>-8.449999999999999</v>
+        <v>-11.24</v>
       </c>
       <c r="L4">
-        <v>-42.15</v>
+        <v>-43.11</v>
       </c>
       <c r="M4">
-        <v>-5.81</v>
+        <v>-5.95</v>
       </c>
       <c r="N4">
         <v>26</v>
@@ -1253,19 +1250,19 @@
         <v>10</v>
       </c>
       <c r="P4">
-        <v>206.82</v>
+        <v>205.47</v>
       </c>
       <c r="Q4">
-        <v>210.2</v>
+        <v>209.7</v>
       </c>
       <c r="R4">
-        <v>218.17</v>
+        <v>217.68</v>
       </c>
       <c r="S4">
-        <v>244.27</v>
+        <v>244.05</v>
       </c>
       <c r="T4">
-        <v>-16.48</v>
+        <v>-16.8</v>
       </c>
       <c r="U4" t="s">
         <v>54</v>
@@ -1280,43 +1277,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>31.25</v>
+        <v>29.87</v>
       </c>
       <c r="Z4">
-        <v>-3.33</v>
+        <v>-3.49</v>
       </c>
       <c r="AA4">
-        <v>-3.21</v>
+        <v>-3.27</v>
       </c>
       <c r="AB4">
-        <v>-0.12</v>
+        <v>-0.22</v>
       </c>
       <c r="AC4">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AD4">
-        <v>21.45</v>
+        <v>7.49</v>
       </c>
       <c r="AE4">
-        <v>4.29</v>
+        <v>4.2</v>
       </c>
       <c r="AF4">
-        <v>-40.01</v>
+        <v>-17.65</v>
       </c>
       <c r="AG4">
-        <v>216.06</v>
+        <v>216.22</v>
       </c>
       <c r="AH4">
-        <v>204.34</v>
+        <v>203.19</v>
       </c>
       <c r="AI4">
-        <v>217.04</v>
+        <v>216.14</v>
       </c>
       <c r="AJ4" t="s">
         <v>57</v>
       </c>
       <c r="AK4">
-        <v>32.36</v>
+        <v>35.36</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1327,10 +1324,10 @@
         <v>53</v>
       </c>
       <c r="C5">
-        <v>603.05</v>
+        <v>610.55</v>
       </c>
       <c r="D5">
-        <v>-0.77</v>
+        <v>1.24</v>
       </c>
       <c r="E5">
         <v>989.9299999999999</v>
@@ -1339,46 +1336,46 @@
         <v>574.42</v>
       </c>
       <c r="G5">
-        <v>-39.08</v>
+        <v>-38.32</v>
       </c>
       <c r="H5">
-        <v>4.98</v>
+        <v>6.29</v>
       </c>
       <c r="I5">
-        <v>-4.87</v>
+        <v>-4.8</v>
       </c>
       <c r="J5">
-        <v>-9.82</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="K5">
-        <v>-18.64</v>
+        <v>-18.15</v>
       </c>
       <c r="L5">
-        <v>-34.4</v>
+        <v>-34.28</v>
       </c>
       <c r="M5">
-        <v>-4.81</v>
+        <v>-4.77</v>
       </c>
       <c r="N5">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="O5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P5">
-        <v>618.11</v>
+        <v>611.95</v>
       </c>
       <c r="Q5">
-        <v>637.79</v>
+        <v>634.72</v>
       </c>
       <c r="R5">
-        <v>667.99</v>
+        <v>666.42</v>
       </c>
       <c r="S5">
-        <v>706.67</v>
+        <v>705.76</v>
       </c>
       <c r="T5">
-        <v>-14.66</v>
+        <v>-13.49</v>
       </c>
       <c r="U5" t="s">
         <v>54</v>
@@ -1393,34 +1390,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>28.73</v>
+        <v>33.89</v>
       </c>
       <c r="Z5">
-        <v>-15.82</v>
+        <v>-15.97</v>
       </c>
       <c r="AA5">
-        <v>-13.77</v>
+        <v>-14.21</v>
       </c>
       <c r="AB5">
-        <v>-2.05</v>
+        <v>-1.75</v>
       </c>
       <c r="AC5">
-        <v>24.97</v>
+        <v>28.13</v>
       </c>
       <c r="AD5">
-        <v>37.85</v>
+        <v>29.45</v>
       </c>
       <c r="AE5">
-        <v>15.26</v>
+        <v>15.17</v>
       </c>
       <c r="AF5">
-        <v>-47.8</v>
+        <v>15.5</v>
       </c>
       <c r="AG5">
-        <v>676.87</v>
+        <v>672.09</v>
       </c>
       <c r="AH5">
-        <v>598.71</v>
+        <v>597.35</v>
       </c>
       <c r="AI5">
         <v>650.02</v>
@@ -1429,7 +1426,7 @@
         <v>57</v>
       </c>
       <c r="AK5">
-        <v>20.51</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1440,10 +1437,10 @@
         <v>53</v>
       </c>
       <c r="C6">
-        <v>1772.8</v>
+        <v>1764.4</v>
       </c>
       <c r="D6">
-        <v>1.14</v>
+        <v>-0.47</v>
       </c>
       <c r="E6">
         <v>2061.7</v>
@@ -1452,46 +1449,46 @@
         <v>1347.9</v>
       </c>
       <c r="G6">
-        <v>-14.01</v>
+        <v>-14.42</v>
       </c>
       <c r="H6">
-        <v>31.52</v>
+        <v>30.9</v>
       </c>
       <c r="I6">
-        <v>3.67</v>
+        <v>4.01</v>
       </c>
       <c r="J6">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="K6">
-        <v>-9.83</v>
+        <v>-10.28</v>
       </c>
       <c r="L6">
-        <v>14.4</v>
+        <v>14.05</v>
       </c>
       <c r="M6">
-        <v>6.73</v>
+        <v>6.82</v>
       </c>
       <c r="N6">
         <v>81</v>
       </c>
       <c r="O6">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P6">
-        <v>1743.32</v>
+        <v>1756.92</v>
       </c>
       <c r="Q6">
-        <v>1708.84</v>
+        <v>1709.15</v>
       </c>
       <c r="R6">
-        <v>1768.76</v>
+        <v>1765.29</v>
       </c>
       <c r="S6">
-        <v>1714.31</v>
+        <v>1713.73</v>
       </c>
       <c r="T6">
-        <v>3.41</v>
+        <v>2.96</v>
       </c>
       <c r="U6" t="s">
         <v>54</v>
@@ -1506,34 +1503,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>56.37</v>
+        <v>54.84</v>
       </c>
       <c r="Z6">
-        <v>-3.74</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="AA6">
-        <v>-17.12</v>
+        <v>-13.83</v>
       </c>
       <c r="AB6">
-        <v>13.38</v>
+        <v>13.14</v>
       </c>
       <c r="AC6">
-        <v>94.95999999999999</v>
+        <v>96.52</v>
       </c>
       <c r="AD6">
-        <v>92.04000000000001</v>
+        <v>95.48</v>
       </c>
       <c r="AE6">
-        <v>46.33</v>
+        <v>45.05</v>
       </c>
       <c r="AF6">
-        <v>-21.58</v>
+        <v>-28.53</v>
       </c>
       <c r="AG6">
-        <v>1779.7</v>
+        <v>1780.97</v>
       </c>
       <c r="AH6">
-        <v>1637.97</v>
+        <v>1637.32</v>
       </c>
       <c r="AI6">
         <v>1813.9</v>
@@ -1542,7 +1539,7 @@
         <v>57</v>
       </c>
       <c r="AK6">
-        <v>24.63</v>
+        <v>25.26</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1553,58 +1550,58 @@
         <v>53</v>
       </c>
       <c r="C7">
-        <v>1001</v>
+        <v>999.6</v>
       </c>
       <c r="D7">
-        <v>-1.29</v>
+        <v>-0.14</v>
       </c>
       <c r="E7">
         <v>1260.34</v>
       </c>
       <c r="F7">
-        <v>1001</v>
+        <v>999.6</v>
       </c>
       <c r="G7">
-        <v>-20.58</v>
+        <v>-20.69</v>
       </c>
       <c r="H7">
         <v>0</v>
       </c>
       <c r="I7">
-        <v>-1.09</v>
+        <v>-1.92</v>
       </c>
       <c r="J7">
-        <v>-7.14</v>
+        <v>-5.87</v>
       </c>
       <c r="K7">
-        <v>-9.710000000000001</v>
+        <v>-9.19</v>
       </c>
       <c r="L7">
-        <v>-5.87</v>
+        <v>-6.16</v>
       </c>
       <c r="M7">
-        <v>3.57</v>
+        <v>3.39</v>
       </c>
       <c r="N7">
         <v>56</v>
       </c>
       <c r="O7">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="P7">
-        <v>1011.86</v>
+        <v>1007.94</v>
       </c>
       <c r="Q7">
-        <v>1043.48</v>
+        <v>1038.93</v>
       </c>
       <c r="R7">
-        <v>1074.99</v>
+        <v>1072.84</v>
       </c>
       <c r="S7">
-        <v>1121.28</v>
+        <v>1120.4</v>
       </c>
       <c r="T7">
-        <v>-10.73</v>
+        <v>-10.78</v>
       </c>
       <c r="U7" t="s">
         <v>54</v>
@@ -1619,43 +1616,43 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>31.7</v>
+        <v>31.36</v>
       </c>
       <c r="Z7">
-        <v>-20.52</v>
+        <v>-21.09</v>
       </c>
       <c r="AA7">
-        <v>-17.61</v>
+        <v>-18.31</v>
       </c>
       <c r="AB7">
-        <v>-2.9</v>
+        <v>-2.78</v>
       </c>
       <c r="AC7">
-        <v>17.81</v>
+        <v>8.59</v>
       </c>
       <c r="AD7">
-        <v>19.72</v>
+        <v>15.72</v>
       </c>
       <c r="AE7">
-        <v>18.06</v>
+        <v>17.71</v>
       </c>
       <c r="AF7">
-        <v>-18.31</v>
+        <v>-12.58</v>
       </c>
       <c r="AG7">
-        <v>1094.86</v>
+        <v>1088.86</v>
       </c>
       <c r="AH7">
-        <v>992.1</v>
+        <v>989.01</v>
       </c>
       <c r="AI7">
-        <v>1061.54</v>
+        <v>1052.18</v>
       </c>
       <c r="AJ7" t="s">
         <v>57</v>
       </c>
       <c r="AK7">
-        <v>64.48999999999999</v>
+        <v>67.48</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1666,10 +1663,10 @@
         <v>53</v>
       </c>
       <c r="C8">
-        <v>3383</v>
+        <v>3409</v>
       </c>
       <c r="D8">
-        <v>-3.12</v>
+        <v>0.77</v>
       </c>
       <c r="E8">
         <v>5749.89</v>
@@ -1678,46 +1675,46 @@
         <v>3383</v>
       </c>
       <c r="G8">
-        <v>-41.16</v>
+        <v>-40.71</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="I8">
-        <v>-6.26</v>
+        <v>-4.78</v>
       </c>
       <c r="J8">
-        <v>-10.86</v>
+        <v>-8.16</v>
       </c>
       <c r="K8">
-        <v>-15.62</v>
+        <v>-16.14</v>
       </c>
       <c r="L8">
-        <v>-36.83</v>
+        <v>-36.55</v>
       </c>
       <c r="M8">
-        <v>-6.29</v>
+        <v>-6.46</v>
       </c>
       <c r="N8">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="O8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P8">
-        <v>3502</v>
+        <v>3467.8</v>
       </c>
       <c r="Q8">
-        <v>3632.81</v>
+        <v>3614.36</v>
       </c>
       <c r="R8">
-        <v>3638.41</v>
+        <v>3633.17</v>
       </c>
       <c r="S8">
-        <v>4360.35</v>
+        <v>4351.7</v>
       </c>
       <c r="T8">
-        <v>-22.41</v>
+        <v>-21.66</v>
       </c>
       <c r="U8" t="s">
         <v>54</v>
@@ -1732,43 +1729,43 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>29.32</v>
+        <v>32.36</v>
       </c>
       <c r="Z8">
-        <v>-60.48</v>
+        <v>-67.95999999999999</v>
       </c>
       <c r="AA8">
-        <v>-35.83</v>
+        <v>-42.25</v>
       </c>
       <c r="AB8">
-        <v>-24.65</v>
+        <v>-25.7</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AD8">
-        <v>1.12</v>
+        <v>1.73</v>
       </c>
       <c r="AE8">
-        <v>88.63</v>
+        <v>88.5</v>
       </c>
       <c r="AF8">
-        <v>51.92</v>
+        <v>25.05</v>
       </c>
       <c r="AG8">
-        <v>3830.99</v>
+        <v>3824.01</v>
       </c>
       <c r="AH8">
-        <v>3434.64</v>
+        <v>3404.72</v>
       </c>
       <c r="AI8">
-        <v>3685.83</v>
+        <v>3678.96</v>
       </c>
       <c r="AJ8" t="s">
         <v>57</v>
       </c>
       <c r="AK8">
-        <v>33.4</v>
+        <v>37.96</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1779,10 +1776,10 @@
         <v>53</v>
       </c>
       <c r="C9">
-        <v>618.8</v>
+        <v>645.15</v>
       </c>
       <c r="D9">
-        <v>-0.52</v>
+        <v>4.26</v>
       </c>
       <c r="E9">
         <v>1052.57</v>
@@ -1791,46 +1788,46 @@
         <v>538.37</v>
       </c>
       <c r="G9">
-        <v>-41.21</v>
+        <v>-38.71</v>
       </c>
       <c r="H9">
-        <v>14.94</v>
+        <v>19.83</v>
       </c>
       <c r="I9">
-        <v>-1.48</v>
+        <v>1.13</v>
       </c>
       <c r="J9">
-        <v>-10.16</v>
+        <v>-5.22</v>
       </c>
       <c r="K9">
-        <v>-2.65</v>
+        <v>-3.12</v>
       </c>
       <c r="L9">
-        <v>-7.97</v>
+        <v>-3.57</v>
       </c>
       <c r="M9">
-        <v>38.95</v>
+        <v>40.36</v>
       </c>
       <c r="N9">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="O9">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="P9">
-        <v>628.0599999999999</v>
+        <v>629.5</v>
       </c>
       <c r="Q9">
-        <v>642.67</v>
+        <v>641.21</v>
       </c>
       <c r="R9">
-        <v>658.47</v>
+        <v>658.02</v>
       </c>
       <c r="S9">
-        <v>665.49</v>
+        <v>665.05</v>
       </c>
       <c r="T9">
-        <v>-7.02</v>
+        <v>-2.99</v>
       </c>
       <c r="U9" t="s">
         <v>54</v>
@@ -1845,34 +1842,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>31.48</v>
+        <v>49.86</v>
       </c>
       <c r="Z9">
-        <v>-10.84</v>
+        <v>-9.15</v>
       </c>
       <c r="AA9">
-        <v>-8.800000000000001</v>
+        <v>-8.869999999999999</v>
       </c>
       <c r="AB9">
-        <v>-2.05</v>
+        <v>-0.28</v>
       </c>
       <c r="AC9">
-        <v>13.21</v>
+        <v>35.99</v>
       </c>
       <c r="AD9">
-        <v>34.36</v>
+        <v>27.37</v>
       </c>
       <c r="AE9">
-        <v>12.34</v>
+        <v>15.79</v>
       </c>
       <c r="AF9">
-        <v>-30.58</v>
+        <v>4410.46</v>
       </c>
       <c r="AG9">
-        <v>670.1900000000001</v>
+        <v>664.4</v>
       </c>
       <c r="AH9">
-        <v>615.16</v>
+        <v>618.02</v>
       </c>
       <c r="AI9">
         <v>657.48</v>
@@ -1881,7 +1878,7 @@
         <v>57</v>
       </c>
       <c r="AK9">
-        <v>14.13</v>
+        <v>18.95</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1892,10 +1889,10 @@
         <v>53</v>
       </c>
       <c r="C10">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="D10">
-        <v>1.22</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E10">
         <v>461.8</v>
@@ -1904,46 +1901,46 @@
         <v>345.25</v>
       </c>
       <c r="G10">
-        <v>-19.88</v>
+        <v>-20.53</v>
       </c>
       <c r="H10">
-        <v>7.17</v>
+        <v>6.3</v>
       </c>
       <c r="I10">
-        <v>1.65</v>
+        <v>0.36</v>
       </c>
       <c r="J10">
-        <v>-2.63</v>
+        <v>-3.28</v>
       </c>
       <c r="K10">
-        <v>-5.19</v>
+        <v>-6.75</v>
       </c>
       <c r="L10">
-        <v>-4.1</v>
+        <v>-4.24</v>
       </c>
       <c r="M10">
-        <v>23.44</v>
+        <v>23.6</v>
       </c>
       <c r="N10">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="O10">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P10">
-        <v>366.99</v>
+        <v>367.25</v>
       </c>
       <c r="Q10">
-        <v>368.21</v>
+        <v>367.42</v>
       </c>
       <c r="R10">
-        <v>374.27</v>
+        <v>374.08</v>
       </c>
       <c r="S10">
-        <v>388.09</v>
+        <v>388.02</v>
       </c>
       <c r="T10">
-        <v>-4.66</v>
+        <v>-5.42</v>
       </c>
       <c r="U10" t="s">
         <v>54</v>
@@ -1958,34 +1955,34 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>50.63</v>
+        <v>47.43</v>
       </c>
       <c r="Z10">
-        <v>-3.76</v>
+        <v>-3.35</v>
       </c>
       <c r="AA10">
-        <v>-4.89</v>
+        <v>-4.58</v>
       </c>
       <c r="AB10">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AC10">
-        <v>94.73</v>
+        <v>93.89</v>
       </c>
       <c r="AD10">
-        <v>93.03</v>
+        <v>93.95999999999999</v>
       </c>
       <c r="AE10">
-        <v>7.21</v>
+        <v>7.12</v>
       </c>
       <c r="AF10">
-        <v>4</v>
+        <v>-48.12</v>
       </c>
       <c r="AG10">
-        <v>390.36</v>
+        <v>388.48</v>
       </c>
       <c r="AH10">
-        <v>346.07</v>
+        <v>346.37</v>
       </c>
       <c r="AI10">
         <v>346.81</v>
@@ -1994,7 +1991,7 @@
         <v>56</v>
       </c>
       <c r="AK10">
-        <v>29.71</v>
+        <v>30.15</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -2005,10 +2002,10 @@
         <v>53</v>
       </c>
       <c r="C11">
-        <v>188.75</v>
+        <v>186.78</v>
       </c>
       <c r="D11">
-        <v>2.5</v>
+        <v>-1.04</v>
       </c>
       <c r="E11">
         <v>216.66</v>
@@ -2017,46 +2014,46 @@
         <v>157.42</v>
       </c>
       <c r="G11">
-        <v>-12.88</v>
+        <v>-13.79</v>
       </c>
       <c r="H11">
-        <v>19.9</v>
+        <v>18.65</v>
       </c>
       <c r="I11">
-        <v>2.67</v>
+        <v>1.4</v>
       </c>
       <c r="J11">
-        <v>0.27</v>
+        <v>0.31</v>
       </c>
       <c r="K11">
-        <v>-2.69</v>
+        <v>-5.6</v>
       </c>
       <c r="L11">
-        <v>14.89</v>
+        <v>12.92</v>
       </c>
       <c r="M11">
-        <v>8.630000000000001</v>
+        <v>8.17</v>
       </c>
       <c r="N11">
         <v>87</v>
       </c>
       <c r="O11">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="P11">
-        <v>186.3</v>
+        <v>186.82</v>
       </c>
       <c r="Q11">
-        <v>185.43</v>
+        <v>185.53</v>
       </c>
       <c r="R11">
-        <v>186.81</v>
+        <v>186.79</v>
       </c>
       <c r="S11">
-        <v>190.29</v>
+        <v>190.41</v>
       </c>
       <c r="T11">
-        <v>-0.8100000000000001</v>
+        <v>-1.91</v>
       </c>
       <c r="U11" t="s">
         <v>54</v>
@@ -2071,34 +2068,34 @@
         <v>0</v>
       </c>
       <c r="Y11">
-        <v>54.93</v>
+        <v>50.74</v>
       </c>
       <c r="Z11">
-        <v>-0.35</v>
+        <v>-0.26</v>
       </c>
       <c r="AA11">
-        <v>-0.6899999999999999</v>
+        <v>-0.6</v>
       </c>
       <c r="AB11">
         <v>0.34</v>
       </c>
       <c r="AC11">
-        <v>58.22</v>
+        <v>61.57</v>
       </c>
       <c r="AD11">
-        <v>59.56</v>
+        <v>60.07</v>
       </c>
       <c r="AE11">
-        <v>4.53</v>
+        <v>4.49</v>
       </c>
       <c r="AF11">
-        <v>69.15000000000001</v>
+        <v>-17.78</v>
       </c>
       <c r="AG11">
-        <v>188.98</v>
+        <v>189.12</v>
       </c>
       <c r="AH11">
-        <v>181.89</v>
+        <v>181.94</v>
       </c>
       <c r="AI11">
         <v>180.21</v>
@@ -2107,7 +2104,7 @@
         <v>56</v>
       </c>
       <c r="AK11">
-        <v>24.66</v>
+        <v>27.64</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -2118,10 +2115,10 @@
         <v>53</v>
       </c>
       <c r="C12">
-        <v>2208</v>
+        <v>2204.1</v>
       </c>
       <c r="D12">
-        <v>-2.11</v>
+        <v>-0.18</v>
       </c>
       <c r="E12">
         <v>3221.85</v>
@@ -2130,46 +2127,46 @@
         <v>1982.6</v>
       </c>
       <c r="G12">
-        <v>-31.47</v>
+        <v>-31.59</v>
       </c>
       <c r="H12">
-        <v>11.37</v>
+        <v>11.17</v>
       </c>
       <c r="I12">
-        <v>-5.96</v>
+        <v>-5</v>
       </c>
       <c r="J12">
-        <v>-9.720000000000001</v>
+        <v>-6.2</v>
       </c>
       <c r="K12">
-        <v>3.39</v>
+        <v>1.98</v>
       </c>
       <c r="L12">
-        <v>-24.97</v>
+        <v>-24.38</v>
       </c>
       <c r="M12">
-        <v>-7.79</v>
+        <v>-8.09</v>
       </c>
       <c r="N12">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O12">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P12">
-        <v>2271.52</v>
+        <v>2248.32</v>
       </c>
       <c r="Q12">
-        <v>2306.64</v>
+        <v>2298.1</v>
       </c>
       <c r="R12">
-        <v>2283.48</v>
+        <v>2286.2</v>
       </c>
       <c r="S12">
-        <v>2555.04</v>
+        <v>2550.84</v>
       </c>
       <c r="T12">
-        <v>-13.58</v>
+        <v>-13.59</v>
       </c>
       <c r="U12" t="s">
         <v>55</v>
@@ -2184,43 +2181,43 @@
         <v>1</v>
       </c>
       <c r="Y12">
-        <v>38.79</v>
+        <v>38.44</v>
       </c>
       <c r="Z12">
-        <v>-12.29</v>
+        <v>-18.47</v>
       </c>
       <c r="AA12">
-        <v>1.34</v>
+        <v>-2.62</v>
       </c>
       <c r="AB12">
-        <v>-13.63</v>
+        <v>-15.85</v>
       </c>
       <c r="AC12">
-        <v>5.12</v>
+        <v>1.06</v>
       </c>
       <c r="AD12">
-        <v>17.28</v>
+        <v>7.54</v>
       </c>
       <c r="AE12">
-        <v>57.88</v>
+        <v>56.7</v>
       </c>
       <c r="AF12">
-        <v>32.51</v>
+        <v>-5.35</v>
       </c>
       <c r="AG12">
-        <v>2402.28</v>
+        <v>2398.44</v>
       </c>
       <c r="AH12">
-        <v>2211</v>
+        <v>2197.75</v>
       </c>
       <c r="AI12">
-        <v>2388.73</v>
+        <v>2381.4</v>
       </c>
       <c r="AJ12" t="s">
         <v>57</v>
       </c>
       <c r="AK12">
-        <v>24.71</v>
+        <v>27.84</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2231,10 +2228,10 @@
         <v>53</v>
       </c>
       <c r="C13">
-        <v>5005</v>
+        <v>5021</v>
       </c>
       <c r="D13">
-        <v>0.36</v>
+        <v>0.32</v>
       </c>
       <c r="E13">
         <v>5169.2</v>
@@ -2243,46 +2240,46 @@
         <v>3327.3</v>
       </c>
       <c r="G13">
-        <v>-3.18</v>
+        <v>-2.87</v>
       </c>
       <c r="H13">
-        <v>50.42</v>
+        <v>50.9</v>
       </c>
       <c r="I13">
-        <v>-1.36</v>
+        <v>-0.12</v>
       </c>
       <c r="J13">
-        <v>-2.4</v>
+        <v>-1.53</v>
       </c>
       <c r="K13">
-        <v>24.34</v>
+        <v>20</v>
       </c>
       <c r="L13">
-        <v>36.55</v>
+        <v>37.26</v>
       </c>
       <c r="M13">
-        <v>20.04</v>
+        <v>20.2</v>
       </c>
       <c r="N13">
         <v>99</v>
       </c>
       <c r="O13">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P13">
-        <v>5006.8</v>
+        <v>5005.6</v>
       </c>
       <c r="Q13">
-        <v>5065.98</v>
+        <v>5063.84</v>
       </c>
       <c r="R13">
-        <v>4875.64</v>
+        <v>4886.44</v>
       </c>
       <c r="S13">
-        <v>4335.28</v>
+        <v>4341.02</v>
       </c>
       <c r="T13">
-        <v>15.45</v>
+        <v>15.66</v>
       </c>
       <c r="U13" t="s">
         <v>55</v>
@@ -2297,34 +2294,34 @@
         <v>3</v>
       </c>
       <c r="Y13">
-        <v>50.84</v>
+        <v>52.71</v>
       </c>
       <c r="Z13">
-        <v>35.17</v>
+        <v>31.19</v>
       </c>
       <c r="AA13">
-        <v>65.27</v>
+        <v>58.46</v>
       </c>
       <c r="AB13">
-        <v>-30.11</v>
+        <v>-27.27</v>
       </c>
       <c r="AC13">
-        <v>2.99</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="AD13">
-        <v>1</v>
+        <v>3.86</v>
       </c>
       <c r="AE13">
-        <v>77.44</v>
+        <v>75.23</v>
       </c>
       <c r="AF13">
-        <v>-15.84</v>
+        <v>-37.8</v>
       </c>
       <c r="AG13">
         <v>5160.01</v>
       </c>
       <c r="AH13">
-        <v>4971.94</v>
+        <v>4967.67</v>
       </c>
       <c r="AI13">
         <v>4921.93</v>
@@ -2333,7 +2330,7 @@
         <v>56</v>
       </c>
       <c r="AK13">
-        <v>38.53</v>
+        <v>38.26</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2344,58 +2341,58 @@
         <v>53</v>
       </c>
       <c r="C14">
-        <v>2820</v>
+        <v>2818.7</v>
       </c>
       <c r="D14">
-        <v>0.95</v>
+        <v>-0.05</v>
       </c>
       <c r="E14">
-        <v>5307.66</v>
+        <v>5210.8</v>
       </c>
       <c r="F14">
         <v>2193.96</v>
       </c>
       <c r="G14">
-        <v>-46.87</v>
+        <v>-45.91</v>
       </c>
       <c r="H14">
-        <v>28.53</v>
+        <v>28.48</v>
       </c>
       <c r="I14">
-        <v>-1.13</v>
+        <v>0.11</v>
       </c>
       <c r="J14">
-        <v>-6</v>
+        <v>-5.63</v>
       </c>
       <c r="K14">
-        <v>4.18</v>
+        <v>2.3</v>
       </c>
       <c r="L14">
-        <v>-48.92</v>
+        <v>-46.89</v>
       </c>
       <c r="M14">
-        <v>22.61</v>
+        <v>23.04</v>
       </c>
       <c r="N14">
         <v>32</v>
       </c>
       <c r="O14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P14">
-        <v>2819.34</v>
+        <v>2819.96</v>
       </c>
       <c r="Q14">
-        <v>2895.34</v>
+        <v>2886.77</v>
       </c>
       <c r="R14">
-        <v>2953.25</v>
+        <v>2943.27</v>
       </c>
       <c r="S14">
-        <v>2965.09</v>
+        <v>2957.66</v>
       </c>
       <c r="T14">
-        <v>-4.89</v>
+        <v>-4.7</v>
       </c>
       <c r="U14" t="s">
         <v>54</v>
@@ -2410,34 +2407,34 @@
         <v>0</v>
       </c>
       <c r="Y14">
-        <v>38.43</v>
+        <v>38.29</v>
       </c>
       <c r="Z14">
-        <v>-43.85</v>
+        <v>-43.51</v>
       </c>
       <c r="AA14">
-        <v>-34.9</v>
+        <v>-36.62</v>
       </c>
       <c r="AB14">
-        <v>-8.94</v>
+        <v>-6.88</v>
       </c>
       <c r="AC14">
-        <v>23.93</v>
+        <v>33.4</v>
       </c>
       <c r="AD14">
-        <v>22.74</v>
+        <v>26.78</v>
       </c>
       <c r="AE14">
-        <v>59.16</v>
+        <v>57.43</v>
       </c>
       <c r="AF14">
-        <v>-11.79</v>
+        <v>-26.2</v>
       </c>
       <c r="AG14">
-        <v>3013.61</v>
+        <v>3000.92</v>
       </c>
       <c r="AH14">
-        <v>2777.06</v>
+        <v>2772.62</v>
       </c>
       <c r="AI14">
         <v>2968.92</v>
@@ -2446,7 +2443,7 @@
         <v>57</v>
       </c>
       <c r="AK14">
-        <v>39.88</v>
+        <v>38.97</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2457,10 +2454,10 @@
         <v>53</v>
       </c>
       <c r="C15">
-        <v>228.79</v>
+        <v>220.8</v>
       </c>
       <c r="D15">
-        <v>-0.95</v>
+        <v>-3.49</v>
       </c>
       <c r="E15">
         <v>392.75</v>
@@ -2469,46 +2466,46 @@
         <v>217.05</v>
       </c>
       <c r="G15">
-        <v>-41.75</v>
+        <v>-43.78</v>
       </c>
       <c r="H15">
-        <v>5.41</v>
+        <v>1.73</v>
       </c>
       <c r="I15">
-        <v>2.3</v>
+        <v>-4.01</v>
       </c>
       <c r="J15">
-        <v>-2.86</v>
+        <v>-4.06</v>
       </c>
       <c r="K15">
-        <v>2.88</v>
+        <v>-3.07</v>
       </c>
       <c r="L15">
-        <v>-27.89</v>
+        <v>-30.16</v>
       </c>
       <c r="M15">
-        <v>13.87</v>
+        <v>13.97</v>
       </c>
       <c r="N15">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="O15">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="P15">
-        <v>231.3</v>
+        <v>229.46</v>
       </c>
       <c r="Q15">
-        <v>229.88</v>
+        <v>229.31</v>
       </c>
       <c r="R15">
-        <v>233.16</v>
+        <v>232.84</v>
       </c>
       <c r="S15">
-        <v>255.92</v>
+        <v>255.48</v>
       </c>
       <c r="T15">
-        <v>-10.6</v>
+        <v>-13.57</v>
       </c>
       <c r="U15" t="s">
         <v>54</v>
@@ -2523,34 +2520,34 @@
         <v>0</v>
       </c>
       <c r="Y15">
-        <v>46.9</v>
+        <v>37.31</v>
       </c>
       <c r="Z15">
-        <v>-0.73</v>
+        <v>-1.4</v>
       </c>
       <c r="AA15">
-        <v>-1.17</v>
+        <v>-1.22</v>
       </c>
       <c r="AB15">
-        <v>0.44</v>
+        <v>-0.19</v>
       </c>
       <c r="AC15">
-        <v>72.48999999999999</v>
+        <v>40.97</v>
       </c>
       <c r="AD15">
-        <v>87.11</v>
+        <v>67.43000000000001</v>
       </c>
       <c r="AE15">
-        <v>5.82</v>
+        <v>6.38</v>
       </c>
       <c r="AF15">
-        <v>-63.14</v>
+        <v>202.97</v>
       </c>
       <c r="AG15">
-        <v>235</v>
+        <v>235.72</v>
       </c>
       <c r="AH15">
-        <v>224.76</v>
+        <v>222.9</v>
       </c>
       <c r="AI15">
         <v>219.81</v>
@@ -2559,7 +2556,7 @@
         <v>56</v>
       </c>
       <c r="AK15">
-        <v>21.83</v>
+        <v>23.2</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2570,10 +2567,10 @@
         <v>53</v>
       </c>
       <c r="C16">
-        <v>36.13</v>
+        <v>35.91</v>
       </c>
       <c r="D16">
-        <v>-0.99</v>
+        <v>-0.61</v>
       </c>
       <c r="E16">
         <v>58.79</v>
@@ -2582,46 +2579,46 @@
         <v>31.36</v>
       </c>
       <c r="G16">
-        <v>-38.54</v>
+        <v>-38.92</v>
       </c>
       <c r="H16">
-        <v>15.21</v>
+        <v>14.51</v>
       </c>
       <c r="I16">
-        <v>-4.92</v>
+        <v>-5.52</v>
       </c>
       <c r="J16">
-        <v>-6.91</v>
+        <v>-5.92</v>
       </c>
       <c r="K16">
-        <v>-14.28</v>
+        <v>-22.67</v>
       </c>
       <c r="L16">
-        <v>-37.15</v>
+        <v>-37.13</v>
       </c>
       <c r="M16">
-        <v>0.02</v>
+        <v>0.46</v>
       </c>
       <c r="N16">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="O16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P16">
-        <v>37.14</v>
+        <v>36.72</v>
       </c>
       <c r="Q16">
-        <v>37.78</v>
+        <v>37.63</v>
       </c>
       <c r="R16">
-        <v>39.26</v>
+        <v>39.12</v>
       </c>
       <c r="S16">
-        <v>42.86</v>
+        <v>42.79</v>
       </c>
       <c r="T16">
-        <v>-15.71</v>
+        <v>-16.08</v>
       </c>
       <c r="U16" t="s">
         <v>54</v>
@@ -2636,43 +2633,43 @@
         <v>0</v>
       </c>
       <c r="Y16">
-        <v>33.57</v>
+        <v>32.43</v>
       </c>
       <c r="Z16">
-        <v>-0.66</v>
+        <v>-0.74</v>
       </c>
       <c r="AA16">
-        <v>-0.6</v>
+        <v>-0.63</v>
       </c>
       <c r="AB16">
-        <v>-0.06</v>
+        <v>-0.11</v>
       </c>
       <c r="AC16">
-        <v>39.64</v>
+        <v>28.67</v>
       </c>
       <c r="AD16">
-        <v>52.55</v>
+        <v>40.29</v>
       </c>
       <c r="AE16">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF16">
-        <v>-69.70999999999999</v>
+        <v>-68.61</v>
       </c>
       <c r="AG16">
-        <v>39.38</v>
+        <v>39.37</v>
       </c>
       <c r="AH16">
-        <v>36.17</v>
+        <v>35.9</v>
       </c>
       <c r="AI16">
-        <v>39.6</v>
+        <v>39.51</v>
       </c>
       <c r="AJ16" t="s">
         <v>57</v>
       </c>
       <c r="AK16">
-        <v>22.23</v>
+        <v>22.53</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2683,10 +2680,10 @@
         <v>53</v>
       </c>
       <c r="C17">
-        <v>1143.8</v>
+        <v>1158.5</v>
       </c>
       <c r="D17">
-        <v>-0.09</v>
+        <v>1.29</v>
       </c>
       <c r="E17">
         <v>1556.41</v>
@@ -2695,46 +2692,46 @@
         <v>1143.8</v>
       </c>
       <c r="G17">
-        <v>-26.51</v>
+        <v>-25.57</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="I17">
-        <v>-0.72</v>
+        <v>-1.66</v>
       </c>
       <c r="J17">
-        <v>-10.64</v>
+        <v>-10.19</v>
       </c>
       <c r="K17">
-        <v>-10.17</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="L17">
-        <v>-19.92</v>
+        <v>-18.11</v>
       </c>
       <c r="M17">
-        <v>-0.71</v>
+        <v>-0.46</v>
       </c>
       <c r="N17">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="O17">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="P17">
-        <v>1160.76</v>
+        <v>1156.86</v>
       </c>
       <c r="Q17">
-        <v>1214.11</v>
+        <v>1207.56</v>
       </c>
       <c r="R17">
-        <v>1273.12</v>
+        <v>1270.48</v>
       </c>
       <c r="S17">
-        <v>1347.41</v>
+        <v>1346.45</v>
       </c>
       <c r="T17">
-        <v>-15.11</v>
+        <v>-13.96</v>
       </c>
       <c r="U17" t="s">
         <v>54</v>
@@ -2749,34 +2746,34 @@
         <v>0</v>
       </c>
       <c r="Y17">
-        <v>30.33</v>
+        <v>35.15</v>
       </c>
       <c r="Z17">
-        <v>-36.45</v>
+        <v>-35.72</v>
       </c>
       <c r="AA17">
-        <v>-31.21</v>
+        <v>-32.11</v>
       </c>
       <c r="AB17">
-        <v>-5.25</v>
+        <v>-3.61</v>
       </c>
       <c r="AC17">
-        <v>28.97</v>
+        <v>32.5</v>
       </c>
       <c r="AD17">
-        <v>39.43</v>
+        <v>33.5</v>
       </c>
       <c r="AE17">
-        <v>28.42</v>
+        <v>28.36</v>
       </c>
       <c r="AF17">
-        <v>-55.21</v>
+        <v>-51.07</v>
       </c>
       <c r="AG17">
-        <v>1309.47</v>
+        <v>1299.03</v>
       </c>
       <c r="AH17">
-        <v>1118.75</v>
+        <v>1116.09</v>
       </c>
       <c r="AI17">
         <v>1226.77</v>
@@ -2785,7 +2782,7 @@
         <v>57</v>
       </c>
       <c r="AK17">
-        <v>51.99</v>
+        <v>51.33</v>
       </c>
     </row>
   </sheetData>
@@ -2926,7 +2923,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F142"/>
+  <dimension ref="A1:F145"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2966,7 +2963,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>64</v>
@@ -2986,7 +2983,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>64</v>
@@ -3005,1726 +3002,1723 @@
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="A5" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>74</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="E7" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="F7" s="5" t="s">
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="2" t="s">
         <v>80</v>
       </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
+      <c r="C9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>85</v>
+      <c r="A10" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="7">
+        <v>-0.17</v>
+      </c>
+      <c r="D10" s="7">
+        <v>-1.14</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-0.97</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="7">
-        <v>-1.19</v>
+        <v>-3.7</v>
       </c>
       <c r="D11" s="7">
-        <v>-0.17</v>
+        <v>-3.75</v>
       </c>
       <c r="E11" s="8">
-        <v>1.02</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="7">
-        <v>-3.42</v>
+        <v>-3.54</v>
       </c>
       <c r="D12" s="7">
-        <v>-3.7</v>
+        <v>-3.03</v>
       </c>
       <c r="E12" s="9">
-        <v>-0.28</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="7">
-        <v>-3.68</v>
+        <v>-9.82</v>
       </c>
       <c r="D13" s="7">
-        <v>-3.54</v>
-      </c>
-      <c r="E13" s="8">
-        <v>0.14</v>
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="E13" s="9">
+        <v>0.52</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="7">
-        <v>-9.15</v>
+        <v>1.53</v>
       </c>
       <c r="D14" s="7">
-        <v>-9.82</v>
+        <v>1.62</v>
       </c>
       <c r="E14" s="9">
-        <v>-0.67</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="7">
-        <v>0.77</v>
+        <v>-7.14</v>
       </c>
       <c r="D15" s="7">
-        <v>1.53</v>
-      </c>
-      <c r="E15" s="8">
-        <v>0.76</v>
+        <v>-5.87</v>
+      </c>
+      <c r="E15" s="9">
+        <v>1.27</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="7">
-        <v>-8.529999999999999</v>
+        <v>-10.86</v>
       </c>
       <c r="D16" s="7">
-        <v>-7.14</v>
-      </c>
-      <c r="E16" s="8">
-        <v>1.39</v>
+        <v>-8.16</v>
+      </c>
+      <c r="E16" s="9">
+        <v>2.7</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="7">
-        <v>-8.300000000000001</v>
+        <v>-10.16</v>
       </c>
       <c r="D17" s="7">
-        <v>-10.86</v>
+        <v>-5.22</v>
       </c>
       <c r="E17" s="9">
-        <v>-2.56</v>
+        <v>4.94</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="7">
-        <v>-9.57</v>
+        <v>-2.63</v>
       </c>
       <c r="D18" s="7">
-        <v>-10.16</v>
-      </c>
-      <c r="E18" s="9">
-        <v>-0.59</v>
+        <v>-3.28</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-0.65</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="7">
-        <v>-4.31</v>
+        <v>0.27</v>
       </c>
       <c r="D19" s="7">
-        <v>-2.63</v>
-      </c>
-      <c r="E19" s="8">
-        <v>1.68</v>
+        <v>0.31</v>
+      </c>
+      <c r="E19" s="9">
+        <v>0.04</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="7">
-        <v>-3.2</v>
+        <v>-9.720000000000001</v>
       </c>
       <c r="D20" s="7">
-        <v>0.27</v>
-      </c>
-      <c r="E20" s="8">
-        <v>3.47</v>
+        <v>-6.2</v>
+      </c>
+      <c r="E20" s="9">
+        <v>3.52</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C21" s="7">
-        <v>-7.02</v>
+        <v>-2.4</v>
       </c>
       <c r="D21" s="7">
-        <v>-9.720000000000001</v>
+        <v>-1.53</v>
       </c>
       <c r="E21" s="9">
-        <v>-2.7</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C22" s="7">
-        <v>-2.02</v>
+        <v>-6</v>
       </c>
       <c r="D22" s="7">
-        <v>-2.4</v>
+        <v>-5.63</v>
       </c>
       <c r="E22" s="9">
-        <v>-0.38</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C23" s="7">
-        <v>-7.65</v>
+        <v>-2.86</v>
       </c>
       <c r="D23" s="7">
-        <v>-6</v>
+        <v>-4.06</v>
       </c>
       <c r="E23" s="8">
-        <v>1.65</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C24" s="7">
-        <v>-1.52</v>
+        <v>-6.91</v>
       </c>
       <c r="D24" s="7">
-        <v>-2.86</v>
+        <v>-5.92</v>
       </c>
       <c r="E24" s="9">
-        <v>-1.34</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C25" s="7">
-        <v>-6.48</v>
+        <v>-10.64</v>
       </c>
       <c r="D25" s="7">
-        <v>-6.91</v>
+        <v>-10.19</v>
       </c>
       <c r="E25" s="9">
-        <v>-0.43</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="6" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C26" s="7">
-        <v>-9.710000000000001</v>
+        <v>-0.68</v>
       </c>
       <c r="D26" s="7">
-        <v>-10.64</v>
-      </c>
-      <c r="E26" s="9">
-        <v>-0.93</v>
+        <v>-2.22</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-1.54</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C27" s="7">
-        <v>0.28</v>
+        <v>3.08</v>
       </c>
       <c r="D27" s="7">
-        <v>-0.68</v>
-      </c>
-      <c r="E27" s="9">
-        <v>-0.96</v>
+        <v>0.41</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-2.67</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C28" s="7">
-        <v>5.27</v>
+        <v>-2.62</v>
       </c>
       <c r="D28" s="7">
-        <v>3.08</v>
-      </c>
-      <c r="E28" s="9">
-        <v>-2.19</v>
+        <v>-3.23</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-0.61</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C29" s="7">
-        <v>-0.91</v>
+        <v>-4.87</v>
       </c>
       <c r="D29" s="7">
-        <v>-2.62</v>
+        <v>-4.8</v>
       </c>
       <c r="E29" s="9">
-        <v>-1.71</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C30" s="7">
-        <v>-4.09</v>
+        <v>3.67</v>
       </c>
       <c r="D30" s="7">
-        <v>-4.87</v>
+        <v>4.01</v>
       </c>
       <c r="E30" s="9">
-        <v>-0.78</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C31" s="7">
-        <v>1.1</v>
+        <v>-1.09</v>
       </c>
       <c r="D31" s="7">
-        <v>3.67</v>
+        <v>-1.92</v>
       </c>
       <c r="E31" s="8">
-        <v>2.57</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C32" s="7">
-        <v>-1.59</v>
+        <v>-6.26</v>
       </c>
       <c r="D32" s="7">
-        <v>-1.09</v>
-      </c>
-      <c r="E32" s="8">
-        <v>0.5</v>
+        <v>-4.78</v>
+      </c>
+      <c r="E32" s="9">
+        <v>1.48</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C33" s="7">
-        <v>-4.01</v>
+        <v>-1.48</v>
       </c>
       <c r="D33" s="7">
-        <v>-6.26</v>
+        <v>1.13</v>
       </c>
       <c r="E33" s="9">
-        <v>-2.25</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C34" s="7">
-        <v>-1.83</v>
+        <v>1.65</v>
       </c>
       <c r="D34" s="7">
-        <v>-1.48</v>
+        <v>0.36</v>
       </c>
       <c r="E34" s="8">
-        <v>0.35</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C35" s="7">
-        <v>4.28</v>
+        <v>2.67</v>
       </c>
       <c r="D35" s="7">
-        <v>1.65</v>
-      </c>
-      <c r="E35" s="9">
-        <v>-2.63</v>
+        <v>1.4</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-1.27</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C36" s="7">
-        <v>0.04</v>
+        <v>-5.96</v>
       </c>
       <c r="D36" s="7">
-        <v>2.67</v>
-      </c>
-      <c r="E36" s="8">
-        <v>2.63</v>
+        <v>-5</v>
+      </c>
+      <c r="E36" s="9">
+        <v>0.96</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C37" s="7">
-        <v>-4.79</v>
+        <v>-1.36</v>
       </c>
       <c r="D37" s="7">
-        <v>-5.96</v>
+        <v>-0.12</v>
       </c>
       <c r="E37" s="9">
-        <v>-1.17</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C38" s="7">
-        <v>-1.25</v>
+        <v>-1.13</v>
       </c>
       <c r="D38" s="7">
-        <v>-1.36</v>
+        <v>0.11</v>
       </c>
       <c r="E38" s="9">
-        <v>-0.11</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C39" s="7">
-        <v>-2.15</v>
+        <v>2.3</v>
       </c>
       <c r="D39" s="7">
-        <v>-1.13</v>
+        <v>-4.01</v>
       </c>
       <c r="E39" s="8">
-        <v>1.02</v>
+        <v>-6.31</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C40" s="7">
-        <v>3.03</v>
+        <v>-4.92</v>
       </c>
       <c r="D40" s="7">
-        <v>2.3</v>
-      </c>
-      <c r="E40" s="9">
-        <v>-0.73</v>
+        <v>-5.52</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-0.6</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C41" s="7">
-        <v>-6.24</v>
+        <v>-0.72</v>
       </c>
       <c r="D41" s="7">
-        <v>-4.92</v>
+        <v>-1.66</v>
       </c>
       <c r="E41" s="8">
-        <v>1.32</v>
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="6" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C42" s="7">
-        <v>-5</v>
+        <v>-6.71</v>
       </c>
       <c r="D42" s="7">
-        <v>-0.72</v>
+        <v>-7.97</v>
       </c>
       <c r="E42" s="8">
-        <v>4.28</v>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C43" s="7">
-        <v>-7.07</v>
+        <v>19.1</v>
       </c>
       <c r="D43" s="7">
-        <v>-6.71</v>
+        <v>15.41</v>
       </c>
       <c r="E43" s="8">
-        <v>0.36</v>
+        <v>-3.69</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C44" s="7">
-        <v>19.84</v>
+        <v>-42.15</v>
       </c>
       <c r="D44" s="7">
-        <v>19.1</v>
-      </c>
-      <c r="E44" s="9">
-        <v>-0.74</v>
+        <v>-43.11</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-0.96</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C45" s="7">
-        <v>-42.45</v>
+        <v>-34.4</v>
       </c>
       <c r="D45" s="7">
-        <v>-42.15</v>
-      </c>
-      <c r="E45" s="8">
-        <v>0.3</v>
+        <v>-34.28</v>
+      </c>
+      <c r="E45" s="9">
+        <v>0.12</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C46" s="7">
-        <v>-34.27</v>
+        <v>14.4</v>
       </c>
       <c r="D46" s="7">
-        <v>-34.4</v>
-      </c>
-      <c r="E46" s="9">
-        <v>-0.13</v>
+        <v>14.05</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-0.35</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C47" s="7">
-        <v>12.77</v>
+        <v>-5.87</v>
       </c>
       <c r="D47" s="7">
-        <v>14.4</v>
+        <v>-6.16</v>
       </c>
       <c r="E47" s="8">
-        <v>1.63</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C48" s="7">
-        <v>-4.52</v>
+        <v>-36.83</v>
       </c>
       <c r="D48" s="7">
-        <v>-5.87</v>
+        <v>-36.55</v>
       </c>
       <c r="E48" s="9">
-        <v>-1.35</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C49" s="7">
-        <v>-34.51</v>
+        <v>-7.97</v>
       </c>
       <c r="D49" s="7">
-        <v>-36.83</v>
+        <v>-3.57</v>
       </c>
       <c r="E49" s="9">
-        <v>-2.32</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C50" s="7">
-        <v>-7.34</v>
+        <v>-4.1</v>
       </c>
       <c r="D50" s="7">
-        <v>-7.97</v>
-      </c>
-      <c r="E50" s="9">
-        <v>-0.63</v>
+        <v>-4.24</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-0.14</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C51" s="7">
-        <v>-4.46</v>
+        <v>14.89</v>
       </c>
       <c r="D51" s="7">
-        <v>-4.1</v>
+        <v>12.92</v>
       </c>
       <c r="E51" s="8">
-        <v>0.36</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C52" s="7">
-        <v>12.67</v>
+        <v>-24.97</v>
       </c>
       <c r="D52" s="7">
-        <v>14.89</v>
-      </c>
-      <c r="E52" s="8">
-        <v>2.22</v>
+        <v>-24.38</v>
+      </c>
+      <c r="E52" s="9">
+        <v>0.59</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C53" s="7">
-        <v>-24.53</v>
+        <v>36.55</v>
       </c>
       <c r="D53" s="7">
-        <v>-24.97</v>
+        <v>37.26</v>
       </c>
       <c r="E53" s="9">
-        <v>-0.44</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C54" s="7">
-        <v>35.11</v>
+        <v>-48.92</v>
       </c>
       <c r="D54" s="7">
-        <v>36.55</v>
-      </c>
-      <c r="E54" s="8">
-        <v>1.44</v>
+        <v>-46.89</v>
+      </c>
+      <c r="E54" s="9">
+        <v>2.03</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C55" s="7">
-        <v>-49.4</v>
+        <v>-27.89</v>
       </c>
       <c r="D55" s="7">
-        <v>-48.92</v>
+        <v>-30.16</v>
       </c>
       <c r="E55" s="8">
-        <v>0.48</v>
+        <v>-2.27</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C56" s="7">
-        <v>-26.51</v>
+        <v>-37.15</v>
       </c>
       <c r="D56" s="7">
-        <v>-27.89</v>
+        <v>-37.13</v>
       </c>
       <c r="E56" s="9">
-        <v>-1.38</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C57" s="7">
-        <v>-36.05</v>
+        <v>-19.92</v>
       </c>
       <c r="D57" s="7">
-        <v>-37.15</v>
+        <v>-18.11</v>
       </c>
       <c r="E57" s="9">
-        <v>-1.1</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="6" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C58" s="7">
-        <v>-18.12</v>
+        <v>10.23</v>
       </c>
       <c r="D58" s="7">
-        <v>-19.92</v>
-      </c>
-      <c r="E58" s="9">
-        <v>-1.8</v>
+        <v>5.34</v>
+      </c>
+      <c r="E58" s="8">
+        <v>-4.89</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C59" s="7">
-        <v>8.130000000000001</v>
+        <v>35.85</v>
       </c>
       <c r="D59" s="7">
-        <v>10.23</v>
+        <v>29.76</v>
       </c>
       <c r="E59" s="8">
-        <v>2.1</v>
+        <v>-6.09</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C60" s="7">
-        <v>36.59</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="D60" s="7">
-        <v>35.85</v>
-      </c>
-      <c r="E60" s="9">
-        <v>-0.74</v>
+        <v>-11.24</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-2.79</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C61" s="7">
-        <v>-9.56</v>
+        <v>-18.64</v>
       </c>
       <c r="D61" s="7">
-        <v>-8.449999999999999</v>
-      </c>
-      <c r="E61" s="8">
-        <v>1.11</v>
+        <v>-18.15</v>
+      </c>
+      <c r="E61" s="9">
+        <v>0.49</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C62" s="7">
-        <v>-15.64</v>
+        <v>-9.83</v>
       </c>
       <c r="D62" s="7">
-        <v>-18.64</v>
-      </c>
-      <c r="E62" s="9">
-        <v>-3</v>
+        <v>-10.28</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-0.45</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C63" s="7">
-        <v>-11.41</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="D63" s="7">
-        <v>-9.83</v>
-      </c>
-      <c r="E63" s="8">
-        <v>1.58</v>
+        <v>-9.19</v>
+      </c>
+      <c r="E63" s="9">
+        <v>0.52</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C64" s="7">
-        <v>-8.470000000000001</v>
+        <v>-15.62</v>
       </c>
       <c r="D64" s="7">
-        <v>-9.710000000000001</v>
-      </c>
-      <c r="E64" s="9">
-        <v>-1.24</v>
+        <v>-16.14</v>
+      </c>
+      <c r="E64" s="8">
+        <v>-0.52</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C65" s="7">
-        <v>-14.67</v>
+        <v>-2.65</v>
       </c>
       <c r="D65" s="7">
-        <v>-15.62</v>
-      </c>
-      <c r="E65" s="9">
-        <v>-0.95</v>
+        <v>-3.12</v>
+      </c>
+      <c r="E65" s="8">
+        <v>-0.47</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C66" s="7">
-        <v>-4.26</v>
+        <v>-5.19</v>
       </c>
       <c r="D66" s="7">
-        <v>-2.65</v>
+        <v>-6.75</v>
       </c>
       <c r="E66" s="8">
-        <v>1.61</v>
+        <v>-1.56</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C67" s="7">
-        <v>-7.4</v>
+        <v>-2.69</v>
       </c>
       <c r="D67" s="7">
-        <v>-5.19</v>
+        <v>-5.6</v>
       </c>
       <c r="E67" s="8">
-        <v>2.21</v>
+        <v>-2.91</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C68" s="7">
-        <v>-5.7</v>
+        <v>3.39</v>
       </c>
       <c r="D68" s="7">
-        <v>-2.69</v>
+        <v>1.98</v>
       </c>
       <c r="E68" s="8">
-        <v>3.01</v>
+        <v>-1.41</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C69" s="7">
-        <v>4.72</v>
+        <v>24.34</v>
       </c>
       <c r="D69" s="7">
-        <v>3.39</v>
-      </c>
-      <c r="E69" s="9">
-        <v>-1.33</v>
+        <v>20</v>
+      </c>
+      <c r="E69" s="8">
+        <v>-4.34</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B70" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C70" s="7">
-        <v>23.38</v>
+        <v>4.18</v>
       </c>
       <c r="D70" s="7">
-        <v>24.34</v>
+        <v>2.3</v>
       </c>
       <c r="E70" s="8">
-        <v>0.96</v>
+        <v>-1.88</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C71" s="7">
-        <v>1.56</v>
+        <v>2.88</v>
       </c>
       <c r="D71" s="7">
-        <v>4.18</v>
+        <v>-3.07</v>
       </c>
       <c r="E71" s="8">
-        <v>2.62</v>
+        <v>-5.95</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B72" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C72" s="7">
-        <v>3.88</v>
+        <v>-14.28</v>
       </c>
       <c r="D72" s="7">
-        <v>2.88</v>
-      </c>
-      <c r="E72" s="9">
-        <v>-1</v>
+        <v>-22.67</v>
+      </c>
+      <c r="E72" s="8">
+        <v>-8.390000000000001</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B73" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C73" s="7">
-        <v>-14.14</v>
+        <v>-10.17</v>
       </c>
       <c r="D73" s="7">
-        <v>-14.28</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="E73" s="9">
-        <v>-0.14</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="6" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C74" s="7">
-        <v>-10.98</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="D74" s="7">
-        <v>-10.17</v>
+        <v>-9.5</v>
       </c>
       <c r="E74" s="8">
-        <v>0.8100000000000001</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C75" s="7">
-        <v>-8.960000000000001</v>
+        <v>-11.39</v>
       </c>
       <c r="D75" s="7">
-        <v>-8.609999999999999</v>
+        <v>-13.31</v>
       </c>
       <c r="E75" s="8">
-        <v>0.35</v>
+        <v>-1.92</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C76" s="7">
-        <v>-10.02</v>
+        <v>-42.84</v>
       </c>
       <c r="D76" s="7">
-        <v>-11.39</v>
+        <v>-40.71</v>
       </c>
       <c r="E76" s="9">
-        <v>-1.37</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C77" s="7">
-        <v>-42.48</v>
+        <v>-39.08</v>
       </c>
       <c r="D77" s="7">
-        <v>-42.84</v>
+        <v>-38.32</v>
       </c>
       <c r="E77" s="9">
-        <v>-0.36</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C78" s="7">
-        <v>-38.61</v>
+        <v>-14.01</v>
       </c>
       <c r="D78" s="7">
-        <v>-39.08</v>
-      </c>
-      <c r="E78" s="9">
-        <v>-0.47</v>
+        <v>-14.42</v>
+      </c>
+      <c r="E78" s="8">
+        <v>-0.41</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C79" s="7">
-        <v>-14.98</v>
+        <v>-20.58</v>
       </c>
       <c r="D79" s="7">
-        <v>-14.01</v>
+        <v>-20.69</v>
       </c>
       <c r="E79" s="8">
-        <v>0.97</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B80" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C80" s="7">
-        <v>-19.54</v>
+        <v>-41.16</v>
       </c>
       <c r="D80" s="7">
-        <v>-20.58</v>
+        <v>-40.71</v>
       </c>
       <c r="E80" s="9">
-        <v>-1.04</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B81" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C81" s="7">
-        <v>-39.27</v>
+        <v>-41.21</v>
       </c>
       <c r="D81" s="7">
-        <v>-41.16</v>
+        <v>-38.71</v>
       </c>
       <c r="E81" s="9">
-        <v>-1.89</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B82" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C82" s="7">
-        <v>-40.9</v>
+        <v>-19.88</v>
       </c>
       <c r="D82" s="7">
-        <v>-41.21</v>
-      </c>
-      <c r="E82" s="9">
-        <v>-0.31</v>
+        <v>-20.53</v>
+      </c>
+      <c r="E82" s="8">
+        <v>-0.65</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B83" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C83" s="7">
-        <v>-20.84</v>
+        <v>-12.88</v>
       </c>
       <c r="D83" s="7">
-        <v>-19.88</v>
+        <v>-13.79</v>
       </c>
       <c r="E83" s="8">
-        <v>0.96</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B84" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C84" s="7">
-        <v>-15.01</v>
+        <v>-31.47</v>
       </c>
       <c r="D84" s="7">
-        <v>-12.88</v>
+        <v>-31.59</v>
       </c>
       <c r="E84" s="8">
-        <v>2.13</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B85" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C85" s="7">
-        <v>-29.99</v>
+        <v>-3.18</v>
       </c>
       <c r="D85" s="7">
-        <v>-31.47</v>
+        <v>-2.87</v>
       </c>
       <c r="E85" s="9">
-        <v>-1.48</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B86" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C86" s="7">
-        <v>-3.52</v>
+        <v>-46.87</v>
       </c>
       <c r="D86" s="7">
-        <v>-3.18</v>
-      </c>
-      <c r="E86" s="8">
-        <v>0.34</v>
+        <v>-45.91</v>
+      </c>
+      <c r="E86" s="9">
+        <v>0.96</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B87" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C87" s="7">
-        <v>-49.39</v>
+        <v>-41.75</v>
       </c>
       <c r="D87" s="7">
-        <v>-46.87</v>
+        <v>-43.78</v>
       </c>
       <c r="E87" s="8">
-        <v>2.52</v>
+        <v>-2.03</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B88" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C88" s="7">
-        <v>-41.19</v>
+        <v>-38.54</v>
       </c>
       <c r="D88" s="7">
-        <v>-41.75</v>
-      </c>
-      <c r="E88" s="9">
-        <v>-0.5600000000000001</v>
+        <v>-38.92</v>
+      </c>
+      <c r="E88" s="8">
+        <v>-0.38</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B89" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C89" s="7">
-        <v>-37.93</v>
+        <v>-26.51</v>
       </c>
       <c r="D89" s="7">
-        <v>-38.54</v>
+        <v>-25.57</v>
       </c>
       <c r="E89" s="9">
-        <v>-0.61</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="6" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C90" s="7">
-        <v>-26.45</v>
+        <v>722.75</v>
       </c>
       <c r="D90" s="7">
-        <v>-26.51</v>
-      </c>
-      <c r="E90" s="9">
-        <v>-0.06</v>
+        <v>715.75</v>
+      </c>
+      <c r="E90" s="8">
+        <v>-7</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B91" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C91" s="7">
-        <v>720</v>
+        <v>958.3</v>
       </c>
       <c r="D91" s="7">
-        <v>722.75</v>
+        <v>937.55</v>
       </c>
       <c r="E91" s="8">
-        <v>2.75</v>
+        <v>-20.75</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B92" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C92" s="7">
-        <v>973.1</v>
+        <v>204.01</v>
       </c>
       <c r="D92" s="7">
-        <v>958.3</v>
-      </c>
-      <c r="E92" s="9">
-        <v>-14.8</v>
+        <v>203.06</v>
+      </c>
+      <c r="E92" s="8">
+        <v>-0.95</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B93" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C93" s="7">
-        <v>205.29</v>
+        <v>603.05</v>
       </c>
       <c r="D93" s="7">
-        <v>204.01</v>
+        <v>610.55</v>
       </c>
       <c r="E93" s="9">
-        <v>-1.28</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B94" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C94" s="7">
-        <v>607.7</v>
+        <v>1772.8</v>
       </c>
       <c r="D94" s="7">
-        <v>603.05</v>
-      </c>
-      <c r="E94" s="9">
-        <v>-4.65</v>
+        <v>1764.4</v>
+      </c>
+      <c r="E94" s="8">
+        <v>-8.4</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B95" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C95" s="7">
-        <v>1752.8</v>
+        <v>1001</v>
       </c>
       <c r="D95" s="7">
-        <v>1772.8</v>
+        <v>999.6</v>
       </c>
       <c r="E95" s="8">
-        <v>20</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B96" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C96" s="7">
-        <v>1014.1</v>
+        <v>3383</v>
       </c>
       <c r="D96" s="7">
-        <v>1001</v>
+        <v>3409</v>
       </c>
       <c r="E96" s="9">
-        <v>-13.1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B97" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C97" s="7">
-        <v>3492</v>
+        <v>618.8</v>
       </c>
       <c r="D97" s="7">
-        <v>3383</v>
+        <v>645.15</v>
       </c>
       <c r="E97" s="9">
-        <v>-109</v>
+        <v>26.35</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B98" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C98" s="7">
-        <v>622.05</v>
+        <v>370</v>
       </c>
       <c r="D98" s="7">
-        <v>618.8</v>
-      </c>
-      <c r="E98" s="9">
-        <v>-3.25</v>
+        <v>367</v>
+      </c>
+      <c r="E98" s="8">
+        <v>-3</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B99" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C99" s="7">
-        <v>365.55</v>
+        <v>188.75</v>
       </c>
       <c r="D99" s="7">
-        <v>370</v>
+        <v>186.78</v>
       </c>
       <c r="E99" s="8">
-        <v>4.45</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B100" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C100" s="7">
-        <v>184.15</v>
+        <v>2208</v>
       </c>
       <c r="D100" s="7">
-        <v>188.75</v>
+        <v>2204.1</v>
       </c>
       <c r="E100" s="8">
-        <v>4.6</v>
+        <v>-3.9</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B101" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C101" s="7">
-        <v>2255.5</v>
+        <v>5005</v>
       </c>
       <c r="D101" s="7">
-        <v>2208</v>
+        <v>5021</v>
       </c>
       <c r="E101" s="9">
-        <v>-47.5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B102" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C102" s="7">
-        <v>4987</v>
+        <v>2820</v>
       </c>
       <c r="D102" s="7">
-        <v>5005</v>
+        <v>2818.7</v>
       </c>
       <c r="E102" s="8">
-        <v>18</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B103" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C103" s="7">
-        <v>2793.6</v>
+        <v>228.79</v>
       </c>
       <c r="D103" s="7">
-        <v>2820</v>
+        <v>220.8</v>
       </c>
       <c r="E103" s="8">
-        <v>26.4</v>
+        <v>-7.99</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B104" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C104" s="7">
-        <v>230.98</v>
+        <v>36.13</v>
       </c>
       <c r="D104" s="7">
-        <v>228.79</v>
-      </c>
-      <c r="E104" s="9">
-        <v>-2.19</v>
+        <v>35.91</v>
+      </c>
+      <c r="E104" s="8">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B105" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C105" s="7">
-        <v>36.49</v>
+        <v>1143.8</v>
       </c>
       <c r="D105" s="7">
-        <v>36.13</v>
+        <v>1158.5</v>
       </c>
       <c r="E105" s="9">
-        <v>-0.36</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="6" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C106" s="7">
-        <v>1144.8</v>
+        <v>7</v>
       </c>
       <c r="D106" s="7">
-        <v>1143.8</v>
+        <v>13</v>
       </c>
       <c r="E106" s="9">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B107" s="6" t="s">
         <v>13</v>
@@ -4733,611 +4727,662 @@
         <v>13</v>
       </c>
       <c r="D107" s="7">
-        <v>26</v>
-      </c>
-      <c r="E107" s="8">
-        <v>13</v>
+        <v>19</v>
+      </c>
+      <c r="E107" s="9">
+        <v>6</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B108" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C108" s="7">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="D108" s="7">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="E108" s="9">
-        <v>-13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B109" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C109" s="7">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="D109" s="7">
-        <v>47</v>
-      </c>
-      <c r="E109" s="9">
-        <v>-3</v>
+        <v>62</v>
+      </c>
+      <c r="E109" s="8">
+        <v>-6</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B110" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C110" s="7">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D110" s="7">
-        <v>47</v>
-      </c>
-      <c r="E110" s="8">
+        <v>50</v>
+      </c>
+      <c r="E110" s="9">
         <v>3</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="6" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C111" s="7">
-        <v>47.63</v>
+        <v>47</v>
       </c>
       <c r="D111" s="7">
-        <v>49.03</v>
+        <v>38</v>
       </c>
       <c r="E111" s="8">
-        <v>1.4</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="6" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C112" s="7">
-        <v>55.07</v>
+        <v>19</v>
       </c>
       <c r="D112" s="7">
-        <v>52.4</v>
-      </c>
-      <c r="E112" s="9">
-        <v>-2.67</v>
+        <v>7</v>
+      </c>
+      <c r="E112" s="8">
+        <v>-12</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="6" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C113" s="7">
-        <v>33.15</v>
+        <v>38</v>
       </c>
       <c r="D113" s="7">
-        <v>31.25</v>
+        <v>44</v>
       </c>
       <c r="E113" s="9">
-        <v>-1.9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B114" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C114" s="7">
-        <v>30.08</v>
+        <v>49.03</v>
       </c>
       <c r="D114" s="7">
-        <v>28.73</v>
-      </c>
-      <c r="E114" s="9">
-        <v>-1.35</v>
+        <v>45.68</v>
+      </c>
+      <c r="E114" s="8">
+        <v>-3.35</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B115" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C115" s="7">
-        <v>53.5</v>
+        <v>52.4</v>
       </c>
       <c r="D115" s="7">
-        <v>56.37</v>
+        <v>48.84</v>
       </c>
       <c r="E115" s="8">
-        <v>2.87</v>
+        <v>-3.56</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B116" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C116" s="7">
-        <v>35.06</v>
+        <v>31.25</v>
       </c>
       <c r="D116" s="7">
-        <v>31.7</v>
-      </c>
-      <c r="E116" s="9">
-        <v>-3.36</v>
+        <v>29.87</v>
+      </c>
+      <c r="E116" s="8">
+        <v>-1.38</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B117" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C117" s="7">
-        <v>35.53</v>
+        <v>28.73</v>
       </c>
       <c r="D117" s="7">
-        <v>29.32</v>
+        <v>33.89</v>
       </c>
       <c r="E117" s="9">
-        <v>-6.21</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B118" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C118" s="7">
-        <v>32.86</v>
+        <v>56.37</v>
       </c>
       <c r="D118" s="7">
-        <v>31.48</v>
-      </c>
-      <c r="E118" s="9">
-        <v>-1.38</v>
+        <v>54.84</v>
+      </c>
+      <c r="E118" s="8">
+        <v>-1.53</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="6" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B119" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C119" s="7">
-        <v>45.57</v>
+        <v>31.7</v>
       </c>
       <c r="D119" s="7">
-        <v>50.63</v>
+        <v>31.36</v>
       </c>
       <c r="E119" s="8">
-        <v>5.06</v>
+        <v>-0.34</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="6" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B120" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C120" s="7">
-        <v>45.09</v>
+        <v>29.32</v>
       </c>
       <c r="D120" s="7">
-        <v>54.93</v>
-      </c>
-      <c r="E120" s="8">
-        <v>9.84</v>
+        <v>32.36</v>
+      </c>
+      <c r="E120" s="9">
+        <v>3.04</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B121" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C121" s="7">
-        <v>43.18</v>
+        <v>31.48</v>
       </c>
       <c r="D121" s="7">
-        <v>38.79</v>
+        <v>49.86</v>
       </c>
       <c r="E121" s="9">
-        <v>-4.39</v>
+        <v>18.38</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="6" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B122" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C122" s="7">
-        <v>48.72</v>
+        <v>50.63</v>
       </c>
       <c r="D122" s="7">
-        <v>50.84</v>
+        <v>47.43</v>
       </c>
       <c r="E122" s="8">
-        <v>2.12</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B123" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C123" s="7">
-        <v>33.8</v>
+        <v>54.93</v>
       </c>
       <c r="D123" s="7">
-        <v>38.43</v>
+        <v>50.74</v>
       </c>
       <c r="E123" s="8">
-        <v>4.63</v>
+        <v>-4.19</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B124" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C124" s="7">
-        <v>50.19</v>
+        <v>38.79</v>
       </c>
       <c r="D124" s="7">
-        <v>46.9</v>
-      </c>
-      <c r="E124" s="9">
-        <v>-3.29</v>
+        <v>38.44</v>
+      </c>
+      <c r="E124" s="8">
+        <v>-0.35</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="6" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B125" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C125" s="7">
-        <v>35.46</v>
+        <v>50.84</v>
       </c>
       <c r="D125" s="7">
-        <v>33.57</v>
+        <v>52.71</v>
       </c>
       <c r="E125" s="9">
-        <v>-1.89</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B126" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C126" s="7">
-        <v>30.47</v>
+        <v>38.43</v>
       </c>
       <c r="D126" s="7">
-        <v>30.33</v>
-      </c>
-      <c r="E126" s="9">
+        <v>38.29</v>
+      </c>
+      <c r="E126" s="8">
         <v>-0.14</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="6" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C127" s="7">
-        <v>-35.82</v>
+        <v>46.9</v>
       </c>
       <c r="D127" s="7">
-        <v>-43.48</v>
-      </c>
-      <c r="E127" s="9">
-        <v>-7.66</v>
+        <v>37.31</v>
+      </c>
+      <c r="E127" s="8">
+        <v>-9.59</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="6" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C128" s="7">
-        <v>295.88</v>
+        <v>33.57</v>
       </c>
       <c r="D128" s="7">
-        <v>-28.85</v>
-      </c>
-      <c r="E128" s="9">
-        <v>-324.73</v>
+        <v>32.43</v>
+      </c>
+      <c r="E128" s="8">
+        <v>-1.14</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="6" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C129" s="7">
-        <v>-45.05</v>
+        <v>30.33</v>
       </c>
       <c r="D129" s="7">
-        <v>-40.01</v>
-      </c>
-      <c r="E129" s="8">
-        <v>5.04</v>
+        <v>35.15</v>
+      </c>
+      <c r="E129" s="9">
+        <v>4.82</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B130" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C130" s="7">
-        <v>-47.39</v>
+        <v>-43.48</v>
       </c>
       <c r="D130" s="7">
-        <v>-47.8</v>
+        <v>-34.71</v>
       </c>
       <c r="E130" s="9">
-        <v>-0.41</v>
+        <v>8.77</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B131" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C131" s="7">
-        <v>-1.53</v>
+        <v>-28.85</v>
       </c>
       <c r="D131" s="7">
-        <v>-21.58</v>
-      </c>
-      <c r="E131" s="9">
-        <v>-20.05</v>
+        <v>-69.2</v>
+      </c>
+      <c r="E131" s="8">
+        <v>-40.35</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B132" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C132" s="7">
-        <v>-41.15</v>
+        <v>-40.01</v>
       </c>
       <c r="D132" s="7">
-        <v>-18.31</v>
-      </c>
-      <c r="E132" s="8">
-        <v>22.84</v>
+        <v>-17.65</v>
+      </c>
+      <c r="E132" s="9">
+        <v>22.36</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B133" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C133" s="7">
-        <v>-45.63</v>
+        <v>-47.8</v>
       </c>
       <c r="D133" s="7">
-        <v>51.92</v>
-      </c>
-      <c r="E133" s="8">
-        <v>97.55</v>
+        <v>15.5</v>
+      </c>
+      <c r="E133" s="9">
+        <v>63.3</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B134" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C134" s="7">
-        <v>-38.69</v>
+        <v>-21.58</v>
       </c>
       <c r="D134" s="7">
-        <v>-30.58</v>
+        <v>-28.53</v>
       </c>
       <c r="E134" s="8">
-        <v>8.109999999999999</v>
+        <v>-6.95</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="6" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B135" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C135" s="7">
-        <v>-48.17</v>
+        <v>-18.31</v>
       </c>
       <c r="D135" s="7">
-        <v>4</v>
-      </c>
-      <c r="E135" s="8">
-        <v>52.17</v>
+        <v>-12.58</v>
+      </c>
+      <c r="E135" s="9">
+        <v>5.73</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="6" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B136" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C136" s="7">
-        <v>-12.12</v>
+        <v>51.92</v>
       </c>
       <c r="D136" s="7">
-        <v>69.15000000000001</v>
+        <v>25.05</v>
       </c>
       <c r="E136" s="8">
-        <v>81.27</v>
+        <v>-26.87</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B137" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C137" s="7">
-        <v>-16.01</v>
+        <v>-30.58</v>
       </c>
       <c r="D137" s="7">
-        <v>32.51</v>
-      </c>
-      <c r="E137" s="8">
-        <v>48.52</v>
+        <v>4410.46</v>
+      </c>
+      <c r="E137" s="9">
+        <v>4441.04</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="6" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B138" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C138" s="7">
-        <v>-42.34</v>
+        <v>4</v>
       </c>
       <c r="D138" s="7">
-        <v>-15.84</v>
+        <v>-48.12</v>
       </c>
       <c r="E138" s="8">
-        <v>26.5</v>
+        <v>-52.12</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B139" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C139" s="7">
-        <v>-16.03</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="D139" s="7">
-        <v>-11.79</v>
+        <v>-17.78</v>
       </c>
       <c r="E139" s="8">
-        <v>4.24</v>
+        <v>-86.93000000000001</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B140" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C140" s="7">
-        <v>-35.92</v>
+        <v>32.51</v>
       </c>
       <c r="D140" s="7">
-        <v>-63.14</v>
-      </c>
-      <c r="E140" s="9">
-        <v>-27.22</v>
+        <v>-5.35</v>
+      </c>
+      <c r="E140" s="8">
+        <v>-37.86</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="6" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B141" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C141" s="7">
-        <v>-60.02</v>
+        <v>-15.84</v>
       </c>
       <c r="D141" s="7">
-        <v>-69.70999999999999</v>
-      </c>
-      <c r="E141" s="9">
-        <v>-9.69</v>
+        <v>-37.8</v>
+      </c>
+      <c r="E141" s="8">
+        <v>-21.96</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B142" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C142" s="7">
-        <v>-21.83</v>
+        <v>-11.79</v>
       </c>
       <c r="D142" s="7">
+        <v>-26.2</v>
+      </c>
+      <c r="E142" s="8">
+        <v>-14.41</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5">
+      <c r="A143" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B143" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C143" s="7">
+        <v>-63.14</v>
+      </c>
+      <c r="D143" s="7">
+        <v>202.97</v>
+      </c>
+      <c r="E143" s="9">
+        <v>266.11</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5">
+      <c r="A144" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B144" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C144" s="7">
+        <v>-69.70999999999999</v>
+      </c>
+      <c r="D144" s="7">
+        <v>-68.61</v>
+      </c>
+      <c r="E144" s="9">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5">
+      <c r="A145" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B145" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C145" s="7">
         <v>-55.21</v>
       </c>
-      <c r="E142" s="9">
-        <v>-33.38</v>
+      <c r="D145" s="7">
+        <v>-51.07</v>
+      </c>
+      <c r="E145" s="9">
+        <v>4.14</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5361,28 +5406,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="C1" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="D1" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="E1" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="F1" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="G1" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="H1" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="I1" s="10" t="s">
         <v>92</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -5396,16 +5441,16 @@
         <v>16</v>
       </c>
       <c r="D2" s="12">
-        <v>40.9</v>
+        <v>41.2</v>
       </c>
       <c r="E2" s="12">
         <v>20</v>
       </c>
       <c r="F2" s="12">
-        <v>-5.3</v>
+        <v>-4.5</v>
       </c>
       <c r="G2" s="12">
-        <v>-1</v>
+        <v>-3.5</v>
       </c>
       <c r="H2" s="12">
         <v>53.1</v>
@@ -5545,34 +5590,34 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="15">
-        <v>0.3895</v>
+        <v>0.4036</v>
       </c>
       <c r="B2" s="15">
-        <v>0.3795</v>
+        <v>0.3716</v>
       </c>
       <c r="C2" s="15">
-        <v>0.2344</v>
+        <v>0.236</v>
       </c>
       <c r="D2" s="15">
-        <v>0.2261</v>
+        <v>0.2304</v>
       </c>
       <c r="E2" s="15">
-        <v>0.2004</v>
+        <v>0.202</v>
       </c>
       <c r="F2" s="15">
-        <v>0.1387</v>
+        <v>0.1397</v>
       </c>
       <c r="G2" s="15">
-        <v>0.1211</v>
+        <v>0.119</v>
       </c>
       <c r="H2" s="15">
-        <v>0.0863</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="I2" s="15">
-        <v>0.0673</v>
+        <v>0.0682</v>
       </c>
       <c r="J2" s="15">
-        <v>0.0357</v>
+        <v>0.0339</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -5597,22 +5642,22 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="15">
-        <v>0.0002</v>
+        <v>0.0046</v>
       </c>
       <c r="B4" s="15">
-        <v>-0.0071</v>
+        <v>-0.0046</v>
       </c>
       <c r="C4" s="15">
-        <v>-0.0481</v>
+        <v>-0.04769999999999999</v>
       </c>
       <c r="D4" s="15">
-        <v>-0.0581</v>
+        <v>-0.0595</v>
       </c>
       <c r="E4" s="15">
-        <v>-0.0629</v>
+        <v>-0.0646</v>
       </c>
       <c r="F4" s="15">
-        <v>-0.0779</v>
+        <v>-0.0809</v>
       </c>
     </row>
   </sheetData>

--- a/TATA_GROUP_Technical_Metrics.xlsx
+++ b/TATA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="89">
   <si>
     <t>Symbol</t>
   </si>
@@ -214,52 +214,40 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>28.7 → 33.9</t>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>48.8 → 50.5</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>28.7</t>
-  </si>
-  <si>
-    <t>33.9</t>
-  </si>
-  <si>
-    <t>29.3 → 32.4</t>
-  </si>
-  <si>
-    <t>29.3</t>
-  </si>
-  <si>
-    <t>32.4</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>52.4 → 48.8</t>
+    <t>48.8</t>
+  </si>
+  <si>
+    <t>50.5</t>
+  </si>
+  <si>
+    <t>49.9 → 52.8</t>
+  </si>
+  <si>
+    <t>49.9</t>
+  </si>
+  <si>
+    <t>52.8</t>
+  </si>
+  <si>
+    <t>50.7 → 43.8</t>
   </si>
   <si>
     <t>🔴 BEARISH</t>
   </si>
   <si>
-    <t>52.4</t>
-  </si>
-  <si>
-    <t>48.8</t>
-  </si>
-  <si>
-    <t>50.6 → 47.4</t>
-  </si>
-  <si>
-    <t>50.6</t>
-  </si>
-  <si>
-    <t>47.4</t>
+    <t>50.7</t>
+  </si>
+  <si>
+    <t>43.8</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -472,8 +460,8 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -985,10 +973,10 @@
         <v>53</v>
       </c>
       <c r="C2">
-        <v>715.75</v>
+        <v>718.5</v>
       </c>
       <c r="D2">
-        <v>-0.97</v>
+        <v>0.38</v>
       </c>
       <c r="E2">
         <v>790.85</v>
@@ -997,46 +985,46 @@
         <v>570.95</v>
       </c>
       <c r="G2">
-        <v>-9.5</v>
+        <v>-9.15</v>
       </c>
       <c r="H2">
-        <v>25.36</v>
+        <v>25.84</v>
       </c>
       <c r="I2">
-        <v>-2.22</v>
+        <v>-0.21</v>
       </c>
       <c r="J2">
-        <v>-1.14</v>
+        <v>-0.45</v>
       </c>
       <c r="K2">
-        <v>5.34</v>
+        <v>4.15</v>
       </c>
       <c r="L2">
-        <v>-7.97</v>
+        <v>-7.35</v>
       </c>
       <c r="M2">
-        <v>37.16</v>
+        <v>37.24</v>
       </c>
       <c r="N2">
         <v>74</v>
       </c>
       <c r="O2">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="P2">
-        <v>718.9400000000001</v>
+        <v>718.64</v>
       </c>
       <c r="Q2">
-        <v>723.17</v>
+        <v>723.09</v>
       </c>
       <c r="R2">
-        <v>729.86</v>
+        <v>729.66</v>
       </c>
       <c r="S2">
-        <v>688.62</v>
+        <v>688.58</v>
       </c>
       <c r="T2">
-        <v>3.94</v>
+        <v>4.35</v>
       </c>
       <c r="U2" t="s">
         <v>54</v>
@@ -1051,34 +1039,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>45.68</v>
+        <v>47.21</v>
       </c>
       <c r="Z2">
-        <v>-2.1</v>
+        <v>-2.21</v>
       </c>
       <c r="AA2">
-        <v>-1.39</v>
+        <v>-1.55</v>
       </c>
       <c r="AB2">
-        <v>-0.71</v>
+        <v>-0.66</v>
       </c>
       <c r="AC2">
-        <v>55.38</v>
+        <v>54.66</v>
       </c>
       <c r="AD2">
-        <v>54.45</v>
+        <v>55.16</v>
       </c>
       <c r="AE2">
-        <v>14.23</v>
+        <v>14.09</v>
       </c>
       <c r="AF2">
-        <v>-34.71</v>
+        <v>-32.25</v>
       </c>
       <c r="AG2">
-        <v>738.37</v>
+        <v>738.38</v>
       </c>
       <c r="AH2">
-        <v>707.96</v>
+        <v>707.8</v>
       </c>
       <c r="AI2">
         <v>700.95</v>
@@ -1087,7 +1075,7 @@
         <v>56</v>
       </c>
       <c r="AK2">
-        <v>13.68</v>
+        <v>14.74</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1098,10 +1086,10 @@
         <v>53</v>
       </c>
       <c r="C3">
-        <v>937.55</v>
+        <v>947.25</v>
       </c>
       <c r="D3">
-        <v>-2.17</v>
+        <v>1.03</v>
       </c>
       <c r="E3">
         <v>1081.5</v>
@@ -1110,46 +1098,46 @@
         <v>505.36</v>
       </c>
       <c r="G3">
-        <v>-13.31</v>
+        <v>-12.41</v>
       </c>
       <c r="H3">
-        <v>85.52</v>
+        <v>87.44</v>
       </c>
       <c r="I3">
-        <v>0.41</v>
+        <v>3.95</v>
       </c>
       <c r="J3">
-        <v>-3.75</v>
+        <v>-9.57</v>
       </c>
       <c r="K3">
-        <v>29.76</v>
+        <v>32.31</v>
       </c>
       <c r="L3">
-        <v>15.41</v>
+        <v>17.85</v>
       </c>
       <c r="M3">
-        <v>11.9</v>
+        <v>12.13</v>
       </c>
       <c r="N3">
         <v>93</v>
       </c>
       <c r="O3">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P3">
-        <v>942.6799999999999</v>
+        <v>949.88</v>
       </c>
       <c r="Q3">
-        <v>946.74</v>
+        <v>942.87</v>
       </c>
       <c r="R3">
-        <v>942.0700000000001</v>
+        <v>942.4299999999999</v>
       </c>
       <c r="S3">
-        <v>755.5</v>
+        <v>756.0700000000001</v>
       </c>
       <c r="T3">
-        <v>24.1</v>
+        <v>25.29</v>
       </c>
       <c r="U3" t="s">
         <v>55</v>
@@ -1164,34 +1152,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>48.84</v>
+        <v>50.53</v>
       </c>
       <c r="Z3">
-        <v>-0.49</v>
+        <v>-0.2</v>
       </c>
       <c r="AA3">
-        <v>0.28</v>
+        <v>0.19</v>
       </c>
       <c r="AB3">
-        <v>-0.77</v>
+        <v>-0.39</v>
       </c>
       <c r="AC3">
-        <v>72.27</v>
+        <v>58.13</v>
       </c>
       <c r="AD3">
-        <v>66.51000000000001</v>
+        <v>68.84999999999999</v>
       </c>
       <c r="AE3">
-        <v>45.76</v>
+        <v>45.02</v>
       </c>
       <c r="AF3">
-        <v>-69.2</v>
+        <v>-70.43000000000001</v>
       </c>
       <c r="AG3">
-        <v>1030.93</v>
+        <v>1018.69</v>
       </c>
       <c r="AH3">
-        <v>862.55</v>
+        <v>867.0599999999999</v>
       </c>
       <c r="AI3">
         <v>1054.09</v>
@@ -1200,7 +1188,7 @@
         <v>57</v>
       </c>
       <c r="AK3">
-        <v>21.15</v>
+        <v>19.45</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1211,58 +1199,58 @@
         <v>53</v>
       </c>
       <c r="C4">
-        <v>203.06</v>
+        <v>201.99</v>
       </c>
       <c r="D4">
-        <v>-0.47</v>
+        <v>-0.53</v>
       </c>
       <c r="E4">
-        <v>342.51</v>
+        <v>336.34</v>
       </c>
       <c r="F4">
-        <v>203.06</v>
+        <v>201.99</v>
       </c>
       <c r="G4">
-        <v>-40.71</v>
+        <v>-39.94</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>-3.23</v>
+        <v>-3.27</v>
       </c>
       <c r="J4">
-        <v>-3.03</v>
+        <v>-5.14</v>
       </c>
       <c r="K4">
-        <v>-11.24</v>
+        <v>-11.73</v>
       </c>
       <c r="L4">
-        <v>-43.11</v>
+        <v>-41.03</v>
       </c>
       <c r="M4">
-        <v>-5.95</v>
+        <v>-6.04</v>
       </c>
       <c r="N4">
         <v>26</v>
       </c>
       <c r="O4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P4">
-        <v>205.47</v>
+        <v>204.1</v>
       </c>
       <c r="Q4">
-        <v>209.7</v>
+        <v>209.18</v>
       </c>
       <c r="R4">
-        <v>217.68</v>
+        <v>217.16</v>
       </c>
       <c r="S4">
-        <v>244.05</v>
+        <v>243.77</v>
       </c>
       <c r="T4">
-        <v>-16.8</v>
+        <v>-17.14</v>
       </c>
       <c r="U4" t="s">
         <v>54</v>
@@ -1277,43 +1265,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>29.87</v>
+        <v>28.36</v>
       </c>
       <c r="Z4">
-        <v>-3.49</v>
+        <v>-3.66</v>
       </c>
       <c r="AA4">
-        <v>-3.27</v>
+        <v>-3.34</v>
       </c>
       <c r="AB4">
-        <v>-0.22</v>
+        <v>-0.32</v>
       </c>
       <c r="AC4">
         <v>0</v>
       </c>
       <c r="AD4">
-        <v>7.49</v>
+        <v>0.97</v>
       </c>
       <c r="AE4">
-        <v>4.2</v>
+        <v>4.09</v>
       </c>
       <c r="AF4">
-        <v>-17.65</v>
+        <v>-46.5</v>
       </c>
       <c r="AG4">
-        <v>216.22</v>
+        <v>216.4</v>
       </c>
       <c r="AH4">
-        <v>203.19</v>
+        <v>201.95</v>
       </c>
       <c r="AI4">
-        <v>216.14</v>
+        <v>214.01</v>
       </c>
       <c r="AJ4" t="s">
         <v>57</v>
       </c>
       <c r="AK4">
-        <v>35.36</v>
+        <v>38.76</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1324,10 +1312,10 @@
         <v>53</v>
       </c>
       <c r="C5">
-        <v>610.55</v>
+        <v>612.45</v>
       </c>
       <c r="D5">
-        <v>1.24</v>
+        <v>0.31</v>
       </c>
       <c r="E5">
         <v>989.9299999999999</v>
@@ -1336,46 +1324,46 @@
         <v>574.42</v>
       </c>
       <c r="G5">
-        <v>-38.32</v>
+        <v>-38.13</v>
       </c>
       <c r="H5">
-        <v>6.29</v>
+        <v>6.62</v>
       </c>
       <c r="I5">
-        <v>-4.8</v>
+        <v>-2.02</v>
       </c>
       <c r="J5">
-        <v>-9.300000000000001</v>
+        <v>-8.869999999999999</v>
       </c>
       <c r="K5">
-        <v>-18.15</v>
+        <v>-16.68</v>
       </c>
       <c r="L5">
-        <v>-34.28</v>
+        <v>-34.23</v>
       </c>
       <c r="M5">
-        <v>-4.77</v>
+        <v>-4.71</v>
       </c>
       <c r="N5">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="O5">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P5">
-        <v>611.95</v>
+        <v>609.42</v>
       </c>
       <c r="Q5">
-        <v>634.72</v>
+        <v>631.8099999999999</v>
       </c>
       <c r="R5">
-        <v>666.42</v>
+        <v>664.8099999999999</v>
       </c>
       <c r="S5">
-        <v>705.76</v>
+        <v>704.86</v>
       </c>
       <c r="T5">
-        <v>-13.49</v>
+        <v>-13.11</v>
       </c>
       <c r="U5" t="s">
         <v>54</v>
@@ -1390,34 +1378,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>33.89</v>
+        <v>35.17</v>
       </c>
       <c r="Z5">
-        <v>-15.97</v>
+        <v>-15.75</v>
       </c>
       <c r="AA5">
-        <v>-14.21</v>
+        <v>-14.52</v>
       </c>
       <c r="AB5">
-        <v>-1.75</v>
+        <v>-1.23</v>
       </c>
       <c r="AC5">
-        <v>28.13</v>
+        <v>35.71</v>
       </c>
       <c r="AD5">
-        <v>29.45</v>
+        <v>29.61</v>
       </c>
       <c r="AE5">
-        <v>15.17</v>
+        <v>15.24</v>
       </c>
       <c r="AF5">
-        <v>15.5</v>
+        <v>27.9</v>
       </c>
       <c r="AG5">
-        <v>672.09</v>
+        <v>666.35</v>
       </c>
       <c r="AH5">
-        <v>597.35</v>
+        <v>597.26</v>
       </c>
       <c r="AI5">
         <v>650.02</v>
@@ -1426,7 +1414,7 @@
         <v>57</v>
       </c>
       <c r="AK5">
-        <v>18.75</v>
+        <v>17.9</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1437,10 +1425,10 @@
         <v>53</v>
       </c>
       <c r="C6">
-        <v>1764.4</v>
+        <v>1761.6</v>
       </c>
       <c r="D6">
-        <v>-0.47</v>
+        <v>-0.16</v>
       </c>
       <c r="E6">
         <v>2061.7</v>
@@ -1449,25 +1437,25 @@
         <v>1347.9</v>
       </c>
       <c r="G6">
-        <v>-14.42</v>
+        <v>-14.56</v>
       </c>
       <c r="H6">
-        <v>30.9</v>
+        <v>30.69</v>
       </c>
       <c r="I6">
-        <v>4.01</v>
+        <v>0.31</v>
       </c>
       <c r="J6">
-        <v>1.62</v>
+        <v>0.19</v>
       </c>
       <c r="K6">
-        <v>-10.28</v>
+        <v>-8.91</v>
       </c>
       <c r="L6">
-        <v>14.05</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="M6">
-        <v>6.82</v>
+        <v>6.78</v>
       </c>
       <c r="N6">
         <v>81</v>
@@ -1476,19 +1464,19 @@
         <v>57</v>
       </c>
       <c r="P6">
-        <v>1756.92</v>
+        <v>1758.02</v>
       </c>
       <c r="Q6">
-        <v>1709.15</v>
+        <v>1711.32</v>
       </c>
       <c r="R6">
-        <v>1765.29</v>
+        <v>1762.38</v>
       </c>
       <c r="S6">
-        <v>1713.73</v>
+        <v>1713.41</v>
       </c>
       <c r="T6">
-        <v>2.96</v>
+        <v>2.81</v>
       </c>
       <c r="U6" t="s">
         <v>54</v>
@@ -1503,34 +1491,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>54.84</v>
+        <v>54.31</v>
       </c>
       <c r="Z6">
-        <v>-0.6899999999999999</v>
+        <v>1.48</v>
       </c>
       <c r="AA6">
-        <v>-13.83</v>
+        <v>-10.77</v>
       </c>
       <c r="AB6">
-        <v>13.14</v>
+        <v>12.25</v>
       </c>
       <c r="AC6">
-        <v>96.52</v>
+        <v>94.31999999999999</v>
       </c>
       <c r="AD6">
-        <v>95.48</v>
+        <v>95.27</v>
       </c>
       <c r="AE6">
-        <v>45.05</v>
+        <v>44.49</v>
       </c>
       <c r="AF6">
-        <v>-28.53</v>
+        <v>-36.25</v>
       </c>
       <c r="AG6">
-        <v>1780.97</v>
+        <v>1786.82</v>
       </c>
       <c r="AH6">
-        <v>1637.32</v>
+        <v>1635.82</v>
       </c>
       <c r="AI6">
         <v>1813.9</v>
@@ -1539,7 +1527,7 @@
         <v>57</v>
       </c>
       <c r="AK6">
-        <v>25.26</v>
+        <v>24.72</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1550,58 +1538,58 @@
         <v>53</v>
       </c>
       <c r="C7">
-        <v>999.6</v>
+        <v>991</v>
       </c>
       <c r="D7">
-        <v>-0.14</v>
+        <v>-0.86</v>
       </c>
       <c r="E7">
         <v>1260.34</v>
       </c>
       <c r="F7">
-        <v>999.6</v>
+        <v>991</v>
       </c>
       <c r="G7">
-        <v>-20.69</v>
+        <v>-21.37</v>
       </c>
       <c r="H7">
         <v>0</v>
       </c>
       <c r="I7">
-        <v>-1.92</v>
+        <v>-1.88</v>
       </c>
       <c r="J7">
-        <v>-5.87</v>
+        <v>-9.119999999999999</v>
       </c>
       <c r="K7">
-        <v>-9.19</v>
+        <v>-9.94</v>
       </c>
       <c r="L7">
-        <v>-6.16</v>
+        <v>-7.76</v>
       </c>
       <c r="M7">
-        <v>3.39</v>
+        <v>3.21</v>
       </c>
       <c r="N7">
         <v>56</v>
       </c>
       <c r="O7">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P7">
-        <v>1007.94</v>
+        <v>1004.14</v>
       </c>
       <c r="Q7">
-        <v>1038.93</v>
+        <v>1034.51</v>
       </c>
       <c r="R7">
-        <v>1072.84</v>
+        <v>1070.33</v>
       </c>
       <c r="S7">
-        <v>1120.4</v>
+        <v>1119.51</v>
       </c>
       <c r="T7">
-        <v>-10.78</v>
+        <v>-11.48</v>
       </c>
       <c r="U7" t="s">
         <v>54</v>
@@ -1616,43 +1604,43 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>31.36</v>
+        <v>29.25</v>
       </c>
       <c r="Z7">
-        <v>-21.09</v>
+        <v>-21.98</v>
       </c>
       <c r="AA7">
-        <v>-18.31</v>
+        <v>-19.04</v>
       </c>
       <c r="AB7">
-        <v>-2.78</v>
+        <v>-2.93</v>
       </c>
       <c r="AC7">
-        <v>8.59</v>
+        <v>0</v>
       </c>
       <c r="AD7">
-        <v>15.72</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AE7">
-        <v>17.71</v>
+        <v>17.3</v>
       </c>
       <c r="AF7">
-        <v>-12.58</v>
+        <v>-18.53</v>
       </c>
       <c r="AG7">
-        <v>1088.86</v>
+        <v>1084.99</v>
       </c>
       <c r="AH7">
-        <v>989.01</v>
+        <v>984.03</v>
       </c>
       <c r="AI7">
-        <v>1052.18</v>
+        <v>1045.9</v>
       </c>
       <c r="AJ7" t="s">
         <v>57</v>
       </c>
       <c r="AK7">
-        <v>67.48</v>
+        <v>70.27</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1663,10 +1651,10 @@
         <v>53</v>
       </c>
       <c r="C8">
-        <v>3409</v>
+        <v>3383</v>
       </c>
       <c r="D8">
-        <v>0.77</v>
+        <v>-0.76</v>
       </c>
       <c r="E8">
         <v>5749.89</v>
@@ -1675,46 +1663,46 @@
         <v>3383</v>
       </c>
       <c r="G8">
-        <v>-40.71</v>
+        <v>-41.16</v>
       </c>
       <c r="H8">
-        <v>0.77</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>-4.78</v>
+        <v>-4.92</v>
       </c>
       <c r="J8">
-        <v>-8.16</v>
+        <v>-10.46</v>
       </c>
       <c r="K8">
-        <v>-16.14</v>
+        <v>-16.84</v>
       </c>
       <c r="L8">
-        <v>-36.55</v>
+        <v>-37.99</v>
       </c>
       <c r="M8">
-        <v>-6.46</v>
+        <v>-6.6</v>
       </c>
       <c r="N8">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="O8">
         <v>9</v>
       </c>
       <c r="P8">
-        <v>3467.8</v>
+        <v>3432.8</v>
       </c>
       <c r="Q8">
-        <v>3614.36</v>
+        <v>3594.88</v>
       </c>
       <c r="R8">
-        <v>3633.17</v>
+        <v>3627.25</v>
       </c>
       <c r="S8">
-        <v>4351.7</v>
+        <v>4343.25</v>
       </c>
       <c r="T8">
-        <v>-21.66</v>
+        <v>-22.11</v>
       </c>
       <c r="U8" t="s">
         <v>54</v>
@@ -1729,43 +1717,43 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>32.36</v>
+        <v>30.93</v>
       </c>
       <c r="Z8">
-        <v>-67.95999999999999</v>
+        <v>-75.12</v>
       </c>
       <c r="AA8">
-        <v>-42.25</v>
+        <v>-48.83</v>
       </c>
       <c r="AB8">
-        <v>-25.7</v>
+        <v>-26.29</v>
       </c>
       <c r="AC8">
-        <v>5.2</v>
+        <v>7.96</v>
       </c>
       <c r="AD8">
-        <v>1.73</v>
+        <v>4.39</v>
       </c>
       <c r="AE8">
-        <v>88.5</v>
+        <v>84.84</v>
       </c>
       <c r="AF8">
-        <v>25.05</v>
+        <v>-32.87</v>
       </c>
       <c r="AG8">
-        <v>3824.01</v>
+        <v>3814.75</v>
       </c>
       <c r="AH8">
-        <v>3404.72</v>
+        <v>3375.01</v>
       </c>
       <c r="AI8">
-        <v>3678.96</v>
+        <v>3646.88</v>
       </c>
       <c r="AJ8" t="s">
         <v>57</v>
       </c>
       <c r="AK8">
-        <v>37.96</v>
+        <v>41.92</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1776,10 +1764,10 @@
         <v>53</v>
       </c>
       <c r="C9">
-        <v>645.15</v>
+        <v>650.9</v>
       </c>
       <c r="D9">
-        <v>4.26</v>
+        <v>0.89</v>
       </c>
       <c r="E9">
         <v>1052.57</v>
@@ -1788,46 +1776,46 @@
         <v>538.37</v>
       </c>
       <c r="G9">
-        <v>-38.71</v>
+        <v>-38.16</v>
       </c>
       <c r="H9">
-        <v>19.83</v>
+        <v>20.9</v>
       </c>
       <c r="I9">
-        <v>1.13</v>
+        <v>2.71</v>
       </c>
       <c r="J9">
-        <v>-5.22</v>
+        <v>-3.48</v>
       </c>
       <c r="K9">
-        <v>-3.12</v>
+        <v>-3.51</v>
       </c>
       <c r="L9">
-        <v>-3.57</v>
+        <v>-2.23</v>
       </c>
       <c r="M9">
-        <v>40.36</v>
+        <v>40.59</v>
       </c>
       <c r="N9">
         <v>68</v>
       </c>
       <c r="O9">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="P9">
-        <v>629.5</v>
+        <v>632.9400000000001</v>
       </c>
       <c r="Q9">
-        <v>641.21</v>
+        <v>640.39</v>
       </c>
       <c r="R9">
-        <v>658.02</v>
+        <v>657.6900000000001</v>
       </c>
       <c r="S9">
-        <v>665.05</v>
+        <v>664.6900000000001</v>
       </c>
       <c r="T9">
-        <v>-2.99</v>
+        <v>-2.07</v>
       </c>
       <c r="U9" t="s">
         <v>54</v>
@@ -1842,34 +1830,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>49.86</v>
+        <v>52.83</v>
       </c>
       <c r="Z9">
-        <v>-9.15</v>
+        <v>-7.27</v>
       </c>
       <c r="AA9">
-        <v>-8.869999999999999</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="AB9">
-        <v>-0.28</v>
+        <v>1.28</v>
       </c>
       <c r="AC9">
-        <v>35.99</v>
+        <v>66.67</v>
       </c>
       <c r="AD9">
-        <v>27.37</v>
+        <v>38.62</v>
       </c>
       <c r="AE9">
-        <v>15.79</v>
+        <v>15.58</v>
       </c>
       <c r="AF9">
-        <v>4410.46</v>
+        <v>7.15</v>
       </c>
       <c r="AG9">
-        <v>664.4</v>
+        <v>660.6799999999999</v>
       </c>
       <c r="AH9">
-        <v>618.02</v>
+        <v>620.11</v>
       </c>
       <c r="AI9">
         <v>657.48</v>
@@ -1878,7 +1866,7 @@
         <v>57</v>
       </c>
       <c r="AK9">
-        <v>18.95</v>
+        <v>23.13</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1889,10 +1877,10 @@
         <v>53</v>
       </c>
       <c r="C10">
-        <v>367</v>
+        <v>364.65</v>
       </c>
       <c r="D10">
-        <v>-0.8100000000000001</v>
+        <v>-0.64</v>
       </c>
       <c r="E10">
         <v>461.8</v>
@@ -1901,46 +1889,46 @@
         <v>345.25</v>
       </c>
       <c r="G10">
-        <v>-20.53</v>
+        <v>-21.04</v>
       </c>
       <c r="H10">
-        <v>6.3</v>
+        <v>5.62</v>
       </c>
       <c r="I10">
-        <v>0.36</v>
+        <v>-0.91</v>
       </c>
       <c r="J10">
-        <v>-3.28</v>
+        <v>-4.74</v>
       </c>
       <c r="K10">
-        <v>-6.75</v>
+        <v>-9.76</v>
       </c>
       <c r="L10">
-        <v>-4.24</v>
+        <v>-5.2</v>
       </c>
       <c r="M10">
-        <v>23.6</v>
+        <v>23.43</v>
       </c>
       <c r="N10">
         <v>62</v>
       </c>
       <c r="O10">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="P10">
-        <v>367.25</v>
+        <v>366.58</v>
       </c>
       <c r="Q10">
-        <v>367.42</v>
+        <v>366.55</v>
       </c>
       <c r="R10">
-        <v>374.08</v>
+        <v>373.87</v>
       </c>
       <c r="S10">
-        <v>388.02</v>
+        <v>387.94</v>
       </c>
       <c r="T10">
-        <v>-5.42</v>
+        <v>-6</v>
       </c>
       <c r="U10" t="s">
         <v>54</v>
@@ -1955,34 +1943,34 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>47.43</v>
+        <v>45.02</v>
       </c>
       <c r="Z10">
-        <v>-3.35</v>
+        <v>-3.18</v>
       </c>
       <c r="AA10">
-        <v>-4.58</v>
+        <v>-4.3</v>
       </c>
       <c r="AB10">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="AC10">
-        <v>93.89</v>
+        <v>90.66</v>
       </c>
       <c r="AD10">
-        <v>93.95999999999999</v>
+        <v>93.09</v>
       </c>
       <c r="AE10">
-        <v>7.12</v>
+        <v>6.93</v>
       </c>
       <c r="AF10">
-        <v>-48.12</v>
+        <v>-55.99</v>
       </c>
       <c r="AG10">
-        <v>388.48</v>
+        <v>386.47</v>
       </c>
       <c r="AH10">
-        <v>346.37</v>
+        <v>346.63</v>
       </c>
       <c r="AI10">
         <v>346.81</v>
@@ -1991,7 +1979,7 @@
         <v>56</v>
       </c>
       <c r="AK10">
-        <v>30.15</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -2002,10 +1990,10 @@
         <v>53</v>
       </c>
       <c r="C11">
-        <v>186.78</v>
+        <v>183</v>
       </c>
       <c r="D11">
-        <v>-1.04</v>
+        <v>-2.02</v>
       </c>
       <c r="E11">
         <v>216.66</v>
@@ -2014,46 +2002,46 @@
         <v>157.42</v>
       </c>
       <c r="G11">
-        <v>-13.79</v>
+        <v>-15.54</v>
       </c>
       <c r="H11">
-        <v>18.65</v>
+        <v>16.25</v>
       </c>
       <c r="I11">
-        <v>1.4</v>
+        <v>-3.07</v>
       </c>
       <c r="J11">
-        <v>0.31</v>
+        <v>-1</v>
       </c>
       <c r="K11">
-        <v>-5.6</v>
+        <v>-7.24</v>
       </c>
       <c r="L11">
-        <v>12.92</v>
+        <v>10.42</v>
       </c>
       <c r="M11">
-        <v>8.17</v>
+        <v>7.73</v>
       </c>
       <c r="N11">
         <v>87</v>
       </c>
       <c r="O11">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P11">
-        <v>186.82</v>
+        <v>185.66</v>
       </c>
       <c r="Q11">
-        <v>185.53</v>
+        <v>185.51</v>
       </c>
       <c r="R11">
-        <v>186.79</v>
+        <v>186.66</v>
       </c>
       <c r="S11">
-        <v>190.41</v>
+        <v>190.51</v>
       </c>
       <c r="T11">
-        <v>-1.91</v>
+        <v>-3.94</v>
       </c>
       <c r="U11" t="s">
         <v>54</v>
@@ -2068,34 +2056,34 @@
         <v>0</v>
       </c>
       <c r="Y11">
-        <v>50.74</v>
+        <v>43.83</v>
       </c>
       <c r="Z11">
-        <v>-0.26</v>
+        <v>-0.49</v>
       </c>
       <c r="AA11">
-        <v>-0.6</v>
+        <v>-0.58</v>
       </c>
       <c r="AB11">
-        <v>0.34</v>
+        <v>0.09</v>
       </c>
       <c r="AC11">
-        <v>61.57</v>
+        <v>54.15</v>
       </c>
       <c r="AD11">
-        <v>60.07</v>
+        <v>57.98</v>
       </c>
       <c r="AE11">
-        <v>4.49</v>
+        <v>4.6</v>
       </c>
       <c r="AF11">
-        <v>-17.78</v>
+        <v>13.55</v>
       </c>
       <c r="AG11">
-        <v>189.12</v>
+        <v>189.16</v>
       </c>
       <c r="AH11">
-        <v>181.94</v>
+        <v>181.85</v>
       </c>
       <c r="AI11">
         <v>180.21</v>
@@ -2104,7 +2092,7 @@
         <v>56</v>
       </c>
       <c r="AK11">
-        <v>27.64</v>
+        <v>24.71</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -2115,10 +2103,10 @@
         <v>53</v>
       </c>
       <c r="C12">
-        <v>2204.1</v>
+        <v>2200.8</v>
       </c>
       <c r="D12">
-        <v>-0.18</v>
+        <v>-0.15</v>
       </c>
       <c r="E12">
         <v>3221.85</v>
@@ -2127,46 +2115,46 @@
         <v>1982.6</v>
       </c>
       <c r="G12">
-        <v>-31.59</v>
+        <v>-31.69</v>
       </c>
       <c r="H12">
-        <v>11.17</v>
+        <v>11.01</v>
       </c>
       <c r="I12">
-        <v>-5</v>
+        <v>-4.48</v>
       </c>
       <c r="J12">
-        <v>-6.2</v>
+        <v>-7.33</v>
       </c>
       <c r="K12">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="L12">
-        <v>-24.38</v>
+        <v>-25.24</v>
       </c>
       <c r="M12">
-        <v>-8.09</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="N12">
         <v>50</v>
       </c>
       <c r="O12">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P12">
-        <v>2248.32</v>
+        <v>2227.68</v>
       </c>
       <c r="Q12">
-        <v>2298.1</v>
+        <v>2290.09</v>
       </c>
       <c r="R12">
-        <v>2286.2</v>
+        <v>2288.35</v>
       </c>
       <c r="S12">
-        <v>2550.84</v>
+        <v>2546.73</v>
       </c>
       <c r="T12">
-        <v>-13.59</v>
+        <v>-13.58</v>
       </c>
       <c r="U12" t="s">
         <v>55</v>
@@ -2181,43 +2169,43 @@
         <v>1</v>
       </c>
       <c r="Y12">
-        <v>38.44</v>
+        <v>38.13</v>
       </c>
       <c r="Z12">
-        <v>-18.47</v>
+        <v>-23.37</v>
       </c>
       <c r="AA12">
-        <v>-2.62</v>
+        <v>-6.77</v>
       </c>
       <c r="AB12">
-        <v>-15.85</v>
+        <v>-16.6</v>
       </c>
       <c r="AC12">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AD12">
-        <v>7.54</v>
+        <v>2.06</v>
       </c>
       <c r="AE12">
-        <v>56.7</v>
+        <v>56.01</v>
       </c>
       <c r="AF12">
-        <v>-5.35</v>
+        <v>9.01</v>
       </c>
       <c r="AG12">
-        <v>2398.44</v>
+        <v>2394.77</v>
       </c>
       <c r="AH12">
-        <v>2197.75</v>
+        <v>2185.4</v>
       </c>
       <c r="AI12">
-        <v>2381.4</v>
+        <v>2377.09</v>
       </c>
       <c r="AJ12" t="s">
         <v>57</v>
       </c>
       <c r="AK12">
-        <v>27.84</v>
+        <v>30.78</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2228,10 +2216,10 @@
         <v>53</v>
       </c>
       <c r="C13">
-        <v>5021</v>
+        <v>5009.5</v>
       </c>
       <c r="D13">
-        <v>0.32</v>
+        <v>-0.23</v>
       </c>
       <c r="E13">
         <v>5169.2</v>
@@ -2240,25 +2228,25 @@
         <v>3327.3</v>
       </c>
       <c r="G13">
-        <v>-2.87</v>
+        <v>-3.09</v>
       </c>
       <c r="H13">
-        <v>50.9</v>
+        <v>50.56</v>
       </c>
       <c r="I13">
-        <v>-0.12</v>
+        <v>-0.21</v>
       </c>
       <c r="J13">
-        <v>-1.53</v>
+        <v>-1.07</v>
       </c>
       <c r="K13">
-        <v>20</v>
+        <v>16.95</v>
       </c>
       <c r="L13">
-        <v>37.26</v>
+        <v>38</v>
       </c>
       <c r="M13">
-        <v>20.2</v>
+        <v>20.13</v>
       </c>
       <c r="N13">
         <v>99</v>
@@ -2267,19 +2255,19 @@
         <v>82</v>
       </c>
       <c r="P13">
-        <v>5005.6</v>
+        <v>5003.5</v>
       </c>
       <c r="Q13">
-        <v>5063.84</v>
+        <v>5061.51</v>
       </c>
       <c r="R13">
-        <v>4886.44</v>
+        <v>4897.41</v>
       </c>
       <c r="S13">
-        <v>4341.02</v>
+        <v>4346.79</v>
       </c>
       <c r="T13">
-        <v>15.66</v>
+        <v>15.25</v>
       </c>
       <c r="U13" t="s">
         <v>55</v>
@@ -2294,34 +2282,34 @@
         <v>3</v>
       </c>
       <c r="Y13">
-        <v>52.71</v>
+        <v>51.2</v>
       </c>
       <c r="Z13">
-        <v>31.19</v>
+        <v>26.8</v>
       </c>
       <c r="AA13">
-        <v>58.46</v>
+        <v>52.12</v>
       </c>
       <c r="AB13">
-        <v>-27.27</v>
+        <v>-25.32</v>
       </c>
       <c r="AC13">
-        <v>8.609999999999999</v>
+        <v>12.1</v>
       </c>
       <c r="AD13">
-        <v>3.86</v>
+        <v>7.9</v>
       </c>
       <c r="AE13">
-        <v>75.23</v>
+        <v>75.43000000000001</v>
       </c>
       <c r="AF13">
-        <v>-37.8</v>
+        <v>-20.09</v>
       </c>
       <c r="AG13">
-        <v>5160.01</v>
+        <v>5160.67</v>
       </c>
       <c r="AH13">
-        <v>4967.67</v>
+        <v>4962.34</v>
       </c>
       <c r="AI13">
         <v>4921.93</v>
@@ -2330,7 +2318,7 @@
         <v>56</v>
       </c>
       <c r="AK13">
-        <v>38.26</v>
+        <v>39.76</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2341,58 +2329,58 @@
         <v>53</v>
       </c>
       <c r="C14">
-        <v>2818.7</v>
+        <v>2802.4</v>
       </c>
       <c r="D14">
-        <v>-0.05</v>
+        <v>-0.58</v>
       </c>
       <c r="E14">
-        <v>5210.8</v>
+        <v>5189.83</v>
       </c>
       <c r="F14">
         <v>2193.96</v>
       </c>
       <c r="G14">
-        <v>-45.91</v>
+        <v>-46</v>
       </c>
       <c r="H14">
-        <v>28.48</v>
+        <v>27.73</v>
       </c>
       <c r="I14">
-        <v>0.11</v>
+        <v>-1.77</v>
       </c>
       <c r="J14">
-        <v>-5.63</v>
+        <v>-6.27</v>
       </c>
       <c r="K14">
-        <v>2.3</v>
+        <v>-3.4</v>
       </c>
       <c r="L14">
-        <v>-46.89</v>
+        <v>-46.22</v>
       </c>
       <c r="M14">
-        <v>23.04</v>
+        <v>22.88</v>
       </c>
       <c r="N14">
         <v>32</v>
       </c>
       <c r="O14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P14">
-        <v>2819.96</v>
+        <v>2809.84</v>
       </c>
       <c r="Q14">
-        <v>2886.77</v>
+        <v>2877.99</v>
       </c>
       <c r="R14">
-        <v>2943.27</v>
+        <v>2932.5</v>
       </c>
       <c r="S14">
-        <v>2957.66</v>
+        <v>2950.48</v>
       </c>
       <c r="T14">
-        <v>-4.7</v>
+        <v>-5.02</v>
       </c>
       <c r="U14" t="s">
         <v>54</v>
@@ -2407,43 +2395,43 @@
         <v>0</v>
       </c>
       <c r="Y14">
-        <v>38.29</v>
+        <v>36.47</v>
       </c>
       <c r="Z14">
-        <v>-43.51</v>
+        <v>-44.05</v>
       </c>
       <c r="AA14">
-        <v>-36.62</v>
+        <v>-38.11</v>
       </c>
       <c r="AB14">
-        <v>-6.88</v>
+        <v>-5.94</v>
       </c>
       <c r="AC14">
-        <v>33.4</v>
+        <v>41.9</v>
       </c>
       <c r="AD14">
-        <v>26.78</v>
+        <v>33.08</v>
       </c>
       <c r="AE14">
-        <v>57.43</v>
+        <v>57.7</v>
       </c>
       <c r="AF14">
-        <v>-26.2</v>
+        <v>0.59</v>
       </c>
       <c r="AG14">
-        <v>3000.92</v>
+        <v>2989.58</v>
       </c>
       <c r="AH14">
-        <v>2772.62</v>
+        <v>2766.4</v>
       </c>
       <c r="AI14">
-        <v>2968.92</v>
+        <v>2959.85</v>
       </c>
       <c r="AJ14" t="s">
         <v>57</v>
       </c>
       <c r="AK14">
-        <v>38.97</v>
+        <v>40.61</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2454,10 +2442,10 @@
         <v>53</v>
       </c>
       <c r="C15">
-        <v>220.8</v>
+        <v>222.05</v>
       </c>
       <c r="D15">
-        <v>-3.49</v>
+        <v>0.57</v>
       </c>
       <c r="E15">
         <v>392.75</v>
@@ -2466,46 +2454,46 @@
         <v>217.05</v>
       </c>
       <c r="G15">
-        <v>-43.78</v>
+        <v>-43.46</v>
       </c>
       <c r="H15">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="I15">
-        <v>-4.01</v>
+        <v>-4.12</v>
       </c>
       <c r="J15">
-        <v>-4.06</v>
+        <v>-4.37</v>
       </c>
       <c r="K15">
-        <v>-3.07</v>
+        <v>-5.51</v>
       </c>
       <c r="L15">
-        <v>-30.16</v>
+        <v>-28.3</v>
       </c>
       <c r="M15">
-        <v>13.97</v>
+        <v>14.09</v>
       </c>
       <c r="N15">
         <v>38</v>
       </c>
       <c r="O15">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P15">
-        <v>229.46</v>
+        <v>227.55</v>
       </c>
       <c r="Q15">
-        <v>229.31</v>
+        <v>228.88</v>
       </c>
       <c r="R15">
-        <v>232.84</v>
+        <v>232.52</v>
       </c>
       <c r="S15">
-        <v>255.48</v>
+        <v>255.05</v>
       </c>
       <c r="T15">
-        <v>-13.57</v>
+        <v>-12.94</v>
       </c>
       <c r="U15" t="s">
         <v>54</v>
@@ -2520,34 +2508,34 @@
         <v>0</v>
       </c>
       <c r="Y15">
-        <v>37.31</v>
+        <v>39.4</v>
       </c>
       <c r="Z15">
-        <v>-1.4</v>
+        <v>-1.81</v>
       </c>
       <c r="AA15">
-        <v>-1.22</v>
+        <v>-1.34</v>
       </c>
       <c r="AB15">
-        <v>-0.19</v>
+        <v>-0.48</v>
       </c>
       <c r="AC15">
-        <v>40.97</v>
+        <v>23.9</v>
       </c>
       <c r="AD15">
-        <v>67.43000000000001</v>
+        <v>45.79</v>
       </c>
       <c r="AE15">
-        <v>6.38</v>
+        <v>6.23</v>
       </c>
       <c r="AF15">
-        <v>202.97</v>
+        <v>36.13</v>
       </c>
       <c r="AG15">
-        <v>235.72</v>
+        <v>236.01</v>
       </c>
       <c r="AH15">
-        <v>222.9</v>
+        <v>221.74</v>
       </c>
       <c r="AI15">
         <v>219.81</v>
@@ -2556,7 +2544,7 @@
         <v>56</v>
       </c>
       <c r="AK15">
-        <v>23.2</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2567,10 +2555,10 @@
         <v>53</v>
       </c>
       <c r="C16">
-        <v>35.91</v>
+        <v>35.6</v>
       </c>
       <c r="D16">
-        <v>-0.61</v>
+        <v>-0.86</v>
       </c>
       <c r="E16">
         <v>58.79</v>
@@ -2579,46 +2567,46 @@
         <v>31.36</v>
       </c>
       <c r="G16">
-        <v>-38.92</v>
+        <v>-39.45</v>
       </c>
       <c r="H16">
-        <v>14.51</v>
+        <v>13.52</v>
       </c>
       <c r="I16">
-        <v>-5.52</v>
+        <v>-5.67</v>
       </c>
       <c r="J16">
-        <v>-5.92</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="K16">
-        <v>-22.67</v>
+        <v>-22.03</v>
       </c>
       <c r="L16">
-        <v>-37.13</v>
+        <v>-37.53</v>
       </c>
       <c r="M16">
-        <v>0.46</v>
+        <v>0.28</v>
       </c>
       <c r="N16">
         <v>7</v>
       </c>
       <c r="O16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P16">
-        <v>36.72</v>
+        <v>36.3</v>
       </c>
       <c r="Q16">
-        <v>37.63</v>
+        <v>37.48</v>
       </c>
       <c r="R16">
-        <v>39.12</v>
+        <v>38.97</v>
       </c>
       <c r="S16">
-        <v>42.79</v>
+        <v>42.71</v>
       </c>
       <c r="T16">
-        <v>-16.08</v>
+        <v>-16.66</v>
       </c>
       <c r="U16" t="s">
         <v>54</v>
@@ -2633,43 +2621,43 @@
         <v>0</v>
       </c>
       <c r="Y16">
-        <v>32.43</v>
+        <v>30.84</v>
       </c>
       <c r="Z16">
-        <v>-0.74</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="AA16">
-        <v>-0.63</v>
+        <v>-0.66</v>
       </c>
       <c r="AB16">
-        <v>-0.11</v>
+        <v>-0.15</v>
       </c>
       <c r="AC16">
-        <v>28.67</v>
+        <v>22.42</v>
       </c>
       <c r="AD16">
-        <v>40.29</v>
+        <v>30.24</v>
       </c>
       <c r="AE16">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF16">
-        <v>-68.61</v>
+        <v>-72.3</v>
       </c>
       <c r="AG16">
-        <v>39.37</v>
+        <v>39.38</v>
       </c>
       <c r="AH16">
-        <v>35.9</v>
+        <v>35.59</v>
       </c>
       <c r="AI16">
-        <v>39.51</v>
+        <v>38.7</v>
       </c>
       <c r="AJ16" t="s">
         <v>57</v>
       </c>
       <c r="AK16">
-        <v>22.53</v>
+        <v>24.61</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2680,10 +2668,10 @@
         <v>53</v>
       </c>
       <c r="C17">
-        <v>1158.5</v>
+        <v>1165</v>
       </c>
       <c r="D17">
-        <v>1.29</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E17">
         <v>1556.41</v>
@@ -2692,46 +2680,46 @@
         <v>1143.8</v>
       </c>
       <c r="G17">
-        <v>-25.57</v>
+        <v>-25.15</v>
       </c>
       <c r="H17">
-        <v>1.29</v>
+        <v>1.85</v>
       </c>
       <c r="I17">
-        <v>-1.66</v>
+        <v>-0.43</v>
       </c>
       <c r="J17">
-        <v>-10.19</v>
+        <v>-9.65</v>
       </c>
       <c r="K17">
-        <v>-9.869999999999999</v>
+        <v>-12.17</v>
       </c>
       <c r="L17">
-        <v>-18.11</v>
+        <v>-17.25</v>
       </c>
       <c r="M17">
-        <v>-0.46</v>
+        <v>-0.34</v>
       </c>
       <c r="N17">
         <v>44</v>
       </c>
       <c r="O17">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P17">
-        <v>1156.86</v>
+        <v>1155.86</v>
       </c>
       <c r="Q17">
-        <v>1207.56</v>
+        <v>1199.79</v>
       </c>
       <c r="R17">
-        <v>1270.48</v>
+        <v>1268.18</v>
       </c>
       <c r="S17">
-        <v>1346.45</v>
+        <v>1345.52</v>
       </c>
       <c r="T17">
-        <v>-13.96</v>
+        <v>-13.42</v>
       </c>
       <c r="U17" t="s">
         <v>54</v>
@@ -2746,34 +2734,34 @@
         <v>0</v>
       </c>
       <c r="Y17">
-        <v>35.15</v>
+        <v>37.22</v>
       </c>
       <c r="Z17">
-        <v>-35.72</v>
+        <v>-34.23</v>
       </c>
       <c r="AA17">
-        <v>-32.11</v>
+        <v>-32.53</v>
       </c>
       <c r="AB17">
-        <v>-3.61</v>
+        <v>-1.69</v>
       </c>
       <c r="AC17">
-        <v>32.5</v>
+        <v>49.96</v>
       </c>
       <c r="AD17">
-        <v>33.5</v>
+        <v>37.14</v>
       </c>
       <c r="AE17">
-        <v>28.36</v>
+        <v>28.55</v>
       </c>
       <c r="AF17">
-        <v>-51.07</v>
+        <v>-26.35</v>
       </c>
       <c r="AG17">
-        <v>1299.03</v>
+        <v>1276</v>
       </c>
       <c r="AH17">
-        <v>1116.09</v>
+        <v>1123.57</v>
       </c>
       <c r="AI17">
         <v>1226.77</v>
@@ -2782,7 +2770,7 @@
         <v>57</v>
       </c>
       <c r="AK17">
-        <v>51.33</v>
+        <v>48.4</v>
       </c>
     </row>
   </sheetData>
@@ -2923,7 +2911,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F145"/>
+  <dimension ref="A1:F138"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2963,7 +2951,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>64</v>
@@ -2983,7 +2971,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>64</v>
@@ -3003,2386 +2991,2264 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="5" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="D5" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="F5" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="F5" s="5" t="s">
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="2" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C6" s="5" t="s">
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E6" s="5" t="s">
+      <c r="C8" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="D8" s="3" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="2" t="s">
+      <c r="E8" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>84</v>
+      <c r="A9" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1.14</v>
+      </c>
+      <c r="D9" s="7">
+        <v>-0.45</v>
+      </c>
+      <c r="E9" s="8">
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="7">
-        <v>-0.17</v>
+        <v>-3.75</v>
       </c>
       <c r="D10" s="7">
-        <v>-1.14</v>
-      </c>
-      <c r="E10" s="8">
-        <v>-0.97</v>
+        <v>-9.57</v>
+      </c>
+      <c r="E10" s="9">
+        <v>-5.82</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="7">
-        <v>-3.7</v>
+        <v>-3.03</v>
       </c>
       <c r="D11" s="7">
-        <v>-3.75</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-0.05</v>
+        <v>-5.14</v>
+      </c>
+      <c r="E11" s="9">
+        <v>-2.11</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="7">
-        <v>-3.54</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="D12" s="7">
-        <v>-3.03</v>
-      </c>
-      <c r="E12" s="9">
-        <v>0.51</v>
+        <v>-8.869999999999999</v>
+      </c>
+      <c r="E12" s="8">
+        <v>0.43</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="7">
-        <v>-9.82</v>
+        <v>1.62</v>
       </c>
       <c r="D13" s="7">
-        <v>-9.300000000000001</v>
+        <v>0.19</v>
       </c>
       <c r="E13" s="9">
-        <v>0.52</v>
+        <v>-1.43</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="7">
-        <v>1.53</v>
+        <v>-5.87</v>
       </c>
       <c r="D14" s="7">
-        <v>1.62</v>
+        <v>-9.119999999999999</v>
       </c>
       <c r="E14" s="9">
-        <v>0.09</v>
+        <v>-3.25</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="7">
-        <v>-7.14</v>
+        <v>-8.16</v>
       </c>
       <c r="D15" s="7">
-        <v>-5.87</v>
+        <v>-10.46</v>
       </c>
       <c r="E15" s="9">
-        <v>1.27</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="7">
-        <v>-10.86</v>
+        <v>-5.22</v>
       </c>
       <c r="D16" s="7">
-        <v>-8.16</v>
-      </c>
-      <c r="E16" s="9">
-        <v>2.7</v>
+        <v>-3.48</v>
+      </c>
+      <c r="E16" s="8">
+        <v>1.74</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="7">
-        <v>-10.16</v>
+        <v>-3.28</v>
       </c>
       <c r="D17" s="7">
-        <v>-5.22</v>
+        <v>-4.74</v>
       </c>
       <c r="E17" s="9">
-        <v>4.94</v>
+        <v>-1.46</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="7">
-        <v>-2.63</v>
+        <v>0.31</v>
       </c>
       <c r="D18" s="7">
-        <v>-3.28</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-0.65</v>
+        <v>-1</v>
+      </c>
+      <c r="E18" s="9">
+        <v>-1.31</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="7">
-        <v>0.27</v>
+        <v>-6.2</v>
       </c>
       <c r="D19" s="7">
-        <v>0.31</v>
+        <v>-7.33</v>
       </c>
       <c r="E19" s="9">
-        <v>0.04</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="7">
-        <v>-9.720000000000001</v>
+        <v>-1.53</v>
       </c>
       <c r="D20" s="7">
-        <v>-6.2</v>
-      </c>
-      <c r="E20" s="9">
-        <v>3.52</v>
+        <v>-1.07</v>
+      </c>
+      <c r="E20" s="8">
+        <v>0.46</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C21" s="7">
-        <v>-2.4</v>
+        <v>-5.63</v>
       </c>
       <c r="D21" s="7">
-        <v>-1.53</v>
+        <v>-6.27</v>
       </c>
       <c r="E21" s="9">
-        <v>0.87</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C22" s="7">
-        <v>-6</v>
+        <v>-4.06</v>
       </c>
       <c r="D22" s="7">
-        <v>-5.63</v>
+        <v>-4.37</v>
       </c>
       <c r="E22" s="9">
-        <v>0.37</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C23" s="7">
-        <v>-2.86</v>
+        <v>-5.92</v>
       </c>
       <c r="D23" s="7">
-        <v>-4.06</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-1.2</v>
+        <v>-8.109999999999999</v>
+      </c>
+      <c r="E23" s="9">
+        <v>-2.19</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C24" s="7">
-        <v>-6.91</v>
+        <v>-10.19</v>
       </c>
       <c r="D24" s="7">
-        <v>-5.92</v>
-      </c>
-      <c r="E24" s="9">
-        <v>0.99</v>
+        <v>-9.65</v>
+      </c>
+      <c r="E24" s="8">
+        <v>0.54</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="6" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C25" s="7">
-        <v>-10.64</v>
+        <v>-2.22</v>
       </c>
       <c r="D25" s="7">
-        <v>-10.19</v>
-      </c>
-      <c r="E25" s="9">
-        <v>0.45</v>
+        <v>-0.21</v>
+      </c>
+      <c r="E25" s="8">
+        <v>2.01</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C26" s="7">
-        <v>-0.68</v>
+        <v>0.41</v>
       </c>
       <c r="D26" s="7">
-        <v>-2.22</v>
+        <v>3.95</v>
       </c>
       <c r="E26" s="8">
-        <v>-1.54</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C27" s="7">
-        <v>3.08</v>
+        <v>-3.23</v>
       </c>
       <c r="D27" s="7">
-        <v>0.41</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-2.67</v>
+        <v>-3.27</v>
+      </c>
+      <c r="E27" s="9">
+        <v>-0.04</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C28" s="7">
-        <v>-2.62</v>
+        <v>-4.8</v>
       </c>
       <c r="D28" s="7">
-        <v>-3.23</v>
+        <v>-2.02</v>
       </c>
       <c r="E28" s="8">
-        <v>-0.61</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C29" s="7">
-        <v>-4.87</v>
+        <v>4.01</v>
       </c>
       <c r="D29" s="7">
-        <v>-4.8</v>
+        <v>0.31</v>
       </c>
       <c r="E29" s="9">
-        <v>0.07000000000000001</v>
+        <v>-3.7</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C30" s="7">
-        <v>3.67</v>
+        <v>-1.92</v>
       </c>
       <c r="D30" s="7">
-        <v>4.01</v>
-      </c>
-      <c r="E30" s="9">
-        <v>0.34</v>
+        <v>-1.88</v>
+      </c>
+      <c r="E30" s="8">
+        <v>0.04</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C31" s="7">
-        <v>-1.09</v>
+        <v>-4.78</v>
       </c>
       <c r="D31" s="7">
-        <v>-1.92</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-0.83</v>
+        <v>-4.92</v>
+      </c>
+      <c r="E31" s="9">
+        <v>-0.14</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C32" s="7">
-        <v>-6.26</v>
+        <v>1.13</v>
       </c>
       <c r="D32" s="7">
-        <v>-4.78</v>
-      </c>
-      <c r="E32" s="9">
-        <v>1.48</v>
+        <v>2.71</v>
+      </c>
+      <c r="E32" s="8">
+        <v>1.58</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C33" s="7">
-        <v>-1.48</v>
+        <v>0.36</v>
       </c>
       <c r="D33" s="7">
-        <v>1.13</v>
+        <v>-0.91</v>
       </c>
       <c r="E33" s="9">
-        <v>2.61</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C34" s="7">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="D34" s="7">
-        <v>0.36</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-1.29</v>
+        <v>-3.07</v>
+      </c>
+      <c r="E34" s="9">
+        <v>-4.47</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C35" s="7">
-        <v>2.67</v>
+        <v>-5</v>
       </c>
       <c r="D35" s="7">
-        <v>1.4</v>
+        <v>-4.48</v>
       </c>
       <c r="E35" s="8">
-        <v>-1.27</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C36" s="7">
-        <v>-5.96</v>
+        <v>-0.12</v>
       </c>
       <c r="D36" s="7">
-        <v>-5</v>
+        <v>-0.21</v>
       </c>
       <c r="E36" s="9">
-        <v>0.96</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C37" s="7">
-        <v>-1.36</v>
+        <v>0.11</v>
       </c>
       <c r="D37" s="7">
-        <v>-0.12</v>
+        <v>-1.77</v>
       </c>
       <c r="E37" s="9">
-        <v>1.24</v>
+        <v>-1.88</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C38" s="7">
-        <v>-1.13</v>
+        <v>-4.01</v>
       </c>
       <c r="D38" s="7">
-        <v>0.11</v>
+        <v>-4.12</v>
       </c>
       <c r="E38" s="9">
-        <v>1.24</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C39" s="7">
-        <v>2.3</v>
+        <v>-5.52</v>
       </c>
       <c r="D39" s="7">
-        <v>-4.01</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-6.31</v>
+        <v>-5.67</v>
+      </c>
+      <c r="E39" s="9">
+        <v>-0.15</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C40" s="7">
-        <v>-4.92</v>
+        <v>-1.66</v>
       </c>
       <c r="D40" s="7">
-        <v>-5.52</v>
+        <v>-0.43</v>
       </c>
       <c r="E40" s="8">
-        <v>-0.6</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="6" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C41" s="7">
-        <v>-0.72</v>
+        <v>-7.97</v>
       </c>
       <c r="D41" s="7">
-        <v>-1.66</v>
+        <v>-7.35</v>
       </c>
       <c r="E41" s="8">
-        <v>-0.9399999999999999</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C42" s="7">
-        <v>-6.71</v>
+        <v>15.41</v>
       </c>
       <c r="D42" s="7">
-        <v>-7.97</v>
+        <v>17.85</v>
       </c>
       <c r="E42" s="8">
-        <v>-1.26</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C43" s="7">
-        <v>19.1</v>
+        <v>-43.11</v>
       </c>
       <c r="D43" s="7">
-        <v>15.41</v>
+        <v>-41.03</v>
       </c>
       <c r="E43" s="8">
-        <v>-3.69</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C44" s="7">
-        <v>-42.15</v>
+        <v>-34.28</v>
       </c>
       <c r="D44" s="7">
-        <v>-43.11</v>
+        <v>-34.23</v>
       </c>
       <c r="E44" s="8">
-        <v>-0.96</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C45" s="7">
-        <v>-34.4</v>
+        <v>14.05</v>
       </c>
       <c r="D45" s="7">
-        <v>-34.28</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="E45" s="9">
-        <v>0.12</v>
+        <v>-4.19</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C46" s="7">
-        <v>14.4</v>
+        <v>-6.16</v>
       </c>
       <c r="D46" s="7">
-        <v>14.05</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-0.35</v>
+        <v>-7.76</v>
+      </c>
+      <c r="E46" s="9">
+        <v>-1.6</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C47" s="7">
-        <v>-5.87</v>
+        <v>-36.55</v>
       </c>
       <c r="D47" s="7">
-        <v>-6.16</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-0.29</v>
+        <v>-37.99</v>
+      </c>
+      <c r="E47" s="9">
+        <v>-1.44</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C48" s="7">
-        <v>-36.83</v>
+        <v>-3.57</v>
       </c>
       <c r="D48" s="7">
-        <v>-36.55</v>
-      </c>
-      <c r="E48" s="9">
-        <v>0.28</v>
+        <v>-2.23</v>
+      </c>
+      <c r="E48" s="8">
+        <v>1.34</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C49" s="7">
-        <v>-7.97</v>
+        <v>-4.24</v>
       </c>
       <c r="D49" s="7">
-        <v>-3.57</v>
+        <v>-5.2</v>
       </c>
       <c r="E49" s="9">
-        <v>4.4</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C50" s="7">
-        <v>-4.1</v>
+        <v>12.92</v>
       </c>
       <c r="D50" s="7">
-        <v>-4.24</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-0.14</v>
+        <v>10.42</v>
+      </c>
+      <c r="E50" s="9">
+        <v>-2.5</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C51" s="7">
-        <v>14.89</v>
+        <v>-24.38</v>
       </c>
       <c r="D51" s="7">
-        <v>12.92</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-1.97</v>
+        <v>-25.24</v>
+      </c>
+      <c r="E51" s="9">
+        <v>-0.86</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C52" s="7">
-        <v>-24.97</v>
+        <v>37.26</v>
       </c>
       <c r="D52" s="7">
-        <v>-24.38</v>
-      </c>
-      <c r="E52" s="9">
-        <v>0.59</v>
+        <v>38</v>
+      </c>
+      <c r="E52" s="8">
+        <v>0.74</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C53" s="7">
-        <v>36.55</v>
+        <v>-46.89</v>
       </c>
       <c r="D53" s="7">
-        <v>37.26</v>
-      </c>
-      <c r="E53" s="9">
-        <v>0.71</v>
+        <v>-46.22</v>
+      </c>
+      <c r="E53" s="8">
+        <v>0.67</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C54" s="7">
-        <v>-48.92</v>
+        <v>-30.16</v>
       </c>
       <c r="D54" s="7">
-        <v>-46.89</v>
-      </c>
-      <c r="E54" s="9">
-        <v>2.03</v>
+        <v>-28.3</v>
+      </c>
+      <c r="E54" s="8">
+        <v>1.86</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C55" s="7">
-        <v>-27.89</v>
+        <v>-37.13</v>
       </c>
       <c r="D55" s="7">
-        <v>-30.16</v>
-      </c>
-      <c r="E55" s="8">
-        <v>-2.27</v>
+        <v>-37.53</v>
+      </c>
+      <c r="E55" s="9">
+        <v>-0.4</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C56" s="7">
-        <v>-37.15</v>
+        <v>-18.11</v>
       </c>
       <c r="D56" s="7">
-        <v>-37.13</v>
-      </c>
-      <c r="E56" s="9">
-        <v>0.02</v>
+        <v>-17.25</v>
+      </c>
+      <c r="E56" s="8">
+        <v>0.86</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="6" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C57" s="7">
-        <v>-19.92</v>
+        <v>5.34</v>
       </c>
       <c r="D57" s="7">
-        <v>-18.11</v>
+        <v>4.15</v>
       </c>
       <c r="E57" s="9">
-        <v>1.81</v>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C58" s="7">
-        <v>10.23</v>
+        <v>29.76</v>
       </c>
       <c r="D58" s="7">
-        <v>5.34</v>
+        <v>32.31</v>
       </c>
       <c r="E58" s="8">
-        <v>-4.89</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C59" s="7">
-        <v>35.85</v>
+        <v>-11.24</v>
       </c>
       <c r="D59" s="7">
-        <v>29.76</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-6.09</v>
+        <v>-11.73</v>
+      </c>
+      <c r="E59" s="9">
+        <v>-0.49</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C60" s="7">
-        <v>-8.449999999999999</v>
+        <v>-18.15</v>
       </c>
       <c r="D60" s="7">
-        <v>-11.24</v>
+        <v>-16.68</v>
       </c>
       <c r="E60" s="8">
-        <v>-2.79</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C61" s="7">
-        <v>-18.64</v>
+        <v>-10.28</v>
       </c>
       <c r="D61" s="7">
-        <v>-18.15</v>
-      </c>
-      <c r="E61" s="9">
-        <v>0.49</v>
+        <v>-8.91</v>
+      </c>
+      <c r="E61" s="8">
+        <v>1.37</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C62" s="7">
-        <v>-9.83</v>
+        <v>-9.19</v>
       </c>
       <c r="D62" s="7">
-        <v>-10.28</v>
-      </c>
-      <c r="E62" s="8">
-        <v>-0.45</v>
+        <v>-9.94</v>
+      </c>
+      <c r="E62" s="9">
+        <v>-0.75</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C63" s="7">
-        <v>-9.710000000000001</v>
+        <v>-16.14</v>
       </c>
       <c r="D63" s="7">
-        <v>-9.19</v>
+        <v>-16.84</v>
       </c>
       <c r="E63" s="9">
-        <v>0.52</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C64" s="7">
-        <v>-15.62</v>
+        <v>-3.12</v>
       </c>
       <c r="D64" s="7">
-        <v>-16.14</v>
-      </c>
-      <c r="E64" s="8">
-        <v>-0.52</v>
+        <v>-3.51</v>
+      </c>
+      <c r="E64" s="9">
+        <v>-0.39</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C65" s="7">
-        <v>-2.65</v>
+        <v>-6.75</v>
       </c>
       <c r="D65" s="7">
-        <v>-3.12</v>
-      </c>
-      <c r="E65" s="8">
-        <v>-0.47</v>
+        <v>-9.76</v>
+      </c>
+      <c r="E65" s="9">
+        <v>-3.01</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C66" s="7">
-        <v>-5.19</v>
+        <v>-5.6</v>
       </c>
       <c r="D66" s="7">
-        <v>-6.75</v>
-      </c>
-      <c r="E66" s="8">
-        <v>-1.56</v>
+        <v>-7.24</v>
+      </c>
+      <c r="E66" s="9">
+        <v>-1.64</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C67" s="7">
-        <v>-2.69</v>
+        <v>1.98</v>
       </c>
       <c r="D67" s="7">
-        <v>-5.6</v>
-      </c>
-      <c r="E67" s="8">
-        <v>-2.91</v>
+        <v>1.79</v>
+      </c>
+      <c r="E67" s="9">
+        <v>-0.19</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C68" s="7">
-        <v>3.39</v>
+        <v>20</v>
       </c>
       <c r="D68" s="7">
-        <v>1.98</v>
-      </c>
-      <c r="E68" s="8">
-        <v>-1.41</v>
+        <v>16.95</v>
+      </c>
+      <c r="E68" s="9">
+        <v>-3.05</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C69" s="7">
-        <v>24.34</v>
+        <v>2.3</v>
       </c>
       <c r="D69" s="7">
-        <v>20</v>
-      </c>
-      <c r="E69" s="8">
-        <v>-4.34</v>
+        <v>-3.4</v>
+      </c>
+      <c r="E69" s="9">
+        <v>-5.7</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B70" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C70" s="7">
-        <v>4.18</v>
+        <v>-3.07</v>
       </c>
       <c r="D70" s="7">
-        <v>2.3</v>
-      </c>
-      <c r="E70" s="8">
-        <v>-1.88</v>
+        <v>-5.51</v>
+      </c>
+      <c r="E70" s="9">
+        <v>-2.44</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C71" s="7">
-        <v>2.88</v>
+        <v>-22.67</v>
       </c>
       <c r="D71" s="7">
-        <v>-3.07</v>
+        <v>-22.03</v>
       </c>
       <c r="E71" s="8">
-        <v>-5.95</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B72" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C72" s="7">
-        <v>-14.28</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="D72" s="7">
-        <v>-22.67</v>
-      </c>
-      <c r="E72" s="8">
-        <v>-8.390000000000001</v>
+        <v>-12.17</v>
+      </c>
+      <c r="E72" s="9">
+        <v>-2.3</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="6" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C73" s="7">
-        <v>-10.17</v>
+        <v>-9.5</v>
       </c>
       <c r="D73" s="7">
-        <v>-9.869999999999999</v>
-      </c>
-      <c r="E73" s="9">
-        <v>0.3</v>
+        <v>-9.15</v>
+      </c>
+      <c r="E73" s="8">
+        <v>0.35</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C74" s="7">
-        <v>-8.609999999999999</v>
+        <v>-13.31</v>
       </c>
       <c r="D74" s="7">
-        <v>-9.5</v>
+        <v>-12.41</v>
       </c>
       <c r="E74" s="8">
-        <v>-0.89</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C75" s="7">
-        <v>-11.39</v>
+        <v>-40.71</v>
       </c>
       <c r="D75" s="7">
-        <v>-13.31</v>
+        <v>-39.94</v>
       </c>
       <c r="E75" s="8">
-        <v>-1.92</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C76" s="7">
-        <v>-42.84</v>
+        <v>-38.32</v>
       </c>
       <c r="D76" s="7">
-        <v>-40.71</v>
-      </c>
-      <c r="E76" s="9">
-        <v>2.13</v>
+        <v>-38.13</v>
+      </c>
+      <c r="E76" s="8">
+        <v>0.19</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C77" s="7">
-        <v>-39.08</v>
+        <v>-14.42</v>
       </c>
       <c r="D77" s="7">
-        <v>-38.32</v>
+        <v>-14.56</v>
       </c>
       <c r="E77" s="9">
-        <v>0.76</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C78" s="7">
-        <v>-14.01</v>
+        <v>-20.69</v>
       </c>
       <c r="D78" s="7">
-        <v>-14.42</v>
-      </c>
-      <c r="E78" s="8">
-        <v>-0.41</v>
+        <v>-21.37</v>
+      </c>
+      <c r="E78" s="9">
+        <v>-0.68</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C79" s="7">
-        <v>-20.58</v>
+        <v>-40.71</v>
       </c>
       <c r="D79" s="7">
-        <v>-20.69</v>
-      </c>
-      <c r="E79" s="8">
-        <v>-0.11</v>
+        <v>-41.16</v>
+      </c>
+      <c r="E79" s="9">
+        <v>-0.45</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B80" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C80" s="7">
-        <v>-41.16</v>
+        <v>-38.71</v>
       </c>
       <c r="D80" s="7">
-        <v>-40.71</v>
-      </c>
-      <c r="E80" s="9">
-        <v>0.45</v>
+        <v>-38.16</v>
+      </c>
+      <c r="E80" s="8">
+        <v>0.55</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B81" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C81" s="7">
-        <v>-41.21</v>
+        <v>-20.53</v>
       </c>
       <c r="D81" s="7">
-        <v>-38.71</v>
+        <v>-21.04</v>
       </c>
       <c r="E81" s="9">
-        <v>2.5</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B82" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C82" s="7">
-        <v>-19.88</v>
+        <v>-13.79</v>
       </c>
       <c r="D82" s="7">
-        <v>-20.53</v>
-      </c>
-      <c r="E82" s="8">
-        <v>-0.65</v>
+        <v>-15.54</v>
+      </c>
+      <c r="E82" s="9">
+        <v>-1.75</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B83" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C83" s="7">
-        <v>-12.88</v>
+        <v>-31.59</v>
       </c>
       <c r="D83" s="7">
-        <v>-13.79</v>
-      </c>
-      <c r="E83" s="8">
-        <v>-0.91</v>
+        <v>-31.69</v>
+      </c>
+      <c r="E83" s="9">
+        <v>-0.1</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B84" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C84" s="7">
-        <v>-31.47</v>
+        <v>-2.87</v>
       </c>
       <c r="D84" s="7">
-        <v>-31.59</v>
-      </c>
-      <c r="E84" s="8">
-        <v>-0.12</v>
+        <v>-3.09</v>
+      </c>
+      <c r="E84" s="9">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B85" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C85" s="7">
-        <v>-3.18</v>
+        <v>-45.91</v>
       </c>
       <c r="D85" s="7">
-        <v>-2.87</v>
+        <v>-46</v>
       </c>
       <c r="E85" s="9">
-        <v>0.31</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B86" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C86" s="7">
-        <v>-46.87</v>
+        <v>-43.78</v>
       </c>
       <c r="D86" s="7">
-        <v>-45.91</v>
-      </c>
-      <c r="E86" s="9">
-        <v>0.96</v>
+        <v>-43.46</v>
+      </c>
+      <c r="E86" s="8">
+        <v>0.32</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B87" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C87" s="7">
-        <v>-41.75</v>
+        <v>-38.92</v>
       </c>
       <c r="D87" s="7">
-        <v>-43.78</v>
-      </c>
-      <c r="E87" s="8">
-        <v>-2.03</v>
+        <v>-39.45</v>
+      </c>
+      <c r="E87" s="9">
+        <v>-0.53</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B88" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C88" s="7">
-        <v>-38.54</v>
+        <v>-25.57</v>
       </c>
       <c r="D88" s="7">
-        <v>-38.92</v>
+        <v>-25.15</v>
       </c>
       <c r="E88" s="8">
-        <v>-0.38</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="6" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C89" s="7">
-        <v>-26.51</v>
+        <v>715.75</v>
       </c>
       <c r="D89" s="7">
-        <v>-25.57</v>
-      </c>
-      <c r="E89" s="9">
-        <v>0.9399999999999999</v>
+        <v>718.5</v>
+      </c>
+      <c r="E89" s="8">
+        <v>2.75</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B90" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C90" s="7">
-        <v>722.75</v>
+        <v>937.55</v>
       </c>
       <c r="D90" s="7">
-        <v>715.75</v>
+        <v>947.25</v>
       </c>
       <c r="E90" s="8">
-        <v>-7</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B91" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C91" s="7">
-        <v>958.3</v>
+        <v>203.06</v>
       </c>
       <c r="D91" s="7">
-        <v>937.55</v>
-      </c>
-      <c r="E91" s="8">
-        <v>-20.75</v>
+        <v>201.99</v>
+      </c>
+      <c r="E91" s="9">
+        <v>-1.07</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B92" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C92" s="7">
-        <v>204.01</v>
+        <v>610.55</v>
       </c>
       <c r="D92" s="7">
-        <v>203.06</v>
+        <v>612.45</v>
       </c>
       <c r="E92" s="8">
-        <v>-0.95</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B93" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C93" s="7">
-        <v>603.05</v>
+        <v>1764.4</v>
       </c>
       <c r="D93" s="7">
-        <v>610.55</v>
+        <v>1761.6</v>
       </c>
       <c r="E93" s="9">
-        <v>7.5</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B94" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C94" s="7">
-        <v>1772.8</v>
+        <v>999.6</v>
       </c>
       <c r="D94" s="7">
-        <v>1764.4</v>
-      </c>
-      <c r="E94" s="8">
-        <v>-8.4</v>
+        <v>991</v>
+      </c>
+      <c r="E94" s="9">
+        <v>-8.6</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B95" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C95" s="7">
-        <v>1001</v>
+        <v>3409</v>
       </c>
       <c r="D95" s="7">
-        <v>999.6</v>
-      </c>
-      <c r="E95" s="8">
-        <v>-1.4</v>
+        <v>3383</v>
+      </c>
+      <c r="E95" s="9">
+        <v>-26</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B96" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C96" s="7">
-        <v>3383</v>
+        <v>645.15</v>
       </c>
       <c r="D96" s="7">
-        <v>3409</v>
-      </c>
-      <c r="E96" s="9">
-        <v>26</v>
+        <v>650.9</v>
+      </c>
+      <c r="E96" s="8">
+        <v>5.75</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B97" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C97" s="7">
-        <v>618.8</v>
+        <v>367</v>
       </c>
       <c r="D97" s="7">
-        <v>645.15</v>
+        <v>364.65</v>
       </c>
       <c r="E97" s="9">
-        <v>26.35</v>
+        <v>-2.35</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B98" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C98" s="7">
-        <v>370</v>
+        <v>186.78</v>
       </c>
       <c r="D98" s="7">
-        <v>367</v>
-      </c>
-      <c r="E98" s="8">
-        <v>-3</v>
+        <v>183</v>
+      </c>
+      <c r="E98" s="9">
+        <v>-3.78</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B99" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C99" s="7">
-        <v>188.75</v>
+        <v>2204.1</v>
       </c>
       <c r="D99" s="7">
-        <v>186.78</v>
-      </c>
-      <c r="E99" s="8">
-        <v>-1.97</v>
+        <v>2200.8</v>
+      </c>
+      <c r="E99" s="9">
+        <v>-3.3</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B100" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C100" s="7">
-        <v>2208</v>
+        <v>5021</v>
       </c>
       <c r="D100" s="7">
-        <v>2204.1</v>
-      </c>
-      <c r="E100" s="8">
-        <v>-3.9</v>
+        <v>5009.5</v>
+      </c>
+      <c r="E100" s="9">
+        <v>-11.5</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B101" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C101" s="7">
-        <v>5005</v>
+        <v>2818.7</v>
       </c>
       <c r="D101" s="7">
-        <v>5021</v>
+        <v>2802.4</v>
       </c>
       <c r="E101" s="9">
-        <v>16</v>
+        <v>-16.3</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B102" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C102" s="7">
-        <v>2820</v>
+        <v>220.8</v>
       </c>
       <c r="D102" s="7">
-        <v>2818.7</v>
+        <v>222.05</v>
       </c>
       <c r="E102" s="8">
-        <v>-1.3</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B103" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C103" s="7">
-        <v>228.79</v>
+        <v>35.91</v>
       </c>
       <c r="D103" s="7">
-        <v>220.8</v>
-      </c>
-      <c r="E103" s="8">
-        <v>-7.99</v>
+        <v>35.6</v>
+      </c>
+      <c r="E103" s="9">
+        <v>-0.31</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B104" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C104" s="7">
-        <v>36.13</v>
+        <v>1158.5</v>
       </c>
       <c r="D104" s="7">
-        <v>35.91</v>
+        <v>1165</v>
       </c>
       <c r="E104" s="8">
-        <v>-0.22</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="6" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C105" s="7">
-        <v>1143.8</v>
+        <v>13</v>
       </c>
       <c r="D105" s="7">
-        <v>1158.5</v>
-      </c>
-      <c r="E105" s="9">
-        <v>14.7</v>
+        <v>19</v>
+      </c>
+      <c r="E105" s="8">
+        <v>6</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B106" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C106" s="7">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D106" s="7">
         <v>13</v>
       </c>
       <c r="E106" s="9">
-        <v>6</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C107" s="7">
-        <v>13</v>
+        <v>45.68</v>
       </c>
       <c r="D107" s="7">
-        <v>19</v>
-      </c>
-      <c r="E107" s="9">
-        <v>6</v>
+        <v>47.21</v>
+      </c>
+      <c r="E107" s="8">
+        <v>1.53</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="6" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C108" s="7">
-        <v>62</v>
+        <v>48.84</v>
       </c>
       <c r="D108" s="7">
-        <v>68</v>
-      </c>
-      <c r="E108" s="9">
-        <v>6</v>
+        <v>50.53</v>
+      </c>
+      <c r="E108" s="8">
+        <v>1.69</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="6" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C109" s="7">
-        <v>68</v>
+        <v>29.87</v>
       </c>
       <c r="D109" s="7">
-        <v>62</v>
-      </c>
-      <c r="E109" s="8">
-        <v>-6</v>
+        <v>28.36</v>
+      </c>
+      <c r="E109" s="9">
+        <v>-1.51</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="6" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C110" s="7">
-        <v>47</v>
+        <v>33.89</v>
       </c>
       <c r="D110" s="7">
-        <v>50</v>
-      </c>
-      <c r="E110" s="9">
-        <v>3</v>
+        <v>35.17</v>
+      </c>
+      <c r="E110" s="8">
+        <v>1.28</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="6" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C111" s="7">
-        <v>47</v>
+        <v>54.84</v>
       </c>
       <c r="D111" s="7">
-        <v>38</v>
-      </c>
-      <c r="E111" s="8">
-        <v>-9</v>
+        <v>54.31</v>
+      </c>
+      <c r="E111" s="9">
+        <v>-0.53</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="6" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C112" s="7">
-        <v>19</v>
+        <v>31.36</v>
       </c>
       <c r="D112" s="7">
-        <v>7</v>
-      </c>
-      <c r="E112" s="8">
-        <v>-12</v>
+        <v>29.25</v>
+      </c>
+      <c r="E112" s="9">
+        <v>-2.11</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="6" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C113" s="7">
-        <v>38</v>
+        <v>32.36</v>
       </c>
       <c r="D113" s="7">
-        <v>44</v>
+        <v>30.93</v>
       </c>
       <c r="E113" s="9">
-        <v>6</v>
+        <v>-1.43</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="6" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B114" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C114" s="7">
-        <v>49.03</v>
+        <v>49.86</v>
       </c>
       <c r="D114" s="7">
-        <v>45.68</v>
+        <v>52.83</v>
       </c>
       <c r="E114" s="8">
-        <v>-3.35</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="6" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B115" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C115" s="7">
-        <v>52.4</v>
+        <v>47.43</v>
       </c>
       <c r="D115" s="7">
-        <v>48.84</v>
-      </c>
-      <c r="E115" s="8">
-        <v>-3.56</v>
+        <v>45.02</v>
+      </c>
+      <c r="E115" s="9">
+        <v>-2.41</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="6" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B116" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C116" s="7">
-        <v>31.25</v>
+        <v>50.74</v>
       </c>
       <c r="D116" s="7">
-        <v>29.87</v>
-      </c>
-      <c r="E116" s="8">
-        <v>-1.38</v>
+        <v>43.83</v>
+      </c>
+      <c r="E116" s="9">
+        <v>-6.91</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="6" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B117" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C117" s="7">
-        <v>28.73</v>
+        <v>38.44</v>
       </c>
       <c r="D117" s="7">
-        <v>33.89</v>
+        <v>38.13</v>
       </c>
       <c r="E117" s="9">
-        <v>5.16</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="6" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B118" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C118" s="7">
-        <v>56.37</v>
+        <v>52.71</v>
       </c>
       <c r="D118" s="7">
-        <v>54.84</v>
-      </c>
-      <c r="E118" s="8">
-        <v>-1.53</v>
+        <v>51.2</v>
+      </c>
+      <c r="E118" s="9">
+        <v>-1.51</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="6" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B119" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C119" s="7">
-        <v>31.7</v>
+        <v>38.29</v>
       </c>
       <c r="D119" s="7">
-        <v>31.36</v>
-      </c>
-      <c r="E119" s="8">
-        <v>-0.34</v>
+        <v>36.47</v>
+      </c>
+      <c r="E119" s="9">
+        <v>-1.82</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="6" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B120" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C120" s="7">
-        <v>29.32</v>
+        <v>37.31</v>
       </c>
       <c r="D120" s="7">
-        <v>32.36</v>
-      </c>
-      <c r="E120" s="9">
-        <v>3.04</v>
+        <v>39.4</v>
+      </c>
+      <c r="E120" s="8">
+        <v>2.09</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="6" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B121" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C121" s="7">
-        <v>31.48</v>
+        <v>32.43</v>
       </c>
       <c r="D121" s="7">
-        <v>49.86</v>
+        <v>30.84</v>
       </c>
       <c r="E121" s="9">
-        <v>18.38</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="6" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B122" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C122" s="7">
-        <v>50.63</v>
+        <v>35.15</v>
       </c>
       <c r="D122" s="7">
-        <v>47.43</v>
+        <v>37.22</v>
       </c>
       <c r="E122" s="8">
-        <v>-3.2</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="6" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C123" s="7">
-        <v>54.93</v>
+        <v>-34.71</v>
       </c>
       <c r="D123" s="7">
-        <v>50.74</v>
+        <v>-32.25</v>
       </c>
       <c r="E123" s="8">
-        <v>-4.19</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="6" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C124" s="7">
-        <v>38.79</v>
+        <v>-69.2</v>
       </c>
       <c r="D124" s="7">
-        <v>38.44</v>
-      </c>
-      <c r="E124" s="8">
-        <v>-0.35</v>
+        <v>-70.43000000000001</v>
+      </c>
+      <c r="E124" s="9">
+        <v>-1.23</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="6" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C125" s="7">
-        <v>50.84</v>
+        <v>-17.65</v>
       </c>
       <c r="D125" s="7">
-        <v>52.71</v>
+        <v>-46.5</v>
       </c>
       <c r="E125" s="9">
-        <v>1.87</v>
+        <v>-28.85</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="6" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C126" s="7">
-        <v>38.43</v>
+        <v>15.5</v>
       </c>
       <c r="D126" s="7">
-        <v>38.29</v>
+        <v>27.9</v>
       </c>
       <c r="E126" s="8">
-        <v>-0.14</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="6" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C127" s="7">
-        <v>46.9</v>
+        <v>-28.53</v>
       </c>
       <c r="D127" s="7">
-        <v>37.31</v>
-      </c>
-      <c r="E127" s="8">
-        <v>-9.59</v>
+        <v>-36.25</v>
+      </c>
+      <c r="E127" s="9">
+        <v>-7.72</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="6" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C128" s="7">
-        <v>33.57</v>
+        <v>-12.58</v>
       </c>
       <c r="D128" s="7">
-        <v>32.43</v>
-      </c>
-      <c r="E128" s="8">
-        <v>-1.14</v>
+        <v>-18.53</v>
+      </c>
+      <c r="E128" s="9">
+        <v>-5.95</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="6" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C129" s="7">
-        <v>30.33</v>
+        <v>25.05</v>
       </c>
       <c r="D129" s="7">
-        <v>35.15</v>
+        <v>-32.87</v>
       </c>
       <c r="E129" s="9">
-        <v>4.82</v>
+        <v>-57.92</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="6" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B130" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C130" s="7">
-        <v>-43.48</v>
+        <v>4410.46</v>
       </c>
       <c r="D130" s="7">
-        <v>-34.71</v>
+        <v>7.15</v>
       </c>
       <c r="E130" s="9">
-        <v>8.77</v>
+        <v>-4403.31</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="6" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B131" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C131" s="7">
-        <v>-28.85</v>
+        <v>-48.12</v>
       </c>
       <c r="D131" s="7">
-        <v>-69.2</v>
-      </c>
-      <c r="E131" s="8">
-        <v>-40.35</v>
+        <v>-55.99</v>
+      </c>
+      <c r="E131" s="9">
+        <v>-7.87</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="6" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B132" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C132" s="7">
-        <v>-40.01</v>
+        <v>-17.78</v>
       </c>
       <c r="D132" s="7">
-        <v>-17.65</v>
-      </c>
-      <c r="E132" s="9">
-        <v>22.36</v>
+        <v>13.55</v>
+      </c>
+      <c r="E132" s="8">
+        <v>31.33</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="6" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B133" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C133" s="7">
-        <v>-47.8</v>
+        <v>-5.35</v>
       </c>
       <c r="D133" s="7">
-        <v>15.5</v>
-      </c>
-      <c r="E133" s="9">
-        <v>63.3</v>
+        <v>9.01</v>
+      </c>
+      <c r="E133" s="8">
+        <v>14.36</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="6" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B134" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C134" s="7">
-        <v>-21.58</v>
+        <v>-37.8</v>
       </c>
       <c r="D134" s="7">
-        <v>-28.53</v>
+        <v>-20.09</v>
       </c>
       <c r="E134" s="8">
-        <v>-6.95</v>
+        <v>17.71</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="6" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B135" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C135" s="7">
-        <v>-18.31</v>
+        <v>-26.2</v>
       </c>
       <c r="D135" s="7">
-        <v>-12.58</v>
-      </c>
-      <c r="E135" s="9">
-        <v>5.73</v>
+        <v>0.59</v>
+      </c>
+      <c r="E135" s="8">
+        <v>26.79</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="6" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B136" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C136" s="7">
-        <v>51.92</v>
+        <v>202.97</v>
       </c>
       <c r="D136" s="7">
-        <v>25.05</v>
-      </c>
-      <c r="E136" s="8">
-        <v>-26.87</v>
+        <v>36.13</v>
+      </c>
+      <c r="E136" s="9">
+        <v>-166.84</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="6" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B137" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C137" s="7">
-        <v>-30.58</v>
+        <v>-68.61</v>
       </c>
       <c r="D137" s="7">
-        <v>4410.46</v>
+        <v>-72.3</v>
       </c>
       <c r="E137" s="9">
-        <v>4441.04</v>
+        <v>-3.69</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="6" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B138" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C138" s="7">
-        <v>4</v>
+        <v>-51.07</v>
       </c>
       <c r="D138" s="7">
-        <v>-48.12</v>
+        <v>-26.35</v>
       </c>
       <c r="E138" s="8">
-        <v>-52.12</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5">
-      <c r="A139" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B139" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C139" s="7">
-        <v>69.15000000000001</v>
-      </c>
-      <c r="D139" s="7">
-        <v>-17.78</v>
-      </c>
-      <c r="E139" s="8">
-        <v>-86.93000000000001</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5">
-      <c r="A140" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B140" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C140" s="7">
-        <v>32.51</v>
-      </c>
-      <c r="D140" s="7">
-        <v>-5.35</v>
-      </c>
-      <c r="E140" s="8">
-        <v>-37.86</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5">
-      <c r="A141" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B141" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C141" s="7">
-        <v>-15.84</v>
-      </c>
-      <c r="D141" s="7">
-        <v>-37.8</v>
-      </c>
-      <c r="E141" s="8">
-        <v>-21.96</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5">
-      <c r="A142" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B142" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C142" s="7">
-        <v>-11.79</v>
-      </c>
-      <c r="D142" s="7">
-        <v>-26.2</v>
-      </c>
-      <c r="E142" s="8">
-        <v>-14.41</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5">
-      <c r="A143" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B143" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C143" s="7">
-        <v>-63.14</v>
-      </c>
-      <c r="D143" s="7">
-        <v>202.97</v>
-      </c>
-      <c r="E143" s="9">
-        <v>266.11</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5">
-      <c r="A144" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B144" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C144" s="7">
-        <v>-69.70999999999999</v>
-      </c>
-      <c r="D144" s="7">
-        <v>-68.61</v>
-      </c>
-      <c r="E144" s="9">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5">
-      <c r="A145" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B145" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C145" s="7">
-        <v>-55.21</v>
-      </c>
-      <c r="D145" s="7">
-        <v>-51.07</v>
-      </c>
-      <c r="E145" s="9">
-        <v>4.14</v>
+        <v>24.72</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5406,28 +5272,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="F1" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="G1" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="H1" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="I1" s="10" t="s">
         <v>88</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -5441,16 +5307,16 @@
         <v>16</v>
       </c>
       <c r="D2" s="12">
-        <v>41.2</v>
+        <v>40.7</v>
       </c>
       <c r="E2" s="12">
         <v>20</v>
       </c>
       <c r="F2" s="12">
+        <v>-5.6</v>
+      </c>
+      <c r="G2" s="12">
         <v>-4.5</v>
-      </c>
-      <c r="G2" s="12">
-        <v>-3.5</v>
       </c>
       <c r="H2" s="12">
         <v>53.1</v>
@@ -5590,34 +5456,34 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="15">
-        <v>0.4036</v>
+        <v>0.4059</v>
       </c>
       <c r="B2" s="15">
-        <v>0.3716</v>
+        <v>0.3724</v>
       </c>
       <c r="C2" s="15">
-        <v>0.236</v>
+        <v>0.2343</v>
       </c>
       <c r="D2" s="15">
-        <v>0.2304</v>
+        <v>0.2288</v>
       </c>
       <c r="E2" s="15">
-        <v>0.202</v>
+        <v>0.2013</v>
       </c>
       <c r="F2" s="15">
-        <v>0.1397</v>
+        <v>0.1409</v>
       </c>
       <c r="G2" s="15">
-        <v>0.119</v>
+        <v>0.1213</v>
       </c>
       <c r="H2" s="15">
-        <v>0.08169999999999999</v>
+        <v>0.07730000000000001</v>
       </c>
       <c r="I2" s="15">
-        <v>0.0682</v>
+        <v>0.0678</v>
       </c>
       <c r="J2" s="15">
-        <v>0.0339</v>
+        <v>0.0321</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -5642,22 +5508,22 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="15">
-        <v>0.0046</v>
+        <v>0.0028</v>
       </c>
       <c r="B4" s="15">
-        <v>-0.0046</v>
+        <v>-0.0034</v>
       </c>
       <c r="C4" s="15">
-        <v>-0.04769999999999999</v>
+        <v>-0.0471</v>
       </c>
       <c r="D4" s="15">
-        <v>-0.0595</v>
+        <v>-0.0604</v>
       </c>
       <c r="E4" s="15">
-        <v>-0.0646</v>
+        <v>-0.066</v>
       </c>
       <c r="F4" s="15">
-        <v>-0.0809</v>
+        <v>-0.08119999999999999</v>
       </c>
     </row>
   </sheetData>
